--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -1,20 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitWork\cardclient\Config\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25380" windowHeight="15840"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,55 +27,64 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>Enum</t>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ItemType</t>
   </si>
   <si>
     <t>None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
   </si>
   <si>
     <t>Currency</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>货币</t>
   </si>
   <si>
     <t>Material</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>货币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>材料</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterType</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>普通敌人</t>
+  </si>
+  <si>
+    <t>Boss</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,29 +93,352 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -119,9 +446,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -132,24 +701,68 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -198,7 +811,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -233,7 +846,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -436,24 +1049,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A4:E10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.8166666666667" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="45.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.05833333333333" customWidth="1"/>
     <col min="4" max="4" width="11.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="34.75" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -467,7 +1080,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="5" customFormat="1" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -478,31 +1091,31 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="6" customFormat="1" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -511,9 +1124,37 @@
         <v>10</v>
       </c>
     </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -3,6 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cardclient\Config\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17655"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
   <si>
     <t>Enum</t>
   </si>
@@ -72,6 +77,60 @@
   </si>
   <si>
     <t>Boss</t>
+  </si>
+  <si>
+    <t>HandType</t>
+  </si>
+  <si>
+    <t>HighCard</t>
+  </si>
+  <si>
+    <t>高牌</t>
+  </si>
+  <si>
+    <t>Couplet</t>
+  </si>
+  <si>
+    <t>对子</t>
+  </si>
+  <si>
+    <t>Straight</t>
+  </si>
+  <si>
+    <t>顺子</t>
+  </si>
+  <si>
+    <t>Flush</t>
+  </si>
+  <si>
+    <t>同花</t>
+  </si>
+  <si>
+    <t>StraightFlush</t>
+  </si>
+  <si>
+    <t>同花顺</t>
+  </si>
+  <si>
+    <t>Leopard</t>
+  </si>
+  <si>
+    <t>三条</t>
+  </si>
+  <si>
+    <t>PointType</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>数字牌</t>
+  </si>
+  <si>
+    <t>Letter</t>
+  </si>
+  <si>
+    <t>字母牌</t>
   </si>
 </sst>
 </file>
@@ -84,14 +143,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -564,147 +616,153 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1055,12 +1113,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:E10"/>
+  <dimension ref="A4:E20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12.8166666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="7.05833333333333" customWidth="1"/>
+    <col min="2" max="2" width="15.1" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.05833333333333" style="2" customWidth="1"/>
     <col min="4" max="4" width="11.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="34.75" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
@@ -1070,13 +1128,13 @@
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="5" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1084,13 +1142,13 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>0</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="1"/>
@@ -1099,13 +1157,13 @@
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="1"/>
@@ -1114,13 +1172,13 @@
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>2</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1131,7 +1189,7 @@
       <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -1145,11 +1203,123 @@
       <c r="B10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="2">
+        <v>4</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="2">
+        <v>5</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="2">
+        <v>6</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="12645" windowHeight="9090"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t>Enum</t>
   </si>
@@ -44,27 +44,6 @@
   </si>
   <si>
     <t>Desc</t>
-  </si>
-  <si>
-    <t>ItemType</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>货币</t>
-  </si>
-  <si>
-    <t>Material</t>
-  </si>
-  <si>
-    <t>材料</t>
   </si>
   <si>
     <t>MonsterType</t>
@@ -1113,8 +1092,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:E20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A4:D17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12.8166666666667" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.1" style="1" customWidth="1"/>
@@ -1124,7 +1103,7 @@
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1138,188 +1117,144 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" customFormat="1" spans="1:5">
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>7</v>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C7" s="2">
         <v>2</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>10</v>
+      <c r="D7" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C10" s="2">
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="2">
+        <v>4</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="2">
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="2">
+        <v>6</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="2">
         <v>1</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="2">
-        <v>2</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="2">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="2">
-        <v>4</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="2">
-        <v>5</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C17" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="2">
-        <v>2</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="12645" windowHeight="9090"/>
+    <workbookView windowWidth="20505" windowHeight="14460"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="59">
   <si>
     <t>Enum</t>
   </si>
@@ -110,6 +110,105 @@
   </si>
   <si>
     <t>字母牌</t>
+  </si>
+  <si>
+    <t>QualityType</t>
+  </si>
+  <si>
+    <t>Ordinary</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>稀有</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>史诗</t>
+  </si>
+  <si>
+    <t>Legend</t>
+  </si>
+  <si>
+    <t>传说</t>
+  </si>
+  <si>
+    <t>MechanismType</t>
+  </si>
+  <si>
+    <t>CardMagnification</t>
+  </si>
+  <si>
+    <t>所有牌型倍率提高</t>
+  </si>
+  <si>
+    <t>SquarePlate</t>
+  </si>
+  <si>
+    <t>方片花色牌倍率提高</t>
+  </si>
+  <si>
+    <t>Spades</t>
+  </si>
+  <si>
+    <t>黑桃花色牌倍率提高</t>
+  </si>
+  <si>
+    <t>RedHeart</t>
+  </si>
+  <si>
+    <t>红心花色牌倍率提高</t>
+  </si>
+  <si>
+    <t>PlumBlossom</t>
+  </si>
+  <si>
+    <t>梅花花色牌倍率提高</t>
+  </si>
+  <si>
+    <t>对子倍率提高</t>
+  </si>
+  <si>
+    <t>同花倍率提高</t>
+  </si>
+  <si>
+    <t>顺子倍率提高</t>
+  </si>
+  <si>
+    <t>MaxHp</t>
+  </si>
+  <si>
+    <t>立即获得300生命值</t>
+  </si>
+  <si>
+    <t>EveryRoundHpUp</t>
+  </si>
+  <si>
+    <t>每次结算生命值+20</t>
+  </si>
+  <si>
+    <t>同花顺倍率提高</t>
+  </si>
+  <si>
+    <t>BloodSucking</t>
+  </si>
+  <si>
+    <t>每次攻击时,获得生命窃取</t>
+  </si>
+  <si>
+    <t>豹子倍率提高</t>
+  </si>
+  <si>
+    <t>TwoThreeFive</t>
+  </si>
+  <si>
+    <t>235牌型</t>
   </si>
 </sst>
 </file>
@@ -1092,13 +1191,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:D17"/>
+  <dimension ref="A4:D37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="12.8166666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.1" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6916666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.05833333333333" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="31.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="34.75" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
@@ -1257,6 +1356,258 @@
         <v>25</v>
       </c>
     </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="2">
+        <v>4</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="2">
+        <v>3</v>
+      </c>
+      <c r="D26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="2">
+        <v>4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="2">
+        <v>5</v>
+      </c>
+      <c r="D28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="2">
+        <v>6</v>
+      </c>
+      <c r="D29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="2">
+        <v>7</v>
+      </c>
+      <c r="D30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="2">
+        <v>8</v>
+      </c>
+      <c r="D31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="2">
+        <v>9</v>
+      </c>
+      <c r="D32" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" s="2">
+        <v>10</v>
+      </c>
+      <c r="D33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="2">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="2">
+        <v>12</v>
+      </c>
+      <c r="D35" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="2">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" s="2">
+        <v>14</v>
+      </c>
+      <c r="D37" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20505" windowHeight="14460"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="16965" windowHeight="13155"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="82">
   <si>
     <t>Enum</t>
   </si>
@@ -184,13 +184,13 @@
     <t>MaxHp</t>
   </si>
   <si>
-    <t>立即获得300生命值</t>
+    <t>立即获得生命值</t>
   </si>
   <si>
     <t>EveryRoundHpUp</t>
   </si>
   <si>
-    <t>每次结算生命值+20</t>
+    <t>每次结算生命值提高</t>
   </si>
   <si>
     <t>同花顺倍率提高</t>
@@ -209,6 +209,75 @@
   </si>
   <si>
     <t>235牌型</t>
+  </si>
+  <si>
+    <t>BossEntryType</t>
+  </si>
+  <si>
+    <t>DisableHeart</t>
+  </si>
+  <si>
+    <t>本局搓牌时,无法出现红心花色</t>
+  </si>
+  <si>
+    <t>DisableSpade</t>
+  </si>
+  <si>
+    <t>本局搓牌时,无法出现黑桃花色</t>
+  </si>
+  <si>
+    <t>DisableDiamond</t>
+  </si>
+  <si>
+    <t>本局搓牌时,无法出现方片花色</t>
+  </si>
+  <si>
+    <t>DisablePlumBlossom</t>
+  </si>
+  <si>
+    <t>本局搓牌时,无法出现梅花花色</t>
+  </si>
+  <si>
+    <t>DisableHead</t>
+  </si>
+  <si>
+    <t>本局搓牌时,无法出现人头牌</t>
+  </si>
+  <si>
+    <t>Flint</t>
+  </si>
+  <si>
+    <t>本局结算时,牌型的倍率降低</t>
+  </si>
+  <si>
+    <t>Edge</t>
+  </si>
+  <si>
+    <t>本局内你的随机一种遗物将失效</t>
+  </si>
+  <si>
+    <t>AllIn</t>
+  </si>
+  <si>
+    <t>领主每次都会投注你当前血量的部分筹码</t>
+  </si>
+  <si>
+    <t>FlushDamage</t>
+  </si>
+  <si>
+    <t>同花牌型在攻击时,伤害降低</t>
+  </si>
+  <si>
+    <t>FlushStraightDamage</t>
+  </si>
+  <si>
+    <t>同花顺牌型在攻击时,伤害降低</t>
+  </si>
+  <si>
+    <t>StraightDamage</t>
+  </si>
+  <si>
+    <t>顺子牌型在攻击时,伤害降低</t>
   </si>
 </sst>
 </file>
@@ -1191,7 +1260,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:D37"/>
+  <dimension ref="A4:D49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="13.6916666666667" style="1" customWidth="1"/>
@@ -1608,6 +1677,160 @@
         <v>58</v>
       </c>
     </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1</v>
+      </c>
+      <c r="D39" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" s="2">
+        <v>2</v>
+      </c>
+      <c r="D40" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C41" s="2">
+        <v>3</v>
+      </c>
+      <c r="D41" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="2">
+        <v>4</v>
+      </c>
+      <c r="D42" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="2">
+        <v>5</v>
+      </c>
+      <c r="D43" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" s="2">
+        <v>6</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C45" s="2">
+        <v>7</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C46" s="2">
+        <v>8</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C47" s="2">
+        <v>9</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C48" s="2">
+        <v>10</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C49" s="2">
+        <v>11</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="99">
   <si>
     <t>Enum</t>
   </si>
@@ -278,6 +278,57 @@
   </si>
   <si>
     <t>顺子牌型在攻击时,伤害降低</t>
+  </si>
+  <si>
+    <t>HeroEntryType</t>
+  </si>
+  <si>
+    <t>AStrongPerson</t>
+  </si>
+  <si>
+    <t>大壮</t>
+  </si>
+  <si>
+    <t>Badass</t>
+  </si>
+  <si>
+    <t>狠人</t>
+  </si>
+  <si>
+    <t>VersatilePerson</t>
+  </si>
+  <si>
+    <t>多面手</t>
+  </si>
+  <si>
+    <t>Archer</t>
+  </si>
+  <si>
+    <t>射手</t>
+  </si>
+  <si>
+    <t>LoudVoice</t>
+  </si>
+  <si>
+    <t>大嗓门</t>
+  </si>
+  <si>
+    <t>NouveauRiche</t>
+  </si>
+  <si>
+    <t>暴发户</t>
+  </si>
+  <si>
+    <t>HomelessPerson</t>
+  </si>
+  <si>
+    <t>流浪汉</t>
+  </si>
+  <si>
+    <t>GodOfGamblers</t>
+  </si>
+  <si>
+    <t>赌神</t>
   </si>
 </sst>
 </file>
@@ -1260,7 +1311,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:D49"/>
+  <dimension ref="A4:D58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="13.6916666666667" style="1" customWidth="1"/>
@@ -1831,6 +1882,118 @@
         <v>81</v>
       </c>
     </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C51" s="2">
+        <v>1</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B52" t="s">
+        <v>85</v>
+      </c>
+      <c r="C52" s="2">
+        <v>2</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B53" t="s">
+        <v>87</v>
+      </c>
+      <c r="C53" s="2">
+        <v>3</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B54" t="s">
+        <v>89</v>
+      </c>
+      <c r="C54" s="2">
+        <v>4</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B55" t="s">
+        <v>91</v>
+      </c>
+      <c r="C55" s="2">
+        <v>5</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C56" s="2">
+        <v>6</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B57" t="s">
+        <v>95</v>
+      </c>
+      <c r="C57" s="2">
+        <v>7</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B58" t="s">
+        <v>97</v>
+      </c>
+      <c r="C58" s="2">
+        <v>8</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16965" windowHeight="13155"/>
+    <workbookView windowWidth="10350" windowHeight="10905"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="123">
   <si>
     <t>Enum</t>
   </si>
@@ -329,6 +329,78 @@
   </si>
   <si>
     <t>赌神</t>
+  </si>
+  <si>
+    <t>TwoCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌2提供攻击力</t>
+  </si>
+  <si>
+    <t>ThreeCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌3提供攻击力</t>
+  </si>
+  <si>
+    <t>FourCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌4提供攻击力</t>
+  </si>
+  <si>
+    <t>FiveCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌5提供攻击力</t>
+  </si>
+  <si>
+    <t>SixCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌6提供攻击力</t>
+  </si>
+  <si>
+    <t>SevenCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌7提供攻击力</t>
+  </si>
+  <si>
+    <t>EightCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌8提供攻击力</t>
+  </si>
+  <si>
+    <t>NineCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌9提供攻击力</t>
+  </si>
+  <si>
+    <t>TenCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌10提供攻击力</t>
+  </si>
+  <si>
+    <t>Sturdy</t>
+  </si>
+  <si>
+    <t>英雄的生命值上限提高</t>
+  </si>
+  <si>
+    <t>ImpregnableFortress</t>
+  </si>
+  <si>
+    <t>受到的伤害降低</t>
+  </si>
+  <si>
+    <t>Strong</t>
+  </si>
+  <si>
+    <t>英雄的基础攻击力提高</t>
   </si>
 </sst>
 </file>
@@ -1311,10 +1383,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:D58"/>
+  <dimension ref="A4:D71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="13.6916666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7416666666667" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.7" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.05833333333333" style="2" customWidth="1"/>
     <col min="4" max="4" width="31.625" style="1" customWidth="1"/>
@@ -1994,6 +2066,174 @@
         <v>98</v>
       </c>
     </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C60" s="2">
+        <v>15</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C61" s="2">
+        <v>16</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C62" s="2">
+        <v>17</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C63" s="2">
+        <v>18</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C64" s="2">
+        <v>19</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C65" s="2">
+        <v>20</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C66" s="2">
+        <v>21</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C67" s="2">
+        <v>22</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C68" s="2">
+        <v>23</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C69" s="2">
+        <v>24</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C70" s="2">
+        <v>25</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C71" s="2">
+        <v>26</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="10350" windowHeight="10905"/>
+    <workbookView windowWidth="14010" windowHeight="10905"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="155">
   <si>
     <t>Enum</t>
   </si>
@@ -139,6 +139,126 @@
     <t>传说</t>
   </si>
   <si>
+    <t>BossEntryType</t>
+  </si>
+  <si>
+    <t>DisableHeart</t>
+  </si>
+  <si>
+    <t>本局搓牌时,无法出现红心花色</t>
+  </si>
+  <si>
+    <t>DisableSpade</t>
+  </si>
+  <si>
+    <t>本局搓牌时,无法出现黑桃花色</t>
+  </si>
+  <si>
+    <t>DisableDiamond</t>
+  </si>
+  <si>
+    <t>本局搓牌时,无法出现方片花色</t>
+  </si>
+  <si>
+    <t>DisablePlumBlossom</t>
+  </si>
+  <si>
+    <t>本局搓牌时,无法出现梅花花色</t>
+  </si>
+  <si>
+    <t>DisableHead</t>
+  </si>
+  <si>
+    <t>本局搓牌时,无法出现人头牌</t>
+  </si>
+  <si>
+    <t>Flint</t>
+  </si>
+  <si>
+    <t>本局结算时,牌型的倍率降低</t>
+  </si>
+  <si>
+    <t>Edge</t>
+  </si>
+  <si>
+    <t>本局内你的随机一种遗物将失效</t>
+  </si>
+  <si>
+    <t>AllIn</t>
+  </si>
+  <si>
+    <t>领主每次都会投注你当前血量的部分筹码</t>
+  </si>
+  <si>
+    <t>FlushDamage</t>
+  </si>
+  <si>
+    <t>同花牌型在攻击时,伤害降低</t>
+  </si>
+  <si>
+    <t>FlushStraightDamage</t>
+  </si>
+  <si>
+    <t>同花顺牌型在攻击时,伤害降低</t>
+  </si>
+  <si>
+    <t>StraightDamage</t>
+  </si>
+  <si>
+    <t>顺子牌型在攻击时,伤害降低</t>
+  </si>
+  <si>
+    <t>HeroEntryType</t>
+  </si>
+  <si>
+    <t>AStrongPerson</t>
+  </si>
+  <si>
+    <t>大壮</t>
+  </si>
+  <si>
+    <t>Badass</t>
+  </si>
+  <si>
+    <t>狠人</t>
+  </si>
+  <si>
+    <t>VersatilePerson</t>
+  </si>
+  <si>
+    <t>多面手</t>
+  </si>
+  <si>
+    <t>Archer</t>
+  </si>
+  <si>
+    <t>射手</t>
+  </si>
+  <si>
+    <t>LoudVoice</t>
+  </si>
+  <si>
+    <t>大嗓门</t>
+  </si>
+  <si>
+    <t>NouveauRiche</t>
+  </si>
+  <si>
+    <t>暴发户</t>
+  </si>
+  <si>
+    <t>HomelessPerson</t>
+  </si>
+  <si>
+    <t>流浪汉</t>
+  </si>
+  <si>
+    <t>GodOfGamblers</t>
+  </si>
+  <si>
+    <t>赌神</t>
+  </si>
+  <si>
     <t>MechanismType</t>
   </si>
   <si>
@@ -211,196 +331,172 @@
     <t>235牌型</t>
   </si>
   <si>
-    <t>BossEntryType</t>
-  </si>
-  <si>
-    <t>DisableHeart</t>
-  </si>
-  <si>
-    <t>本局搓牌时,无法出现红心花色</t>
-  </si>
-  <si>
-    <t>DisableSpade</t>
-  </si>
-  <si>
-    <t>本局搓牌时,无法出现黑桃花色</t>
-  </si>
-  <si>
-    <t>DisableDiamond</t>
-  </si>
-  <si>
-    <t>本局搓牌时,无法出现方片花色</t>
-  </si>
-  <si>
-    <t>DisablePlumBlossom</t>
-  </si>
-  <si>
-    <t>本局搓牌时,无法出现梅花花色</t>
-  </si>
-  <si>
-    <t>DisableHead</t>
-  </si>
-  <si>
-    <t>本局搓牌时,无法出现人头牌</t>
-  </si>
-  <si>
-    <t>Flint</t>
-  </si>
-  <si>
-    <t>本局结算时,牌型的倍率降低</t>
-  </si>
-  <si>
-    <t>Edge</t>
-  </si>
-  <si>
-    <t>本局内你的随机一种遗物将失效</t>
-  </si>
-  <si>
-    <t>AllIn</t>
-  </si>
-  <si>
-    <t>领主每次都会投注你当前血量的部分筹码</t>
-  </si>
-  <si>
-    <t>FlushDamage</t>
-  </si>
-  <si>
-    <t>同花牌型在攻击时,伤害降低</t>
-  </si>
-  <si>
-    <t>FlushStraightDamage</t>
-  </si>
-  <si>
-    <t>同花顺牌型在攻击时,伤害降低</t>
-  </si>
-  <si>
-    <t>StraightDamage</t>
-  </si>
-  <si>
-    <t>顺子牌型在攻击时,伤害降低</t>
-  </si>
-  <si>
-    <t>HeroEntryType</t>
-  </si>
-  <si>
-    <t>AStrongPerson</t>
-  </si>
-  <si>
-    <t>大壮</t>
-  </si>
-  <si>
-    <t>Badass</t>
-  </si>
-  <si>
-    <t>狠人</t>
-  </si>
-  <si>
-    <t>VersatilePerson</t>
-  </si>
-  <si>
-    <t>多面手</t>
-  </si>
-  <si>
-    <t>Archer</t>
-  </si>
-  <si>
-    <t>射手</t>
-  </si>
-  <si>
-    <t>LoudVoice</t>
-  </si>
-  <si>
-    <t>大嗓门</t>
-  </si>
-  <si>
-    <t>NouveauRiche</t>
-  </si>
-  <si>
-    <t>暴发户</t>
-  </si>
-  <si>
-    <t>HomelessPerson</t>
-  </si>
-  <si>
-    <t>流浪汉</t>
-  </si>
-  <si>
-    <t>GodOfGamblers</t>
-  </si>
-  <si>
-    <t>赌神</t>
-  </si>
-  <si>
     <t>TwoCardAttack</t>
   </si>
   <si>
-    <t>数字牌2提供攻击力</t>
+    <t>数字牌2提供额外攻击力</t>
   </si>
   <si>
     <t>ThreeCardAttack</t>
   </si>
   <si>
-    <t>数字牌3提供攻击力</t>
+    <t>数字牌3提供额外攻击力</t>
   </si>
   <si>
     <t>FourCardAttack</t>
   </si>
   <si>
-    <t>数字牌4提供攻击力</t>
+    <t>数字牌4提供额外攻击力</t>
   </si>
   <si>
     <t>FiveCardAttack</t>
   </si>
   <si>
-    <t>数字牌5提供攻击力</t>
+    <t>数字牌5提供额外攻击力</t>
   </si>
   <si>
     <t>SixCardAttack</t>
   </si>
   <si>
-    <t>数字牌6提供攻击力</t>
+    <t>数字牌6提供额外攻击力</t>
   </si>
   <si>
     <t>SevenCardAttack</t>
   </si>
   <si>
-    <t>数字牌7提供攻击力</t>
+    <t>数字牌7提供额外攻击力</t>
   </si>
   <si>
     <t>EightCardAttack</t>
   </si>
   <si>
-    <t>数字牌8提供攻击力</t>
+    <t>数字牌8提供额外攻击力</t>
   </si>
   <si>
     <t>NineCardAttack</t>
   </si>
   <si>
-    <t>数字牌9提供攻击力</t>
+    <t>数字牌9提供额外攻击力</t>
   </si>
   <si>
     <t>TenCardAttack</t>
   </si>
   <si>
-    <t>数字牌10提供攻击力</t>
-  </si>
-  <si>
-    <t>Sturdy</t>
-  </si>
-  <si>
-    <t>英雄的生命值上限提高</t>
-  </si>
-  <si>
-    <t>ImpregnableFortress</t>
-  </si>
-  <si>
-    <t>受到的伤害降低</t>
-  </si>
-  <si>
-    <t>Strong</t>
-  </si>
-  <si>
-    <t>英雄的基础攻击力提高</t>
+    <t>数字牌10提供额外攻击力</t>
+  </si>
+  <si>
+    <t>ACardAttack</t>
+  </si>
+  <si>
+    <t>A牌提供额外攻击力</t>
+  </si>
+  <si>
+    <t>HeadCardAttack</t>
+  </si>
+  <si>
+    <t>人头牌提供额外攻击力</t>
+  </si>
+  <si>
+    <t>HeroHpMax</t>
+  </si>
+  <si>
+    <t>英雄的血量上限</t>
+  </si>
+  <si>
+    <t>HeroTakeDamage</t>
+  </si>
+  <si>
+    <t>英雄承受的伤害</t>
+  </si>
+  <si>
+    <t>HeroAttack</t>
+  </si>
+  <si>
+    <t>英雄的基础攻击力</t>
+  </si>
+  <si>
+    <t>HeroCritical</t>
+  </si>
+  <si>
+    <t>英雄的暴击率</t>
+  </si>
+  <si>
+    <t>AttackBossDamage</t>
+  </si>
+  <si>
+    <t>对BOSS的伤害</t>
+  </si>
+  <si>
+    <t>FirstShowCardEveryLevel</t>
+  </si>
+  <si>
+    <t>每关首次亮牌后结算倍率</t>
+  </si>
+  <si>
+    <t>KillingProbabilityTen</t>
+  </si>
+  <si>
+    <t>斩杀10%血量以下非BOSS敌人的概率</t>
+  </si>
+  <si>
+    <t>KillingBringsBackBlood</t>
+  </si>
+  <si>
+    <t>血量低于20%以下时,杀人回血</t>
+  </si>
+  <si>
+    <t>ManyMonsterDamage</t>
+  </si>
+  <si>
+    <t>敌人数量大于1时,造成的伤害</t>
+  </si>
+  <si>
+    <t>UsingRubbingCards</t>
+  </si>
+  <si>
+    <t>亮牌前使用过搓牌,结算时的攻击力</t>
+  </si>
+  <si>
+    <t>HeroHpReplyEveryLevelEnding</t>
+  </si>
+  <si>
+    <t>每关结束后,回复的血量</t>
+  </si>
+  <si>
+    <t>ProOfObtainingFundsEverySettlement</t>
+  </si>
+  <si>
+    <t>结算时,获得额外资金的概率</t>
+  </si>
+  <si>
+    <t>OneMonsterDamage</t>
+  </si>
+  <si>
+    <t>只剩1名敌人时,造成的伤害</t>
+  </si>
+  <si>
+    <t>HpUnderDamage</t>
+  </si>
+  <si>
+    <t>血量低于20%时,造成的伤害</t>
+  </si>
+  <si>
+    <t>KillingProOfObtainingFunds</t>
+  </si>
+  <si>
+    <t>击杀敌人时,获得额外资金的概率</t>
+  </si>
+  <si>
+    <t>InitialFunds</t>
+  </si>
+  <si>
+    <t>初始拥有资金</t>
+  </si>
+  <si>
+    <t>ProOfExtraAttack</t>
+  </si>
+  <si>
+    <t>额外造成1次10%伤害的概率</t>
   </si>
 </sst>
 </file>
@@ -1383,7 +1479,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:D71"/>
+  <dimension ref="A4:D102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.7416666666667" style="1" customWidth="1"/>
@@ -1604,634 +1700,858 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" s="2">
-        <v>1</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="2">
-        <v>2</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="2">
-        <v>3</v>
-      </c>
-      <c r="D26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="2">
-        <v>4</v>
-      </c>
-      <c r="D27" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="2">
-        <v>5</v>
-      </c>
-      <c r="D28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="2">
-        <v>6</v>
-      </c>
-      <c r="D29" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="2">
-        <v>7</v>
-      </c>
-      <c r="D30" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="2">
-        <v>8</v>
-      </c>
-      <c r="D31" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="2">
-        <v>9</v>
-      </c>
-      <c r="D32" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" s="2">
-        <v>10</v>
-      </c>
-      <c r="D33" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" s="2">
-        <v>11</v>
-      </c>
-      <c r="D34" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="2">
-        <v>12</v>
-      </c>
-      <c r="D35" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C36" s="2">
-        <v>13</v>
-      </c>
-      <c r="D36" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37" s="2">
-        <v>14</v>
-      </c>
-      <c r="D37" t="s">
-        <v>58</v>
-      </c>
-    </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C39" s="2">
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="C40" s="2">
         <v>2</v>
       </c>
       <c r="D40" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C41" s="2">
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="C42" s="2">
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C43" s="2">
         <v>5</v>
       </c>
       <c r="D43" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="C44" s="2">
         <v>6</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C45" s="2">
         <v>7</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="C46" s="2">
         <v>8</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="C47" s="2">
         <v>9</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="C48" s="2">
         <v>10</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="C49" s="2">
         <v>11</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="C51" s="2">
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="C52" s="2">
         <v>2</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="C53" s="2">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B54" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="C54" s="2">
         <v>4</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B55" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C55" s="2">
         <v>5</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="C56" s="2">
         <v>6</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="C57" s="2">
         <v>7</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="C58" s="2">
         <v>8</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="C60" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>101</v>
+        <v>75</v>
+      </c>
+      <c r="B61" t="s">
+        <v>78</v>
       </c>
       <c r="C61" s="2">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>103</v>
+        <v>75</v>
+      </c>
+      <c r="B62" t="s">
+        <v>80</v>
       </c>
       <c r="C62" s="2">
-        <v>17</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>104</v>
+        <v>3</v>
+      </c>
+      <c r="D62" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>105</v>
+        <v>75</v>
+      </c>
+      <c r="B63" t="s">
+        <v>82</v>
       </c>
       <c r="C63" s="2">
-        <v>18</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>106</v>
+        <v>4</v>
+      </c>
+      <c r="D63" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>107</v>
+        <v>75</v>
+      </c>
+      <c r="B64" t="s">
+        <v>84</v>
       </c>
       <c r="C64" s="2">
-        <v>19</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>108</v>
+        <v>5</v>
+      </c>
+      <c r="D64" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>109</v>
+        <v>75</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="C65" s="2">
-        <v>20</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>110</v>
+        <v>6</v>
+      </c>
+      <c r="D65" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>111</v>
+        <v>75</v>
+      </c>
+      <c r="B66" t="s">
+        <v>15</v>
       </c>
       <c r="C66" s="2">
-        <v>21</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>112</v>
+        <v>7</v>
+      </c>
+      <c r="D66" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>113</v>
+        <v>75</v>
+      </c>
+      <c r="B67" t="s">
+        <v>13</v>
       </c>
       <c r="C67" s="2">
-        <v>22</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>114</v>
+        <v>8</v>
+      </c>
+      <c r="D67" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>115</v>
+        <v>75</v>
+      </c>
+      <c r="B68" t="s">
+        <v>89</v>
       </c>
       <c r="C68" s="2">
-        <v>23</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>116</v>
+        <v>9</v>
+      </c>
+      <c r="D68" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>117</v>
+        <v>75</v>
+      </c>
+      <c r="B69" t="s">
+        <v>91</v>
       </c>
       <c r="C69" s="2">
-        <v>24</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>118</v>
+        <v>10</v>
+      </c>
+      <c r="D69" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>119</v>
+        <v>75</v>
+      </c>
+      <c r="B70" t="s">
+        <v>17</v>
       </c>
       <c r="C70" s="2">
-        <v>25</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>120</v>
+        <v>11</v>
+      </c>
+      <c r="D70" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C71" s="2">
+        <v>12</v>
+      </c>
+      <c r="D71" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C72" s="2">
+        <v>13</v>
+      </c>
+      <c r="D72" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C73" s="2">
+        <v>14</v>
+      </c>
+      <c r="D73" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C75" s="2">
+        <v>15</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C76" s="2">
+        <v>16</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C77" s="2">
+        <v>17</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C78" s="2">
+        <v>18</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C79" s="2">
+        <v>19</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C80" s="2">
+        <v>20</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C81" s="2">
+        <v>21</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C82" s="2">
+        <v>22</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C83" s="2">
+        <v>23</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C84" s="2">
+        <v>24</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C85" s="2">
+        <v>25</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C86" s="2">
+        <v>26</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C87" s="2">
+        <v>27</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C88" s="2">
+        <v>28</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C89" s="2">
+        <v>29</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C90" s="2">
+        <v>30</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C91" s="2">
+        <v>31</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C92" s="2">
+        <v>32</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C93" s="2">
+        <v>33</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C94" s="2">
+        <v>34</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C95" s="2">
         <v>35</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C71" s="2">
-        <v>26</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>122</v>
+      <c r="D95" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C96" s="2">
+        <v>36</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C97" s="2">
+        <v>37</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C98" s="2">
+        <v>38</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C99" s="2">
+        <v>39</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C100" s="2">
+        <v>40</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C101" s="2">
+        <v>41</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C102" s="2">
+        <v>42</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14010" windowHeight="10905"/>
+    <workbookView windowWidth="12315" windowHeight="10185"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="241">
   <si>
     <t>Enum</t>
   </si>
@@ -262,43 +262,481 @@
     <t>MechanismType</t>
   </si>
   <si>
+    <t>TwoCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌2提供额外攻击力</t>
+  </si>
+  <si>
+    <t>ThreeCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌3提供额外攻击力</t>
+  </si>
+  <si>
+    <t>FourCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌4提供额外攻击力</t>
+  </si>
+  <si>
+    <t>FiveCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌5提供额外攻击力</t>
+  </si>
+  <si>
+    <t>SixCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌6提供额外攻击力</t>
+  </si>
+  <si>
+    <t>SevenCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌7提供额外攻击力</t>
+  </si>
+  <si>
+    <t>EightCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌8提供额外攻击力</t>
+  </si>
+  <si>
+    <t>NineCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌9提供额外攻击力</t>
+  </si>
+  <si>
+    <t>TenCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌10提供额外攻击力</t>
+  </si>
+  <si>
+    <t>ACardAttack</t>
+  </si>
+  <si>
+    <t>A牌提供额外攻击力</t>
+  </si>
+  <si>
+    <t>HeadCardAttack</t>
+  </si>
+  <si>
+    <t>人头牌提供额外攻击力</t>
+  </si>
+  <si>
+    <t>HeroHpMax</t>
+  </si>
+  <si>
+    <t>英雄的血量上限</t>
+  </si>
+  <si>
+    <t>HeroTakeDamage</t>
+  </si>
+  <si>
+    <t>英雄承受的伤害</t>
+  </si>
+  <si>
+    <t>HeroAttack</t>
+  </si>
+  <si>
+    <t>英雄的基础攻击力</t>
+  </si>
+  <si>
+    <t>HeroCritical</t>
+  </si>
+  <si>
+    <t>英雄的暴击率</t>
+  </si>
+  <si>
+    <t>AttackBossDamage</t>
+  </si>
+  <si>
+    <t>对BOSS的伤害</t>
+  </si>
+  <si>
+    <t>FirstShowCardEveryLevel</t>
+  </si>
+  <si>
+    <t>每关首次亮牌后结算倍率</t>
+  </si>
+  <si>
+    <t>KillingProbabilityTen</t>
+  </si>
+  <si>
+    <t>斩杀10%血量以下非BOSS敌人的概率</t>
+  </si>
+  <si>
+    <t>KillingBringsBackBlood</t>
+  </si>
+  <si>
+    <t>血量低于20%以下时,杀人回血</t>
+  </si>
+  <si>
+    <t>ManyMonsterDamage</t>
+  </si>
+  <si>
+    <t>敌人数量大于1时,造成的伤害</t>
+  </si>
+  <si>
+    <t>UsingRubbingCards</t>
+  </si>
+  <si>
+    <t>亮牌前使用过搓牌,结算时的攻击力</t>
+  </si>
+  <si>
+    <t>HeroHpReplyEveryLevelEnding</t>
+  </si>
+  <si>
+    <t>每关结束后,回复的血量百分比</t>
+  </si>
+  <si>
+    <t>ProOfObtainingFundsEverySettlement</t>
+  </si>
+  <si>
+    <t>结算时,获得额外资金的概率</t>
+  </si>
+  <si>
+    <t>OneMonsterDamage</t>
+  </si>
+  <si>
+    <t>只剩1名敌人时,造成的伤害</t>
+  </si>
+  <si>
+    <t>HpUnderDamage</t>
+  </si>
+  <si>
+    <t>血量低于20%时,造成的伤害</t>
+  </si>
+  <si>
+    <t>KillingProOfObtainingFunds</t>
+  </si>
+  <si>
+    <t>击杀敌人时,获得额外资金的概率</t>
+  </si>
+  <si>
+    <t>InitialFunds</t>
+  </si>
+  <si>
+    <t>初始拥有资金</t>
+  </si>
+  <si>
+    <t>ProOfExtraAttack</t>
+  </si>
+  <si>
+    <t>额外造成1次10%伤害的概率</t>
+  </si>
+  <si>
     <t>CardMagnification</t>
   </si>
   <si>
-    <t>所有牌型倍率提高</t>
+    <t>结算时获得额外倍率</t>
   </si>
   <si>
     <t>SquarePlate</t>
   </si>
   <si>
-    <t>方片花色牌倍率提高</t>
+    <t>每张方片牌在结算时提供倍率</t>
   </si>
   <si>
     <t>Spades</t>
   </si>
   <si>
-    <t>黑桃花色牌倍率提高</t>
+    <t>每张黑桃牌在结算时提供倍率</t>
   </si>
   <si>
     <t>RedHeart</t>
   </si>
   <si>
-    <t>红心花色牌倍率提高</t>
+    <t>每张红心牌在结算时提供倍率</t>
   </si>
   <si>
     <t>PlumBlossom</t>
   </si>
   <si>
-    <t>梅花花色牌倍率提高</t>
+    <t>每张梅花牌在结算时提供倍率</t>
   </si>
   <si>
     <t>对子倍率提高</t>
   </si>
   <si>
+    <t>顺子倍率提高</t>
+  </si>
+  <si>
     <t>同花倍率提高</t>
   </si>
   <si>
-    <t>顺子倍率提高</t>
+    <t>同花顺倍率提高</t>
+  </si>
+  <si>
+    <t>豹子倍率提高</t>
+  </si>
+  <si>
+    <t>SquarePlateAttack</t>
+  </si>
+  <si>
+    <t>每张方片牌在结算时提供攻击力</t>
+  </si>
+  <si>
+    <t>SpadesAttack</t>
+  </si>
+  <si>
+    <t>每张黑桃牌在结算时提供攻击力</t>
+  </si>
+  <si>
+    <t>RedHeartAttack</t>
+  </si>
+  <si>
+    <t>每张红心牌在结算时提供攻击力</t>
+  </si>
+  <si>
+    <t>PlumBlossomAttack</t>
+  </si>
+  <si>
+    <t>每张梅花牌在结算时提供攻击力</t>
+  </si>
+  <si>
+    <t>CoupletAttack</t>
+  </si>
+  <si>
+    <t>对子牌型在结算时提供攻击力</t>
+  </si>
+  <si>
+    <t>StraightAttack</t>
+  </si>
+  <si>
+    <t>顺子牌型在结算时提供攻击力</t>
+  </si>
+  <si>
+    <t>FlushAttack</t>
+  </si>
+  <si>
+    <t>同花牌型在结算时提供攻击力</t>
+  </si>
+  <si>
+    <t>StraightFlushAttack</t>
+  </si>
+  <si>
+    <t>同花顺牌型在结算时提供攻击力</t>
+  </si>
+  <si>
+    <t>LeopardAttack</t>
+  </si>
+  <si>
+    <t>豹子牌型在结算时提供攻击力</t>
+  </si>
+  <si>
+    <t>HeroHpReplyEveryRoundEnding</t>
+  </si>
+  <si>
+    <t>回合结束回复当前生命值</t>
+  </si>
+  <si>
+    <t>Liability</t>
+  </si>
+  <si>
+    <t>资金可以为负数</t>
+  </si>
+  <si>
+    <t>EveryRubbingNum</t>
+  </si>
+  <si>
+    <t>每剩余1个搓牌次数,提供倍率</t>
+  </si>
+  <si>
+    <t>ProOfHeadCardFunds</t>
+  </si>
+  <si>
+    <t>人头牌提供1资金的概率</t>
+  </si>
+  <si>
+    <t>Camera</t>
+  </si>
+  <si>
+    <t>每有1张留在手里的每张黑桃/梅花,提供倍率</t>
+  </si>
+  <si>
+    <t>Cupid</t>
+  </si>
+  <si>
+    <t>每有1张留在手里的每张方片/红心,提供倍率</t>
+  </si>
+  <si>
+    <t>ConsumeFundsGetAttack</t>
+  </si>
+  <si>
+    <t>每花费10资金,提供英雄攻击力</t>
+  </si>
+  <si>
+    <t>TakeDamageGetFunds</t>
+  </si>
+  <si>
+    <t>受到伤害,提供资金</t>
+  </si>
+  <si>
+    <t>BloodSucking</t>
+  </si>
+  <si>
+    <t>吸血效果</t>
+  </si>
+  <si>
+    <t>DoubleCardAttack</t>
+  </si>
+  <si>
+    <t>亮出的牌点数提供的攻击力提高</t>
+  </si>
+  <si>
+    <t>TheSwordOfVictory</t>
+  </si>
+  <si>
+    <t>结算伤害时,将留在手牌上最大牌点数转化为额外攻击力</t>
+  </si>
+  <si>
+    <t>EveryUseRubbingNum</t>
+  </si>
+  <si>
+    <t>每回合内,每搓1次牌,结算时提供倍率</t>
+  </si>
+  <si>
+    <t>FreeShopRefresh</t>
+  </si>
+  <si>
+    <t>免费商店刷新次数</t>
+  </si>
+  <si>
+    <t>SpecialStraight</t>
+  </si>
+  <si>
+    <t>顺子牌型可以相隔1点组成</t>
+  </si>
+  <si>
+    <t>SpecialEightCard</t>
+  </si>
+  <si>
+    <t>亮出的每张8在结算时提供+8攻击力</t>
+  </si>
+  <si>
+    <t>EvenNumberCard</t>
+  </si>
+  <si>
+    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供倍率</t>
+  </si>
+  <si>
+    <t>OddNumberCard</t>
+  </si>
+  <si>
+    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供倍率</t>
+  </si>
+  <si>
+    <t>HeadCard</t>
+  </si>
+  <si>
+    <t>人头牌提供额外倍率</t>
+  </si>
+  <si>
+    <t>KillAfterSellingPrice</t>
+  </si>
+  <si>
+    <t>击杀敌人,收藏品出售价格提高</t>
+  </si>
+  <si>
+    <t>EveryCardAttackForever</t>
+  </si>
+  <si>
+    <t>亮出的每张牌的点数在结算时会使其提供的攻击力永久提高</t>
+  </si>
+  <si>
+    <t>SpecialNineCard</t>
+  </si>
+  <si>
+    <t>亮出的每张9在结算时提供资金</t>
+  </si>
+  <si>
+    <t>SpecialTwoThreeFive</t>
+  </si>
+  <si>
+    <t>散排235牌型等同于豹子牌型,并且可以战胜所有牌型</t>
+  </si>
+  <si>
+    <t>SpecialFlush</t>
+  </si>
+  <si>
+    <t>红桃和方片视为同一花色,黑桃和梅花视为同一花色</t>
+  </si>
+  <si>
+    <t>RubbingCardsNum</t>
+  </si>
+  <si>
+    <t>每回合搓牌次数</t>
+  </si>
+  <si>
+    <t>NoSkill</t>
+  </si>
+  <si>
+    <t>结算时,所有技能都无剩余使用次数时,提供倍率</t>
+  </si>
+  <si>
+    <t>EveryRelic</t>
+  </si>
+  <si>
+    <t>每有1个收藏品,结算时提供倍率</t>
+  </si>
+  <si>
+    <t>NoUseRubbingEveryRubbingNum</t>
+  </si>
+  <si>
+    <t>结算时,若未使用过搓牌,每个搓牌次数提供+6倍率</t>
+  </si>
+  <si>
+    <t>AllCardIsHeadCard</t>
+  </si>
+  <si>
+    <t>所有牌均视为人头牌</t>
+  </si>
+  <si>
+    <t>SpecialACard</t>
+  </si>
+  <si>
+    <t>A牌在结算时提供倍率</t>
+  </si>
+  <si>
+    <t>AccumulatedNumOfCardType</t>
+  </si>
+  <si>
+    <t>亮牌时,将该牌型在本局内亮出过的次数来提供倍率</t>
+  </si>
+  <si>
+    <t>ProOfUpCardType</t>
+  </si>
+  <si>
+    <t>亮牌时,有概率将该牌型提供的倍率永久+1</t>
+  </si>
+  <si>
+    <t>RubbingCardRelic</t>
+  </si>
+  <si>
+    <t>每使用1次搓牌,结算时该收藏品永久提供倍率</t>
+  </si>
+  <si>
+    <t>SpecialSevenCardPro</t>
+  </si>
+  <si>
+    <t>幸运七触发概率</t>
+  </si>
+  <si>
+    <t>SpecialSevenCardAttack</t>
+  </si>
+  <si>
+    <t>幸运七触发时提供的攻击力</t>
+  </si>
+  <si>
+    <t>SpecialSevenCard</t>
+  </si>
+  <si>
+    <t>幸运七触发时提供的倍率</t>
   </si>
   <si>
     <t>MaxHp</t>
@@ -313,190 +751,10 @@
     <t>每次结算生命值提高</t>
   </si>
   <si>
-    <t>同花顺倍率提高</t>
-  </si>
-  <si>
-    <t>BloodSucking</t>
-  </si>
-  <si>
-    <t>每次攻击时,获得生命窃取</t>
-  </si>
-  <si>
-    <t>豹子倍率提高</t>
-  </si>
-  <si>
     <t>TwoThreeFive</t>
   </si>
   <si>
     <t>235牌型</t>
-  </si>
-  <si>
-    <t>TwoCardAttack</t>
-  </si>
-  <si>
-    <t>数字牌2提供额外攻击力</t>
-  </si>
-  <si>
-    <t>ThreeCardAttack</t>
-  </si>
-  <si>
-    <t>数字牌3提供额外攻击力</t>
-  </si>
-  <si>
-    <t>FourCardAttack</t>
-  </si>
-  <si>
-    <t>数字牌4提供额外攻击力</t>
-  </si>
-  <si>
-    <t>FiveCardAttack</t>
-  </si>
-  <si>
-    <t>数字牌5提供额外攻击力</t>
-  </si>
-  <si>
-    <t>SixCardAttack</t>
-  </si>
-  <si>
-    <t>数字牌6提供额外攻击力</t>
-  </si>
-  <si>
-    <t>SevenCardAttack</t>
-  </si>
-  <si>
-    <t>数字牌7提供额外攻击力</t>
-  </si>
-  <si>
-    <t>EightCardAttack</t>
-  </si>
-  <si>
-    <t>数字牌8提供额外攻击力</t>
-  </si>
-  <si>
-    <t>NineCardAttack</t>
-  </si>
-  <si>
-    <t>数字牌9提供额外攻击力</t>
-  </si>
-  <si>
-    <t>TenCardAttack</t>
-  </si>
-  <si>
-    <t>数字牌10提供额外攻击力</t>
-  </si>
-  <si>
-    <t>ACardAttack</t>
-  </si>
-  <si>
-    <t>A牌提供额外攻击力</t>
-  </si>
-  <si>
-    <t>HeadCardAttack</t>
-  </si>
-  <si>
-    <t>人头牌提供额外攻击力</t>
-  </si>
-  <si>
-    <t>HeroHpMax</t>
-  </si>
-  <si>
-    <t>英雄的血量上限</t>
-  </si>
-  <si>
-    <t>HeroTakeDamage</t>
-  </si>
-  <si>
-    <t>英雄承受的伤害</t>
-  </si>
-  <si>
-    <t>HeroAttack</t>
-  </si>
-  <si>
-    <t>英雄的基础攻击力</t>
-  </si>
-  <si>
-    <t>HeroCritical</t>
-  </si>
-  <si>
-    <t>英雄的暴击率</t>
-  </si>
-  <si>
-    <t>AttackBossDamage</t>
-  </si>
-  <si>
-    <t>对BOSS的伤害</t>
-  </si>
-  <si>
-    <t>FirstShowCardEveryLevel</t>
-  </si>
-  <si>
-    <t>每关首次亮牌后结算倍率</t>
-  </si>
-  <si>
-    <t>KillingProbabilityTen</t>
-  </si>
-  <si>
-    <t>斩杀10%血量以下非BOSS敌人的概率</t>
-  </si>
-  <si>
-    <t>KillingBringsBackBlood</t>
-  </si>
-  <si>
-    <t>血量低于20%以下时,杀人回血</t>
-  </si>
-  <si>
-    <t>ManyMonsterDamage</t>
-  </si>
-  <si>
-    <t>敌人数量大于1时,造成的伤害</t>
-  </si>
-  <si>
-    <t>UsingRubbingCards</t>
-  </si>
-  <si>
-    <t>亮牌前使用过搓牌,结算时的攻击力</t>
-  </si>
-  <si>
-    <t>HeroHpReplyEveryLevelEnding</t>
-  </si>
-  <si>
-    <t>每关结束后,回复的血量</t>
-  </si>
-  <si>
-    <t>ProOfObtainingFundsEverySettlement</t>
-  </si>
-  <si>
-    <t>结算时,获得额外资金的概率</t>
-  </si>
-  <si>
-    <t>OneMonsterDamage</t>
-  </si>
-  <si>
-    <t>只剩1名敌人时,造成的伤害</t>
-  </si>
-  <si>
-    <t>HpUnderDamage</t>
-  </si>
-  <si>
-    <t>血量低于20%时,造成的伤害</t>
-  </si>
-  <si>
-    <t>KillingProOfObtainingFunds</t>
-  </si>
-  <si>
-    <t>击杀敌人时,获得额外资金的概率</t>
-  </si>
-  <si>
-    <t>InitialFunds</t>
-  </si>
-  <si>
-    <t>初始拥有资金</t>
-  </si>
-  <si>
-    <t>ProOfExtraAttack</t>
-  </si>
-  <si>
-    <t>额外造成1次10%伤害的概率</t>
   </si>
 </sst>
 </file>
@@ -1479,7 +1737,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:D102"/>
+  <dimension ref="A4:D158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.7416666666667" style="1" customWidth="1"/>
@@ -1984,7 +2242,7 @@
       <c r="A61" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C61" s="2">
@@ -1998,13 +2256,13 @@
       <c r="A62" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C62" s="2">
         <v>3</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="1" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2012,13 +2270,13 @@
       <c r="A63" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C63" s="2">
         <v>4</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="1" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2026,13 +2284,13 @@
       <c r="A64" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C64" s="2">
         <v>5</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="1" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2040,84 +2298,84 @@
       <c r="A65" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>11</v>
+      <c r="B65" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="C65" s="2">
         <v>6</v>
       </c>
-      <c r="D65" t="s">
-        <v>86</v>
+      <c r="D65" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B66" t="s">
-        <v>15</v>
+      <c r="B66" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="C66" s="2">
         <v>7</v>
       </c>
-      <c r="D66" t="s">
-        <v>87</v>
+      <c r="D66" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B67" t="s">
-        <v>13</v>
+      <c r="B67" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="C67" s="2">
         <v>8</v>
       </c>
-      <c r="D67" t="s">
-        <v>88</v>
+      <c r="D67" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B68" t="s">
-        <v>89</v>
+      <c r="B68" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="C68" s="2">
         <v>9</v>
       </c>
-      <c r="D68" t="s">
-        <v>90</v>
+      <c r="D68" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B69" t="s">
-        <v>91</v>
+      <c r="B69" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="C69" s="2">
         <v>10</v>
       </c>
-      <c r="D69" t="s">
-        <v>92</v>
+      <c r="D69" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B70" t="s">
-        <v>17</v>
+      <c r="B70" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C70" s="2">
         <v>11</v>
       </c>
-      <c r="D70" t="s">
-        <v>93</v>
+      <c r="D70" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2125,13 +2383,13 @@
         <v>75</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C71" s="2">
         <v>12</v>
       </c>
-      <c r="D71" t="s">
-        <v>95</v>
+      <c r="D71" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2139,13 +2397,13 @@
         <v>75</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="C72" s="2">
         <v>13</v>
       </c>
-      <c r="D72" t="s">
-        <v>96</v>
+      <c r="D72" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2153,13 +2411,27 @@
         <v>75</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C73" s="2">
         <v>14</v>
       </c>
-      <c r="D73" t="s">
-        <v>98</v>
+      <c r="D73" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C74" s="2">
+        <v>15</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2167,27 +2439,27 @@
         <v>75</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C75" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>101</v>
+      <c r="B76" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="C76" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2195,13 +2467,13 @@
         <v>75</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C77" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2209,41 +2481,41 @@
         <v>75</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C78" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>107</v>
+      <c r="B79" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="C79" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>109</v>
+      <c r="B80" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="C80" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2251,13 +2523,13 @@
         <v>75</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C81" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2265,167 +2537,153 @@
         <v>75</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C82" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>115</v>
+      <c r="B83" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="C83" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>117</v>
+      <c r="B84" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="C84" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>119</v>
+      <c r="B85" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="C85" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>121</v>
+      <c r="B86" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="C86" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>123</v>
+      <c r="B87" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="C87" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C88" s="2">
-        <v>28</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>127</v>
+      <c r="B89" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="C89" s="2">
         <v>29</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>129</v>
+      <c r="B90" t="s">
+        <v>134</v>
       </c>
       <c r="C90" s="2">
         <v>30</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>131</v>
+      <c r="B91" t="s">
+        <v>136</v>
       </c>
       <c r="C91" s="2">
         <v>31</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>133</v>
+      <c r="B92" t="s">
+        <v>138</v>
       </c>
       <c r="C92" s="2">
         <v>32</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>135</v>
+      <c r="B93" t="s">
+        <v>140</v>
       </c>
       <c r="C93" s="2">
         <v>33</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2433,68 +2691,68 @@
         <v>75</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>137</v>
+        <v>11</v>
       </c>
       <c r="C94" s="2">
         <v>34</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>138</v>
+      <c r="D94" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>139</v>
+      <c r="B95" t="s">
+        <v>13</v>
       </c>
       <c r="C95" s="2">
         <v>35</v>
       </c>
-      <c r="D95" s="1" t="s">
-        <v>140</v>
+      <c r="D95" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>141</v>
+      <c r="B96" t="s">
+        <v>15</v>
       </c>
       <c r="C96" s="2">
         <v>36</v>
       </c>
-      <c r="D96" s="1" t="s">
-        <v>142</v>
+      <c r="D96" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>143</v>
+      <c r="B97" t="s">
+        <v>17</v>
       </c>
       <c r="C97" s="2">
         <v>37</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>144</v>
+      <c r="D97" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>145</v>
+      <c r="B98" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="C98" s="2">
         <v>38</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D98" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2502,13 +2760,13 @@
       <c r="A99" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B99" t="s">
         <v>147</v>
       </c>
       <c r="C99" s="2">
         <v>39</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="D99" t="s">
         <v>148</v>
       </c>
     </row>
@@ -2516,13 +2774,13 @@
       <c r="A100" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B100" t="s">
         <v>149</v>
       </c>
       <c r="C100" s="2">
         <v>40</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="D100" t="s">
         <v>150</v>
       </c>
     </row>
@@ -2530,13 +2788,13 @@
       <c r="A101" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B101" t="s">
         <v>151</v>
       </c>
       <c r="C101" s="2">
         <v>41</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="D101" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2544,14 +2802,660 @@
       <c r="A102" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B102" t="s">
         <v>153</v>
       </c>
       <c r="C102" s="2">
         <v>42</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="D102" t="s">
         <v>154</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C103" s="2">
+        <v>43</v>
+      </c>
+      <c r="D103" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B104" t="s">
+        <v>157</v>
+      </c>
+      <c r="C104" s="2">
+        <v>44</v>
+      </c>
+      <c r="D104" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B105" t="s">
+        <v>159</v>
+      </c>
+      <c r="C105" s="2">
+        <v>45</v>
+      </c>
+      <c r="D105" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B106" t="s">
+        <v>161</v>
+      </c>
+      <c r="C106" s="2">
+        <v>46</v>
+      </c>
+      <c r="D106" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C107" s="2">
+        <v>47</v>
+      </c>
+      <c r="D107" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C108" s="2">
+        <v>48</v>
+      </c>
+      <c r="D108" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B109" t="s">
+        <v>167</v>
+      </c>
+      <c r="C109" s="2">
+        <v>49</v>
+      </c>
+      <c r="D109" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B110" t="s">
+        <v>169</v>
+      </c>
+      <c r="C110" s="2">
+        <v>50</v>
+      </c>
+      <c r="D110" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C111" s="2">
+        <v>51</v>
+      </c>
+      <c r="D111" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B112" t="s">
+        <v>173</v>
+      </c>
+      <c r="C112" s="2">
+        <v>52</v>
+      </c>
+      <c r="D112" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B113" t="s">
+        <v>175</v>
+      </c>
+      <c r="C113" s="2">
+        <v>53</v>
+      </c>
+      <c r="D113" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B114" t="s">
+        <v>177</v>
+      </c>
+      <c r="C114" s="2">
+        <v>54</v>
+      </c>
+      <c r="D114" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B115" t="s">
+        <v>179</v>
+      </c>
+      <c r="C115" s="2">
+        <v>55</v>
+      </c>
+      <c r="D115" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C116" s="2">
+        <v>56</v>
+      </c>
+      <c r="D116" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B117" t="s">
+        <v>183</v>
+      </c>
+      <c r="C117" s="2">
+        <v>57</v>
+      </c>
+      <c r="D117" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B118" t="s">
+        <v>185</v>
+      </c>
+      <c r="C118" s="2">
+        <v>58</v>
+      </c>
+      <c r="D118" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B119" t="s">
+        <v>187</v>
+      </c>
+      <c r="C119" s="2">
+        <v>59</v>
+      </c>
+      <c r="D119" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B120" t="s">
+        <v>189</v>
+      </c>
+      <c r="C120" s="2">
+        <v>60</v>
+      </c>
+      <c r="D120" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B121" t="s">
+        <v>191</v>
+      </c>
+      <c r="C121" s="2">
+        <v>61</v>
+      </c>
+      <c r="D121" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B122" t="s">
+        <v>193</v>
+      </c>
+      <c r="C122" s="2">
+        <v>62</v>
+      </c>
+      <c r="D122" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B123" t="s">
+        <v>195</v>
+      </c>
+      <c r="C123" s="2">
+        <v>63</v>
+      </c>
+      <c r="D123" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B124" t="s">
+        <v>197</v>
+      </c>
+      <c r="C124" s="2">
+        <v>64</v>
+      </c>
+      <c r="D124" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B125" t="s">
+        <v>199</v>
+      </c>
+      <c r="C125" s="2">
+        <v>65</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B126" t="s">
+        <v>201</v>
+      </c>
+      <c r="C126" s="2">
+        <v>66</v>
+      </c>
+      <c r="D126" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B127" t="s">
+        <v>203</v>
+      </c>
+      <c r="C127" s="2">
+        <v>67</v>
+      </c>
+      <c r="D127" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B128" t="s">
+        <v>205</v>
+      </c>
+      <c r="C128" s="2">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B129" t="s">
+        <v>207</v>
+      </c>
+      <c r="C129" s="2">
+        <v>69</v>
+      </c>
+      <c r="D129" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B130" t="s">
+        <v>209</v>
+      </c>
+      <c r="C130" s="2">
+        <v>70</v>
+      </c>
+      <c r="D130" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C131" s="2">
+        <v>71</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C132" s="2">
+        <v>72</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B133" t="s">
+        <v>215</v>
+      </c>
+      <c r="C133" s="2">
+        <v>73</v>
+      </c>
+      <c r="D133" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B134" t="s">
+        <v>217</v>
+      </c>
+      <c r="C134" s="2">
+        <v>74</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B135" t="s">
+        <v>219</v>
+      </c>
+      <c r="C135" s="2">
+        <v>75</v>
+      </c>
+      <c r="D135" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B136" t="s">
+        <v>221</v>
+      </c>
+      <c r="C136" s="2">
+        <v>76</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B137" t="s">
+        <v>223</v>
+      </c>
+      <c r="C137" s="2">
+        <v>77</v>
+      </c>
+      <c r="D137" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B138" t="s">
+        <v>225</v>
+      </c>
+      <c r="C138" s="2">
+        <v>78</v>
+      </c>
+      <c r="D138" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B139" t="s">
+        <v>227</v>
+      </c>
+      <c r="C139" s="2">
+        <v>79</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B140" t="s">
+        <v>229</v>
+      </c>
+      <c r="C140" s="2">
+        <v>80</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B141" t="s">
+        <v>231</v>
+      </c>
+      <c r="C141" s="2">
+        <v>81</v>
+      </c>
+      <c r="D141" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B142" t="s">
+        <v>233</v>
+      </c>
+      <c r="C142" s="2">
+        <v>82</v>
+      </c>
+      <c r="D142" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="B143"/>
+      <c r="D143"/>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="B144"/>
+      <c r="D144"/>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="B145"/>
+      <c r="D145"/>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="B146"/>
+      <c r="D146"/>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="B147"/>
+      <c r="D147"/>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="B148"/>
+      <c r="D148"/>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="B149"/>
+      <c r="D149"/>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="B150"/>
+      <c r="D150"/>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="B151"/>
+      <c r="D151"/>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="B152"/>
+      <c r="D152"/>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="B153"/>
+      <c r="D153"/>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B154" t="s">
+        <v>235</v>
+      </c>
+      <c r="C154" s="2">
+        <v>11</v>
+      </c>
+      <c r="D154" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B155" t="s">
+        <v>237</v>
+      </c>
+      <c r="C155" s="2">
+        <v>12</v>
+      </c>
+      <c r="D155" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C158" s="2">
+        <v>14</v>
+      </c>
+      <c r="D158" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="12315" windowHeight="10185"/>
+    <workbookView windowWidth="11535" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="240">
   <si>
     <t>Enum</t>
   </si>
@@ -208,553 +208,550 @@
     <t>顺子牌型在攻击时,伤害降低</t>
   </si>
   <si>
-    <t>HeroEntryType</t>
-  </si>
-  <si>
-    <t>AStrongPerson</t>
-  </si>
-  <si>
-    <t>大壮</t>
-  </si>
-  <si>
-    <t>Badass</t>
-  </si>
-  <si>
-    <t>狠人</t>
+    <t>MechanismType</t>
+  </si>
+  <si>
+    <t>TwoCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌2提供额外攻击力</t>
+  </si>
+  <si>
+    <t>ThreeCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌3提供额外攻击力</t>
+  </si>
+  <si>
+    <t>FourCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌4提供额外攻击力</t>
+  </si>
+  <si>
+    <t>FiveCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌5提供额外攻击力</t>
+  </si>
+  <si>
+    <t>SixCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌6提供额外攻击力</t>
+  </si>
+  <si>
+    <t>SevenCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌7提供额外攻击力</t>
+  </si>
+  <si>
+    <t>EightCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌8提供额外攻击力</t>
+  </si>
+  <si>
+    <t>NineCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌9提供额外攻击力</t>
+  </si>
+  <si>
+    <t>TenCardAttack</t>
+  </si>
+  <si>
+    <t>数字牌10提供额外攻击力</t>
+  </si>
+  <si>
+    <t>ACardAttack</t>
+  </si>
+  <si>
+    <t>A牌提供额外攻击力</t>
+  </si>
+  <si>
+    <t>HeadCardAttack</t>
+  </si>
+  <si>
+    <t>人头牌提供额外攻击力</t>
+  </si>
+  <si>
+    <t>HeroHpMax</t>
+  </si>
+  <si>
+    <t>英雄的血量上限</t>
+  </si>
+  <si>
+    <t>HeroTakeDamage</t>
+  </si>
+  <si>
+    <t>英雄承受的伤害</t>
+  </si>
+  <si>
+    <t>HeroAttack</t>
+  </si>
+  <si>
+    <t>英雄的基础攻击力</t>
+  </si>
+  <si>
+    <t>HeroCritical</t>
+  </si>
+  <si>
+    <t>英雄的暴击率</t>
+  </si>
+  <si>
+    <t>AttackBossDamage</t>
+  </si>
+  <si>
+    <t>对BOSS的伤害</t>
+  </si>
+  <si>
+    <t>FirstShowCardEveryLevel</t>
+  </si>
+  <si>
+    <t>每关首次亮牌后结算倍率</t>
+  </si>
+  <si>
+    <t>KillingProbabilityTen</t>
+  </si>
+  <si>
+    <t>斩杀10%血量以下非BOSS敌人的概率</t>
+  </si>
+  <si>
+    <t>KillingBringsBackBlood</t>
+  </si>
+  <si>
+    <t>血量低于20%以下时,杀人回血</t>
+  </si>
+  <si>
+    <t>ManyMonsterDamage</t>
+  </si>
+  <si>
+    <t>敌人数量大于1时,造成的伤害</t>
+  </si>
+  <si>
+    <t>UsingRubbingCards</t>
+  </si>
+  <si>
+    <t>亮牌前使用过搓牌,结算时的攻击力</t>
+  </si>
+  <si>
+    <t>HeroHpReplyEveryLevelEnding</t>
+  </si>
+  <si>
+    <t>每关结束后,回复的血量百分比</t>
+  </si>
+  <si>
+    <t>ProOfObtainingFundsEverySettlement</t>
+  </si>
+  <si>
+    <t>结算时,获得额外资金的概率</t>
+  </si>
+  <si>
+    <t>OneMonsterDamage</t>
+  </si>
+  <si>
+    <t>只剩1名敌人时,造成的伤害</t>
+  </si>
+  <si>
+    <t>HpUnderDamage</t>
+  </si>
+  <si>
+    <t>血量低于20%时,造成的伤害</t>
+  </si>
+  <si>
+    <t>KillingProOfObtainingFunds</t>
+  </si>
+  <si>
+    <t>击杀敌人时,获得额外资金的概率</t>
+  </si>
+  <si>
+    <t>InitialFunds</t>
+  </si>
+  <si>
+    <t>初始拥有资金</t>
+  </si>
+  <si>
+    <t>ProOfExtraAttack</t>
+  </si>
+  <si>
+    <t>额外造成1次10%伤害的概率</t>
+  </si>
+  <si>
+    <t>CardMagnification</t>
+  </si>
+  <si>
+    <t>结算时获得额外倍率</t>
+  </si>
+  <si>
+    <t>SquarePlate</t>
+  </si>
+  <si>
+    <t>每张方片牌在结算时提供倍率</t>
+  </si>
+  <si>
+    <t>Spades</t>
+  </si>
+  <si>
+    <t>每张黑桃牌在结算时提供倍率</t>
+  </si>
+  <si>
+    <t>RedHeart</t>
+  </si>
+  <si>
+    <t>每张红心牌在结算时提供倍率</t>
+  </si>
+  <si>
+    <t>PlumBlossom</t>
+  </si>
+  <si>
+    <t>每张梅花牌在结算时提供倍率</t>
+  </si>
+  <si>
+    <t>对子倍率提高</t>
+  </si>
+  <si>
+    <t>顺子倍率提高</t>
+  </si>
+  <si>
+    <t>同花倍率提高</t>
+  </si>
+  <si>
+    <t>同花顺倍率提高</t>
+  </si>
+  <si>
+    <t>豹子倍率提高</t>
+  </si>
+  <si>
+    <t>SquarePlateAttack</t>
+  </si>
+  <si>
+    <t>每张方片牌在结算时提供攻击力</t>
+  </si>
+  <si>
+    <t>SpadesAttack</t>
+  </si>
+  <si>
+    <t>每张黑桃牌在结算时提供攻击力</t>
+  </si>
+  <si>
+    <t>RedHeartAttack</t>
+  </si>
+  <si>
+    <t>每张红心牌在结算时提供攻击力</t>
+  </si>
+  <si>
+    <t>PlumBlossomAttack</t>
+  </si>
+  <si>
+    <t>每张梅花牌在结算时提供攻击力</t>
+  </si>
+  <si>
+    <t>CoupletAttack</t>
+  </si>
+  <si>
+    <t>对子牌型在结算时提供攻击力</t>
+  </si>
+  <si>
+    <t>StraightAttack</t>
+  </si>
+  <si>
+    <t>顺子牌型在结算时提供攻击力</t>
+  </si>
+  <si>
+    <t>FlushAttack</t>
+  </si>
+  <si>
+    <t>同花牌型在结算时提供攻击力</t>
+  </si>
+  <si>
+    <t>StraightFlushAttack</t>
+  </si>
+  <si>
+    <t>同花顺牌型在结算时提供攻击力</t>
+  </si>
+  <si>
+    <t>LeopardAttack</t>
+  </si>
+  <si>
+    <t>豹子牌型在结算时提供攻击力</t>
+  </si>
+  <si>
+    <t>HeroHpReplyEveryRoundEnding</t>
+  </si>
+  <si>
+    <t>回合结束回复当前生命值</t>
+  </si>
+  <si>
+    <t>Liability</t>
+  </si>
+  <si>
+    <t>资金可以为负数</t>
+  </si>
+  <si>
+    <t>EveryRubbingNum</t>
+  </si>
+  <si>
+    <t>每剩余1个搓牌次数,提供倍率</t>
+  </si>
+  <si>
+    <t>ProOfHeadCardFunds</t>
+  </si>
+  <si>
+    <t>人头牌提供1资金的概率</t>
+  </si>
+  <si>
+    <t>Camera</t>
+  </si>
+  <si>
+    <t>每有1张留在手里的每张黑桃/梅花,提供倍率</t>
+  </si>
+  <si>
+    <t>Cupid</t>
+  </si>
+  <si>
+    <t>每有1张留在手里的每张方片/红心,提供倍率</t>
+  </si>
+  <si>
+    <t>ConsumeFundsGetAttack</t>
+  </si>
+  <si>
+    <t>每花费10资金,提供英雄攻击力</t>
+  </si>
+  <si>
+    <t>TakeDamageGetFunds</t>
+  </si>
+  <si>
+    <t>受到伤害,提供资金</t>
+  </si>
+  <si>
+    <t>BloodSucking</t>
+  </si>
+  <si>
+    <t>吸血效果</t>
+  </si>
+  <si>
+    <t>DoubleCardAttack</t>
+  </si>
+  <si>
+    <t>亮出的牌点数提供的攻击力提高</t>
+  </si>
+  <si>
+    <t>TheSwordOfVictory</t>
+  </si>
+  <si>
+    <t>结算伤害时,将留在手牌上最大牌点数转化为额外攻击力</t>
+  </si>
+  <si>
+    <t>EveryUseRubbingNum</t>
+  </si>
+  <si>
+    <t>每回合内,每搓1次牌,结算时提供倍率</t>
+  </si>
+  <si>
+    <t>FreeShopRefresh</t>
+  </si>
+  <si>
+    <t>免费商店刷新次数</t>
+  </si>
+  <si>
+    <t>SpecialStraight</t>
+  </si>
+  <si>
+    <t>顺子牌型可以相隔1点组成</t>
+  </si>
+  <si>
+    <t>SpecialEightCard</t>
+  </si>
+  <si>
+    <t>亮出的每张8在结算时提供+8攻击力</t>
+  </si>
+  <si>
+    <t>EvenNumberCard</t>
+  </si>
+  <si>
+    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供倍率</t>
+  </si>
+  <si>
+    <t>OddNumberCard</t>
+  </si>
+  <si>
+    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供倍率</t>
+  </si>
+  <si>
+    <t>HeadCard</t>
+  </si>
+  <si>
+    <t>人头牌提供额外倍率</t>
+  </si>
+  <si>
+    <t>KillAfterSellingPrice</t>
+  </si>
+  <si>
+    <t>击杀敌人,收藏品出售价格提高</t>
+  </si>
+  <si>
+    <t>EveryCardAttackForever</t>
+  </si>
+  <si>
+    <t>亮出的每张牌的点数在结算时会使其提供的攻击力永久提高</t>
+  </si>
+  <si>
+    <t>SpecialNineCard</t>
+  </si>
+  <si>
+    <t>亮出的每张9在结算时提供资金</t>
+  </si>
+  <si>
+    <t>SpecialTwoThreeFive</t>
+  </si>
+  <si>
+    <t>散排235牌型等同于豹子牌型,并且可以战胜所有牌型</t>
+  </si>
+  <si>
+    <t>SpecialFlush</t>
+  </si>
+  <si>
+    <t>红桃和方片视为同一花色,黑桃和梅花视为同一花色</t>
+  </si>
+  <si>
+    <t>RubbingCardsNum</t>
+  </si>
+  <si>
+    <t>每回合搓牌次数</t>
+  </si>
+  <si>
+    <t>NoSkill</t>
+  </si>
+  <si>
+    <t>结算时,所有技能都无剩余使用次数时,提供倍率</t>
+  </si>
+  <si>
+    <t>EveryRelic</t>
+  </si>
+  <si>
+    <t>每有1个收藏品,结算时提供倍率</t>
+  </si>
+  <si>
+    <t>NoUseRubbingEveryRubbingNum</t>
+  </si>
+  <si>
+    <t>结算时,若未使用过搓牌,每个搓牌次数提供+6倍率</t>
+  </si>
+  <si>
+    <t>AllCardIsHeadCard</t>
+  </si>
+  <si>
+    <t>所有牌均视为人头牌</t>
+  </si>
+  <si>
+    <t>SpecialACard</t>
+  </si>
+  <si>
+    <t>A牌在结算时提供倍率</t>
+  </si>
+  <si>
+    <t>AccumulatedNumOfCardType</t>
+  </si>
+  <si>
+    <t>亮牌时,将该牌型在本局内亮出过的次数来提供倍率</t>
+  </si>
+  <si>
+    <t>ProOfUpCardType</t>
+  </si>
+  <si>
+    <t>亮牌时,有概率将该牌型提供的倍率永久+1</t>
+  </si>
+  <si>
+    <t>RubbingCardRelic</t>
+  </si>
+  <si>
+    <t>每使用1次搓牌,结算时该收藏品永久提供倍率</t>
+  </si>
+  <si>
+    <t>SpecialSevenCardPro</t>
+  </si>
+  <si>
+    <t>幸运七触发概率</t>
+  </si>
+  <si>
+    <t>SpecialSevenCardAttack</t>
+  </si>
+  <si>
+    <t>幸运七触发时提供的攻击力</t>
+  </si>
+  <si>
+    <t>SpecialSevenCard</t>
+  </si>
+  <si>
+    <t>幸运七触发时提供的倍率</t>
+  </si>
+  <si>
+    <t>HeroTakeDamagePer</t>
+  </si>
+  <si>
+    <t>英雄承受的伤害百分比</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>英雄造成的伤害百分比</t>
   </si>
   <si>
     <t>VersatilePerson</t>
   </si>
   <si>
-    <t>多面手</t>
-  </si>
-  <si>
-    <t>Archer</t>
-  </si>
-  <si>
-    <t>射手</t>
-  </si>
-  <si>
-    <t>LoudVoice</t>
-  </si>
-  <si>
-    <t>大嗓门</t>
-  </si>
-  <si>
-    <t>NouveauRiche</t>
-  </si>
-  <si>
-    <t>暴发户</t>
-  </si>
-  <si>
-    <t>HomelessPerson</t>
-  </si>
-  <si>
-    <t>流浪汉</t>
-  </si>
-  <si>
-    <t>GodOfGamblers</t>
-  </si>
-  <si>
-    <t>赌神</t>
-  </si>
-  <si>
-    <t>MechanismType</t>
-  </si>
-  <si>
-    <t>TwoCardAttack</t>
-  </si>
-  <si>
-    <t>数字牌2提供额外攻击力</t>
-  </si>
-  <si>
-    <t>ThreeCardAttack</t>
-  </si>
-  <si>
-    <t>数字牌3提供额外攻击力</t>
-  </si>
-  <si>
-    <t>FourCardAttack</t>
-  </si>
-  <si>
-    <t>数字牌4提供额外攻击力</t>
-  </si>
-  <si>
-    <t>FiveCardAttack</t>
-  </si>
-  <si>
-    <t>数字牌5提供额外攻击力</t>
-  </si>
-  <si>
-    <t>SixCardAttack</t>
-  </si>
-  <si>
-    <t>数字牌6提供额外攻击力</t>
-  </si>
-  <si>
-    <t>SevenCardAttack</t>
-  </si>
-  <si>
-    <t>数字牌7提供额外攻击力</t>
-  </si>
-  <si>
-    <t>EightCardAttack</t>
-  </si>
-  <si>
-    <t>数字牌8提供额外攻击力</t>
-  </si>
-  <si>
-    <t>NineCardAttack</t>
-  </si>
-  <si>
-    <t>数字牌9提供额外攻击力</t>
-  </si>
-  <si>
-    <t>TenCardAttack</t>
-  </si>
-  <si>
-    <t>数字牌10提供额外攻击力</t>
-  </si>
-  <si>
-    <t>ACardAttack</t>
-  </si>
-  <si>
-    <t>A牌提供额外攻击力</t>
-  </si>
-  <si>
-    <t>HeadCardAttack</t>
-  </si>
-  <si>
-    <t>人头牌提供额外攻击力</t>
-  </si>
-  <si>
-    <t>HeroHpMax</t>
-  </si>
-  <si>
-    <t>英雄的血量上限</t>
-  </si>
-  <si>
-    <t>HeroTakeDamage</t>
-  </si>
-  <si>
-    <t>英雄承受的伤害</t>
-  </si>
-  <si>
-    <t>HeroAttack</t>
-  </si>
-  <si>
-    <t>英雄的基础攻击力</t>
-  </si>
-  <si>
-    <t>HeroCritical</t>
-  </si>
-  <si>
-    <t>英雄的暴击率</t>
-  </si>
-  <si>
-    <t>AttackBossDamage</t>
-  </si>
-  <si>
-    <t>对BOSS的伤害</t>
-  </si>
-  <si>
-    <t>FirstShowCardEveryLevel</t>
-  </si>
-  <si>
-    <t>每关首次亮牌后结算倍率</t>
-  </si>
-  <si>
-    <t>KillingProbabilityTen</t>
-  </si>
-  <si>
-    <t>斩杀10%血量以下非BOSS敌人的概率</t>
-  </si>
-  <si>
-    <t>KillingBringsBackBlood</t>
-  </si>
-  <si>
-    <t>血量低于20%以下时,杀人回血</t>
-  </si>
-  <si>
-    <t>ManyMonsterDamage</t>
-  </si>
-  <si>
-    <t>敌人数量大于1时,造成的伤害</t>
-  </si>
-  <si>
-    <t>UsingRubbingCards</t>
-  </si>
-  <si>
-    <t>亮牌前使用过搓牌,结算时的攻击力</t>
-  </si>
-  <si>
-    <t>HeroHpReplyEveryLevelEnding</t>
-  </si>
-  <si>
-    <t>每关结束后,回复的血量百分比</t>
-  </si>
-  <si>
-    <t>ProOfObtainingFundsEverySettlement</t>
-  </si>
-  <si>
-    <t>结算时,获得额外资金的概率</t>
-  </si>
-  <si>
-    <t>OneMonsterDamage</t>
-  </si>
-  <si>
-    <t>只剩1名敌人时,造成的伤害</t>
-  </si>
-  <si>
-    <t>HpUnderDamage</t>
-  </si>
-  <si>
-    <t>血量低于20%时,造成的伤害</t>
-  </si>
-  <si>
-    <t>KillingProOfObtainingFunds</t>
-  </si>
-  <si>
-    <t>击杀敌人时,获得额外资金的概率</t>
-  </si>
-  <si>
-    <t>InitialFunds</t>
-  </si>
-  <si>
-    <t>初始拥有资金</t>
-  </si>
-  <si>
-    <t>ProOfExtraAttack</t>
-  </si>
-  <si>
-    <t>额外造成1次10%伤害的概率</t>
-  </si>
-  <si>
-    <t>CardMagnification</t>
-  </si>
-  <si>
-    <t>结算时获得额外倍率</t>
-  </si>
-  <si>
-    <t>SquarePlate</t>
-  </si>
-  <si>
-    <t>每张方片牌在结算时提供倍率</t>
-  </si>
-  <si>
-    <t>Spades</t>
-  </si>
-  <si>
-    <t>每张黑桃牌在结算时提供倍率</t>
-  </si>
-  <si>
-    <t>RedHeart</t>
-  </si>
-  <si>
-    <t>每张红心牌在结算时提供倍率</t>
-  </si>
-  <si>
-    <t>PlumBlossom</t>
-  </si>
-  <si>
-    <t>每张梅花牌在结算时提供倍率</t>
-  </si>
-  <si>
-    <t>对子倍率提高</t>
-  </si>
-  <si>
-    <t>顺子倍率提高</t>
-  </si>
-  <si>
-    <t>同花倍率提高</t>
-  </si>
-  <si>
-    <t>同花顺倍率提高</t>
-  </si>
-  <si>
-    <t>豹子倍率提高</t>
-  </si>
-  <si>
-    <t>SquarePlateAttack</t>
-  </si>
-  <si>
-    <t>每张方片牌在结算时提供攻击力</t>
-  </si>
-  <si>
-    <t>SpadesAttack</t>
-  </si>
-  <si>
-    <t>每张黑桃牌在结算时提供攻击力</t>
-  </si>
-  <si>
-    <t>RedHeartAttack</t>
-  </si>
-  <si>
-    <t>每张红心牌在结算时提供攻击力</t>
-  </si>
-  <si>
-    <t>PlumBlossomAttack</t>
-  </si>
-  <si>
-    <t>每张梅花牌在结算时提供攻击力</t>
-  </si>
-  <si>
-    <t>CoupletAttack</t>
-  </si>
-  <si>
-    <t>对子牌型在结算时提供攻击力</t>
-  </si>
-  <si>
-    <t>StraightAttack</t>
-  </si>
-  <si>
-    <t>顺子牌型在结算时提供攻击力</t>
-  </si>
-  <si>
-    <t>FlushAttack</t>
-  </si>
-  <si>
-    <t>同花牌型在结算时提供攻击力</t>
-  </si>
-  <si>
-    <t>StraightFlushAttack</t>
-  </si>
-  <si>
-    <t>同花顺牌型在结算时提供攻击力</t>
-  </si>
-  <si>
-    <t>LeopardAttack</t>
-  </si>
-  <si>
-    <t>豹子牌型在结算时提供攻击力</t>
-  </si>
-  <si>
-    <t>HeroHpReplyEveryRoundEnding</t>
-  </si>
-  <si>
-    <t>回合结束回复当前生命值</t>
-  </si>
-  <si>
-    <t>Liability</t>
-  </si>
-  <si>
-    <t>资金可以为负数</t>
-  </si>
-  <si>
-    <t>EveryRubbingNum</t>
-  </si>
-  <si>
-    <t>每剩余1个搓牌次数,提供倍率</t>
-  </si>
-  <si>
-    <t>ProOfHeadCardFunds</t>
-  </si>
-  <si>
-    <t>人头牌提供1资金的概率</t>
-  </si>
-  <si>
-    <t>Camera</t>
-  </si>
-  <si>
-    <t>每有1张留在手里的每张黑桃/梅花,提供倍率</t>
-  </si>
-  <si>
-    <t>Cupid</t>
-  </si>
-  <si>
-    <t>每有1张留在手里的每张方片/红心,提供倍率</t>
-  </si>
-  <si>
-    <t>ConsumeFundsGetAttack</t>
-  </si>
-  <si>
-    <t>每花费10资金,提供英雄攻击力</t>
-  </si>
-  <si>
-    <t>TakeDamageGetFunds</t>
-  </si>
-  <si>
-    <t>受到伤害,提供资金</t>
-  </si>
-  <si>
-    <t>BloodSucking</t>
-  </si>
-  <si>
-    <t>吸血效果</t>
-  </si>
-  <si>
-    <t>DoubleCardAttack</t>
-  </si>
-  <si>
-    <t>亮出的牌点数提供的攻击力提高</t>
-  </si>
-  <si>
-    <t>TheSwordOfVictory</t>
-  </si>
-  <si>
-    <t>结算伤害时,将留在手牌上最大牌点数转化为额外攻击力</t>
-  </si>
-  <si>
-    <t>EveryUseRubbingNum</t>
-  </si>
-  <si>
-    <t>每回合内,每搓1次牌,结算时提供倍率</t>
-  </si>
-  <si>
-    <t>FreeShopRefresh</t>
-  </si>
-  <si>
-    <t>免费商店刷新次数</t>
-  </si>
-  <si>
-    <t>SpecialStraight</t>
-  </si>
-  <si>
-    <t>顺子牌型可以相隔1点组成</t>
-  </si>
-  <si>
-    <t>SpecialEightCard</t>
-  </si>
-  <si>
-    <t>亮出的每张8在结算时提供+8攻击力</t>
-  </si>
-  <si>
-    <t>EvenNumberCard</t>
-  </si>
-  <si>
-    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供倍率</t>
-  </si>
-  <si>
-    <t>OddNumberCard</t>
-  </si>
-  <si>
-    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供倍率</t>
-  </si>
-  <si>
-    <t>HeadCard</t>
-  </si>
-  <si>
-    <t>人头牌提供额外倍率</t>
-  </si>
-  <si>
-    <t>KillAfterSellingPrice</t>
-  </si>
-  <si>
-    <t>击杀敌人,收藏品出售价格提高</t>
-  </si>
-  <si>
-    <t>EveryCardAttackForever</t>
-  </si>
-  <si>
-    <t>亮出的每张牌的点数在结算时会使其提供的攻击力永久提高</t>
-  </si>
-  <si>
-    <t>SpecialNineCard</t>
-  </si>
-  <si>
-    <t>亮出的每张9在结算时提供资金</t>
-  </si>
-  <si>
-    <t>SpecialTwoThreeFive</t>
-  </si>
-  <si>
-    <t>散排235牌型等同于豹子牌型,并且可以战胜所有牌型</t>
-  </si>
-  <si>
-    <t>SpecialFlush</t>
-  </si>
-  <si>
-    <t>红桃和方片视为同一花色,黑桃和梅花视为同一花色</t>
-  </si>
-  <si>
-    <t>RubbingCardsNum</t>
-  </si>
-  <si>
-    <t>每回合搓牌次数</t>
-  </si>
-  <si>
-    <t>NoSkill</t>
-  </si>
-  <si>
-    <t>结算时,所有技能都无剩余使用次数时,提供倍率</t>
-  </si>
-  <si>
-    <t>EveryRelic</t>
-  </si>
-  <si>
-    <t>每有1个收藏品,结算时提供倍率</t>
-  </si>
-  <si>
-    <t>NoUseRubbingEveryRubbingNum</t>
-  </si>
-  <si>
-    <t>结算时,若未使用过搓牌,每个搓牌次数提供+6倍率</t>
-  </si>
-  <si>
-    <t>AllCardIsHeadCard</t>
-  </si>
-  <si>
-    <t>所有牌均视为人头牌</t>
-  </si>
-  <si>
-    <t>SpecialACard</t>
-  </si>
-  <si>
-    <t>A牌在结算时提供倍率</t>
-  </si>
-  <si>
-    <t>AccumulatedNumOfCardType</t>
-  </si>
-  <si>
-    <t>亮牌时,将该牌型在本局内亮出过的次数来提供倍率</t>
-  </si>
-  <si>
-    <t>ProOfUpCardType</t>
-  </si>
-  <si>
-    <t>亮牌时,有概率将该牌型提供的倍率永久+1</t>
-  </si>
-  <si>
-    <t>RubbingCardRelic</t>
-  </si>
-  <si>
-    <t>每使用1次搓牌,结算时该收藏品永久提供倍率</t>
-  </si>
-  <si>
-    <t>SpecialSevenCardPro</t>
-  </si>
-  <si>
-    <t>幸运七触发概率</t>
-  </si>
-  <si>
-    <t>SpecialSevenCardAttack</t>
-  </si>
-  <si>
-    <t>幸运七触发时提供的攻击力</t>
-  </si>
-  <si>
-    <t>SpecialSevenCard</t>
-  </si>
-  <si>
-    <t>幸运七触发时提供的倍率</t>
+    <t>攻击时,对其他人造成百分比伤害</t>
+  </si>
+  <si>
+    <t>ExtraAttackOneTime</t>
+  </si>
+  <si>
+    <t>额外攻击敌人1次的概率</t>
+  </si>
+  <si>
+    <t>AoeDamage</t>
+  </si>
+  <si>
+    <t>攻击变成原伤害百分比的群体伤害</t>
+  </si>
+  <si>
+    <t>EpicLegendRelicProUp</t>
+  </si>
+  <si>
+    <t>史诗/传说的收藏品概率提高</t>
+  </si>
+  <si>
+    <t>RelicPricePer</t>
+  </si>
+  <si>
+    <t>收藏品价格百分比</t>
+  </si>
+  <si>
+    <t>GetGoldAfterLevel</t>
+  </si>
+  <si>
+    <t>每关通过后获得的金币数量百分比</t>
+  </si>
+  <si>
+    <t>MissDamagePer</t>
+  </si>
+  <si>
+    <t>免疫伤害的概率</t>
   </si>
   <si>
     <t>MaxHp</t>
   </si>
   <si>
-    <t>立即获得生命值</t>
-  </si>
-  <si>
     <t>EveryRoundHpUp</t>
   </si>
   <si>
-    <t>每次结算生命值提高</t>
-  </si>
-  <si>
     <t>TwoThreeFive</t>
   </si>
   <si>
-    <t>235牌型</t>
+    <t>235</t>
   </si>
 </sst>
 </file>
@@ -1737,7 +1734,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:D158"/>
+  <dimension ref="A4:D148"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.7416666666667" style="1" customWidth="1"/>
@@ -2112,1269 +2109,1279 @@
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C51" s="2">
-        <v>1</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
     <row r="52" spans="1:4">
       <c r="A52" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B52" t="s">
-        <v>61</v>
+      <c r="B52" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="C52" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B53" t="s">
-        <v>63</v>
+      <c r="B53" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="C53" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B54" t="s">
-        <v>65</v>
+      <c r="B54" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="C54" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B55" t="s">
-        <v>67</v>
+      <c r="B55" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="C55" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>69</v>
+      <c r="B56" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="C56" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B57" t="s">
-        <v>71</v>
+      <c r="B57" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="C57" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C58" s="2">
+        <v>7</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C59" s="2">
         <v>8</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="2">
+        <v>9</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="C60" s="2">
-        <v>1</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B61" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C61" s="2">
+        <v>10</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="C61" s="2">
-        <v>2</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B62" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C62" s="2">
+        <v>11</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="C62" s="2">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C63" s="2">
+        <v>12</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="C63" s="2">
-        <v>4</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C64" s="2">
+        <v>13</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="C64" s="2">
-        <v>5</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B65" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C65" s="2">
+        <v>14</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="C65" s="2">
-        <v>6</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B66" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C66" s="2">
+        <v>15</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="C66" s="2">
-        <v>7</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B67" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C67" s="2">
+        <v>16</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="C67" s="2">
-        <v>8</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C68" s="2">
+        <v>17</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="C68" s="2">
-        <v>9</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B69" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C69" s="2">
+        <v>18</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="C69" s="2">
-        <v>10</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B70" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C70" s="2">
+        <v>19</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="C70" s="2">
-        <v>11</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B71" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C71" s="2">
+        <v>20</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="C71" s="2">
-        <v>12</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B72" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C72" s="2">
+        <v>21</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="C72" s="2">
-        <v>13</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C73" s="2">
+        <v>22</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="C73" s="2">
-        <v>14</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B74" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C74" s="2">
+        <v>23</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="C74" s="2">
-        <v>15</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C75" s="2">
+        <v>24</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="C75" s="2">
-        <v>16</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B76" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C76" s="2">
+        <v>25</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="C76" s="2">
-        <v>17</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B77" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C77" s="2">
+        <v>26</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C77" s="2">
-        <v>18</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B78" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C78" s="2">
+        <v>27</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="C78" s="2">
-        <v>19</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B79" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C79" s="2">
+        <v>28</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C79" s="2">
-        <v>20</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C80" s="2">
-        <v>21</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>118</v>
+        <v>58</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="C81" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>120</v>
+        <v>58</v>
+      </c>
+      <c r="B82" t="s">
+        <v>117</v>
       </c>
       <c r="C82" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>122</v>
+        <v>58</v>
+      </c>
+      <c r="B83" t="s">
+        <v>119</v>
       </c>
       <c r="C83" s="2">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>124</v>
+        <v>58</v>
+      </c>
+      <c r="B84" t="s">
+        <v>121</v>
       </c>
       <c r="C84" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>126</v>
+        <v>58</v>
+      </c>
+      <c r="B85" t="s">
+        <v>123</v>
       </c>
       <c r="C85" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>128</v>
+        <v>11</v>
       </c>
       <c r="C86" s="2">
-        <v>27</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>129</v>
+        <v>34</v>
+      </c>
+      <c r="D86" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>130</v>
+        <v>58</v>
+      </c>
+      <c r="B87" t="s">
+        <v>13</v>
       </c>
       <c r="C87" s="2">
-        <v>28</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>131</v>
+        <v>35</v>
+      </c>
+      <c r="D87" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B88" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88" s="2">
+        <v>36</v>
+      </c>
+      <c r="D88" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>132</v>
+        <v>58</v>
+      </c>
+      <c r="B89" t="s">
+        <v>17</v>
       </c>
       <c r="C89" s="2">
-        <v>29</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>133</v>
+        <v>37</v>
+      </c>
+      <c r="D89" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B90" t="s">
-        <v>134</v>
+        <v>58</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="C90" s="2">
-        <v>30</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>135</v>
+        <v>38</v>
+      </c>
+      <c r="D90" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B91" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C91" s="2">
-        <v>31</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>137</v>
+        <v>39</v>
+      </c>
+      <c r="D91" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B92" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C92" s="2">
-        <v>32</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>139</v>
+        <v>40</v>
+      </c>
+      <c r="D92" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B93" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C93" s="2">
-        <v>33</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
+      </c>
+      <c r="D93" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>11</v>
+        <v>58</v>
+      </c>
+      <c r="B94" t="s">
+        <v>136</v>
       </c>
       <c r="C94" s="2">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D94" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B95" t="s">
-        <v>13</v>
+        <v>58</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="C95" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D95" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="C96" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D96" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B97" t="s">
-        <v>17</v>
+        <v>142</v>
       </c>
       <c r="C97" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D97" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>19</v>
+        <v>58</v>
+      </c>
+      <c r="B98" t="s">
+        <v>144</v>
       </c>
       <c r="C98" s="2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D98" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B99" t="s">
+        <v>58</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C99" s="2">
+        <v>47</v>
+      </c>
+      <c r="D99" t="s">
         <v>147</v>
-      </c>
-      <c r="C99" s="2">
-        <v>39</v>
-      </c>
-      <c r="D99" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B100" t="s">
+        <v>58</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C100" s="2">
+        <v>48</v>
+      </c>
+      <c r="D100" t="s">
         <v>149</v>
-      </c>
-      <c r="C100" s="2">
-        <v>40</v>
-      </c>
-      <c r="D100" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B101" t="s">
+        <v>150</v>
+      </c>
+      <c r="C101" s="2">
+        <v>49</v>
+      </c>
+      <c r="D101" t="s">
         <v>151</v>
-      </c>
-      <c r="C101" s="2">
-        <v>41</v>
-      </c>
-      <c r="D101" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B102" t="s">
+        <v>152</v>
+      </c>
+      <c r="C102" s="2">
+        <v>50</v>
+      </c>
+      <c r="D102" t="s">
         <v>153</v>
-      </c>
-      <c r="C102" s="2">
-        <v>42</v>
-      </c>
-      <c r="D102" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B103" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C103" s="2">
+        <v>51</v>
+      </c>
+      <c r="D103" t="s">
         <v>155</v>
-      </c>
-      <c r="C103" s="2">
-        <v>43</v>
-      </c>
-      <c r="D103" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B104" t="s">
+        <v>156</v>
+      </c>
+      <c r="C104" s="2">
+        <v>52</v>
+      </c>
+      <c r="D104" t="s">
         <v>157</v>
-      </c>
-      <c r="C104" s="2">
-        <v>44</v>
-      </c>
-      <c r="D104" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B105" t="s">
+        <v>158</v>
+      </c>
+      <c r="C105" s="2">
+        <v>53</v>
+      </c>
+      <c r="D105" t="s">
         <v>159</v>
-      </c>
-      <c r="C105" s="2">
-        <v>45</v>
-      </c>
-      <c r="D105" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B106" t="s">
+        <v>160</v>
+      </c>
+      <c r="C106" s="2">
+        <v>54</v>
+      </c>
+      <c r="D106" t="s">
         <v>161</v>
-      </c>
-      <c r="C106" s="2">
-        <v>46</v>
-      </c>
-      <c r="D106" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B107" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B107" t="s">
+        <v>162</v>
+      </c>
+      <c r="C107" s="2">
+        <v>55</v>
+      </c>
+      <c r="D107" t="s">
         <v>163</v>
-      </c>
-      <c r="C107" s="2">
-        <v>47</v>
-      </c>
-      <c r="D107" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B108" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C108" s="2">
+        <v>56</v>
+      </c>
+      <c r="D108" t="s">
         <v>165</v>
-      </c>
-      <c r="C108" s="2">
-        <v>48</v>
-      </c>
-      <c r="D108" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B109" t="s">
+        <v>166</v>
+      </c>
+      <c r="C109" s="2">
+        <v>57</v>
+      </c>
+      <c r="D109" t="s">
         <v>167</v>
-      </c>
-      <c r="C109" s="2">
-        <v>49</v>
-      </c>
-      <c r="D109" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B110" t="s">
+        <v>168</v>
+      </c>
+      <c r="C110" s="2">
+        <v>58</v>
+      </c>
+      <c r="D110" t="s">
         <v>169</v>
-      </c>
-      <c r="C110" s="2">
-        <v>50</v>
-      </c>
-      <c r="D110" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B111" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B111" t="s">
+        <v>170</v>
+      </c>
+      <c r="C111" s="2">
+        <v>59</v>
+      </c>
+      <c r="D111" t="s">
         <v>171</v>
-      </c>
-      <c r="C111" s="2">
-        <v>51</v>
-      </c>
-      <c r="D111" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B112" t="s">
+        <v>172</v>
+      </c>
+      <c r="C112" s="2">
+        <v>60</v>
+      </c>
+      <c r="D112" t="s">
         <v>173</v>
-      </c>
-      <c r="C112" s="2">
-        <v>52</v>
-      </c>
-      <c r="D112" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B113" t="s">
+        <v>174</v>
+      </c>
+      <c r="C113" s="2">
+        <v>61</v>
+      </c>
+      <c r="D113" t="s">
         <v>175</v>
-      </c>
-      <c r="C113" s="2">
-        <v>53</v>
-      </c>
-      <c r="D113" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B114" t="s">
+        <v>176</v>
+      </c>
+      <c r="C114" s="2">
+        <v>62</v>
+      </c>
+      <c r="D114" t="s">
         <v>177</v>
-      </c>
-      <c r="C114" s="2">
-        <v>54</v>
-      </c>
-      <c r="D114" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B115" t="s">
+        <v>178</v>
+      </c>
+      <c r="C115" s="2">
+        <v>63</v>
+      </c>
+      <c r="D115" t="s">
         <v>179</v>
-      </c>
-      <c r="C115" s="2">
-        <v>55</v>
-      </c>
-      <c r="D115" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B116" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B116" t="s">
+        <v>180</v>
+      </c>
+      <c r="C116" s="2">
+        <v>64</v>
+      </c>
+      <c r="D116" t="s">
         <v>181</v>
-      </c>
-      <c r="C116" s="2">
-        <v>56</v>
-      </c>
-      <c r="D116" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B117" t="s">
+        <v>182</v>
+      </c>
+      <c r="C117" s="2">
+        <v>65</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="C117" s="2">
-        <v>57</v>
-      </c>
-      <c r="D117" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B118" t="s">
+        <v>184</v>
+      </c>
+      <c r="C118" s="2">
+        <v>66</v>
+      </c>
+      <c r="D118" t="s">
         <v>185</v>
-      </c>
-      <c r="C118" s="2">
-        <v>58</v>
-      </c>
-      <c r="D118" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B119" t="s">
+        <v>186</v>
+      </c>
+      <c r="C119" s="2">
+        <v>67</v>
+      </c>
+      <c r="D119" t="s">
         <v>187</v>
-      </c>
-      <c r="C119" s="2">
-        <v>59</v>
-      </c>
-      <c r="D119" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B120" t="s">
+        <v>188</v>
+      </c>
+      <c r="C120" s="2">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
         <v>189</v>
-      </c>
-      <c r="C120" s="2">
-        <v>60</v>
-      </c>
-      <c r="D120" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B121" t="s">
+        <v>190</v>
+      </c>
+      <c r="C121" s="2">
+        <v>69</v>
+      </c>
+      <c r="D121" t="s">
         <v>191</v>
-      </c>
-      <c r="C121" s="2">
-        <v>61</v>
-      </c>
-      <c r="D121" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B122" t="s">
+        <v>192</v>
+      </c>
+      <c r="C122" s="2">
+        <v>70</v>
+      </c>
+      <c r="D122" t="s">
         <v>193</v>
-      </c>
-      <c r="C122" s="2">
-        <v>62</v>
-      </c>
-      <c r="D122" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B123" t="s">
+        <v>58</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C123" s="2">
+        <v>71</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="C123" s="2">
-        <v>63</v>
-      </c>
-      <c r="D123" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B124" t="s">
+        <v>58</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C124" s="2">
+        <v>72</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="C124" s="2">
-        <v>64</v>
-      </c>
-      <c r="D124" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B125" t="s">
+        <v>198</v>
+      </c>
+      <c r="C125" s="2">
+        <v>73</v>
+      </c>
+      <c r="D125" t="s">
         <v>199</v>
-      </c>
-      <c r="C125" s="2">
-        <v>65</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B126" t="s">
+        <v>200</v>
+      </c>
+      <c r="C126" s="2">
+        <v>74</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="C126" s="2">
-        <v>66</v>
-      </c>
-      <c r="D126" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B127" t="s">
+        <v>202</v>
+      </c>
+      <c r="C127" s="2">
         <v>75</v>
       </c>
-      <c r="B127" t="s">
+      <c r="D127" t="s">
         <v>203</v>
-      </c>
-      <c r="C127" s="2">
-        <v>67</v>
-      </c>
-      <c r="D127" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B128" t="s">
+        <v>204</v>
+      </c>
+      <c r="C128" s="2">
+        <v>76</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="C128" s="2">
-        <v>68</v>
-      </c>
-      <c r="D128" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B129" t="s">
+        <v>206</v>
+      </c>
+      <c r="C129" s="2">
+        <v>77</v>
+      </c>
+      <c r="D129" t="s">
         <v>207</v>
-      </c>
-      <c r="C129" s="2">
-        <v>69</v>
-      </c>
-      <c r="D129" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B130" t="s">
+        <v>208</v>
+      </c>
+      <c r="C130" s="2">
+        <v>78</v>
+      </c>
+      <c r="D130" t="s">
         <v>209</v>
-      </c>
-      <c r="C130" s="2">
-        <v>70</v>
-      </c>
-      <c r="D130" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B131" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B131" t="s">
+        <v>210</v>
+      </c>
+      <c r="C131" s="2">
+        <v>79</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="C131" s="2">
-        <v>71</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B132" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B132" t="s">
+        <v>212</v>
+      </c>
+      <c r="C132" s="2">
+        <v>80</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="C132" s="2">
-        <v>72</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B133" t="s">
+        <v>214</v>
+      </c>
+      <c r="C133" s="2">
+        <v>81</v>
+      </c>
+      <c r="D133" t="s">
         <v>215</v>
-      </c>
-      <c r="C133" s="2">
-        <v>73</v>
-      </c>
-      <c r="D133" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B134" t="s">
+        <v>216</v>
+      </c>
+      <c r="C134" s="2">
+        <v>82</v>
+      </c>
+      <c r="D134" t="s">
         <v>217</v>
-      </c>
-      <c r="C134" s="2">
-        <v>74</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B135" t="s">
+        <v>58</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C135" s="2">
+        <v>83</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="C135" s="2">
-        <v>75</v>
-      </c>
-      <c r="D135" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B136" t="s">
+        <v>220</v>
+      </c>
+      <c r="C136" s="2">
+        <v>84</v>
+      </c>
+      <c r="D136" t="s">
         <v>221</v>
-      </c>
-      <c r="C136" s="2">
-        <v>76</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B137" t="s">
+        <v>222</v>
+      </c>
+      <c r="C137" s="2">
+        <v>85</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="C137" s="2">
-        <v>77</v>
-      </c>
-      <c r="D137" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B138" t="s">
+        <v>224</v>
+      </c>
+      <c r="C138" s="2">
+        <v>86</v>
+      </c>
+      <c r="D138" t="s">
         <v>225</v>
-      </c>
-      <c r="C138" s="2">
-        <v>78</v>
-      </c>
-      <c r="D138" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B139" t="s">
+        <v>226</v>
+      </c>
+      <c r="C139" s="2">
+        <v>87</v>
+      </c>
+      <c r="D139" t="s">
         <v>227</v>
-      </c>
-      <c r="C139" s="2">
-        <v>79</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B140" t="s">
+        <v>228</v>
+      </c>
+      <c r="C140" s="2">
+        <v>88</v>
+      </c>
+      <c r="D140" t="s">
         <v>229</v>
-      </c>
-      <c r="C140" s="2">
-        <v>80</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B141" t="s">
+        <v>58</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C141" s="2">
+        <v>89</v>
+      </c>
+      <c r="D141" t="s">
         <v>231</v>
-      </c>
-      <c r="C141" s="2">
-        <v>81</v>
-      </c>
-      <c r="D141" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B142" t="s">
+        <v>58</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C142" s="2">
+        <v>90</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C142" s="2">
-        <v>82</v>
-      </c>
-      <c r="D142" t="s">
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B143" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="143" spans="1:4">
-      <c r="B143"/>
-      <c r="D143"/>
+      <c r="C143" s="2">
+        <v>91</v>
+      </c>
+      <c r="D143" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="144" spans="1:4">
       <c r="B144"/>
@@ -3385,77 +3392,45 @@
       <c r="D145"/>
     </row>
     <row r="146" spans="1:4">
-      <c r="B146"/>
-      <c r="D146"/>
+      <c r="A146" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B146" t="s">
+        <v>236</v>
+      </c>
+      <c r="C146" s="2">
+        <v>92</v>
+      </c>
+      <c r="D146" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="147" spans="1:4">
-      <c r="B147"/>
-      <c r="D147"/>
+      <c r="A147" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C147" s="2">
+        <v>93</v>
+      </c>
+      <c r="D147" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="148" spans="1:4">
-      <c r="B148"/>
-      <c r="D148"/>
-    </row>
-    <row r="149" spans="1:4">
-      <c r="B149"/>
-      <c r="D149"/>
-    </row>
-    <row r="150" spans="1:4">
-      <c r="B150"/>
-      <c r="D150"/>
-    </row>
-    <row r="151" spans="1:4">
-      <c r="B151"/>
-      <c r="D151"/>
-    </row>
-    <row r="152" spans="1:4">
-      <c r="B152"/>
-      <c r="D152"/>
-    </row>
-    <row r="153" spans="1:4">
-      <c r="B153"/>
-      <c r="D153"/>
-    </row>
-    <row r="154" spans="1:4">
-      <c r="A154" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B154" t="s">
-        <v>235</v>
-      </c>
-      <c r="C154" s="2">
-        <v>11</v>
-      </c>
-      <c r="D154" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4">
-      <c r="A155" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B155" t="s">
-        <v>237</v>
-      </c>
-      <c r="C155" s="2">
-        <v>12</v>
-      </c>
-      <c r="D155" t="s">
+      <c r="A148" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="158" spans="1:4">
-      <c r="A158" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B158" s="2" t="s">
+      <c r="C148" s="2">
+        <v>94</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="C158" s="2">
-        <v>14</v>
-      </c>
-      <c r="D158" t="s">
-        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11535" windowHeight="9750"/>
+    <workbookView windowWidth="11850" windowHeight="11805"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="253">
   <si>
     <t>Enum</t>
   </si>
@@ -752,6 +752,45 @@
   </si>
   <si>
     <t>235</t>
+  </si>
+  <si>
+    <t>ContidionType</t>
+  </si>
+  <si>
+    <t>KillMonster</t>
+  </si>
+  <si>
+    <t>杀敌</t>
+  </si>
+  <si>
+    <t>ShuffleCard</t>
+  </si>
+  <si>
+    <t>搓牌</t>
+  </si>
+  <si>
+    <t>RefreshStore</t>
+  </si>
+  <si>
+    <t>刷新商店</t>
+  </si>
+  <si>
+    <t>亮出顺子</t>
+  </si>
+  <si>
+    <t>亮出散牌235</t>
+  </si>
+  <si>
+    <t>ShuffleCardAndVictory</t>
+  </si>
+  <si>
+    <t>搓牌并战胜对手</t>
+  </si>
+  <si>
+    <t>Seven</t>
+  </si>
+  <si>
+    <t>亮出数字牌7</t>
   </si>
 </sst>
 </file>
@@ -1734,7 +1773,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:D148"/>
+  <dimension ref="A4:D156"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.7416666666667" style="1" customWidth="1"/>
@@ -3433,6 +3472,104 @@
         <v>239</v>
       </c>
     </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C150" s="2">
+        <v>1</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C151" s="2">
+        <v>2</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C152" s="2">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C153" s="2">
+        <v>4</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C154" s="2">
+        <v>5</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C155" s="2">
+        <v>6</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C156" s="2">
+        <v>7</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11850" windowHeight="11805"/>
+    <workbookView windowWidth="15480" windowHeight="10815"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="330">
   <si>
     <t>Enum</t>
   </si>
@@ -742,6 +742,240 @@
     <t>免疫伤害的概率</t>
   </si>
   <si>
+    <t>EveryRoundGetGold</t>
+  </si>
+  <si>
+    <t>每回合开始获得金币</t>
+  </si>
+  <si>
+    <t>EveryRoundEndingGetGoldPer</t>
+  </si>
+  <si>
+    <t>每回合结束概率获得金币</t>
+  </si>
+  <si>
+    <t>EveryRoundEndingGetCritical</t>
+  </si>
+  <si>
+    <t>暴击叠加</t>
+  </si>
+  <si>
+    <t>SteppingStone</t>
+  </si>
+  <si>
+    <t>亮牌大于所有人加攻击力</t>
+  </si>
+  <si>
+    <t>BounceDamage</t>
+  </si>
+  <si>
+    <t>受到伤害反弹伤害</t>
+  </si>
+  <si>
+    <t>AllPeacePer</t>
+  </si>
+  <si>
+    <t>承伤或伤害降低为0的概率</t>
+  </si>
+  <si>
+    <t>DefeatGetAttack</t>
+  </si>
+  <si>
+    <t>牌小获得攻击力</t>
+  </si>
+  <si>
+    <t>DefeatGetHpMax</t>
+  </si>
+  <si>
+    <t>牌小获得生命上限</t>
+  </si>
+  <si>
+    <t>DefeatAllGetGold</t>
+  </si>
+  <si>
+    <t>未造成伤害获得金币</t>
+  </si>
+  <si>
+    <t>IronRiceBowl</t>
+  </si>
+  <si>
+    <t>亮牌后获得金币</t>
+  </si>
+  <si>
+    <t>EveryRoundGetHpMax</t>
+  </si>
+  <si>
+    <t>每回合开始获得生命上限</t>
+  </si>
+  <si>
+    <t>LuckyFlush</t>
+  </si>
+  <si>
+    <t>强行视敌人牌为同花</t>
+  </si>
+  <si>
+    <t>EveryRoundEndingGetEvade</t>
+  </si>
+  <si>
+    <t>闪避叠加</t>
+  </si>
+  <si>
+    <t>ThermosCup</t>
+  </si>
+  <si>
+    <t>半血回血</t>
+  </si>
+  <si>
+    <t>Interest</t>
+  </si>
+  <si>
+    <t>利息</t>
+  </si>
+  <si>
+    <t>Abacus</t>
+  </si>
+  <si>
+    <t>搓牌次数换金币</t>
+  </si>
+  <si>
+    <t>DefeatAllGetGoldAndReplyHp</t>
+  </si>
+  <si>
+    <t>牌小获得金币和回血</t>
+  </si>
+  <si>
+    <t>MissFirstDamage</t>
+  </si>
+  <si>
+    <t>免疫第一次承伤</t>
+  </si>
+  <si>
+    <t>DefeatGetMagnification</t>
+  </si>
+  <si>
+    <t>牌小获得倍率</t>
+  </si>
+  <si>
+    <t>LuckyStraight</t>
+  </si>
+  <si>
+    <t>强行视敌人牌为顺子</t>
+  </si>
+  <si>
+    <t>ReverseResult</t>
+  </si>
+  <si>
+    <t>反转结果的概率</t>
+  </si>
+  <si>
+    <t>NoKillMonsterGetMagnification</t>
+  </si>
+  <si>
+    <t>回合内未进行击杀提高倍率</t>
+  </si>
+  <si>
+    <t>Revenge</t>
+  </si>
+  <si>
+    <t>对赢过自己的怪物类型提高伤害</t>
+  </si>
+  <si>
+    <t>NobleBadge</t>
+  </si>
+  <si>
+    <t>半血以上得金币</t>
+  </si>
+  <si>
+    <t>Trap</t>
+  </si>
+  <si>
+    <t>赢过自己的怪物类型降低伤害</t>
+  </si>
+  <si>
+    <t>DownGrade</t>
+  </si>
+  <si>
+    <t>降级牌型概率</t>
+  </si>
+  <si>
+    <t>AdmissionTicket</t>
+  </si>
+  <si>
+    <t>额外攻击的次数</t>
+  </si>
+  <si>
+    <t>MonsterDamage</t>
+  </si>
+  <si>
+    <t>敌人伤害降低</t>
+  </si>
+  <si>
+    <t>MissGetDamage</t>
+  </si>
+  <si>
+    <t>闪避反击</t>
+  </si>
+  <si>
+    <t>LuckyCouplet</t>
+  </si>
+  <si>
+    <t>强行视敌人牌为对子</t>
+  </si>
+  <si>
+    <t>DefeatGetDamage</t>
+  </si>
+  <si>
+    <t>每次失败提升伤害</t>
+  </si>
+  <si>
+    <t>AstrawToClutchAt</t>
+  </si>
+  <si>
+    <t>免死一次</t>
+  </si>
+  <si>
+    <t>OneMonsterGetDamage</t>
+  </si>
+  <si>
+    <t>孤立无援</t>
+  </si>
+  <si>
+    <t>CardUpGrade</t>
+  </si>
+  <si>
+    <t>牌型升级</t>
+  </si>
+  <si>
+    <t>MonsterHpMax</t>
+  </si>
+  <si>
+    <t>敌人血量上限</t>
+  </si>
+  <si>
+    <t>CriticalAoe</t>
+  </si>
+  <si>
+    <t>暴击触发AOE</t>
+  </si>
+  <si>
+    <t>PerspectiveNum</t>
+  </si>
+  <si>
+    <t>透视次数</t>
+  </si>
+  <si>
+    <t>DamageTurnToGold</t>
+  </si>
+  <si>
+    <t>伤害转为金币</t>
+  </si>
+  <si>
+    <t>GapDamage</t>
+  </si>
+  <si>
+    <t>差距胶囊</t>
+  </si>
+  <si>
     <t>MaxHp</t>
   </si>
   <si>
@@ -749,9 +983,6 @@
   </si>
   <si>
     <t>TwoThreeFive</t>
-  </si>
-  <si>
-    <t>235</t>
   </si>
   <si>
     <t>ContidionType</t>
@@ -956,12 +1187,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1282,7 +1519,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1306,16 +1543,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1324,89 +1561,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1424,6 +1661,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1773,8 +2016,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:D156"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A4:E216"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16.7416666666667" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.7" style="1" customWidth="1"/>
@@ -3212,7 +3455,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:5">
       <c r="A129" s="1" t="s">
         <v>58</v>
       </c>
@@ -3226,7 +3469,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:5">
       <c r="A130" s="1" t="s">
         <v>58</v>
       </c>
@@ -3240,7 +3483,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:5">
       <c r="A131" s="1" t="s">
         <v>58</v>
       </c>
@@ -3254,7 +3497,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:5">
       <c r="A132" s="1" t="s">
         <v>58</v>
       </c>
@@ -3268,7 +3511,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:5">
       <c r="A133" s="1" t="s">
         <v>58</v>
       </c>
@@ -3282,7 +3525,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:5">
       <c r="A134" s="1" t="s">
         <v>58</v>
       </c>
@@ -3296,7 +3539,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="135" spans="1:4">
+    <row r="135" spans="1:5">
       <c r="A135" s="1" t="s">
         <v>58</v>
       </c>
@@ -3310,7 +3553,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="136" spans="1:4">
+    <row r="136" spans="1:5">
       <c r="A136" s="1" t="s">
         <v>58</v>
       </c>
@@ -3324,7 +3567,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="137" spans="1:4">
+    <row r="137" spans="1:5">
       <c r="A137" s="1" t="s">
         <v>58</v>
       </c>
@@ -3338,7 +3581,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="138" spans="1:4">
+    <row r="138" spans="1:5">
       <c r="A138" s="1" t="s">
         <v>58</v>
       </c>
@@ -3352,7 +3595,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="139" spans="1:4">
+    <row r="139" spans="1:5">
       <c r="A139" s="1" t="s">
         <v>58</v>
       </c>
@@ -3366,7 +3609,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="140" spans="1:4">
+    <row r="140" spans="1:5">
       <c r="A140" s="1" t="s">
         <v>58</v>
       </c>
@@ -3380,7 +3623,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:5">
       <c r="A141" s="1" t="s">
         <v>58</v>
       </c>
@@ -3394,7 +3637,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="142" spans="1:4">
+    <row r="142" spans="1:5">
       <c r="A142" s="1" t="s">
         <v>58</v>
       </c>
@@ -3408,7 +3651,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:5">
       <c r="A143" s="1" t="s">
         <v>58</v>
       </c>
@@ -3422,152 +3665,803 @@
         <v>235</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
-      <c r="B144"/>
-      <c r="D144"/>
-    </row>
-    <row r="145" spans="1:4">
-      <c r="B145"/>
-      <c r="D145"/>
-    </row>
-    <row r="146" spans="1:4">
+    <row r="144" spans="1:5">
+      <c r="A144" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C144" s="2">
+        <v>92</v>
+      </c>
+      <c r="D144" t="s">
+        <v>237</v>
+      </c>
+      <c r="E144"/>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C145" s="2">
+        <v>93</v>
+      </c>
+      <c r="D145" t="s">
+        <v>239</v>
+      </c>
+      <c r="E145"/>
+    </row>
+    <row r="146" spans="1:5">
       <c r="A146" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B146" t="s">
-        <v>236</v>
+      <c r="B146" s="6" t="s">
+        <v>240</v>
       </c>
       <c r="C146" s="2">
+        <v>94</v>
+      </c>
+      <c r="D146" t="s">
+        <v>241</v>
+      </c>
+      <c r="E146"/>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C147" s="2">
+        <v>95</v>
+      </c>
+      <c r="D147" t="s">
+        <v>243</v>
+      </c>
+      <c r="E147"/>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C148" s="2">
+        <v>96</v>
+      </c>
+      <c r="D148" t="s">
+        <v>245</v>
+      </c>
+      <c r="E148"/>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="C149" s="2">
+        <v>97</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E149"/>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C150" s="2">
+        <v>98</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E150"/>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C151" s="2">
+        <v>99</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E151"/>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C152" s="2">
+        <v>100</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E152"/>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="C153" s="2">
+        <v>101</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E153"/>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C154" s="2">
+        <v>102</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E154"/>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C155" s="2">
+        <v>103</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E155"/>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C156" s="2">
+        <v>104</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E156"/>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C157" s="2">
+        <v>105</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E157"/>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="C158" s="2">
+        <v>106</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E158"/>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C159" s="2">
+        <v>107</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E159"/>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C160" s="2">
+        <v>108</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E160"/>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C161" s="2">
+        <v>109</v>
+      </c>
+      <c r="D161" t="s">
+        <v>271</v>
+      </c>
+      <c r="E161"/>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="C162" s="2">
+        <v>110</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E162"/>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="C163" s="2">
+        <v>111</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E163"/>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C164" s="2">
+        <v>112</v>
+      </c>
+      <c r="D164" t="s">
+        <v>277</v>
+      </c>
+      <c r="E164"/>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C165" s="2">
+        <v>113</v>
+      </c>
+      <c r="D165" t="s">
+        <v>279</v>
+      </c>
+      <c r="E165"/>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C166" s="2">
+        <v>114</v>
+      </c>
+      <c r="D166" t="s">
+        <v>281</v>
+      </c>
+      <c r="E166"/>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="C167" s="2">
+        <v>115</v>
+      </c>
+      <c r="D167" t="s">
+        <v>283</v>
+      </c>
+      <c r="E167"/>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="C168" s="2">
+        <v>116</v>
+      </c>
+      <c r="D168" t="s">
+        <v>285</v>
+      </c>
+      <c r="E168"/>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C169" s="2">
+        <v>117</v>
+      </c>
+      <c r="D169" t="s">
+        <v>287</v>
+      </c>
+      <c r="E169"/>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="C170" s="2">
+        <v>118</v>
+      </c>
+      <c r="D170" t="s">
+        <v>289</v>
+      </c>
+      <c r="E170"/>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C171" s="2">
+        <v>119</v>
+      </c>
+      <c r="D171" t="s">
+        <v>291</v>
+      </c>
+      <c r="E171"/>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="C172" s="2">
+        <v>120</v>
+      </c>
+      <c r="D172" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C173" s="2">
+        <v>121</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C174" s="2">
+        <v>122</v>
+      </c>
+      <c r="D174" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B175" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="C175" s="2">
+        <v>123</v>
+      </c>
+      <c r="D175" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B176" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="C176" s="2">
+        <v>124</v>
+      </c>
+      <c r="D176" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B177" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="C177" s="2">
+        <v>125</v>
+      </c>
+      <c r="D177" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B178" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="C178" s="2">
+        <v>126</v>
+      </c>
+      <c r="D178" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
+      <c r="A179" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B179" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="C179" s="2">
+        <v>127</v>
+      </c>
+      <c r="D179" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B180" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C180" s="2">
+        <v>128</v>
+      </c>
+      <c r="D180" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B181" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="C181" s="2">
+        <v>129</v>
+      </c>
+      <c r="D181" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B182" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C182" s="2">
+        <v>130</v>
+      </c>
+      <c r="D182" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="B183"/>
+      <c r="D183"/>
+    </row>
+    <row r="184" spans="1:4">
+      <c r="B184"/>
+      <c r="D184"/>
+    </row>
+    <row r="185" spans="1:4">
+      <c r="B185"/>
+      <c r="D185"/>
+    </row>
+    <row r="186" spans="1:4">
+      <c r="B186"/>
+      <c r="D186"/>
+    </row>
+    <row r="187" spans="1:4">
+      <c r="B187"/>
+      <c r="D187"/>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="B188"/>
+      <c r="D188"/>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="B189"/>
+      <c r="D189"/>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="B190"/>
+      <c r="D190"/>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="B191"/>
+      <c r="D191"/>
+    </row>
+    <row r="192" spans="1:4">
+      <c r="B192"/>
+      <c r="D192"/>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="B193"/>
+      <c r="D193"/>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="B194"/>
+      <c r="D194"/>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="B195"/>
+      <c r="D195"/>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="B196"/>
+      <c r="D196"/>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="B197"/>
+      <c r="D197"/>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="B198"/>
+      <c r="D198"/>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="B199"/>
+      <c r="D199"/>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="B200"/>
+      <c r="D200"/>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="B201"/>
+      <c r="D201"/>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="B202"/>
+      <c r="D202"/>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="B203"/>
+      <c r="D203"/>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="B204"/>
+      <c r="D204"/>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="B205"/>
+      <c r="D205"/>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B206" t="s">
+        <v>314</v>
+      </c>
+      <c r="C206" s="2">
         <v>92</v>
       </c>
-      <c r="D146" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4">
-      <c r="A147" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C147" s="2">
+      <c r="D206"/>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C207" s="2">
         <v>93</v>
       </c>
-      <c r="D147" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4">
-      <c r="A148" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C148" s="2">
+      <c r="D207"/>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C208" s="2">
         <v>94</v>
       </c>
-      <c r="D148" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4">
-      <c r="A150" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C150" s="2">
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C210" s="2">
         <v>1</v>
       </c>
-      <c r="D150" s="1" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4">
-      <c r="A151" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C151" s="2">
+      <c r="D210" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C211" s="2">
         <v>2</v>
       </c>
-      <c r="D151" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4">
-      <c r="A152" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C152" s="2">
+      <c r="D211" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C212" s="2">
         <v>3</v>
       </c>
-      <c r="D152" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4">
-      <c r="A153" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B153" s="2" t="s">
+      <c r="D212" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B213" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C153" s="2">
+      <c r="C213" s="2">
         <v>4</v>
       </c>
-      <c r="D153" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4">
-      <c r="A154" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C154" s="2">
+      <c r="D213" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C214" s="2">
         <v>5</v>
       </c>
-      <c r="D154" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4">
-      <c r="A155" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C155" s="2">
+      <c r="D214" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C215" s="2">
         <v>6</v>
       </c>
-      <c r="D155" s="1" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4">
-      <c r="A156" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C156" s="2">
+      <c r="D215" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C216" s="2">
         <v>7</v>
       </c>
-      <c r="D156" s="1" t="s">
-        <v>252</v>
+      <c r="D216" s="1" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="15480" windowHeight="10815" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
@@ -625,7 +625,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -634,15 +634,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1064,3516 +1055,3799 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:E219"/>
+  <dimension ref="A1:E230"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="16.7416666666667" customWidth="1" style="3" min="1" max="1"/>
-    <col width="18.7" customWidth="1" style="3" min="2" max="2"/>
-    <col width="7.05833333333333" customWidth="1" style="4" min="3" max="3"/>
-    <col width="31.625" customWidth="1" style="3" min="4" max="4"/>
-    <col width="34.75" customWidth="1" style="3" min="5" max="5"/>
-    <col width="9" customWidth="1" style="3" min="6" max="16384"/>
+    <col width="16.7416666666667" customWidth="1" style="1" min="1" max="1"/>
+    <col width="18.7" customWidth="1" style="1" min="2" max="2"/>
+    <col width="7.05833333333333" customWidth="1" style="2" min="3" max="3"/>
+    <col width="31.625" customWidth="1" style="1" min="4" max="4"/>
+    <col width="34.75" customWidth="1" style="1" min="5" max="5"/>
+    <col width="9" customWidth="1" style="1" min="6" max="16384"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Enum</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>MonsterType</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>普通敌人</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>MonsterType</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>HandType</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>HighCard</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>高牌</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>HandType</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>Couplet</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>对子</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>HandType</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>Straight</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>顺子</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>HandType</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>Flush</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>同花</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>HandType</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>StraightFlush</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>同花顺</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>HandType</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>Leopard</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="1" t="inlineStr">
         <is>
           <t>三条</t>
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>PointType</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="1" t="inlineStr">
         <is>
           <t>数字牌</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>PointType</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>Letter</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="1" t="inlineStr">
         <is>
           <t>字母牌</t>
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>QualityType</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>Ordinary</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="1" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>QualityType</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="1" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>QualityType</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="1" t="inlineStr">
         <is>
           <t>史诗</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>QualityType</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="1" t="inlineStr">
         <is>
           <t>传说</t>
         </is>
       </c>
     </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>BossEntryType</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>DisableHeart</t>
         </is>
       </c>
-      <c r="C39" s="4" t="n">
+      <c r="C39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="0" t="inlineStr">
         <is>
           <t>本局搓牌时,无法出现红心花色</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>BossEntryType</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="1" t="inlineStr">
         <is>
           <t>DisableSpade</t>
         </is>
       </c>
-      <c r="C40" s="4" t="n">
+      <c r="C40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="0" t="inlineStr">
         <is>
           <t>本局搓牌时,无法出现黑桃花色</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>BossEntryType</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="1" t="inlineStr">
         <is>
           <t>DisableDiamond</t>
         </is>
       </c>
-      <c r="C41" s="4" t="n">
+      <c r="C41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="0" t="inlineStr">
         <is>
           <t>本局搓牌时,无法出现方片花色</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>BossEntryType</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="1" t="inlineStr">
         <is>
           <t>DisablePlumBlossom</t>
         </is>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="C42" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
         <is>
           <t>本局搓牌时,无法出现梅花花色</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="1" t="inlineStr">
         <is>
           <t>BossEntryType</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="1" t="inlineStr">
         <is>
           <t>DisableHead</t>
         </is>
       </c>
-      <c r="C43" s="4" t="n">
+      <c r="C43" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="0" t="inlineStr">
         <is>
           <t>本局搓牌时,无法出现人头牌</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>BossEntryType</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="1" t="inlineStr">
         <is>
           <t>Flint</t>
         </is>
       </c>
-      <c r="C44" s="4" t="n">
+      <c r="C44" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="1" t="inlineStr">
         <is>
           <t>本局结算时,牌型的倍率降低</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>BossEntryType</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="1" t="inlineStr">
         <is>
           <t>Edge</t>
         </is>
       </c>
-      <c r="C45" s="4" t="n">
+      <c r="C45" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="1" t="inlineStr">
         <is>
           <t>本局内你的随机一种遗物将失效</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="1" t="inlineStr">
         <is>
           <t>BossEntryType</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="1" t="inlineStr">
         <is>
           <t>AllIn</t>
         </is>
       </c>
-      <c r="C46" s="4" t="n">
+      <c r="C46" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="1" t="inlineStr">
         <is>
           <t>领主每次都会投注你当前血量的部分筹码</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="1" t="inlineStr">
         <is>
           <t>BossEntryType</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="1" t="inlineStr">
         <is>
           <t>FlushDamage</t>
         </is>
       </c>
-      <c r="C47" s="4" t="n">
+      <c r="C47" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="1" t="inlineStr">
         <is>
           <t>同花牌型在攻击时,伤害降低</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="1" t="inlineStr">
         <is>
           <t>BossEntryType</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="1" t="inlineStr">
         <is>
           <t>FlushStraightDamage</t>
         </is>
       </c>
-      <c r="C48" s="4" t="n">
+      <c r="C48" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="1" t="inlineStr">
         <is>
           <t>同花顺牌型在攻击时,伤害降低</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="1" t="inlineStr">
         <is>
           <t>BossEntryType</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="1" t="inlineStr">
         <is>
           <t>StraightDamage</t>
         </is>
       </c>
-      <c r="C49" s="4" t="n">
+      <c r="C49" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="1" t="inlineStr">
         <is>
           <t>顺子牌型在攻击时,伤害降低</t>
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CurseBody</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>12</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>玩家受到的伤害提高,且攻击时自损当前生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PlayerDamageDown</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>13</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>玩家造成的伤害降低</t>
+        </is>
+      </c>
+    </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SkillDisable</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>14</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>玩家无法使用任何技能</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HandBrand</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>15</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>玩家亮出手牌中随机1张不参与牌型构成</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MonsterEvade</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>16</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>敌人获得闪避率,闪避成功时反击</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>MonsterDamageUp</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>17</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>敌人造成的伤害提高</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RelicDisable</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>18</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>每回合随机失效玩家的收藏品</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>GoldThorn</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>19</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>敌人伤害附加玩家已消耗金币比例的额外伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>FragileBody</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>20</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>玩家生命上限降低且无法恢复生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>HandCompress</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>21</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>玩家每回合手牌数量降低</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BossRage</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>22</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>BOSS损失生命后攻击力提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BossShield</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>23</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>BOSS免疫前N次伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>RoundLimit</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>24</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>限制回合数,超时玩家直接死亡</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>AttackSteal</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>25</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>BOSS每回合偷取玩家当前攻击力</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BossTimid</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>26</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>非BOSS敌人存活时BOSS免疫伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>DisableRedSuit</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>27</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>玩家的方片和红桃牌失效</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>DisableBlackSuit</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>28</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>玩家的黑桃和梅花牌失效</t>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
         <is>
           <t>TwoCardAttack</t>
         </is>
       </c>
-      <c r="C52" s="4" t="n">
+      <c r="C69" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D69" s="1" t="inlineStr">
         <is>
           <t>数字牌2提供额外攻击力</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
         <is>
           <t>ThreeCardAttack</t>
         </is>
       </c>
-      <c r="C53" s="4" t="n">
+      <c r="C70" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D70" s="1" t="inlineStr">
         <is>
           <t>数字牌3提供额外攻击力</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
         <is>
           <t>FourCardAttack</t>
         </is>
       </c>
-      <c r="C54" s="4" t="n">
+      <c r="C71" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D71" s="1" t="inlineStr">
         <is>
           <t>数字牌4提供额外攻击力</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>FiveCardAttack</t>
         </is>
       </c>
-      <c r="C55" s="4" t="n">
+      <c r="C72" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D72" s="1" t="inlineStr">
         <is>
           <t>数字牌5提供额外攻击力</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>SixCardAttack</t>
         </is>
       </c>
-      <c r="C56" s="4" t="n">
+      <c r="C73" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D73" s="1" t="inlineStr">
         <is>
           <t>数字牌6提供额外攻击力</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>SevenCardAttack</t>
         </is>
       </c>
-      <c r="C57" s="4" t="n">
+      <c r="C74" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D74" s="1" t="inlineStr">
         <is>
           <t>数字牌7提供额外攻击力</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>EightCardAttack</t>
         </is>
       </c>
-      <c r="C58" s="4" t="n">
+      <c r="C75" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D75" s="1" t="inlineStr">
         <is>
           <t>数字牌8提供额外攻击力</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>NineCardAttack</t>
         </is>
       </c>
-      <c r="C59" s="4" t="n">
+      <c r="C76" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D76" s="1" t="inlineStr">
         <is>
           <t>数字牌9提供额外攻击力</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>TenCardAttack</t>
         </is>
       </c>
-      <c r="C60" s="4" t="n">
+      <c r="C77" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D77" s="1" t="inlineStr">
         <is>
           <t>数字牌10提供额外攻击力</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>ACardAttack</t>
         </is>
       </c>
-      <c r="C61" s="4" t="n">
+      <c r="C78" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D78" s="1" t="inlineStr">
         <is>
           <t>A牌提供额外攻击力</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>HeadCardAttack</t>
         </is>
       </c>
-      <c r="C62" s="4" t="n">
+      <c r="C79" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D79" s="1" t="inlineStr">
         <is>
           <t>人头牌提供额外攻击力</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>HeroHpMax</t>
         </is>
       </c>
-      <c r="C63" s="4" t="n">
+      <c r="C80" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D80" s="1" t="inlineStr">
         <is>
           <t>英雄的血量上限</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>HeroTakeDamage</t>
         </is>
       </c>
-      <c r="C64" s="4" t="n">
+      <c r="C81" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D81" s="1" t="inlineStr">
         <is>
           <t>英雄承受的伤害</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>HeroAttack</t>
         </is>
       </c>
-      <c r="C65" s="4" t="n">
+      <c r="C82" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D82" s="1" t="inlineStr">
         <is>
           <t>英雄的基础攻击力</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>HeroCritical</t>
         </is>
       </c>
-      <c r="C66" s="4" t="n">
+      <c r="C83" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D83" s="1" t="inlineStr">
         <is>
           <t>英雄的暴击率</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B84" s="1" t="inlineStr">
         <is>
           <t>AttackBossDamage</t>
         </is>
       </c>
-      <c r="C67" s="4" t="n">
+      <c r="C84" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D84" s="1" t="inlineStr">
         <is>
           <t>对BOSS的伤害</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>FirstShowCardEveryLevel</t>
         </is>
       </c>
-      <c r="C68" s="4" t="n">
+      <c r="C85" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D85" s="1" t="inlineStr">
         <is>
           <t>每关首次亮牌后结算倍率</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B86" s="1" t="inlineStr">
         <is>
           <t>KillingProbabilityTen</t>
         </is>
       </c>
-      <c r="C69" s="4" t="n">
+      <c r="C86" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D86" s="1" t="inlineStr">
         <is>
           <t>斩杀10%血量以下非BOSS敌人的概率</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>KillingBringsBackBlood</t>
         </is>
       </c>
-      <c r="C70" s="4" t="n">
+      <c r="C87" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D87" s="1" t="inlineStr">
         <is>
           <t>血量低于20%以下时,杀人回血</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B88" s="1" t="inlineStr">
         <is>
           <t>ManyMonsterDamage</t>
         </is>
       </c>
-      <c r="C71" s="4" t="n">
+      <c r="C88" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D88" s="1" t="inlineStr">
         <is>
           <t>敌人数量大于1时,造成的伤害</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B89" s="1" t="inlineStr">
         <is>
           <t>UsingRubbingCards</t>
         </is>
       </c>
-      <c r="C72" s="4" t="n">
+      <c r="C89" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D89" s="1" t="inlineStr">
         <is>
           <t>亮牌前使用过搓牌,结算时的攻击力</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>HeroHpReplyEveryLevelEnding</t>
         </is>
       </c>
-      <c r="C73" s="4" t="n">
+      <c r="C90" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D90" s="1" t="inlineStr">
         <is>
           <t>每关结束后,回复的血量百分比</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>ProOfObtainingFundsEverySettlement</t>
         </is>
       </c>
-      <c r="C74" s="4" t="n">
+      <c r="C91" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D91" s="1" t="inlineStr">
         <is>
           <t>结算时,获得额外资金的概率</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
         <is>
           <t>OneMonsterDamage</t>
         </is>
       </c>
-      <c r="C75" s="4" t="n">
+      <c r="C92" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D92" s="1" t="inlineStr">
         <is>
           <t>只剩1名敌人时,造成的伤害</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B93" s="1" t="inlineStr">
         <is>
           <t>HpUnderDamage</t>
         </is>
       </c>
-      <c r="C76" s="4" t="n">
+      <c r="C93" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D93" s="1" t="inlineStr">
         <is>
           <t>血量低于20%时,造成的伤害</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
         <is>
           <t>KillingProOfObtainingFunds</t>
         </is>
       </c>
-      <c r="C77" s="4" t="n">
+      <c r="C94" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D94" s="1" t="inlineStr">
         <is>
           <t>击杀敌人时,获得额外资金的概率</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B95" s="1" t="inlineStr">
         <is>
           <t>InitialFunds</t>
         </is>
       </c>
-      <c r="C78" s="4" t="n">
+      <c r="C95" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D95" s="1" t="inlineStr">
         <is>
           <t>初始拥有资金</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B96" s="1" t="inlineStr">
         <is>
           <t>ProOfExtraAttack</t>
         </is>
       </c>
-      <c r="C79" s="4" t="n">
+      <c r="C96" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D96" s="1" t="inlineStr">
         <is>
           <t>额外造成1次10%伤害的概率</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
+    <row r="97"/>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="inlineStr">
         <is>
           <t>CardMagnification</t>
         </is>
       </c>
-      <c r="C81" s="4" t="n">
+      <c r="C98" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="D98" s="1" t="inlineStr">
         <is>
           <t>结算时获得额外倍率</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="inlineStr">
         <is>
           <t>SquarePlate</t>
         </is>
       </c>
-      <c r="C82" s="4" t="n">
+      <c r="C99" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="D99" s="1" t="inlineStr">
         <is>
           <t>每张方片牌在结算时提供倍率</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B100" s="0" t="inlineStr">
         <is>
           <t>Spades</t>
         </is>
       </c>
-      <c r="C83" s="4" t="n">
+      <c r="C100" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D100" s="1" t="inlineStr">
         <is>
           <t>每张黑桃牌在结算时提供倍率</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B101" s="0" t="inlineStr">
         <is>
           <t>RedHeart</t>
         </is>
       </c>
-      <c r="C84" s="4" t="n">
+      <c r="C101" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="D101" s="1" t="inlineStr">
         <is>
           <t>每张红心牌在结算时提供倍率</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B102" s="0" t="inlineStr">
         <is>
           <t>PlumBlossom</t>
         </is>
       </c>
-      <c r="C85" s="4" t="n">
+      <c r="C102" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="D102" s="1" t="inlineStr">
         <is>
           <t>每张梅花牌在结算时提供倍率</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B103" s="1" t="inlineStr">
         <is>
           <t>Couplet</t>
         </is>
       </c>
-      <c r="C86" s="4" t="n">
+      <c r="C103" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D103" s="0" t="inlineStr">
         <is>
           <t>对子倍率提高</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B104" s="0" t="inlineStr">
         <is>
           <t>Straight</t>
         </is>
       </c>
-      <c r="C87" s="4" t="n">
+      <c r="C104" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D104" s="0" t="inlineStr">
         <is>
           <t>顺子倍率提高</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B88" s="5" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B105" s="0" t="inlineStr">
         <is>
           <t>Flush</t>
         </is>
       </c>
-      <c r="C88" s="4" t="n">
+      <c r="C105" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D105" s="0" t="inlineStr">
         <is>
           <t>同花倍率提高</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B106" s="0" t="inlineStr">
         <is>
           <t>StraightFlush</t>
         </is>
       </c>
-      <c r="C89" s="4" t="n">
+      <c r="C106" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D106" s="0" t="inlineStr">
         <is>
           <t>同花顺倍率提高</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Leopard</t>
         </is>
       </c>
-      <c r="C90" s="4" t="n">
+      <c r="C107" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D107" s="0" t="inlineStr">
         <is>
           <t>豹子倍率提高</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B108" s="0" t="inlineStr">
         <is>
           <t>SquarePlateAttack</t>
         </is>
       </c>
-      <c r="C91" s="4" t="n">
+      <c r="C108" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D108" s="0" t="inlineStr">
         <is>
           <t>每张方片牌在结算时提供攻击力</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B109" s="0" t="inlineStr">
         <is>
           <t>SpadesAttack</t>
         </is>
       </c>
-      <c r="C92" s="4" t="n">
+      <c r="C109" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D109" s="0" t="inlineStr">
         <is>
           <t>每张黑桃牌在结算时提供攻击力</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B110" s="0" t="inlineStr">
         <is>
           <t>RedHeartAttack</t>
         </is>
       </c>
-      <c r="C93" s="4" t="n">
+      <c r="C110" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D110" s="0" t="inlineStr">
         <is>
           <t>每张红心牌在结算时提供攻击力</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B111" s="0" t="inlineStr">
         <is>
           <t>PlumBlossomAttack</t>
         </is>
       </c>
-      <c r="C94" s="4" t="n">
+      <c r="C111" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="D111" s="0" t="inlineStr">
         <is>
           <t>每张梅花牌在结算时提供攻击力</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="inlineStr">
         <is>
           <t>CoupletAttack</t>
         </is>
       </c>
-      <c r="C95" s="4" t="n">
+      <c r="C112" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D112" s="0" t="inlineStr">
         <is>
           <t>对子牌型在结算时提供攻击力</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B113" s="0" t="inlineStr">
         <is>
           <t>StraightAttack</t>
         </is>
       </c>
-      <c r="C96" s="4" t="n">
+      <c r="C113" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D113" s="0" t="inlineStr">
         <is>
           <t>顺子牌型在结算时提供攻击力</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B114" s="0" t="inlineStr">
         <is>
           <t>FlushAttack</t>
         </is>
       </c>
-      <c r="C97" s="4" t="n">
+      <c r="C114" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D114" s="0" t="inlineStr">
         <is>
           <t>同花牌型在结算时提供攻击力</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B98" s="5" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B115" s="0" t="inlineStr">
         <is>
           <t>StraightFlushAttack</t>
         </is>
       </c>
-      <c r="C98" s="4" t="n">
+      <c r="C115" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="D115" s="0" t="inlineStr">
         <is>
           <t>同花顺牌型在结算时提供攻击力</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>LeopardAttack</t>
         </is>
       </c>
-      <c r="C99" s="4" t="n">
+      <c r="C116" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D116" s="0" t="inlineStr">
         <is>
           <t>豹子牌型在结算时提供攻击力</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>HeroHpReplyEveryRoundEnding</t>
         </is>
       </c>
-      <c r="C100" s="4" t="n">
+      <c r="C117" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="D117" s="0" t="inlineStr">
         <is>
           <t>回合结束回复当前生命值</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B118" s="0" t="inlineStr">
         <is>
           <t>Liability</t>
         </is>
       </c>
-      <c r="C101" s="4" t="n">
+      <c r="C118" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="D118" s="0" t="inlineStr">
         <is>
           <t>资金可以为负数</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B119" s="0" t="inlineStr">
         <is>
           <t>EveryRubbingNum</t>
         </is>
       </c>
-      <c r="C102" s="4" t="n">
+      <c r="C119" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="D119" s="0" t="inlineStr">
         <is>
           <t>每剩余1个搓牌次数,提供倍率</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>ProOfHeadCardFunds</t>
         </is>
       </c>
-      <c r="C103" s="4" t="n">
+      <c r="C120" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="D103" s="5" t="inlineStr">
+      <c r="D120" s="0" t="inlineStr">
         <is>
           <t>人头牌提供1资金的概率</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B121" s="0" t="inlineStr">
         <is>
           <t>Camera</t>
         </is>
       </c>
-      <c r="C104" s="4" t="n">
+      <c r="C121" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="D104" s="5" t="inlineStr">
+      <c r="D121" s="0" t="inlineStr">
         <is>
           <t>每有1张留在手里的每张黑桃/梅花,提供倍率</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B122" s="0" t="inlineStr">
         <is>
           <t>Cupid</t>
         </is>
       </c>
-      <c r="C105" s="4" t="n">
+      <c r="C122" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="D105" s="5" t="inlineStr">
+      <c r="D122" s="0" t="inlineStr">
         <is>
           <t>每有1张留在手里的每张方片/红心,提供倍率</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B123" s="0" t="inlineStr">
         <is>
           <t>ConsumeFundsGetAttack</t>
         </is>
       </c>
-      <c r="C106" s="4" t="n">
+      <c r="C123" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="D123" s="0" t="inlineStr">
         <is>
           <t>每花费10资金,提供英雄攻击力</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B124" s="0" t="inlineStr">
         <is>
           <t>TakeDamageGetFunds</t>
         </is>
       </c>
-      <c r="C107" s="4" t="n">
+      <c r="C124" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="D107" s="5" t="inlineStr">
+      <c r="D124" s="0" t="inlineStr">
         <is>
           <t>受到伤害,提供资金</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>BloodSucking</t>
         </is>
       </c>
-      <c r="C108" s="4" t="n">
+      <c r="C125" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="D108" s="5" t="inlineStr">
+      <c r="D125" s="0" t="inlineStr">
         <is>
           <t>吸血效果</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B126" s="0" t="inlineStr">
         <is>
           <t>DoubleCardAttack</t>
         </is>
       </c>
-      <c r="C109" s="4" t="n">
+      <c r="C126" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="D109" s="5" t="inlineStr">
+      <c r="D126" s="0" t="inlineStr">
         <is>
           <t>亮出的牌点数提供的攻击力提高</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B110" s="5" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B127" s="0" t="inlineStr">
         <is>
           <t>TheSwordOfVictory</t>
         </is>
       </c>
-      <c r="C110" s="4" t="n">
+      <c r="C127" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="D110" s="5" t="inlineStr">
+      <c r="D127" s="0" t="inlineStr">
         <is>
           <t>结算伤害时,将留在手牌上最大牌点数转化为额外攻击力</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B128" s="0" t="inlineStr">
         <is>
           <t>EveryUseRubbingNum</t>
         </is>
       </c>
-      <c r="C111" s="4" t="n">
+      <c r="C128" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="D111" s="5" t="inlineStr">
+      <c r="D128" s="0" t="inlineStr">
         <is>
           <t>每回合内,每搓1次牌,结算时提供倍率</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B112" s="5" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B129" s="0" t="inlineStr">
         <is>
           <t>FreeShopRefresh</t>
         </is>
       </c>
-      <c r="C112" s="4" t="n">
+      <c r="C129" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="D112" s="5" t="inlineStr">
+      <c r="D129" s="0" t="inlineStr">
         <is>
           <t>免费商店刷新次数</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B130" s="0" t="inlineStr">
         <is>
           <t>SpecialStraight</t>
         </is>
       </c>
-      <c r="C113" s="4" t="n">
+      <c r="C130" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="D130" s="0" t="inlineStr">
         <is>
           <t>顺子牌型可以相隔1点组成</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B131" s="0" t="inlineStr">
         <is>
           <t>SpecialEightCard</t>
         </is>
       </c>
-      <c r="C114" s="4" t="n">
+      <c r="C131" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="D114" s="5" t="inlineStr">
+      <c r="D131" s="0" t="inlineStr">
         <is>
           <t>亮出的每张8在结算时提供+8攻击力</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B132" s="0" t="inlineStr">
         <is>
           <t>EvenNumberCard</t>
         </is>
       </c>
-      <c r="C115" s="4" t="n">
+      <c r="C132" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="D115" s="5" t="inlineStr">
+      <c r="D132" s="0" t="inlineStr">
         <is>
           <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供倍率</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B133" s="0" t="inlineStr">
         <is>
           <t>OddNumberCard</t>
         </is>
       </c>
-      <c r="C116" s="4" t="n">
+      <c r="C133" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="D116" s="5" t="inlineStr">
+      <c r="D133" s="0" t="inlineStr">
         <is>
           <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供倍率</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B134" s="0" t="inlineStr">
         <is>
           <t>HeadCard</t>
         </is>
       </c>
-      <c r="C117" s="4" t="n">
+      <c r="C134" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="D134" s="1" t="inlineStr">
         <is>
           <t>人头牌提供额外倍率</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B118" s="5" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B135" s="0" t="inlineStr">
         <is>
           <t>KillAfterSellingPrice</t>
         </is>
       </c>
-      <c r="C118" s="4" t="n">
+      <c r="C135" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="D118" s="5" t="inlineStr">
+      <c r="D135" s="0" t="inlineStr">
         <is>
           <t>击杀敌人,收藏品出售价格提高</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B119" s="5" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B136" s="0" t="inlineStr">
         <is>
           <t>EveryCardAttackForever</t>
         </is>
       </c>
-      <c r="C119" s="4" t="n">
+      <c r="C136" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="D119" s="5" t="inlineStr">
+      <c r="D136" s="0" t="inlineStr">
         <is>
           <t>亮出的每张牌的点数在结算时会使其提供的攻击力永久提高</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B137" s="0" t="inlineStr">
         <is>
           <t>SpecialNineCard</t>
         </is>
       </c>
-      <c r="C120" s="4" t="n">
+      <c r="C137" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="D120" s="5" t="inlineStr">
+      <c r="D137" s="0" t="inlineStr">
         <is>
           <t>亮出的每张9在结算时提供资金</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B138" s="0" t="inlineStr">
         <is>
           <t>SpecialTwoThreeFive</t>
         </is>
       </c>
-      <c r="C121" s="4" t="n">
+      <c r="C138" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="D138" s="0" t="inlineStr">
         <is>
           <t>散排235牌型等同于豹子牌型,并且可以战胜所有牌型</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B139" s="0" t="inlineStr">
         <is>
           <t>SpecialFlush</t>
         </is>
       </c>
-      <c r="C122" s="4" t="n">
+      <c r="C139" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="D122" s="5" t="inlineStr">
+      <c r="D139" s="0" t="inlineStr">
         <is>
           <t>红桃和方片视为同一花色,黑桃和梅花视为同一花色</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B140" s="1" t="inlineStr">
         <is>
           <t>RubbingCardsNum</t>
         </is>
       </c>
-      <c r="C123" s="4" t="n">
+      <c r="C140" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="D123" s="3" t="inlineStr">
+      <c r="D140" s="1" t="inlineStr">
         <is>
           <t>每回合搓牌次数</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B141" s="1" t="inlineStr">
         <is>
           <t>NoSkill</t>
         </is>
       </c>
-      <c r="C124" s="4" t="n">
+      <c r="C141" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="D141" s="1" t="inlineStr">
         <is>
           <t>结算时,所有技能都无剩余使用次数时,提供倍率</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B142" s="0" t="inlineStr">
         <is>
           <t>EveryRelic</t>
         </is>
       </c>
-      <c r="C125" s="4" t="n">
+      <c r="C142" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="D125" s="5" t="inlineStr">
+      <c r="D142" s="0" t="inlineStr">
         <is>
           <t>每有1个收藏品,结算时提供倍率</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B143" s="0" t="inlineStr">
         <is>
           <t>NoUseRubbingEveryRubbingNum</t>
         </is>
       </c>
-      <c r="C126" s="4" t="n">
+      <c r="C143" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="D126" s="3" t="inlineStr">
+      <c r="D143" s="1" t="inlineStr">
         <is>
           <t>结算时,若未使用过搓牌,每个搓牌次数提供+6倍率</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B144" s="0" t="inlineStr">
         <is>
           <t>AllCardIsHeadCard</t>
         </is>
       </c>
-      <c r="C127" s="4" t="n">
+      <c r="C144" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="D127" s="5" t="inlineStr">
+      <c r="D144" s="0" t="inlineStr">
         <is>
           <t>所有牌均视为人头牌</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B145" s="0" t="inlineStr">
         <is>
           <t>SpecialACard</t>
         </is>
       </c>
-      <c r="C128" s="4" t="n">
+      <c r="C145" s="2" t="n">
         <v>76</v>
       </c>
-      <c r="D128" s="3" t="inlineStr">
+      <c r="D145" s="1" t="inlineStr">
         <is>
           <t>A牌在结算时提供倍率</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B129" s="5" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B146" s="0" t="inlineStr">
         <is>
           <t>AccumulatedNumOfCardType</t>
         </is>
       </c>
-      <c r="C129" s="4" t="n">
+      <c r="C146" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="D129" s="5" t="inlineStr">
+      <c r="D146" s="0" t="inlineStr">
         <is>
           <t>亮牌时,将该牌型在本局内亮出过的次数来提供倍率</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B130" s="5" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B147" s="0" t="inlineStr">
         <is>
           <t>ProOfUpCardType</t>
         </is>
       </c>
-      <c r="C130" s="4" t="n">
+      <c r="C147" s="2" t="n">
         <v>78</v>
       </c>
-      <c r="D130" s="5" t="inlineStr">
+      <c r="D147" s="0" t="inlineStr">
         <is>
           <t>亮牌时,有概率将该牌型提供的倍率永久+1</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B148" s="0" t="inlineStr">
         <is>
           <t>RubbingCardRelic</t>
         </is>
       </c>
-      <c r="C131" s="4" t="n">
+      <c r="C148" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="D131" s="3" t="inlineStr">
+      <c r="D148" s="1" t="inlineStr">
         <is>
           <t>每使用1次搓牌,结算时该收藏品永久提供倍率</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B149" s="0" t="inlineStr">
         <is>
           <t>SpecialSevenCardPro</t>
         </is>
       </c>
-      <c r="C132" s="4" t="n">
+      <c r="C149" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="D132" s="3" t="inlineStr">
+      <c r="D149" s="1" t="inlineStr">
         <is>
           <t>幸运七触发概率</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B150" s="0" t="inlineStr">
         <is>
           <t>SpecialSevenCardAttack</t>
         </is>
       </c>
-      <c r="C133" s="4" t="n">
+      <c r="C150" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="D133" s="5" t="inlineStr">
+      <c r="D150" s="0" t="inlineStr">
         <is>
           <t>幸运七触发时提供的攻击力</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B151" s="0" t="inlineStr">
         <is>
           <t>SpecialSevenCard</t>
         </is>
       </c>
-      <c r="C134" s="4" t="n">
+      <c r="C151" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="D134" s="5" t="inlineStr">
+      <c r="D151" s="0" t="inlineStr">
         <is>
           <t>幸运七触发时提供的倍率</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>HeroTakeDamagePer</t>
         </is>
       </c>
-      <c r="C135" s="4" t="n">
+      <c r="C152" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="D135" s="3" t="inlineStr">
+      <c r="D152" s="1" t="inlineStr">
         <is>
           <t>英雄承受的伤害百分比</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B153" s="0" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="C136" s="4" t="n">
+      <c r="C153" s="2" t="n">
         <v>84</v>
       </c>
-      <c r="D136" s="5" t="inlineStr">
+      <c r="D153" s="0" t="inlineStr">
         <is>
           <t>英雄造成的伤害百分比</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B137" s="5" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B154" s="0" t="inlineStr">
         <is>
           <t>VersatilePerson</t>
         </is>
       </c>
-      <c r="C137" s="4" t="n">
+      <c r="C154" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="D137" s="3" t="inlineStr">
+      <c r="D154" s="1" t="inlineStr">
         <is>
           <t>攻击时,对其他人造成百分比伤害</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B138" s="5" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B155" s="0" t="inlineStr">
         <is>
           <t>ExtraAttackOneTime</t>
         </is>
       </c>
-      <c r="C138" s="4" t="n">
+      <c r="C155" s="2" t="n">
         <v>86</v>
       </c>
-      <c r="D138" s="5" t="inlineStr">
+      <c r="D155" s="0" t="inlineStr">
         <is>
           <t>额外攻击敌人1次的概率</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B156" s="0" t="inlineStr">
         <is>
           <t>AoeDamage</t>
         </is>
       </c>
-      <c r="C139" s="4" t="n">
+      <c r="C156" s="2" t="n">
         <v>87</v>
       </c>
-      <c r="D139" s="5" t="inlineStr">
+      <c r="D156" s="0" t="inlineStr">
         <is>
           <t>攻击变成原伤害百分比的群体伤害</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B157" s="0" t="inlineStr">
         <is>
           <t>EpicLegendRelicProUp</t>
         </is>
       </c>
-      <c r="C140" s="4" t="n">
+      <c r="C157" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="D140" s="5" t="inlineStr">
+      <c r="D157" s="0" t="inlineStr">
         <is>
           <t>史诗/传说的收藏品概率提高</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>RelicPricePer</t>
         </is>
       </c>
-      <c r="C141" s="4" t="n">
+      <c r="C158" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="D141" s="5" t="inlineStr">
+      <c r="D158" s="0" t="inlineStr">
         <is>
           <t>收藏品价格百分比</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B142" s="4" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>GetGoldAfterLevel</t>
         </is>
       </c>
-      <c r="C142" s="4" t="n">
+      <c r="C159" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="D142" s="3" t="inlineStr">
+      <c r="D159" s="1" t="inlineStr">
         <is>
           <t>每关通过后获得的金币数量百分比</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B143" s="5" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B160" s="0" t="inlineStr">
         <is>
           <t>MissDamagePer</t>
         </is>
       </c>
-      <c r="C143" s="4" t="n">
+      <c r="C160" s="2" t="n">
         <v>91</v>
       </c>
-      <c r="D143" s="5" t="inlineStr">
+      <c r="D160" s="0" t="inlineStr">
         <is>
           <t>免疫伤害的概率</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B144" s="6" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
         <is>
           <t>EveryRoundGetGold</t>
         </is>
       </c>
-      <c r="C144" s="4" t="n">
+      <c r="C161" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="D144" s="5" t="inlineStr">
+      <c r="D161" s="0" t="inlineStr">
         <is>
           <t>每回合开始获得金币</t>
         </is>
       </c>
-      <c r="E144" s="5" t="n"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B145" s="6" t="inlineStr">
+      <c r="E161" s="0" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
         <is>
           <t>EveryRoundEndingGetGoldPer</t>
         </is>
       </c>
-      <c r="C145" s="4" t="n">
+      <c r="C162" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="D145" s="5" t="inlineStr">
+      <c r="D162" s="0" t="inlineStr">
         <is>
           <t>每回合结束概率获得金币</t>
         </is>
       </c>
-      <c r="E145" s="5" t="n"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="inlineStr">
+      <c r="E162" s="0" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
         <is>
           <t>EveryRoundEndingGetCritical</t>
         </is>
       </c>
-      <c r="C146" s="4" t="n">
+      <c r="C163" s="2" t="n">
         <v>94</v>
       </c>
-      <c r="D146" s="5" t="inlineStr">
+      <c r="D163" s="0" t="inlineStr">
         <is>
           <t>暴击叠加</t>
         </is>
       </c>
-      <c r="E146" s="5" t="n"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B147" s="6" t="inlineStr">
+      <c r="E163" s="0" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
         <is>
           <t>SteppingStone</t>
         </is>
       </c>
-      <c r="C147" s="4" t="n">
+      <c r="C164" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="D147" s="5" t="inlineStr">
+      <c r="D164" s="0" t="inlineStr">
         <is>
           <t>亮牌大于所有人加攻击力</t>
         </is>
       </c>
-      <c r="E147" s="5" t="n"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B148" s="6" t="inlineStr">
+      <c r="E164" s="0" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
         <is>
           <t>BounceDamage</t>
         </is>
       </c>
-      <c r="C148" s="4" t="n">
+      <c r="C165" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="D148" s="5" t="inlineStr">
+      <c r="D165" s="0" t="inlineStr">
         <is>
           <t>受到伤害反弹伤害</t>
         </is>
       </c>
-      <c r="E148" s="5" t="n"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B149" s="6" t="inlineStr">
+      <c r="E165" s="0" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
         <is>
           <t>AllPeacePer</t>
         </is>
       </c>
-      <c r="C149" s="4" t="n">
+      <c r="C166" s="2" t="n">
         <v>97</v>
       </c>
-      <c r="D149" s="3" t="inlineStr">
+      <c r="D166" s="1" t="inlineStr">
         <is>
           <t>承伤或伤害降低为0的概率</t>
         </is>
       </c>
-      <c r="E149" s="5" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="inlineStr">
+      <c r="E166" s="0" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
         <is>
           <t>DefeatGetAttack</t>
         </is>
       </c>
-      <c r="C150" s="4" t="n">
+      <c r="C167" s="2" t="n">
         <v>98</v>
       </c>
-      <c r="D150" s="3" t="inlineStr">
+      <c r="D167" s="1" t="inlineStr">
         <is>
           <t>牌小获得攻击力</t>
         </is>
       </c>
-      <c r="E150" s="5" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B151" s="6" t="inlineStr">
+      <c r="E167" s="0" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
         <is>
           <t>DefeatGetHpMax</t>
         </is>
       </c>
-      <c r="C151" s="4" t="n">
+      <c r="C168" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="D151" s="3" t="inlineStr">
+      <c r="D168" s="1" t="inlineStr">
         <is>
           <t>牌小获得生命上限</t>
         </is>
       </c>
-      <c r="E151" s="5" t="n"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B152" s="6" t="inlineStr">
+      <c r="E168" s="0" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
         <is>
           <t>DefeatAllGetGold</t>
         </is>
       </c>
-      <c r="C152" s="4" t="n">
+      <c r="C169" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D152" s="3" t="inlineStr">
+      <c r="D169" s="1" t="inlineStr">
         <is>
           <t>未造成伤害获得金币</t>
         </is>
       </c>
-      <c r="E152" s="5" t="n"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B153" s="6" t="inlineStr">
+      <c r="E169" s="0" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
         <is>
           <t>IronRiceBowl</t>
         </is>
       </c>
-      <c r="C153" s="4" t="n">
+      <c r="C170" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="D153" s="3" t="inlineStr">
+      <c r="D170" s="1" t="inlineStr">
         <is>
           <t>亮牌后获得金币</t>
         </is>
       </c>
-      <c r="E153" s="5" t="n"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B154" s="6" t="inlineStr">
+      <c r="E170" s="0" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
         <is>
           <t>EveryRoundGetHpMax</t>
         </is>
       </c>
-      <c r="C154" s="4" t="n">
+      <c r="C171" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="D154" s="3" t="inlineStr">
+      <c r="D171" s="1" t="inlineStr">
         <is>
           <t>每回合开始获得生命上限</t>
         </is>
       </c>
-      <c r="E154" s="5" t="n"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B155" s="6" t="inlineStr">
+      <c r="E171" s="0" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
         <is>
           <t>LuckyFlush</t>
         </is>
       </c>
-      <c r="C155" s="4" t="n">
+      <c r="C172" s="2" t="n">
         <v>103</v>
       </c>
-      <c r="D155" s="3" t="inlineStr">
+      <c r="D172" s="1" t="inlineStr">
         <is>
           <t>强行视敌人牌为同花</t>
         </is>
       </c>
-      <c r="E155" s="5" t="n"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B156" s="6" t="inlineStr">
+      <c r="E172" s="0" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
         <is>
           <t>EveryRoundEndingGetEvade</t>
         </is>
       </c>
-      <c r="C156" s="4" t="n">
+      <c r="C173" s="2" t="n">
         <v>104</v>
       </c>
-      <c r="D156" s="3" t="inlineStr">
+      <c r="D173" s="1" t="inlineStr">
         <is>
           <t>闪避叠加</t>
         </is>
       </c>
-      <c r="E156" s="5" t="n"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B157" s="6" t="inlineStr">
+      <c r="E173" s="0" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
         <is>
           <t>ThermosCup</t>
         </is>
       </c>
-      <c r="C157" s="4" t="n">
+      <c r="C174" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="D157" s="3" t="inlineStr">
+      <c r="D174" s="1" t="inlineStr">
         <is>
           <t>半血回血</t>
         </is>
       </c>
-      <c r="E157" s="5" t="n"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B158" s="6" t="inlineStr">
+      <c r="E174" s="0" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
         <is>
           <t>Interest</t>
         </is>
       </c>
-      <c r="C158" s="4" t="n">
+      <c r="C175" s="2" t="n">
         <v>106</v>
       </c>
-      <c r="D158" s="3" t="inlineStr">
+      <c r="D175" s="1" t="inlineStr">
         <is>
           <t>利息</t>
         </is>
       </c>
-      <c r="E158" s="5" t="n"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B159" s="6" t="inlineStr">
+      <c r="E175" s="0" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
         <is>
           <t>Abacus</t>
         </is>
       </c>
-      <c r="C159" s="4" t="n">
+      <c r="C176" s="2" t="n">
         <v>107</v>
       </c>
-      <c r="D159" s="3" t="inlineStr">
+      <c r="D176" s="1" t="inlineStr">
         <is>
           <t>搓牌次数换金币</t>
         </is>
       </c>
-      <c r="E159" s="5" t="n"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B160" s="6" t="inlineStr">
+      <c r="E176" s="0" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
         <is>
           <t>DefeatAllGetGoldAndReplyHp</t>
         </is>
       </c>
-      <c r="C160" s="4" t="n">
+      <c r="C177" s="2" t="n">
         <v>108</v>
       </c>
-      <c r="D160" s="3" t="inlineStr">
+      <c r="D177" s="1" t="inlineStr">
         <is>
           <t>牌小获得金币和回血</t>
         </is>
       </c>
-      <c r="E160" s="5" t="n"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
+      <c r="E177" s="0" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
         <is>
           <t>MissFirstDamage</t>
         </is>
       </c>
-      <c r="C161" s="4" t="n">
+      <c r="C178" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="D161" s="5" t="inlineStr">
+      <c r="D178" s="0" t="inlineStr">
         <is>
           <t>免疫第一次承伤</t>
         </is>
       </c>
-      <c r="E161" s="5" t="n"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B162" s="6" t="inlineStr">
+      <c r="E178" s="0" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
         <is>
           <t>DefeatGetMagnification</t>
         </is>
       </c>
-      <c r="C162" s="4" t="n">
+      <c r="C179" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="D162" s="3" t="inlineStr">
+      <c r="D179" s="1" t="inlineStr">
         <is>
           <t>牌小获得倍率</t>
         </is>
       </c>
-      <c r="E162" s="5" t="n"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
+      <c r="E179" s="0" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
         <is>
           <t>LuckyStraight</t>
         </is>
       </c>
-      <c r="C163" s="4" t="n">
+      <c r="C180" s="2" t="n">
         <v>111</v>
       </c>
-      <c r="D163" s="3" t="inlineStr">
+      <c r="D180" s="1" t="inlineStr">
         <is>
           <t>强行视敌人牌为顺子</t>
         </is>
       </c>
-      <c r="E163" s="5" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B164" s="6" t="inlineStr">
+      <c r="E180" s="0" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
         <is>
           <t>ReverseResult</t>
         </is>
       </c>
-      <c r="C164" s="4" t="n">
+      <c r="C181" s="2" t="n">
         <v>112</v>
       </c>
-      <c r="D164" s="5" t="inlineStr">
+      <c r="D181" s="0" t="inlineStr">
         <is>
           <t>反转结果的概率</t>
         </is>
       </c>
-      <c r="E164" s="5" t="n"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B165" s="6" t="inlineStr">
+      <c r="E181" s="0" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
         <is>
           <t>NoKillMonsterGetMagnification</t>
         </is>
       </c>
-      <c r="C165" s="4" t="n">
+      <c r="C182" s="2" t="n">
         <v>113</v>
       </c>
-      <c r="D165" s="5" t="inlineStr">
+      <c r="D182" s="0" t="inlineStr">
         <is>
           <t>回合内未进行击杀提高倍率</t>
         </is>
       </c>
-      <c r="E165" s="5" t="n"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B166" s="6" t="inlineStr">
+      <c r="E182" s="0" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
         <is>
           <t>Revenge</t>
         </is>
       </c>
-      <c r="C166" s="4" t="n">
+      <c r="C183" s="2" t="n">
         <v>114</v>
       </c>
-      <c r="D166" s="5" t="inlineStr">
+      <c r="D183" s="0" t="inlineStr">
         <is>
           <t>对赢过自己的怪物类型提高伤害</t>
         </is>
       </c>
-      <c r="E166" s="5" t="n"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B167" s="6" t="inlineStr">
+      <c r="E183" s="0" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
         <is>
           <t>NobleBadge</t>
         </is>
       </c>
-      <c r="C167" s="4" t="n">
+      <c r="C184" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="D167" s="5" t="inlineStr">
+      <c r="D184" s="0" t="inlineStr">
         <is>
           <t>半血以上得金币</t>
         </is>
       </c>
-      <c r="E167" s="5" t="n"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B168" s="6" t="inlineStr">
+      <c r="E184" s="0" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
         <is>
           <t>Trap</t>
         </is>
       </c>
-      <c r="C168" s="4" t="n">
+      <c r="C185" s="2" t="n">
         <v>116</v>
       </c>
-      <c r="D168" s="5" t="inlineStr">
+      <c r="D185" s="0" t="inlineStr">
         <is>
           <t>赢过自己的怪物类型降低伤害</t>
         </is>
       </c>
-      <c r="E168" s="5" t="n"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B169" s="6" t="inlineStr">
+      <c r="E185" s="0" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
         <is>
           <t>DownGrade</t>
         </is>
       </c>
-      <c r="C169" s="4" t="n">
+      <c r="C186" s="2" t="n">
         <v>117</v>
       </c>
-      <c r="D169" s="5" t="inlineStr">
+      <c r="D186" s="0" t="inlineStr">
         <is>
           <t>降级牌型概率</t>
         </is>
       </c>
-      <c r="E169" s="5" t="n"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B170" s="6" t="inlineStr">
+      <c r="E186" s="0" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
         <is>
           <t>AdmissionTicket</t>
         </is>
       </c>
-      <c r="C170" s="4" t="n">
+      <c r="C187" s="2" t="n">
         <v>118</v>
       </c>
-      <c r="D170" s="5" t="inlineStr">
+      <c r="D187" s="0" t="inlineStr">
         <is>
           <t>额外攻击的次数</t>
         </is>
       </c>
-      <c r="E170" s="5" t="n"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B171" s="6" t="inlineStr">
+      <c r="E187" s="0" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
         <is>
           <t>MonsterDamage</t>
         </is>
       </c>
-      <c r="C171" s="4" t="n">
+      <c r="C188" s="2" t="n">
         <v>119</v>
       </c>
-      <c r="D171" s="5" t="inlineStr">
+      <c r="D188" s="0" t="inlineStr">
         <is>
           <t>敌人伤害降低</t>
         </is>
       </c>
-      <c r="E171" s="5" t="n"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B172" s="6" t="inlineStr">
+      <c r="E188" s="0" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
         <is>
           <t>MissGetDamage</t>
         </is>
       </c>
-      <c r="C172" s="4" t="n">
+      <c r="C189" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="D172" s="5" t="inlineStr">
+      <c r="D189" s="0" t="inlineStr">
         <is>
           <t>闪避反击</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B173" s="6" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
         <is>
           <t>LuckyCouplet</t>
         </is>
       </c>
-      <c r="C173" s="4" t="n">
+      <c r="C190" s="2" t="n">
         <v>121</v>
       </c>
-      <c r="D173" s="3" t="inlineStr">
+      <c r="D190" s="1" t="inlineStr">
         <is>
           <t>强行视敌人牌为对子</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B174" s="6" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
         <is>
           <t>DefeatGetDamage</t>
         </is>
       </c>
-      <c r="C174" s="4" t="n">
+      <c r="C191" s="2" t="n">
         <v>122</v>
       </c>
-      <c r="D174" s="5" t="inlineStr">
+      <c r="D191" s="0" t="inlineStr">
         <is>
           <t>每次失败提升伤害</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B175" s="7" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
         <is>
           <t>AstrawToClutchAt</t>
         </is>
       </c>
-      <c r="C175" s="4" t="n">
+      <c r="C192" s="2" t="n">
         <v>123</v>
       </c>
-      <c r="D175" s="5" t="inlineStr">
+      <c r="D192" s="0" t="inlineStr">
         <is>
           <t>免死一次</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B176" s="7" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
         <is>
           <t>OneMonsterGetDamage</t>
         </is>
       </c>
-      <c r="C176" s="4" t="n">
+      <c r="C193" s="2" t="n">
         <v>124</v>
       </c>
-      <c r="D176" s="5" t="inlineStr">
+      <c r="D193" s="0" t="inlineStr">
         <is>
           <t>孤立无援</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B177" s="7" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
         <is>
           <t>CardUpGrade</t>
         </is>
       </c>
-      <c r="C177" s="4" t="n">
+      <c r="C194" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="D177" s="5" t="inlineStr">
+      <c r="D194" s="0" t="inlineStr">
         <is>
           <t>牌型升级</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B178" s="7" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
         <is>
           <t>MonsterHpMax</t>
         </is>
       </c>
-      <c r="C178" s="4" t="n">
+      <c r="C195" s="2" t="n">
         <v>126</v>
       </c>
-      <c r="D178" s="5" t="inlineStr">
+      <c r="D195" s="0" t="inlineStr">
         <is>
           <t>敌人血量上限</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B179" s="7" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
         <is>
           <t>CriticalAoe</t>
         </is>
       </c>
-      <c r="C179" s="4" t="n">
+      <c r="C196" s="2" t="n">
         <v>127</v>
       </c>
-      <c r="D179" s="5" t="inlineStr">
+      <c r="D196" s="0" t="inlineStr">
         <is>
           <t>暴击触发AOE</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B180" s="7" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
         <is>
           <t>PerspectiveNum</t>
         </is>
       </c>
-      <c r="C180" s="4" t="n">
+      <c r="C197" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="D180" s="5" t="inlineStr">
+      <c r="D197" s="0" t="inlineStr">
         <is>
           <t>透视次数</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B181" s="7" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
         <is>
           <t>DamageTurnToGold</t>
         </is>
       </c>
-      <c r="C181" s="4" t="n">
+      <c r="C198" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="D181" s="5" t="inlineStr">
+      <c r="D198" s="0" t="inlineStr">
         <is>
           <t>伤害转为金币</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="3" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B182" s="7" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
         <is>
           <t>GapDamage</t>
         </is>
       </c>
-      <c r="C182" s="4" t="n">
+      <c r="C199" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="D182" s="5" t="inlineStr">
+      <c r="D199" s="0" t="inlineStr">
         <is>
           <t>差距胶囊</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="B183" s="5" t="n"/>
-      <c r="D183" s="5" t="n"/>
-    </row>
-    <row r="184">
-      <c r="B184" s="5" t="n"/>
-      <c r="D184" s="5" t="n"/>
-    </row>
-    <row r="185">
-      <c r="B185" s="5" t="n"/>
-      <c r="D185" s="5" t="n"/>
-    </row>
-    <row r="186">
-      <c r="B186" s="5" t="n"/>
-      <c r="D186" s="5" t="n"/>
-    </row>
-    <row r="187">
-      <c r="B187" s="5" t="n"/>
-      <c r="D187" s="5" t="n"/>
-    </row>
-    <row r="188">
-      <c r="B188" s="5" t="n"/>
-      <c r="D188" s="5" t="n"/>
-    </row>
-    <row r="189">
-      <c r="B189" s="5" t="n"/>
-      <c r="D189" s="5" t="n"/>
-    </row>
-    <row r="190">
-      <c r="B190" s="5" t="n"/>
-      <c r="D190" s="5" t="n"/>
-    </row>
-    <row r="191">
-      <c r="B191" s="5" t="n"/>
-      <c r="D191" s="5" t="n"/>
-    </row>
-    <row r="192">
-      <c r="B192" s="5" t="n"/>
-      <c r="D192" s="5" t="n"/>
-    </row>
-    <row r="193">
-      <c r="B193" s="5" t="n"/>
-      <c r="D193" s="5" t="n"/>
-    </row>
-    <row r="194">
-      <c r="B194" s="5" t="n"/>
-      <c r="D194" s="5" t="n"/>
-    </row>
-    <row r="195">
-      <c r="B195" s="5" t="n"/>
-      <c r="D195" s="5" t="n"/>
-    </row>
-    <row r="196">
-      <c r="B196" s="5" t="n"/>
-      <c r="D196" s="5" t="n"/>
-    </row>
-    <row r="197">
-      <c r="B197" s="5" t="n"/>
-      <c r="D197" s="5" t="n"/>
-    </row>
-    <row r="198">
-      <c r="B198" s="5" t="n"/>
-      <c r="D198" s="5" t="n"/>
-    </row>
-    <row r="199">
-      <c r="B199" s="5" t="n"/>
-      <c r="D199" s="5" t="n"/>
-    </row>
     <row r="200">
-      <c r="B200" s="5" t="n"/>
-      <c r="D200" s="5" t="n"/>
+      <c r="B200" s="0" t="n"/>
+      <c r="D200" s="0" t="n"/>
     </row>
     <row r="201">
-      <c r="B201" s="5" t="n"/>
-      <c r="D201" s="5" t="n"/>
+      <c r="B201" s="0" t="n"/>
+      <c r="D201" s="0" t="n"/>
     </row>
     <row r="202">
-      <c r="B202" s="5" t="n"/>
-      <c r="D202" s="5" t="n"/>
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>MaxHp</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="D202" s="0" t="n"/>
     </row>
     <row r="203">
-      <c r="B203" s="5" t="n"/>
-      <c r="D203" s="5" t="n"/>
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B203" s="0" t="inlineStr">
+        <is>
+          <t>EveryRoundHpUp</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="D203" s="0" t="n"/>
     </row>
     <row r="204">
-      <c r="B204" s="5" t="n"/>
-      <c r="D204" s="5" t="n"/>
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B204" s="0" t="inlineStr">
+        <is>
+          <t>TwoThreeFive</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="D204" s="0" t="n"/>
     </row>
     <row r="205">
-      <c r="B205" s="5" t="n"/>
-      <c r="D205" s="5" t="n"/>
+      <c r="B205" s="0" t="n"/>
+      <c r="D205" s="0" t="n"/>
+    </row>
+    <row r="206">
+      <c r="B206" s="0" t="n"/>
+      <c r="D206" s="0" t="n"/>
     </row>
     <row r="207">
-      <c r="A207" s="3" t="inlineStr">
+      <c r="B207" s="0" t="n"/>
+      <c r="D207" s="0" t="n"/>
+    </row>
+    <row r="208">
+      <c r="B208" s="0" t="n"/>
+      <c r="D208" s="0" t="n"/>
+    </row>
+    <row r="209">
+      <c r="B209" s="0" t="n"/>
+      <c r="D209" s="0" t="n"/>
+    </row>
+    <row r="210">
+      <c r="B210" s="0" t="n"/>
+      <c r="D210" s="0" t="n"/>
+    </row>
+    <row r="211">
+      <c r="B211" s="0" t="n"/>
+      <c r="D211" s="0" t="n"/>
+    </row>
+    <row r="212">
+      <c r="B212" s="0" t="n"/>
+      <c r="D212" s="0" t="n"/>
+    </row>
+    <row r="213">
+      <c r="B213" s="0" t="n"/>
+      <c r="D213" s="0" t="n"/>
+    </row>
+    <row r="214">
+      <c r="B214" s="0" t="n"/>
+      <c r="D214" s="0" t="n"/>
+    </row>
+    <row r="215">
+      <c r="B215" s="0" t="n"/>
+      <c r="D215" s="0" t="n"/>
+    </row>
+    <row r="216">
+      <c r="B216" s="0" t="n"/>
+      <c r="D216" s="0" t="n"/>
+    </row>
+    <row r="217">
+      <c r="B217" s="0" t="n"/>
+      <c r="D217" s="0" t="n"/>
+    </row>
+    <row r="218">
+      <c r="B218" s="0" t="n"/>
+      <c r="D218" s="0" t="n"/>
+    </row>
+    <row r="219">
+      <c r="B219" s="0" t="n"/>
+      <c r="D219" s="0" t="n"/>
+    </row>
+    <row r="220">
+      <c r="B220" s="0" t="n"/>
+      <c r="D220" s="0" t="n"/>
+    </row>
+    <row r="221">
+      <c r="B221" s="0" t="n"/>
+      <c r="D221" s="0" t="n"/>
+    </row>
+    <row r="222">
+      <c r="B222" s="0" t="n"/>
+      <c r="D222" s="0" t="n"/>
+    </row>
+    <row r="223"/>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B207" s="3" t="inlineStr">
+      <c r="B224" s="1" t="inlineStr">
         <is>
           <t>KillMonster</t>
         </is>
       </c>
-      <c r="C207" s="4" t="n">
+      <c r="C224" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D207" s="3" t="inlineStr">
+      <c r="D224" s="1" t="inlineStr">
         <is>
           <t>杀敌</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="3" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B208" s="4" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
         <is>
           <t>ShuffleCard</t>
         </is>
       </c>
-      <c r="C208" s="4" t="n">
+      <c r="C225" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D208" s="3" t="inlineStr">
+      <c r="D225" s="1" t="inlineStr">
         <is>
           <t>搓牌</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="3" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B209" s="4" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
         <is>
           <t>RefreshStore</t>
         </is>
       </c>
-      <c r="C209" s="4" t="n">
+      <c r="C226" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D209" s="3" t="inlineStr">
+      <c r="D226" s="1" t="inlineStr">
         <is>
           <t>刷新商店</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="3" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B210" s="4" t="inlineStr">
+      <c r="B227" s="2" t="inlineStr">
         <is>
           <t>Straight</t>
         </is>
       </c>
-      <c r="C210" s="4" t="n">
+      <c r="C227" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D210" s="3" t="inlineStr">
+      <c r="D227" s="1" t="inlineStr">
         <is>
           <t>亮出顺子</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="3" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B211" s="4" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
         <is>
           <t>TwoThreeFive</t>
         </is>
       </c>
-      <c r="C211" s="4" t="n">
+      <c r="C228" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D211" s="3" t="inlineStr">
+      <c r="D228" s="1" t="inlineStr">
         <is>
           <t>亮出散牌235</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="3" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B212" s="4" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
         <is>
           <t>ShuffleCardAndVictory</t>
         </is>
       </c>
-      <c r="C212" s="4" t="n">
+      <c r="C229" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D212" s="3" t="inlineStr">
+      <c r="D229" s="1" t="inlineStr">
         <is>
           <t>搓牌并战胜对手</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="3" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B213" s="4" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
         <is>
           <t>Seven</t>
         </is>
       </c>
-      <c r="C213" s="4" t="n">
+      <c r="C230" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D213" s="3" t="inlineStr">
+      <c r="D230" s="1" t="inlineStr">
         <is>
           <t>亮出数字牌7</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>GuideTriggerType</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>ScreenOpen</t>
-        </is>
-      </c>
-      <c r="C214" t="n">
-        <v>1</v>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>界面打开时触发</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>GuideTriggerType</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>GamePhase</t>
-        </is>
-      </c>
-      <c r="C215" t="n">
-        <v>2</v>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>对局阶段变化时触发</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>GuideTriggerType</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="C216" t="n">
-        <v>3</v>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>代码手动触发</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>GuideStepType</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Click</t>
-        </is>
-      </c>
-      <c r="C217" t="n">
-        <v>1</v>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>点击高亮目标后推进</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>GuideStepType</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Wait</t>
-        </is>
-      </c>
-      <c r="C218" t="n">
-        <v>2</v>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>等待代码处理器完成后推进</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>GuideStepType</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Dialog</t>
-        </is>
-      </c>
-      <c r="C219" t="n">
-        <v>3</v>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>点击气泡下一步后推进</t>
         </is>
       </c>
     </row>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -1055,7 +1055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E252"/>
+  <dimension ref="A1:E256"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.7416666666667" customWidth="1" style="1" min="1" max="1"/>
@@ -5172,120 +5172,200 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="0" t="inlineStr">
-        <is>
-          <t>GuideTriggerType</t>
-        </is>
-      </c>
-      <c r="B247" s="0" t="inlineStr">
-        <is>
-          <t>ScreenOpen</t>
-        </is>
-      </c>
-      <c r="C247" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D247" s="0" t="inlineStr">
-        <is>
-          <t>界面打开时触发</t>
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Flush</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>8</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>亮出同花</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="0" t="inlineStr">
-        <is>
-          <t>GuideTriggerType</t>
-        </is>
-      </c>
-      <c r="B248" s="0" t="inlineStr">
-        <is>
-          <t>GamePhase</t>
-        </is>
-      </c>
-      <c r="C248" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D248" s="0" t="inlineStr">
-        <is>
-          <t>对局阶段变化时触发</t>
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>ClearDifficulty</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>9</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>通关指定难度</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="0" t="inlineStr">
-        <is>
-          <t>GuideTriggerType</t>
-        </is>
-      </c>
-      <c r="B249" s="0" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="C249" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D249" s="0" t="inlineStr">
-        <is>
-          <t>代码手动触发</t>
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>AccumulateGold</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>10</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>累计获得金币</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="0" t="inlineStr">
-        <is>
-          <t>GuideStepType</t>
-        </is>
-      </c>
-      <c r="B250" s="0" t="inlineStr">
-        <is>
-          <t>Click</t>
-        </is>
-      </c>
-      <c r="C250" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D250" s="0" t="inlineStr">
-        <is>
-          <t>点击高亮目标后推进</t>
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>SingleDamage</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>11</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>单次比牌造成伤害达到指定值</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0" t="inlineStr">
         <is>
-          <t>GuideStepType</t>
+          <t>GuideTriggerType</t>
         </is>
       </c>
       <c r="B251" s="0" t="inlineStr">
         <is>
-          <t>Wait</t>
+          <t>ScreenOpen</t>
         </is>
       </c>
       <c r="C251" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D251" s="0" t="inlineStr">
         <is>
-          <t>等待代码处理器完成后推进</t>
+          <t>界面打开时触发</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="inlineStr">
         <is>
+          <t>GuideTriggerType</t>
+        </is>
+      </c>
+      <c r="B252" s="0" t="inlineStr">
+        <is>
+          <t>GamePhase</t>
+        </is>
+      </c>
+      <c r="C252" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D252" s="0" t="inlineStr">
+        <is>
+          <t>对局阶段变化时触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="0" t="inlineStr">
+        <is>
+          <t>GuideTriggerType</t>
+        </is>
+      </c>
+      <c r="B253" s="0" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="C253" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D253" s="0" t="inlineStr">
+        <is>
+          <t>代码手动触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="0" t="inlineStr">
+        <is>
           <t>GuideStepType</t>
         </is>
       </c>
-      <c r="B252" s="0" t="inlineStr">
+      <c r="B254" s="0" t="inlineStr">
+        <is>
+          <t>Click</t>
+        </is>
+      </c>
+      <c r="C254" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D254" s="0" t="inlineStr">
+        <is>
+          <t>点击高亮目标后推进</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="0" t="inlineStr">
+        <is>
+          <t>GuideStepType</t>
+        </is>
+      </c>
+      <c r="B255" s="0" t="inlineStr">
+        <is>
+          <t>Wait</t>
+        </is>
+      </c>
+      <c r="C255" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D255" s="0" t="inlineStr">
+        <is>
+          <t>等待代码处理器完成后推进</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="0" t="inlineStr">
+        <is>
+          <t>GuideStepType</t>
+        </is>
+      </c>
+      <c r="B256" s="0" t="inlineStr">
         <is>
           <t>Dialog</t>
         </is>
       </c>
-      <c r="C252" s="0" t="n">
+      <c r="C256" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D252" s="0" t="inlineStr">
+      <c r="D256" s="0" t="inlineStr">
         <is>
           <t>点击气泡下一步后推进</t>
         </is>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14175" windowHeight="10740"/>
+    <workbookView windowWidth="10350" windowHeight="11325"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="427">
   <si>
     <t>Enum</t>
   </si>
@@ -1190,6 +1190,18 @@
   </si>
   <si>
     <t>允许携带的圣物容量提高</t>
+  </si>
+  <si>
+    <t>ReduceLevel</t>
+  </si>
+  <si>
+    <t>比牌时,对方的牌型顺位降低</t>
+  </si>
+  <si>
+    <t>UpLevel</t>
+  </si>
+  <si>
+    <t>比牌时,自己的牌型顺位提高</t>
   </si>
   <si>
     <t>MaxHp</t>
@@ -5017,12 +5029,32 @@
       </c>
     </row>
     <row r="219" spans="1:4">
-      <c r="B219"/>
-      <c r="D219"/>
+      <c r="A219" t="s">
+        <v>92</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C219">
+        <v>150</v>
+      </c>
+      <c r="D219" s="5" t="s">
+        <v>387</v>
+      </c>
     </row>
     <row r="220" spans="1:4">
-      <c r="B220"/>
-      <c r="D220"/>
+      <c r="A220" t="s">
+        <v>92</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C220">
+        <v>151</v>
+      </c>
+      <c r="D220" s="5" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="221" spans="1:4">
       <c r="B221"/>
@@ -5045,7 +5077,7 @@
         <v>92</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C225" s="2">
         <v>1111</v>
@@ -5057,7 +5089,7 @@
         <v>92</v>
       </c>
       <c r="B226" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C226" s="2">
         <v>1112</v>
@@ -5069,7 +5101,7 @@
         <v>92</v>
       </c>
       <c r="B227" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C227" s="2">
         <v>1113</v>
@@ -5150,49 +5182,49 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C247" s="2">
         <v>1</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C248" s="2">
         <v>2</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C249" s="2">
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>13</v>
@@ -5201,54 +5233,54 @@
         <v>4</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C251" s="2">
         <v>5</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="252" spans="1:4">
       <c r="A252" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C252" s="2">
         <v>6</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="253" spans="1:4">
       <c r="A253" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C253" s="2">
         <v>7</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B254" t="s">
         <v>15</v>
@@ -5257,133 +5289,133 @@
         <v>8</v>
       </c>
       <c r="D254" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B255" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C255">
         <v>9</v>
       </c>
       <c r="D255" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B256" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C256">
         <v>10</v>
       </c>
       <c r="D256" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B257" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C257">
         <v>11</v>
       </c>
       <c r="D257" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B258" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C258">
         <v>1</v>
       </c>
       <c r="D258" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B259" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C259">
         <v>2</v>
       </c>
       <c r="D259" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B260" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C260">
         <v>3</v>
       </c>
       <c r="D260" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B261" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C261">
         <v>1</v>
       </c>
       <c r="D261" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B262" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C262">
         <v>2</v>
       </c>
       <c r="D262" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B263" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C263">
         <v>3</v>
       </c>
       <c r="D263" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -1934,7 +1934,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1952,6 +1952,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -5076,7 +5079,7 @@
       <c r="A225" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B225" s="4" t="s">
+      <c r="B225" s="6" t="s">
         <v>390</v>
       </c>
       <c r="C225" s="2">

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="10350" windowHeight="11325"/>
+    <workbookView windowWidth="13695" windowHeight="11505"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="459">
   <si>
     <t>Enum</t>
   </si>
@@ -196,7 +196,7 @@
     <t>同花牌型在攻击时,伤害降低</t>
   </si>
   <si>
-    <t>FlushStraightDamage</t>
+    <t>CoupletDamage</t>
   </si>
   <si>
     <t>同花顺牌型在攻击时,伤害降低</t>
@@ -268,16 +268,16 @@
     <t>玩家每回合手牌数量降低</t>
   </si>
   <si>
-    <t>BossRage</t>
-  </si>
-  <si>
-    <t>BOSS损失生命后攻击力提升</t>
-  </si>
-  <si>
-    <t>BossShield</t>
-  </si>
-  <si>
-    <t>BOSS免疫前N次伤害</t>
+    <t>MonsterRage</t>
+  </si>
+  <si>
+    <t>敌人损失生命后攻击力提升</t>
+  </si>
+  <si>
+    <t>MonsterShield</t>
+  </si>
+  <si>
+    <t>敌人免疫前N次伤害</t>
   </si>
   <si>
     <t>RoundLimit</t>
@@ -308,6 +308,102 @@
   </si>
   <si>
     <t>玩家的黑桃和梅花牌失效</t>
+  </si>
+  <si>
+    <t>DisableEven</t>
+  </si>
+  <si>
+    <t>本关内搓牌时,无法出现偶数点数的牌</t>
+  </si>
+  <si>
+    <t>DisableAce</t>
+  </si>
+  <si>
+    <t>本关内搓牌时,无法出现A</t>
+  </si>
+  <si>
+    <t>FaceDevalue</t>
+  </si>
+  <si>
+    <t>本关内人头牌[J/Q/K]伤害点数按5计算,比牌大小不变</t>
+  </si>
+  <si>
+    <t>AceDown</t>
+  </si>
+  <si>
+    <t>本关内A的伤害点数由11降为1,比牌大小不变</t>
+  </si>
+  <si>
+    <t>RubDown</t>
+  </si>
+  <si>
+    <t>本关内搓牌次数减少1次</t>
+  </si>
+  <si>
+    <t>SwapLock</t>
+  </si>
+  <si>
+    <t>本关内无法使用换牌技能</t>
+  </si>
+  <si>
+    <t>RubFee</t>
+  </si>
+  <si>
+    <t>本关内每次搓牌需要消耗50金币,金币不足时无法搓牌</t>
+  </si>
+  <si>
+    <t>MonsterRegen</t>
+  </si>
+  <si>
+    <t>本关内所有敌人每回合开始时回复10%的生命值</t>
+  </si>
+  <si>
+    <t>MonsterGrow</t>
+  </si>
+  <si>
+    <t>本关内所有敌人每回合结束时攻击力+2</t>
+  </si>
+  <si>
+    <t>ThornShell</t>
+  </si>
+  <si>
+    <t>本关内玩家每次攻击敌人后,自身会受到该伤害15%的伤害</t>
+  </si>
+  <si>
+    <t>VengefulSoul</t>
+  </si>
+  <si>
+    <t>本关内敌人死亡后,会使玩家的攻击力永久降低2点</t>
+  </si>
+  <si>
+    <t>HealBan</t>
+  </si>
+  <si>
+    <t>本关内玩家受到的所有治疗与回复效果降低50%</t>
+  </si>
+  <si>
+    <t>TieLose</t>
+  </si>
+  <si>
+    <t>本关内比牌时双方牌型顺位一致时,敌人将获胜</t>
+  </si>
+  <si>
+    <t>PhaseRage</t>
+  </si>
+  <si>
+    <t>本关内敌人生命值首次低于50%时,攻击力+50%,并获得2次伤害免疫</t>
+  </si>
+  <si>
+    <t>SecondWind</t>
+  </si>
+  <si>
+    <t>本关内敌人被击败时,将以30%的生命值复活一次</t>
+  </si>
+  <si>
+    <t>LifeSiphon</t>
+  </si>
+  <si>
+    <t>本关内敌人攻击玩家时,按造成伤害的50%回复自身生命值</t>
   </si>
   <si>
     <t>MechanismType</t>
@@ -1478,18 +1574,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1810,7 +1900,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -1834,16 +1924,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -1852,109 +1942,121 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2304,25 +2406,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:E263"/>
+  <dimension ref="A4:E282"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="16.7416666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.05833333333333" style="2" customWidth="1"/>
-    <col min="4" max="4" width="31.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="34.75" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7416666666667" style="3" customWidth="1"/>
+    <col min="2" max="2" width="18.7" style="3" customWidth="1"/>
+    <col min="3" max="3" width="7.05833333333333" style="4" customWidth="1"/>
+    <col min="4" max="4" width="31.625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="34.75" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
@@ -2330,142 +2432,142 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="4">
         <v>1</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="4">
         <v>2</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="4">
         <v>1</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="4">
         <v>2</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="4">
         <v>4</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="4">
         <v>3</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="4">
         <v>5</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="4">
         <v>6</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="4">
         <v>1</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="4">
         <v>2</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2473,13 +2575,13 @@
       <c r="A19" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="4">
         <v>1</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="3" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2487,13 +2589,13 @@
       <c r="A20" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="4">
         <v>2</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2501,13 +2603,13 @@
       <c r="A21" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="4">
         <v>3</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="3" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2515,24 +2617,24 @@
       <c r="A22" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="4">
         <v>4</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B39" t="s">
         <v>36</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="4">
         <v>1</v>
       </c>
       <c r="D39" t="s">
@@ -2540,13 +2642,13 @@
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="4">
         <v>2</v>
       </c>
       <c r="D40" t="s">
@@ -2554,13 +2656,13 @@
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="4">
         <v>3</v>
       </c>
       <c r="D41" t="s">
@@ -2568,13 +2670,13 @@
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="4">
         <v>4</v>
       </c>
       <c r="D42" t="s">
@@ -2582,13 +2684,13 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="4">
         <v>5</v>
       </c>
       <c r="D43" t="s">
@@ -2596,86 +2698,86 @@
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="4">
         <v>6</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="4">
         <v>7</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="4">
         <v>8</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="3" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="4">
         <v>9</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="3" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" s="4">
         <v>10</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="2">
+      <c r="C49" s="4">
         <v>11</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="3" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2686,7 +2788,7 @@
       <c r="B50" t="s">
         <v>58</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="4">
         <v>12</v>
       </c>
       <c r="D50" t="s">
@@ -2700,7 +2802,7 @@
       <c r="B51" t="s">
         <v>60</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="4">
         <v>13</v>
       </c>
       <c r="D51" t="s">
@@ -2714,7 +2816,7 @@
       <c r="B52" t="s">
         <v>62</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="4">
         <v>14</v>
       </c>
       <c r="D52" t="s">
@@ -2728,7 +2830,7 @@
       <c r="B53" t="s">
         <v>64</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="4">
         <v>15</v>
       </c>
       <c r="D53" t="s">
@@ -2742,7 +2844,7 @@
       <c r="B54" t="s">
         <v>66</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="4">
         <v>16</v>
       </c>
       <c r="D54" t="s">
@@ -2756,7 +2858,7 @@
       <c r="B55" t="s">
         <v>68</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="4">
         <v>17</v>
       </c>
       <c r="D55" t="s">
@@ -2770,7 +2872,7 @@
       <c r="B56" t="s">
         <v>70</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="4">
         <v>18</v>
       </c>
       <c r="D56" t="s">
@@ -2784,7 +2886,7 @@
       <c r="B57" t="s">
         <v>72</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="4">
         <v>19</v>
       </c>
       <c r="D57" t="s">
@@ -2798,7 +2900,7 @@
       <c r="B58" t="s">
         <v>74</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="4">
         <v>20</v>
       </c>
       <c r="D58" t="s">
@@ -2812,7 +2914,7 @@
       <c r="B59" t="s">
         <v>76</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="4">
         <v>21</v>
       </c>
       <c r="D59" t="s">
@@ -2826,7 +2928,7 @@
       <c r="B60" t="s">
         <v>78</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="4">
         <v>22</v>
       </c>
       <c r="D60" t="s">
@@ -2840,7 +2942,7 @@
       <c r="B61" t="s">
         <v>80</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="4">
         <v>23</v>
       </c>
       <c r="D61" t="s">
@@ -2854,7 +2956,7 @@
       <c r="B62" t="s">
         <v>82</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="4">
         <v>24</v>
       </c>
       <c r="D62" t="s">
@@ -2868,7 +2970,7 @@
       <c r="B63" t="s">
         <v>84</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="4">
         <v>25</v>
       </c>
       <c r="D63" t="s">
@@ -2882,7 +2984,7 @@
       <c r="B64" t="s">
         <v>86</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="4">
         <v>26</v>
       </c>
       <c r="D64" t="s">
@@ -2896,7 +2998,7 @@
       <c r="B65" t="s">
         <v>88</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="4">
         <v>27</v>
       </c>
       <c r="D65" t="s">
@@ -2910,2254 +3012,2378 @@
       <c r="B66" t="s">
         <v>90</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="4">
         <v>28</v>
       </c>
       <c r="D66" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="1" t="s">
+    <row r="67" s="1" customFormat="1" spans="1:4">
+      <c r="A67" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B67" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="C67" s="7">
+        <v>29</v>
+      </c>
+      <c r="D67" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C69" s="2">
+    </row>
+    <row r="68" s="1" customFormat="1" spans="1:4">
+      <c r="A68" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C68" s="7">
+        <v>30</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="1" spans="1:4">
+      <c r="A69" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C69" s="7">
+        <v>31</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="70" s="1" customFormat="1" spans="1:4">
+      <c r="A70" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C70" s="7">
+        <v>32</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="71" s="1" customFormat="1" spans="1:4">
+      <c r="A71" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C71" s="7">
+        <v>33</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="72" s="1" customFormat="1" spans="1:4">
+      <c r="A72" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C72" s="7">
+        <v>34</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" spans="1:4">
+      <c r="A73" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C73" s="7">
+        <v>35</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="74" s="1" customFormat="1" spans="1:4">
+      <c r="A74" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C74" s="7">
+        <v>36</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="75" s="1" customFormat="1" spans="1:4">
+      <c r="A75" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C75" s="7">
+        <v>37</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="76" s="1" customFormat="1" spans="1:4">
+      <c r="A76" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C76" s="7">
+        <v>38</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="77" s="1" customFormat="1" spans="1:4">
+      <c r="A77" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C77" s="7">
+        <v>39</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="78" s="1" customFormat="1" spans="1:4">
+      <c r="A78" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C78" s="7">
+        <v>40</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="79" s="1" customFormat="1" spans="1:4">
+      <c r="A79" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C79" s="7">
+        <v>41</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="80" s="1" customFormat="1" spans="1:4">
+      <c r="A80" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C80" s="7">
+        <v>42</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="81" s="1" customFormat="1" spans="1:4">
+      <c r="A81" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C81" s="7">
+        <v>43</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="82" s="1" customFormat="1" spans="1:4">
+      <c r="A82" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C82" s="7">
+        <v>44</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C88" s="4">
         <v>1</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D88" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C89" s="4">
+        <v>2</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C90" s="4">
+        <v>3</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C91" s="4">
+        <v>4</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C92" s="4">
+        <v>5</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C93" s="4">
+        <v>6</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C94" s="4">
+        <v>7</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C95" s="4">
+        <v>8</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C96" s="4">
+        <v>9</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C97" s="4">
+        <v>10</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C98" s="4">
+        <v>11</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C99" s="4">
+        <v>12</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C100" s="4">
+        <v>13</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C101" s="4">
+        <v>14</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C102" s="4">
+        <v>15</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C103" s="4">
+        <v>16</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C104" s="4">
+        <v>17</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C105" s="4">
+        <v>18</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C106" s="4">
+        <v>19</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C107" s="4">
+        <v>20</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C108" s="4">
+        <v>21</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C109" s="4">
+        <v>22</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C110" s="4">
+        <v>23</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C111" s="4">
+        <v>24</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C112" s="4">
+        <v>25</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C113" s="4">
+        <v>26</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C114" s="4">
+        <v>27</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C115" s="4">
+        <v>28</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C117" s="4">
+        <v>29</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B118" t="s">
+        <v>183</v>
+      </c>
+      <c r="C118" s="4">
+        <v>30</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B119" t="s">
+        <v>185</v>
+      </c>
+      <c r="C119" s="4">
+        <v>31</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B120" t="s">
+        <v>187</v>
+      </c>
+      <c r="C120" s="4">
+        <v>32</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B121" t="s">
+        <v>189</v>
+      </c>
+      <c r="C121" s="4">
+        <v>33</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C122" s="4">
+        <v>34</v>
+      </c>
+      <c r="D122" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B123" t="s">
+        <v>13</v>
+      </c>
+      <c r="C123" s="4">
+        <v>35</v>
+      </c>
+      <c r="D123" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B124" t="s">
+        <v>15</v>
+      </c>
+      <c r="C124" s="4">
+        <v>36</v>
+      </c>
+      <c r="D124" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>17</v>
+      </c>
+      <c r="C125" s="4">
+        <v>37</v>
+      </c>
+      <c r="D125" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C126" s="4">
+        <v>38</v>
+      </c>
+      <c r="D126" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B127" t="s">
+        <v>196</v>
+      </c>
+      <c r="C127" s="4">
+        <v>39</v>
+      </c>
+      <c r="D127" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B128" t="s">
+        <v>198</v>
+      </c>
+      <c r="C128" s="4">
+        <v>40</v>
+      </c>
+      <c r="D128" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B129" t="s">
+        <v>200</v>
+      </c>
+      <c r="C129" s="4">
+        <v>41</v>
+      </c>
+      <c r="D129" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B130" t="s">
+        <v>202</v>
+      </c>
+      <c r="C130" s="4">
+        <v>42</v>
+      </c>
+      <c r="D130" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C131" s="4">
+        <v>43</v>
+      </c>
+      <c r="D131" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B132" t="s">
+        <v>206</v>
+      </c>
+      <c r="C132" s="4">
+        <v>44</v>
+      </c>
+      <c r="D132" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B133" t="s">
+        <v>208</v>
+      </c>
+      <c r="C133" s="4">
+        <v>45</v>
+      </c>
+      <c r="D133" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B134" t="s">
+        <v>210</v>
+      </c>
+      <c r="C134" s="4">
+        <v>46</v>
+      </c>
+      <c r="D134" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C135" s="4">
+        <v>47</v>
+      </c>
+      <c r="D135" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C136" s="4">
+        <v>48</v>
+      </c>
+      <c r="D136" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B137" t="s">
+        <v>216</v>
+      </c>
+      <c r="C137" s="4">
+        <v>49</v>
+      </c>
+      <c r="D137" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B138" t="s">
+        <v>218</v>
+      </c>
+      <c r="C138" s="4">
+        <v>50</v>
+      </c>
+      <c r="D138" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C139" s="4">
+        <v>51</v>
+      </c>
+      <c r="D139" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B140" t="s">
+        <v>222</v>
+      </c>
+      <c r="C140" s="4">
+        <v>52</v>
+      </c>
+      <c r="D140" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B141" t="s">
+        <v>224</v>
+      </c>
+      <c r="C141" s="4">
+        <v>53</v>
+      </c>
+      <c r="D141" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B142" t="s">
+        <v>226</v>
+      </c>
+      <c r="C142" s="4">
+        <v>54</v>
+      </c>
+      <c r="D142" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B143" t="s">
+        <v>228</v>
+      </c>
+      <c r="C143" s="4">
+        <v>55</v>
+      </c>
+      <c r="D143" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C144" s="4">
+        <v>56</v>
+      </c>
+      <c r="D144" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B145" t="s">
+        <v>232</v>
+      </c>
+      <c r="C145" s="4">
+        <v>57</v>
+      </c>
+      <c r="D145" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B146" t="s">
+        <v>234</v>
+      </c>
+      <c r="C146" s="4">
+        <v>58</v>
+      </c>
+      <c r="D146" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B147" t="s">
+        <v>236</v>
+      </c>
+      <c r="C147" s="4">
+        <v>59</v>
+      </c>
+      <c r="D147" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B148" t="s">
+        <v>238</v>
+      </c>
+      <c r="C148" s="4">
+        <v>60</v>
+      </c>
+      <c r="D148" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B149" t="s">
+        <v>240</v>
+      </c>
+      <c r="C149" s="4">
+        <v>61</v>
+      </c>
+      <c r="D149" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B150" t="s">
+        <v>242</v>
+      </c>
+      <c r="C150" s="4">
+        <v>62</v>
+      </c>
+      <c r="D150" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B151" t="s">
+        <v>244</v>
+      </c>
+      <c r="C151" s="4">
+        <v>63</v>
+      </c>
+      <c r="D151" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B152" t="s">
+        <v>246</v>
+      </c>
+      <c r="C152" s="4">
+        <v>64</v>
+      </c>
+      <c r="D152" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B153" t="s">
+        <v>248</v>
+      </c>
+      <c r="C153" s="4">
+        <v>65</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B154" t="s">
+        <v>250</v>
+      </c>
+      <c r="C154" s="4">
+        <v>66</v>
+      </c>
+      <c r="D154" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B155" t="s">
+        <v>252</v>
+      </c>
+      <c r="C155" s="4">
+        <v>67</v>
+      </c>
+      <c r="D155" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B156" t="s">
+        <v>254</v>
+      </c>
+      <c r="C156" s="4">
+        <v>68</v>
+      </c>
+      <c r="D156" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B157" t="s">
+        <v>256</v>
+      </c>
+      <c r="C157" s="4">
+        <v>69</v>
+      </c>
+      <c r="D157" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B158" t="s">
+        <v>258</v>
+      </c>
+      <c r="C158" s="4">
+        <v>70</v>
+      </c>
+      <c r="D158" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C159" s="4">
+        <v>71</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C160" s="4">
+        <v>72</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B161" t="s">
+        <v>264</v>
+      </c>
+      <c r="C161" s="4">
+        <v>73</v>
+      </c>
+      <c r="D161" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B162" t="s">
+        <v>266</v>
+      </c>
+      <c r="C162" s="4">
+        <v>74</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B163" t="s">
+        <v>268</v>
+      </c>
+      <c r="C163" s="4">
+        <v>75</v>
+      </c>
+      <c r="D163" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B164" t="s">
+        <v>270</v>
+      </c>
+      <c r="C164" s="4">
+        <v>76</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B165" t="s">
+        <v>272</v>
+      </c>
+      <c r="C165" s="4">
+        <v>77</v>
+      </c>
+      <c r="D165" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B166" t="s">
+        <v>274</v>
+      </c>
+      <c r="C166" s="4">
+        <v>78</v>
+      </c>
+      <c r="D166" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B167" t="s">
+        <v>276</v>
+      </c>
+      <c r="C167" s="4">
+        <v>79</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B168" t="s">
+        <v>278</v>
+      </c>
+      <c r="C168" s="4">
+        <v>80</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B169" t="s">
+        <v>280</v>
+      </c>
+      <c r="C169" s="4">
+        <v>81</v>
+      </c>
+      <c r="D169" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B170" t="s">
+        <v>282</v>
+      </c>
+      <c r="C170" s="4">
+        <v>82</v>
+      </c>
+      <c r="D170" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C171" s="4">
+        <v>83</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B172" t="s">
+        <v>286</v>
+      </c>
+      <c r="C172" s="4">
+        <v>84</v>
+      </c>
+      <c r="D172" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B173" t="s">
+        <v>288</v>
+      </c>
+      <c r="C173" s="4">
+        <v>85</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B174" t="s">
+        <v>290</v>
+      </c>
+      <c r="C174" s="4">
+        <v>86</v>
+      </c>
+      <c r="D174" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B175" t="s">
+        <v>292</v>
+      </c>
+      <c r="C175" s="4">
+        <v>87</v>
+      </c>
+      <c r="D175" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B176" t="s">
+        <v>294</v>
+      </c>
+      <c r="C176" s="4">
+        <v>88</v>
+      </c>
+      <c r="D176" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C177" s="4">
+        <v>89</v>
+      </c>
+      <c r="D177" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C178" s="4">
+        <v>90</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B179" t="s">
+        <v>300</v>
+      </c>
+      <c r="C179" s="4">
+        <v>91</v>
+      </c>
+      <c r="D179" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="180" s="2" customFormat="1" spans="1:5">
+      <c r="A180" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B180" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="C180" s="9">
+        <v>92</v>
+      </c>
+      <c r="D180" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="E180" s="8"/>
+    </row>
+    <row r="181" s="2" customFormat="1" spans="1:5">
+      <c r="A181" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B181" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="C181" s="9">
+        <v>93</v>
+      </c>
+      <c r="D181" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="E181" s="8"/>
+    </row>
+    <row r="182" s="2" customFormat="1" spans="1:5">
+      <c r="A182" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B182" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="C182" s="9">
         <v>94</v>
       </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B70" s="1" t="s">
+      <c r="D182" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="E182" s="8"/>
+    </row>
+    <row r="183" s="2" customFormat="1" spans="1:5">
+      <c r="A183" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B183" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="C183" s="9">
         <v>95</v>
       </c>
-      <c r="C70" s="2">
-        <v>2</v>
-      </c>
-      <c r="D70" s="1" t="s">
+      <c r="D183" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="E183" s="8"/>
+    </row>
+    <row r="184" s="2" customFormat="1" spans="1:5">
+      <c r="A184" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B184" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C184" s="9">
         <v>96</v>
       </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B71" s="1" t="s">
+      <c r="D184" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="E184" s="8"/>
+    </row>
+    <row r="185" s="2" customFormat="1" spans="1:5">
+      <c r="A185" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C185" s="9">
         <v>97</v>
       </c>
-      <c r="C71" s="2">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
+      <c r="D185" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E185" s="8"/>
+    </row>
+    <row r="186" s="2" customFormat="1" spans="1:5">
+      <c r="A186" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B186" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="C186" s="9">
         <v>98</v>
       </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B72" s="2" t="s">
+      <c r="D186" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E186" s="8"/>
+    </row>
+    <row r="187" s="2" customFormat="1" spans="1:5">
+      <c r="A187" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B187" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="C187" s="9">
         <v>99</v>
       </c>
-      <c r="C72" s="2">
-        <v>4</v>
-      </c>
-      <c r="D72" s="1" t="s">
+      <c r="D187" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E187" s="8"/>
+    </row>
+    <row r="188" s="2" customFormat="1" spans="1:5">
+      <c r="A188" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B188" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C188" s="9">
         <v>100</v>
       </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B73" s="2" t="s">
+      <c r="D188" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E188" s="8"/>
+    </row>
+    <row r="189" s="2" customFormat="1" spans="1:5">
+      <c r="A189" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B189" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="C189" s="9">
         <v>101</v>
       </c>
-      <c r="C73" s="2">
-        <v>5</v>
-      </c>
-      <c r="D73" s="1" t="s">
+      <c r="D189" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E189" s="8"/>
+    </row>
+    <row r="190" s="2" customFormat="1" spans="1:5">
+      <c r="A190" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B190" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="C190" s="9">
         <v>102</v>
       </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B74" s="2" t="s">
+      <c r="D190" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E190" s="8"/>
+    </row>
+    <row r="191" s="2" customFormat="1" spans="1:5">
+      <c r="A191" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B191" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="C191" s="9">
         <v>103</v>
       </c>
-      <c r="C74" s="2">
-        <v>6</v>
-      </c>
-      <c r="D74" s="1" t="s">
+      <c r="D191" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E191" s="8"/>
+    </row>
+    <row r="192" s="2" customFormat="1" spans="1:5">
+      <c r="A192" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B192" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="C192" s="9">
         <v>104</v>
       </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B75" s="2" t="s">
+      <c r="D192" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E192" s="8"/>
+    </row>
+    <row r="193" s="2" customFormat="1" spans="1:5">
+      <c r="A193" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B193" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="C193" s="9">
         <v>105</v>
       </c>
-      <c r="C75" s="2">
-        <v>7</v>
-      </c>
-      <c r="D75" s="1" t="s">
+      <c r="D193" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E193" s="8"/>
+    </row>
+    <row r="194" s="2" customFormat="1" spans="1:5">
+      <c r="A194" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B194" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C194" s="9">
         <v>106</v>
       </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B76" s="2" t="s">
+      <c r="D194" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E194" s="8"/>
+    </row>
+    <row r="195" s="2" customFormat="1" spans="1:5">
+      <c r="A195" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B195" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="C195" s="9">
         <v>107</v>
       </c>
-      <c r="C76" s="2">
-        <v>8</v>
-      </c>
-      <c r="D76" s="1" t="s">
+      <c r="D195" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E195" s="8"/>
+    </row>
+    <row r="196" s="2" customFormat="1" spans="1:5">
+      <c r="A196" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B196" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="C196" s="9">
         <v>108</v>
       </c>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B77" s="2" t="s">
+      <c r="D196" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E196" s="8"/>
+    </row>
+    <row r="197" s="2" customFormat="1" spans="1:5">
+      <c r="A197" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B197" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="C197" s="9">
         <v>109</v>
       </c>
-      <c r="C77" s="2">
-        <v>9</v>
-      </c>
-      <c r="D77" s="1" t="s">
+      <c r="D197" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="E197" s="8"/>
+    </row>
+    <row r="198" s="2" customFormat="1" spans="1:5">
+      <c r="A198" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B198" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="C198" s="9">
         <v>110</v>
       </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B78" s="2" t="s">
+      <c r="D198" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E198" s="8"/>
+    </row>
+    <row r="199" s="2" customFormat="1" spans="1:5">
+      <c r="A199" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B199" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C199" s="9">
         <v>111</v>
       </c>
-      <c r="C78" s="2">
-        <v>10</v>
-      </c>
-      <c r="D78" s="1" t="s">
+      <c r="D199" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E199" s="8"/>
+    </row>
+    <row r="200" s="2" customFormat="1" spans="1:5">
+      <c r="A200" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B200" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="C200" s="9">
         <v>112</v>
       </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B79" s="2" t="s">
+      <c r="D200" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="E200" s="8"/>
+    </row>
+    <row r="201" s="2" customFormat="1" spans="1:5">
+      <c r="A201" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B201" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="C201" s="9">
         <v>113</v>
       </c>
-      <c r="C79" s="2">
-        <v>11</v>
-      </c>
-      <c r="D79" s="1" t="s">
+      <c r="D201" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="E201" s="8"/>
+    </row>
+    <row r="202" s="2" customFormat="1" spans="1:5">
+      <c r="A202" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B202" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="C202" s="9">
         <v>114</v>
       </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B80" s="2" t="s">
+      <c r="D202" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="E202" s="8"/>
+    </row>
+    <row r="203" s="2" customFormat="1" spans="1:5">
+      <c r="A203" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B203" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="C203" s="9">
         <v>115</v>
       </c>
-      <c r="C80" s="2">
-        <v>12</v>
-      </c>
-      <c r="D80" s="1" t="s">
+      <c r="D203" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="E203" s="8"/>
+    </row>
+    <row r="204" s="2" customFormat="1" spans="1:5">
+      <c r="A204" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B204" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="C204" s="9">
         <v>116</v>
       </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B81" s="2" t="s">
+      <c r="D204" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="E204" s="8"/>
+    </row>
+    <row r="205" s="2" customFormat="1" spans="1:5">
+      <c r="A205" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B205" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="C205" s="9">
         <v>117</v>
       </c>
-      <c r="C81" s="2">
-        <v>13</v>
-      </c>
-      <c r="D81" s="1" t="s">
+      <c r="D205" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="E205" s="8"/>
+    </row>
+    <row r="206" s="2" customFormat="1" spans="1:5">
+      <c r="A206" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B206" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="C206" s="9">
         <v>118</v>
       </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B82" s="2" t="s">
+      <c r="D206" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="E206" s="8"/>
+    </row>
+    <row r="207" s="2" customFormat="1" spans="1:5">
+      <c r="A207" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B207" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="C207" s="9">
         <v>119</v>
       </c>
-      <c r="C82" s="2">
-        <v>14</v>
-      </c>
-      <c r="D82" s="1" t="s">
+      <c r="D207" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="E207" s="8"/>
+    </row>
+    <row r="208" s="2" customFormat="1" spans="1:5">
+      <c r="A208" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B208" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="C208" s="9">
         <v>120</v>
       </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B83" s="2" t="s">
+      <c r="D208" s="8" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="209" s="2" customFormat="1" spans="1:4">
+      <c r="A209" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B209" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="C209" s="9">
         <v>121</v>
       </c>
-      <c r="C83" s="2">
-        <v>15</v>
-      </c>
-      <c r="D83" s="1" t="s">
+      <c r="D209" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="210" s="2" customFormat="1" spans="1:4">
+      <c r="A210" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B210" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="C210" s="9">
         <v>122</v>
       </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B84" s="1" t="s">
+      <c r="D210" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="211" s="2" customFormat="1" spans="1:4">
+      <c r="A211" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B211" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="C211" s="9">
         <v>123</v>
       </c>
-      <c r="C84" s="2">
-        <v>16</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B85" s="2" t="s">
+      <c r="D211" s="8" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="212" s="2" customFormat="1" spans="1:4">
+      <c r="A212" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B212" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="C212" s="9">
+        <v>124</v>
+      </c>
+      <c r="D212" s="8" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="213" s="2" customFormat="1" spans="1:4">
+      <c r="A213" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B213" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="C213" s="9">
         <v>125</v>
       </c>
-      <c r="C85" s="2">
-        <v>17</v>
-      </c>
-      <c r="D85" s="1" t="s">
+      <c r="D213" s="8" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="214" s="2" customFormat="1" spans="1:4">
+      <c r="A214" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B214" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="C214" s="9">
         <v>126</v>
       </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B86" s="1" t="s">
+      <c r="D214" s="8" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="215" s="2" customFormat="1" spans="1:4">
+      <c r="A215" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B215" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="C215" s="9">
         <v>127</v>
       </c>
-      <c r="C86" s="2">
-        <v>18</v>
-      </c>
-      <c r="D86" s="1" t="s">
+      <c r="D215" s="8" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="216" s="2" customFormat="1" spans="1:4">
+      <c r="A216" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B216" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="C216" s="9">
         <v>128</v>
       </c>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B87" s="2" t="s">
+      <c r="D216" s="8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="217" s="2" customFormat="1" spans="1:4">
+      <c r="A217" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B217" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C217" s="9">
         <v>129</v>
       </c>
-      <c r="C87" s="2">
-        <v>19</v>
-      </c>
-      <c r="D87" s="1" t="s">
+      <c r="D217" s="8" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="218" s="2" customFormat="1" spans="1:4">
+      <c r="A218" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B218" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="C218" s="9">
         <v>130</v>
       </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C88" s="2">
-        <v>20</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C89" s="2">
-        <v>21</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C90" s="2">
-        <v>22</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C91" s="2">
-        <v>23</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C92" s="2">
-        <v>24</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C93" s="2">
-        <v>25</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C94" s="2">
-        <v>26</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C95" s="2">
-        <v>27</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C96" s="2">
-        <v>28</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C98" s="2">
-        <v>29</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B99" t="s">
-        <v>151</v>
-      </c>
-      <c r="C99" s="2">
-        <v>30</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B100" t="s">
-        <v>153</v>
-      </c>
-      <c r="C100" s="2">
-        <v>31</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B101" t="s">
-        <v>155</v>
-      </c>
-      <c r="C101" s="2">
-        <v>32</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B102" t="s">
-        <v>157</v>
-      </c>
-      <c r="C102" s="2">
-        <v>33</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C103" s="2">
-        <v>34</v>
-      </c>
-      <c r="D103" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B104" t="s">
-        <v>13</v>
-      </c>
-      <c r="C104" s="2">
-        <v>35</v>
-      </c>
-      <c r="D104" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B105" t="s">
-        <v>15</v>
-      </c>
-      <c r="C105" s="2">
-        <v>36</v>
-      </c>
-      <c r="D105" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B106" t="s">
-        <v>17</v>
-      </c>
-      <c r="C106" s="2">
-        <v>37</v>
-      </c>
-      <c r="D106" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C107" s="2">
-        <v>38</v>
-      </c>
-      <c r="D107" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B108" t="s">
-        <v>164</v>
-      </c>
-      <c r="C108" s="2">
-        <v>39</v>
-      </c>
-      <c r="D108" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B109" t="s">
-        <v>166</v>
-      </c>
-      <c r="C109" s="2">
-        <v>40</v>
-      </c>
-      <c r="D109" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B110" t="s">
-        <v>168</v>
-      </c>
-      <c r="C110" s="2">
-        <v>41</v>
-      </c>
-      <c r="D110" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B111" t="s">
-        <v>170</v>
-      </c>
-      <c r="C111" s="2">
-        <v>42</v>
-      </c>
-      <c r="D111" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C112" s="2">
-        <v>43</v>
-      </c>
-      <c r="D112" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B113" t="s">
-        <v>174</v>
-      </c>
-      <c r="C113" s="2">
-        <v>44</v>
-      </c>
-      <c r="D113" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4">
-      <c r="A114" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B114" t="s">
-        <v>176</v>
-      </c>
-      <c r="C114" s="2">
-        <v>45</v>
-      </c>
-      <c r="D114" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
-      <c r="A115" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B115" t="s">
-        <v>178</v>
-      </c>
-      <c r="C115" s="2">
-        <v>46</v>
-      </c>
-      <c r="D115" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4">
-      <c r="A116" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C116" s="2">
-        <v>47</v>
-      </c>
-      <c r="D116" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4">
-      <c r="A117" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C117" s="2">
-        <v>48</v>
-      </c>
-      <c r="D117" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4">
-      <c r="A118" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B118" t="s">
-        <v>184</v>
-      </c>
-      <c r="C118" s="2">
-        <v>49</v>
-      </c>
-      <c r="D118" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4">
-      <c r="A119" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B119" t="s">
-        <v>186</v>
-      </c>
-      <c r="C119" s="2">
-        <v>50</v>
-      </c>
-      <c r="D119" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4">
-      <c r="A120" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C120" s="2">
-        <v>51</v>
-      </c>
-      <c r="D120" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4">
-      <c r="A121" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B121" t="s">
-        <v>190</v>
-      </c>
-      <c r="C121" s="2">
-        <v>52</v>
-      </c>
-      <c r="D121" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4">
-      <c r="A122" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B122" t="s">
-        <v>192</v>
-      </c>
-      <c r="C122" s="2">
-        <v>53</v>
-      </c>
-      <c r="D122" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4">
-      <c r="A123" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B123" t="s">
-        <v>194</v>
-      </c>
-      <c r="C123" s="2">
-        <v>54</v>
-      </c>
-      <c r="D123" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4">
-      <c r="A124" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B124" t="s">
-        <v>196</v>
-      </c>
-      <c r="C124" s="2">
-        <v>55</v>
-      </c>
-      <c r="D124" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4">
-      <c r="A125" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C125" s="2">
-        <v>56</v>
-      </c>
-      <c r="D125" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4">
-      <c r="A126" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B126" t="s">
-        <v>200</v>
-      </c>
-      <c r="C126" s="2">
-        <v>57</v>
-      </c>
-      <c r="D126" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4">
-      <c r="A127" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B127" t="s">
-        <v>202</v>
-      </c>
-      <c r="C127" s="2">
-        <v>58</v>
-      </c>
-      <c r="D127" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4">
-      <c r="A128" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B128" t="s">
-        <v>204</v>
-      </c>
-      <c r="C128" s="2">
-        <v>59</v>
-      </c>
-      <c r="D128" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4">
-      <c r="A129" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B129" t="s">
-        <v>206</v>
-      </c>
-      <c r="C129" s="2">
-        <v>60</v>
-      </c>
-      <c r="D129" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4">
-      <c r="A130" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B130" t="s">
-        <v>208</v>
-      </c>
-      <c r="C130" s="2">
-        <v>61</v>
-      </c>
-      <c r="D130" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4">
-      <c r="A131" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B131" t="s">
-        <v>210</v>
-      </c>
-      <c r="C131" s="2">
-        <v>62</v>
-      </c>
-      <c r="D131" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4">
-      <c r="A132" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B132" t="s">
-        <v>212</v>
-      </c>
-      <c r="C132" s="2">
-        <v>63</v>
-      </c>
-      <c r="D132" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4">
-      <c r="A133" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B133" t="s">
-        <v>214</v>
-      </c>
-      <c r="C133" s="2">
-        <v>64</v>
-      </c>
-      <c r="D133" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4">
-      <c r="A134" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B134" t="s">
-        <v>216</v>
-      </c>
-      <c r="C134" s="2">
-        <v>65</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4">
-      <c r="A135" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B135" t="s">
-        <v>218</v>
-      </c>
-      <c r="C135" s="2">
-        <v>66</v>
-      </c>
-      <c r="D135" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4">
-      <c r="A136" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B136" t="s">
-        <v>220</v>
-      </c>
-      <c r="C136" s="2">
-        <v>67</v>
-      </c>
-      <c r="D136" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4">
-      <c r="A137" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B137" t="s">
-        <v>222</v>
-      </c>
-      <c r="C137" s="2">
-        <v>68</v>
-      </c>
-      <c r="D137" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4">
-      <c r="A138" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B138" t="s">
-        <v>224</v>
-      </c>
-      <c r="C138" s="2">
-        <v>69</v>
-      </c>
-      <c r="D138" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4">
-      <c r="A139" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B139" t="s">
-        <v>226</v>
-      </c>
-      <c r="C139" s="2">
-        <v>70</v>
-      </c>
-      <c r="D139" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4">
-      <c r="A140" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C140" s="2">
-        <v>71</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4">
-      <c r="A141" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C141" s="2">
-        <v>72</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4">
-      <c r="A142" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B142" t="s">
-        <v>232</v>
-      </c>
-      <c r="C142" s="2">
-        <v>73</v>
-      </c>
-      <c r="D142" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4">
-      <c r="A143" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B143" t="s">
-        <v>234</v>
-      </c>
-      <c r="C143" s="2">
-        <v>74</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4">
-      <c r="A144" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B144" t="s">
-        <v>236</v>
-      </c>
-      <c r="C144" s="2">
-        <v>75</v>
-      </c>
-      <c r="D144" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4">
-      <c r="A145" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B145" t="s">
-        <v>238</v>
-      </c>
-      <c r="C145" s="2">
-        <v>76</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4">
-      <c r="A146" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B146" t="s">
-        <v>240</v>
-      </c>
-      <c r="C146" s="2">
-        <v>77</v>
-      </c>
-      <c r="D146" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4">
-      <c r="A147" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B147" t="s">
-        <v>242</v>
-      </c>
-      <c r="C147" s="2">
-        <v>78</v>
-      </c>
-      <c r="D147" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4">
-      <c r="A148" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B148" t="s">
-        <v>244</v>
-      </c>
-      <c r="C148" s="2">
-        <v>79</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4">
-      <c r="A149" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B149" t="s">
-        <v>246</v>
-      </c>
-      <c r="C149" s="2">
-        <v>80</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4">
-      <c r="A150" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B150" t="s">
-        <v>248</v>
-      </c>
-      <c r="C150" s="2">
-        <v>81</v>
-      </c>
-      <c r="D150" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4">
-      <c r="A151" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B151" t="s">
-        <v>250</v>
-      </c>
-      <c r="C151" s="2">
-        <v>82</v>
-      </c>
-      <c r="D151" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4">
-      <c r="A152" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C152" s="2">
-        <v>83</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4">
-      <c r="A153" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B153" t="s">
-        <v>254</v>
-      </c>
-      <c r="C153" s="2">
-        <v>84</v>
-      </c>
-      <c r="D153" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4">
-      <c r="A154" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B154" t="s">
-        <v>256</v>
-      </c>
-      <c r="C154" s="2">
-        <v>85</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4">
-      <c r="A155" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B155" t="s">
-        <v>258</v>
-      </c>
-      <c r="C155" s="2">
-        <v>86</v>
-      </c>
-      <c r="D155" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4">
-      <c r="A156" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B156" t="s">
-        <v>260</v>
-      </c>
-      <c r="C156" s="2">
-        <v>87</v>
-      </c>
-      <c r="D156" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4">
-      <c r="A157" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B157" t="s">
-        <v>262</v>
-      </c>
-      <c r="C157" s="2">
-        <v>88</v>
-      </c>
-      <c r="D157" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4">
-      <c r="A158" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C158" s="2">
-        <v>89</v>
-      </c>
-      <c r="D158" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4">
-      <c r="A159" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="C159" s="2">
-        <v>90</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4">
-      <c r="A160" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B160" t="s">
-        <v>268</v>
-      </c>
-      <c r="C160" s="2">
-        <v>91</v>
-      </c>
-      <c r="D160" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5">
-      <c r="A161" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="C161" s="2">
-        <v>92</v>
-      </c>
-      <c r="D161" t="s">
-        <v>271</v>
-      </c>
-      <c r="E161"/>
-    </row>
-    <row r="162" spans="1:5">
-      <c r="A162" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B162" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="C162" s="2">
-        <v>93</v>
-      </c>
-      <c r="D162" t="s">
-        <v>273</v>
-      </c>
-      <c r="E162"/>
-    </row>
-    <row r="163" spans="1:5">
-      <c r="A163" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B163" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C163" s="2">
-        <v>94</v>
-      </c>
-      <c r="D163" t="s">
-        <v>275</v>
-      </c>
-      <c r="E163"/>
-    </row>
-    <row r="164" spans="1:5">
-      <c r="A164" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="C164" s="2">
-        <v>95</v>
-      </c>
-      <c r="D164" t="s">
-        <v>277</v>
-      </c>
-      <c r="E164"/>
-    </row>
-    <row r="165" spans="1:5">
-      <c r="A165" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B165" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C165" s="2">
-        <v>96</v>
-      </c>
-      <c r="D165" t="s">
-        <v>279</v>
-      </c>
-      <c r="E165"/>
-    </row>
-    <row r="166" spans="1:5">
-      <c r="A166" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B166" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C166" s="2">
-        <v>97</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="E166"/>
-    </row>
-    <row r="167" spans="1:5">
-      <c r="A167" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C167" s="2">
-        <v>98</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E167"/>
-    </row>
-    <row r="168" spans="1:5">
-      <c r="A168" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C168" s="2">
-        <v>99</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E168"/>
-    </row>
-    <row r="169" spans="1:5">
-      <c r="A169" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B169" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C169" s="2">
-        <v>100</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E169"/>
-    </row>
-    <row r="170" spans="1:5">
-      <c r="A170" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C170" s="2">
-        <v>101</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="E170"/>
-    </row>
-    <row r="171" spans="1:5">
-      <c r="A171" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B171" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="C171" s="2">
-        <v>102</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E171"/>
-    </row>
-    <row r="172" spans="1:5">
-      <c r="A172" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="C172" s="2">
-        <v>103</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E172"/>
-    </row>
-    <row r="173" spans="1:5">
-      <c r="A173" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B173" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C173" s="2">
-        <v>104</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="E173"/>
-    </row>
-    <row r="174" spans="1:5">
-      <c r="A174" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C174" s="2">
-        <v>105</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E174"/>
-    </row>
-    <row r="175" spans="1:5">
-      <c r="A175" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C175" s="2">
-        <v>106</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="E175"/>
-    </row>
-    <row r="176" spans="1:5">
-      <c r="A176" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C176" s="2">
-        <v>107</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="E176"/>
-    </row>
-    <row r="177" spans="1:5">
-      <c r="A177" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B177" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C177" s="2">
-        <v>108</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E177"/>
-    </row>
-    <row r="178" spans="1:5">
-      <c r="A178" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B178" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C178" s="2">
-        <v>109</v>
-      </c>
-      <c r="D178" t="s">
-        <v>305</v>
-      </c>
-      <c r="E178"/>
-    </row>
-    <row r="179" spans="1:5">
-      <c r="A179" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C179" s="2">
-        <v>110</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="E179"/>
-    </row>
-    <row r="180" spans="1:5">
-      <c r="A180" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C180" s="2">
-        <v>111</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E180"/>
-    </row>
-    <row r="181" spans="1:5">
-      <c r="A181" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B181" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C181" s="2">
-        <v>112</v>
-      </c>
-      <c r="D181" t="s">
-        <v>311</v>
-      </c>
-      <c r="E181"/>
-    </row>
-    <row r="182" spans="1:5">
-      <c r="A182" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B182" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C182" s="2">
-        <v>113</v>
-      </c>
-      <c r="D182" t="s">
-        <v>313</v>
-      </c>
-      <c r="E182"/>
-    </row>
-    <row r="183" spans="1:5">
-      <c r="A183" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B183" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C183" s="2">
-        <v>114</v>
-      </c>
-      <c r="D183" t="s">
-        <v>315</v>
-      </c>
-      <c r="E183"/>
-    </row>
-    <row r="184" spans="1:5">
-      <c r="A184" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B184" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C184" s="2">
-        <v>115</v>
-      </c>
-      <c r="D184" t="s">
-        <v>317</v>
-      </c>
-      <c r="E184"/>
-    </row>
-    <row r="185" spans="1:5">
-      <c r="A185" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B185" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C185" s="2">
-        <v>116</v>
-      </c>
-      <c r="D185" t="s">
-        <v>319</v>
-      </c>
-      <c r="E185"/>
-    </row>
-    <row r="186" spans="1:5">
-      <c r="A186" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B186" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C186" s="2">
-        <v>117</v>
-      </c>
-      <c r="D186" t="s">
-        <v>321</v>
-      </c>
-      <c r="E186"/>
-    </row>
-    <row r="187" spans="1:5">
-      <c r="A187" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B187" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C187" s="2">
-        <v>118</v>
-      </c>
-      <c r="D187" t="s">
-        <v>323</v>
-      </c>
-      <c r="E187"/>
-    </row>
-    <row r="188" spans="1:5">
-      <c r="A188" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B188" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="C188" s="2">
-        <v>119</v>
-      </c>
-      <c r="D188" t="s">
-        <v>325</v>
-      </c>
-      <c r="E188"/>
-    </row>
-    <row r="189" spans="1:5">
-      <c r="A189" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="C189" s="2">
-        <v>120</v>
-      </c>
-      <c r="D189" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5">
-      <c r="A190" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B190" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C190" s="2">
-        <v>121</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5">
-      <c r="A191" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B191" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="C191" s="2">
-        <v>122</v>
-      </c>
-      <c r="D191" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5">
-      <c r="A192" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B192" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="C192" s="2">
-        <v>123</v>
-      </c>
-      <c r="D192" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4">
-      <c r="A193" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B193" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="C193" s="2">
-        <v>124</v>
-      </c>
-      <c r="D193" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4">
-      <c r="A194" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B194" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="C194" s="2">
-        <v>125</v>
-      </c>
-      <c r="D194" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4">
-      <c r="A195" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B195" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="C195" s="2">
-        <v>126</v>
-      </c>
-      <c r="D195" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4">
-      <c r="A196" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B196" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="C196" s="2">
-        <v>127</v>
-      </c>
-      <c r="D196" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4">
-      <c r="A197" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B197" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="C197" s="2">
-        <v>128</v>
-      </c>
-      <c r="D197" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4">
-      <c r="A198" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B198" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="C198" s="2">
-        <v>129</v>
-      </c>
-      <c r="D198" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4">
-      <c r="A199" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B199" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="C199" s="2">
-        <v>130</v>
-      </c>
-      <c r="D199" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4">
-      <c r="A200" t="s">
-        <v>92</v>
-      </c>
-      <c r="B200" t="s">
-        <v>348</v>
-      </c>
-      <c r="C200">
-        <v>131</v>
-      </c>
-      <c r="D200" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4">
-      <c r="A201" t="s">
-        <v>92</v>
-      </c>
-      <c r="B201" t="s">
-        <v>350</v>
-      </c>
-      <c r="C201">
-        <v>132</v>
-      </c>
-      <c r="D201" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4">
-      <c r="A202" t="s">
-        <v>92</v>
-      </c>
-      <c r="B202" t="s">
-        <v>352</v>
-      </c>
-      <c r="C202">
-        <v>133</v>
-      </c>
-      <c r="D202" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4">
-      <c r="A203" t="s">
-        <v>92</v>
-      </c>
-      <c r="B203" t="s">
-        <v>354</v>
-      </c>
-      <c r="C203">
-        <v>134</v>
-      </c>
-      <c r="D203" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4">
-      <c r="A204" t="s">
-        <v>92</v>
-      </c>
-      <c r="B204" t="s">
-        <v>356</v>
-      </c>
-      <c r="C204">
-        <v>135</v>
-      </c>
-      <c r="D204" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4">
-      <c r="A205" t="s">
-        <v>92</v>
-      </c>
-      <c r="B205" t="s">
-        <v>358</v>
-      </c>
-      <c r="C205">
-        <v>136</v>
-      </c>
-      <c r="D205" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4">
-      <c r="A206" t="s">
-        <v>92</v>
-      </c>
-      <c r="B206" t="s">
-        <v>360</v>
-      </c>
-      <c r="C206">
-        <v>137</v>
-      </c>
-      <c r="D206" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4">
-      <c r="A207" t="s">
-        <v>92</v>
-      </c>
-      <c r="B207" t="s">
-        <v>362</v>
-      </c>
-      <c r="C207">
-        <v>138</v>
-      </c>
-      <c r="D207" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4">
-      <c r="A208" t="s">
-        <v>92</v>
-      </c>
-      <c r="B208" t="s">
-        <v>364</v>
-      </c>
-      <c r="C208">
-        <v>139</v>
-      </c>
-      <c r="D208" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4">
-      <c r="A209" t="s">
-        <v>92</v>
-      </c>
-      <c r="B209" t="s">
-        <v>366</v>
-      </c>
-      <c r="C209">
-        <v>140</v>
-      </c>
-      <c r="D209" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4">
-      <c r="A210" t="s">
-        <v>92</v>
-      </c>
-      <c r="B210" t="s">
-        <v>368</v>
-      </c>
-      <c r="C210">
-        <v>141</v>
-      </c>
-      <c r="D210" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4">
-      <c r="A211" t="s">
-        <v>92</v>
-      </c>
-      <c r="B211" t="s">
-        <v>370</v>
-      </c>
-      <c r="C211">
-        <v>142</v>
-      </c>
-      <c r="D211" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4">
-      <c r="A212" t="s">
-        <v>92</v>
-      </c>
-      <c r="B212" t="s">
-        <v>372</v>
-      </c>
-      <c r="C212">
-        <v>143</v>
-      </c>
-      <c r="D212" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4">
-      <c r="A213" t="s">
-        <v>92</v>
-      </c>
-      <c r="B213" t="s">
-        <v>374</v>
-      </c>
-      <c r="C213">
-        <v>144</v>
-      </c>
-      <c r="D213" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4">
-      <c r="A214" t="s">
-        <v>92</v>
-      </c>
-      <c r="B214" t="s">
-        <v>376</v>
-      </c>
-      <c r="C214">
-        <v>145</v>
-      </c>
-      <c r="D214" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4">
-      <c r="A215" t="s">
-        <v>92</v>
-      </c>
-      <c r="B215" t="s">
-        <v>378</v>
-      </c>
-      <c r="C215">
-        <v>146</v>
-      </c>
-      <c r="D215" t="s">
+      <c r="D218" s="8" t="s">
         <v>379</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4">
-      <c r="A216" t="s">
-        <v>92</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="C216">
-        <v>147</v>
-      </c>
-      <c r="D216" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4">
-      <c r="A217" t="s">
-        <v>92</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="C217">
-        <v>148</v>
-      </c>
-      <c r="D217" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4">
-      <c r="A218" t="s">
-        <v>92</v>
-      </c>
-      <c r="B218" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="C218">
-        <v>149</v>
-      </c>
-      <c r="D218" s="5" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>92</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="C219">
-        <v>150</v>
-      </c>
-      <c r="D219" s="5" t="s">
-        <v>387</v>
+        <v>124</v>
+      </c>
+      <c r="B219" t="s">
+        <v>380</v>
+      </c>
+      <c r="C219" s="4">
+        <v>131</v>
+      </c>
+      <c r="D219" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>92</v>
-      </c>
-      <c r="B220" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B220" t="s">
+        <v>382</v>
+      </c>
+      <c r="C220" s="4">
+        <v>132</v>
+      </c>
+      <c r="D220" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" t="s">
+        <v>124</v>
+      </c>
+      <c r="B221" t="s">
+        <v>384</v>
+      </c>
+      <c r="C221" s="4">
+        <v>133</v>
+      </c>
+      <c r="D221" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" t="s">
+        <v>124</v>
+      </c>
+      <c r="B222" t="s">
+        <v>386</v>
+      </c>
+      <c r="C222" s="4">
+        <v>134</v>
+      </c>
+      <c r="D222" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" t="s">
+        <v>124</v>
+      </c>
+      <c r="B223" t="s">
         <v>388</v>
       </c>
-      <c r="C220">
+      <c r="C223" s="4">
+        <v>135</v>
+      </c>
+      <c r="D223" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" t="s">
+        <v>124</v>
+      </c>
+      <c r="B224" t="s">
+        <v>390</v>
+      </c>
+      <c r="C224" s="4">
+        <v>136</v>
+      </c>
+      <c r="D224" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" t="s">
+        <v>124</v>
+      </c>
+      <c r="B225" t="s">
+        <v>392</v>
+      </c>
+      <c r="C225" s="4">
+        <v>137</v>
+      </c>
+      <c r="D225" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" t="s">
+        <v>124</v>
+      </c>
+      <c r="B226" t="s">
+        <v>394</v>
+      </c>
+      <c r="C226" s="4">
+        <v>138</v>
+      </c>
+      <c r="D226" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" t="s">
+        <v>124</v>
+      </c>
+      <c r="B227" t="s">
+        <v>396</v>
+      </c>
+      <c r="C227" s="4">
+        <v>139</v>
+      </c>
+      <c r="D227" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" t="s">
+        <v>124</v>
+      </c>
+      <c r="B228" t="s">
+        <v>398</v>
+      </c>
+      <c r="C228" s="4">
+        <v>140</v>
+      </c>
+      <c r="D228" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" t="s">
+        <v>124</v>
+      </c>
+      <c r="B229" t="s">
+        <v>400</v>
+      </c>
+      <c r="C229" s="4">
+        <v>141</v>
+      </c>
+      <c r="D229" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" t="s">
+        <v>124</v>
+      </c>
+      <c r="B230" t="s">
+        <v>402</v>
+      </c>
+      <c r="C230" s="4">
+        <v>142</v>
+      </c>
+      <c r="D230" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" t="s">
+        <v>124</v>
+      </c>
+      <c r="B231" t="s">
+        <v>404</v>
+      </c>
+      <c r="C231" s="4">
+        <v>143</v>
+      </c>
+      <c r="D231" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" t="s">
+        <v>124</v>
+      </c>
+      <c r="B232" t="s">
+        <v>406</v>
+      </c>
+      <c r="C232" s="4">
+        <v>144</v>
+      </c>
+      <c r="D232" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" t="s">
+        <v>124</v>
+      </c>
+      <c r="B233" t="s">
+        <v>408</v>
+      </c>
+      <c r="C233" s="4">
+        <v>145</v>
+      </c>
+      <c r="D233" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" t="s">
+        <v>124</v>
+      </c>
+      <c r="B234" t="s">
+        <v>410</v>
+      </c>
+      <c r="C234" s="4">
+        <v>146</v>
+      </c>
+      <c r="D234" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" t="s">
+        <v>124</v>
+      </c>
+      <c r="B235" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="C235" s="4">
+        <v>147</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" t="s">
+        <v>124</v>
+      </c>
+      <c r="B236" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="C236" s="4">
+        <v>148</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" t="s">
+        <v>124</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="C237" s="4">
+        <v>149</v>
+      </c>
+      <c r="D237" s="10" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" t="s">
+        <v>124</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C238" s="4">
+        <v>150</v>
+      </c>
+      <c r="D238" s="10" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" t="s">
+        <v>124</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C239" s="4">
         <v>151</v>
       </c>
-      <c r="D220" s="5" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4">
-      <c r="B221"/>
-      <c r="D221"/>
-    </row>
-    <row r="222" spans="1:4">
-      <c r="B222"/>
-      <c r="D222"/>
-    </row>
-    <row r="223" spans="1:4">
-      <c r="B223"/>
-      <c r="D223"/>
-    </row>
-    <row r="224" spans="1:4">
-      <c r="B224"/>
-      <c r="D224"/>
-    </row>
-    <row r="225" spans="1:4">
-      <c r="A225" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B225" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="C225" s="2">
-        <v>1111</v>
-      </c>
-      <c r="D225"/>
-    </row>
-    <row r="226" spans="1:4">
-      <c r="A226" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B226" t="s">
-        <v>391</v>
-      </c>
-      <c r="C226" s="2">
-        <v>1112</v>
-      </c>
-      <c r="D226"/>
-    </row>
-    <row r="227" spans="1:4">
-      <c r="A227" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B227" t="s">
-        <v>392</v>
-      </c>
-      <c r="C227" s="2">
-        <v>1113</v>
-      </c>
-      <c r="D227"/>
-    </row>
-    <row r="228" spans="1:4">
-      <c r="B228"/>
-      <c r="D228"/>
-    </row>
-    <row r="229" spans="1:4">
-      <c r="B229"/>
-      <c r="D229"/>
-    </row>
-    <row r="230" spans="1:4">
-      <c r="B230"/>
-      <c r="D230"/>
-    </row>
-    <row r="231" spans="1:4">
-      <c r="B231"/>
-      <c r="D231"/>
-    </row>
-    <row r="232" spans="1:4">
-      <c r="B232"/>
-      <c r="D232"/>
-    </row>
-    <row r="233" spans="1:4">
-      <c r="B233"/>
-      <c r="D233"/>
-    </row>
-    <row r="234" spans="1:4">
-      <c r="B234"/>
-      <c r="D234"/>
-    </row>
-    <row r="235" spans="1:4">
-      <c r="B235"/>
-      <c r="D235"/>
-    </row>
-    <row r="236" spans="1:4">
-      <c r="B236"/>
-      <c r="D236"/>
-    </row>
-    <row r="237" spans="1:4">
-      <c r="B237"/>
-      <c r="D237"/>
-    </row>
-    <row r="238" spans="1:4">
-      <c r="B238"/>
-      <c r="D238"/>
-    </row>
-    <row r="239" spans="1:4">
-      <c r="B239"/>
-      <c r="D239"/>
+      <c r="D239" s="10" t="s">
+        <v>421</v>
+      </c>
     </row>
     <row r="240" spans="1:4">
       <c r="B240"/>
@@ -5176,249 +5402,349 @@
       <c r="D243"/>
     </row>
     <row r="244" spans="1:4">
-      <c r="B244"/>
+      <c r="A244" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B244" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="C244" s="4">
+        <v>1111</v>
+      </c>
       <c r="D244"/>
     </row>
     <row r="245" spans="1:4">
-      <c r="B245"/>
+      <c r="A245" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B245" t="s">
+        <v>423</v>
+      </c>
+      <c r="C245" s="4">
+        <v>1112</v>
+      </c>
       <c r="D245"/>
     </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B246" t="s">
+        <v>424</v>
+      </c>
+      <c r="C246" s="4">
+        <v>1113</v>
+      </c>
+      <c r="D246"/>
+    </row>
     <row r="247" spans="1:4">
-      <c r="A247" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="C247" s="2">
+      <c r="B247"/>
+      <c r="D247"/>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="B248"/>
+      <c r="D248"/>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="B249"/>
+      <c r="D249"/>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="B250"/>
+      <c r="D250"/>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="B251"/>
+      <c r="D251"/>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="B252"/>
+      <c r="D252"/>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="B253"/>
+      <c r="D253"/>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="B254"/>
+      <c r="D254"/>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="B255"/>
+      <c r="D255"/>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="B256"/>
+      <c r="D256"/>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="B257"/>
+      <c r="D257"/>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="B258"/>
+      <c r="D258"/>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="B259"/>
+      <c r="D259"/>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="B260"/>
+      <c r="D260"/>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="B261"/>
+      <c r="D261"/>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="B262"/>
+      <c r="D262"/>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="B263"/>
+      <c r="D263"/>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="B264"/>
+      <c r="D264"/>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C266" s="4">
         <v>1</v>
       </c>
-      <c r="D247" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4">
-      <c r="A248" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="C248" s="2">
+      <c r="D266" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C267" s="4">
         <v>2</v>
       </c>
-      <c r="D248" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4">
-      <c r="A249" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="C249" s="2">
+      <c r="D267" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B268" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C268" s="4">
         <v>3</v>
       </c>
-      <c r="D249" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4">
-      <c r="A250" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B250" s="2" t="s">
+      <c r="D268" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B269" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C250" s="2">
+      <c r="C269" s="4">
         <v>4</v>
       </c>
-      <c r="D250" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4">
-      <c r="A251" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="C251" s="2">
+      <c r="D269" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B270" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C270" s="4">
         <v>5</v>
       </c>
-      <c r="D251" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4">
-      <c r="A252" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C252" s="2">
+      <c r="D270" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B271" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="C271" s="4">
         <v>6</v>
       </c>
-      <c r="D252" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4">
-      <c r="A253" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="C253" s="2">
+      <c r="D271" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B272" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C272" s="4">
         <v>7</v>
       </c>
-      <c r="D253" s="1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="254" spans="1:4">
-      <c r="A254" t="s">
-        <v>393</v>
-      </c>
-      <c r="B254" t="s">
+      <c r="D272" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" t="s">
+        <v>425</v>
+      </c>
+      <c r="B273" t="s">
         <v>15</v>
       </c>
-      <c r="C254">
+      <c r="C273" s="4">
         <v>8</v>
       </c>
-      <c r="D254" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4">
-      <c r="A255" t="s">
-        <v>393</v>
-      </c>
-      <c r="B255" t="s">
-        <v>407</v>
-      </c>
-      <c r="C255">
+      <c r="D273" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" t="s">
+        <v>425</v>
+      </c>
+      <c r="B274" t="s">
+        <v>439</v>
+      </c>
+      <c r="C274" s="4">
         <v>9</v>
       </c>
-      <c r="D255" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4">
-      <c r="A256" t="s">
-        <v>393</v>
-      </c>
-      <c r="B256" t="s">
-        <v>409</v>
-      </c>
-      <c r="C256">
+      <c r="D274" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" t="s">
+        <v>425</v>
+      </c>
+      <c r="B275" t="s">
+        <v>441</v>
+      </c>
+      <c r="C275" s="4">
         <v>10</v>
       </c>
-      <c r="D256" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4">
-      <c r="A257" t="s">
-        <v>393</v>
-      </c>
-      <c r="B257" t="s">
-        <v>411</v>
-      </c>
-      <c r="C257">
+      <c r="D275" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" t="s">
+        <v>425</v>
+      </c>
+      <c r="B276" t="s">
+        <v>443</v>
+      </c>
+      <c r="C276" s="4">
         <v>11</v>
       </c>
-      <c r="D257" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4">
-      <c r="A258" t="s">
-        <v>413</v>
-      </c>
-      <c r="B258" t="s">
-        <v>414</v>
-      </c>
-      <c r="C258">
+      <c r="D276" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" t="s">
+        <v>445</v>
+      </c>
+      <c r="B277" t="s">
+        <v>446</v>
+      </c>
+      <c r="C277" s="4">
         <v>1</v>
       </c>
-      <c r="D258" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4">
-      <c r="A259" t="s">
-        <v>413</v>
-      </c>
-      <c r="B259" t="s">
-        <v>416</v>
-      </c>
-      <c r="C259">
+      <c r="D277" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" t="s">
+        <v>445</v>
+      </c>
+      <c r="B278" t="s">
+        <v>448</v>
+      </c>
+      <c r="C278" s="4">
         <v>2</v>
       </c>
-      <c r="D259" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4">
-      <c r="A260" t="s">
-        <v>413</v>
-      </c>
-      <c r="B260" t="s">
-        <v>418</v>
-      </c>
-      <c r="C260">
+      <c r="D278" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" t="s">
+        <v>445</v>
+      </c>
+      <c r="B279" t="s">
+        <v>450</v>
+      </c>
+      <c r="C279" s="4">
         <v>3</v>
       </c>
-      <c r="D260" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4">
-      <c r="A261" t="s">
-        <v>420</v>
-      </c>
-      <c r="B261" t="s">
-        <v>421</v>
-      </c>
-      <c r="C261">
+      <c r="D279" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" t="s">
+        <v>452</v>
+      </c>
+      <c r="B280" t="s">
+        <v>453</v>
+      </c>
+      <c r="C280" s="4">
         <v>1</v>
       </c>
-      <c r="D261" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="262" spans="1:4">
-      <c r="A262" t="s">
-        <v>420</v>
-      </c>
-      <c r="B262" t="s">
-        <v>423</v>
-      </c>
-      <c r="C262">
+      <c r="D280" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" t="s">
+        <v>452</v>
+      </c>
+      <c r="B281" t="s">
+        <v>455</v>
+      </c>
+      <c r="C281" s="4">
         <v>2</v>
       </c>
-      <c r="D262" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4">
-      <c r="A263" t="s">
-        <v>420</v>
-      </c>
-      <c r="B263" t="s">
-        <v>425</v>
-      </c>
-      <c r="C263">
+      <c r="D281" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" t="s">
+        <v>452</v>
+      </c>
+      <c r="B282" t="s">
+        <v>457</v>
+      </c>
+      <c r="C282" s="4">
         <v>3</v>
       </c>
-      <c r="D263" t="s">
-        <v>426</v>
+      <c r="D282" t="s">
+        <v>458</v>
       </c>
     </row>
   </sheetData>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="13695" windowHeight="11505"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="469">
   <si>
     <t>Enum</t>
   </si>
@@ -181,7 +181,7 @@
     <t>Edge</t>
   </si>
   <si>
-    <t>本局内你的随机一种遗物将失效</t>
+    <t>本局内你的随机一种圣物将失效</t>
   </si>
   <si>
     <t>AllIn</t>
@@ -199,7 +199,7 @@
     <t>CoupletDamage</t>
   </si>
   <si>
-    <t>同花顺牌型在攻击时,伤害降低</t>
+    <t>对子牌型在攻击时,伤害降低</t>
   </si>
   <si>
     <t>StraightDamage</t>
@@ -247,7 +247,7 @@
     <t>RelicDisable</t>
   </si>
   <si>
-    <t>每回合随机失效玩家的收藏品</t>
+    <t>每回合随机失效玩家的圣物</t>
   </si>
   <si>
     <t>GoldThorn</t>
@@ -406,6 +406,36 @@
     <t>本关内敌人攻击玩家时,按造成伤害的50%回复自身生命值</t>
   </si>
   <si>
+    <t>DisableHeartUesd</t>
+  </si>
+  <si>
+    <t>本局亮牌时,红心花色失效</t>
+  </si>
+  <si>
+    <t>DisableSpadeUesd</t>
+  </si>
+  <si>
+    <t>本局亮牌时,黑桃色失效</t>
+  </si>
+  <si>
+    <t>DisableDiamonUesdd</t>
+  </si>
+  <si>
+    <t>本局亮牌时,方片花色失效</t>
+  </si>
+  <si>
+    <t>DisablePlumBlossomUesd</t>
+  </si>
+  <si>
+    <t>本局亮牌时,梅花花色失效</t>
+  </si>
+  <si>
+    <t>DisableHeadUesd</t>
+  </si>
+  <si>
+    <t>本局亮牌时,人头牌失效</t>
+  </si>
+  <si>
     <t>MechanismType</t>
   </si>
   <si>
@@ -787,7 +817,7 @@
     <t>KillAfterSellingPrice</t>
   </si>
   <si>
-    <t>击杀敌人,收藏品出售价格提高</t>
+    <t>击杀敌人,圣物出售价格提高</t>
   </si>
   <si>
     <t>EveryCardAttackForever</t>
@@ -829,7 +859,7 @@
     <t>EveryRelic</t>
   </si>
   <si>
-    <t>每有1个收藏品,结算时提供倍率</t>
+    <t>每有1个圣物,结算时提供倍率</t>
   </si>
   <si>
     <t>NoUseRubbingEveryRubbingNum</t>
@@ -865,7 +895,7 @@
     <t>RubbingCardRelic</t>
   </si>
   <si>
-    <t>每使用1次搓牌,结算时该收藏品永久提供倍率</t>
+    <t>每使用1次搓牌,结算时该圣物永久提供倍率</t>
   </si>
   <si>
     <t>SpecialSevenCardPro</t>
@@ -919,13 +949,13 @@
     <t>EpicLegendRelicProUp</t>
   </si>
   <si>
-    <t>史诗/传说的收藏品概率提高</t>
+    <t>史诗/传说的圣物概率提高</t>
   </si>
   <si>
     <t>RelicPricePer</t>
   </si>
   <si>
-    <t>收藏品价格百分比</t>
+    <t>圣物价格百分比</t>
   </si>
   <si>
     <t>GetGoldAfterLevel</t>
@@ -2024,39 +2054,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2406,25 +2412,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:E282"/>
+  <dimension ref="A4:E288"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="16.7416666666667" style="3" customWidth="1"/>
-    <col min="2" max="2" width="18.7" style="3" customWidth="1"/>
-    <col min="3" max="3" width="7.05833333333333" style="4" customWidth="1"/>
-    <col min="4" max="4" width="31.625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="34.75" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="3" customWidth="1"/>
+    <col min="1" max="1" width="16.7416666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.05833333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="31.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="34.75" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="1:4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
@@ -2432,142 +2438,142 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <v>2</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="2">
         <v>1</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="2">
         <v>2</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="2">
         <v>4</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="2">
         <v>3</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="2">
         <v>5</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="2">
         <v>6</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="2">
         <v>1</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="2">
         <v>2</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2575,13 +2581,13 @@
       <c r="A19" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="2">
         <v>1</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="1" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2589,13 +2595,13 @@
       <c r="A20" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="2">
         <v>2</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2603,13 +2609,13 @@
       <c r="A21" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="2">
         <v>3</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2617,24 +2623,24 @@
       <c r="A22" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="2">
         <v>4</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B39" t="s">
         <v>36</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="2">
         <v>1</v>
       </c>
       <c r="D39" t="s">
@@ -2642,13 +2648,13 @@
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="2">
         <v>2</v>
       </c>
       <c r="D40" t="s">
@@ -2656,13 +2662,13 @@
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="2">
         <v>3</v>
       </c>
       <c r="D41" t="s">
@@ -2670,13 +2676,13 @@
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="2">
         <v>4</v>
       </c>
       <c r="D42" t="s">
@@ -2684,13 +2690,13 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="2">
         <v>5</v>
       </c>
       <c r="D43" t="s">
@@ -2698,86 +2704,86 @@
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="2">
         <v>6</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="2">
         <v>7</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="2">
         <v>8</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="2">
         <v>9</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="2">
         <v>10</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="2">
         <v>11</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" s="1" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2788,7 +2794,7 @@
       <c r="B50" t="s">
         <v>58</v>
       </c>
-      <c r="C50" s="4">
+      <c r="C50" s="2">
         <v>12</v>
       </c>
       <c r="D50" t="s">
@@ -2802,7 +2808,7 @@
       <c r="B51" t="s">
         <v>60</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C51" s="2">
         <v>13</v>
       </c>
       <c r="D51" t="s">
@@ -2816,7 +2822,7 @@
       <c r="B52" t="s">
         <v>62</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="2">
         <v>14</v>
       </c>
       <c r="D52" t="s">
@@ -2830,7 +2836,7 @@
       <c r="B53" t="s">
         <v>64</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="2">
         <v>15</v>
       </c>
       <c r="D53" t="s">
@@ -2844,7 +2850,7 @@
       <c r="B54" t="s">
         <v>66</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54" s="2">
         <v>16</v>
       </c>
       <c r="D54" t="s">
@@ -2858,7 +2864,7 @@
       <c r="B55" t="s">
         <v>68</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="2">
         <v>17</v>
       </c>
       <c r="D55" t="s">
@@ -2872,7 +2878,7 @@
       <c r="B56" t="s">
         <v>70</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="2">
         <v>18</v>
       </c>
       <c r="D56" t="s">
@@ -2886,7 +2892,7 @@
       <c r="B57" t="s">
         <v>72</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C57" s="2">
         <v>19</v>
       </c>
       <c r="D57" t="s">
@@ -2900,7 +2906,7 @@
       <c r="B58" t="s">
         <v>74</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="2">
         <v>20</v>
       </c>
       <c r="D58" t="s">
@@ -2914,7 +2920,7 @@
       <c r="B59" t="s">
         <v>76</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59" s="2">
         <v>21</v>
       </c>
       <c r="D59" t="s">
@@ -2928,7 +2934,7 @@
       <c r="B60" t="s">
         <v>78</v>
       </c>
-      <c r="C60" s="4">
+      <c r="C60" s="2">
         <v>22</v>
       </c>
       <c r="D60" t="s">
@@ -2942,7 +2948,7 @@
       <c r="B61" t="s">
         <v>80</v>
       </c>
-      <c r="C61" s="4">
+      <c r="C61" s="2">
         <v>23</v>
       </c>
       <c r="D61" t="s">
@@ -2956,7 +2962,7 @@
       <c r="B62" t="s">
         <v>82</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C62" s="2">
         <v>24</v>
       </c>
       <c r="D62" t="s">
@@ -2970,7 +2976,7 @@
       <c r="B63" t="s">
         <v>84</v>
       </c>
-      <c r="C63" s="4">
+      <c r="C63" s="2">
         <v>25</v>
       </c>
       <c r="D63" t="s">
@@ -2984,7 +2990,7 @@
       <c r="B64" t="s">
         <v>86</v>
       </c>
-      <c r="C64" s="4">
+      <c r="C64" s="2">
         <v>26</v>
       </c>
       <c r="D64" t="s">
@@ -2998,7 +3004,7 @@
       <c r="B65" t="s">
         <v>88</v>
       </c>
-      <c r="C65" s="4">
+      <c r="C65" s="2">
         <v>27</v>
       </c>
       <c r="D65" t="s">
@@ -3012,7 +3018,7 @@
       <c r="B66" t="s">
         <v>90</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C66" s="2">
         <v>28</v>
       </c>
       <c r="D66" t="s">
@@ -3020,2421 +3026,2449 @@
       </c>
     </row>
     <row r="67" s="1" customFormat="1" spans="1:4">
-      <c r="A67" s="5" t="s">
+      <c r="A67" t="s">
         <v>35</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" t="s">
         <v>92</v>
       </c>
-      <c r="C67" s="7">
+      <c r="C67" s="2">
         <v>29</v>
       </c>
-      <c r="D67" s="6" t="s">
+      <c r="D67" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" spans="1:4">
-      <c r="A68" s="5" t="s">
+      <c r="A68" t="s">
         <v>35</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" t="s">
         <v>94</v>
       </c>
-      <c r="C68" s="7">
+      <c r="C68" s="2">
         <v>30</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="D68" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" spans="1:4">
-      <c r="A69" s="5" t="s">
+      <c r="A69" t="s">
         <v>35</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" t="s">
         <v>96</v>
       </c>
-      <c r="C69" s="7">
+      <c r="C69" s="2">
         <v>31</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D69" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" spans="1:4">
-      <c r="A70" s="5" t="s">
+      <c r="A70" t="s">
         <v>35</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" t="s">
         <v>98</v>
       </c>
-      <c r="C70" s="7">
+      <c r="C70" s="2">
         <v>32</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D70" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" spans="1:4">
-      <c r="A71" s="5" t="s">
+      <c r="A71" t="s">
         <v>35</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" t="s">
         <v>100</v>
       </c>
-      <c r="C71" s="7">
+      <c r="C71" s="2">
         <v>33</v>
       </c>
-      <c r="D71" s="6" t="s">
+      <c r="D71" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" spans="1:4">
-      <c r="A72" s="5" t="s">
+      <c r="A72" t="s">
         <v>35</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" t="s">
         <v>102</v>
       </c>
-      <c r="C72" s="7">
+      <c r="C72" s="2">
         <v>34</v>
       </c>
-      <c r="D72" s="6" t="s">
+      <c r="D72" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" spans="1:4">
-      <c r="A73" s="5" t="s">
+      <c r="A73" t="s">
         <v>35</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="B73" t="s">
         <v>104</v>
       </c>
-      <c r="C73" s="7">
+      <c r="C73" s="2">
         <v>35</v>
       </c>
-      <c r="D73" s="6" t="s">
+      <c r="D73" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" spans="1:4">
-      <c r="A74" s="5" t="s">
+      <c r="A74" t="s">
         <v>35</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="B74" t="s">
         <v>106</v>
       </c>
-      <c r="C74" s="7">
+      <c r="C74" s="2">
         <v>36</v>
       </c>
-      <c r="D74" s="6" t="s">
+      <c r="D74" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" spans="1:4">
-      <c r="A75" s="5" t="s">
+      <c r="A75" t="s">
         <v>35</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="B75" t="s">
         <v>108</v>
       </c>
-      <c r="C75" s="7">
+      <c r="C75" s="2">
         <v>37</v>
       </c>
-      <c r="D75" s="6" t="s">
+      <c r="D75" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" spans="1:4">
-      <c r="A76" s="5" t="s">
+      <c r="A76" t="s">
         <v>35</v>
       </c>
-      <c r="B76" s="6" t="s">
+      <c r="B76" t="s">
         <v>110</v>
       </c>
-      <c r="C76" s="7">
+      <c r="C76" s="2">
         <v>38</v>
       </c>
-      <c r="D76" s="6" t="s">
+      <c r="D76" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" spans="1:4">
-      <c r="A77" s="5" t="s">
+      <c r="A77" t="s">
         <v>35</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" t="s">
         <v>112</v>
       </c>
-      <c r="C77" s="7">
+      <c r="C77" s="2">
         <v>39</v>
       </c>
-      <c r="D77" s="6" t="s">
+      <c r="D77" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" spans="1:4">
-      <c r="A78" s="5" t="s">
+      <c r="A78" t="s">
         <v>35</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" t="s">
         <v>114</v>
       </c>
-      <c r="C78" s="7">
+      <c r="C78" s="2">
         <v>40</v>
       </c>
-      <c r="D78" s="6" t="s">
+      <c r="D78" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="79" s="1" customFormat="1" spans="1:4">
-      <c r="A79" s="5" t="s">
+      <c r="A79" t="s">
         <v>35</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="B79" t="s">
         <v>116</v>
       </c>
-      <c r="C79" s="7">
+      <c r="C79" s="2">
         <v>41</v>
       </c>
-      <c r="D79" s="6" t="s">
+      <c r="D79" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" spans="1:4">
-      <c r="A80" s="5" t="s">
+      <c r="A80" t="s">
         <v>35</v>
       </c>
-      <c r="B80" s="6" t="s">
+      <c r="B80" t="s">
         <v>118</v>
       </c>
-      <c r="C80" s="7">
+      <c r="C80" s="2">
         <v>42</v>
       </c>
-      <c r="D80" s="6" t="s">
+      <c r="D80" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="81" s="1" customFormat="1" spans="1:4">
-      <c r="A81" s="5" t="s">
+      <c r="A81" t="s">
         <v>35</v>
       </c>
-      <c r="B81" s="6" t="s">
+      <c r="B81" t="s">
         <v>120</v>
       </c>
-      <c r="C81" s="7">
+      <c r="C81" s="2">
         <v>43</v>
       </c>
-      <c r="D81" s="6" t="s">
+      <c r="D81" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="82" s="1" customFormat="1" spans="1:4">
-      <c r="A82" s="5" t="s">
+      <c r="A82" t="s">
         <v>35</v>
       </c>
-      <c r="B82" s="6" t="s">
+      <c r="B82" t="s">
         <v>122</v>
       </c>
-      <c r="C82" s="7">
+      <c r="C82" s="2">
         <v>44</v>
       </c>
-      <c r="D82" s="6" t="s">
+      <c r="D82" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="3" t="s">
+    <row r="83" customFormat="1" spans="1:4">
+      <c r="A83" t="s">
+        <v>35</v>
+      </c>
+      <c r="B83" t="s">
         <v>124</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="C83" s="2">
+        <v>45</v>
+      </c>
+      <c r="D83" t="s">
         <v>125</v>
       </c>
-      <c r="C88" s="4">
+    </row>
+    <row r="84" customFormat="1" spans="1:4">
+      <c r="A84" t="s">
+        <v>35</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C84" s="2">
+        <v>46</v>
+      </c>
+      <c r="D84" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="85" customFormat="1" spans="1:4">
+      <c r="A85" t="s">
+        <v>35</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C85" s="2">
+        <v>47</v>
+      </c>
+      <c r="D85" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="86" customFormat="1" spans="1:4">
+      <c r="A86" t="s">
+        <v>35</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C86" s="2">
+        <v>48</v>
+      </c>
+      <c r="D86" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="87" customFormat="1" spans="1:4">
+      <c r="A87" t="s">
+        <v>35</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C87" s="2">
+        <v>49</v>
+      </c>
+      <c r="D87" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="88" customFormat="1" spans="1:4">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="1"/>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C94" s="2">
         <v>1</v>
       </c>
-      <c r="D88" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C89" s="4">
+      <c r="D94" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C95" s="2">
         <v>2</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C90" s="4">
+      <c r="D95" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C96" s="2">
         <v>3</v>
       </c>
-      <c r="D90" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C91" s="4">
+      <c r="D96" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C97" s="2">
         <v>4</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C92" s="4">
+      <c r="D97" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C98" s="2">
         <v>5</v>
       </c>
-      <c r="D92" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C93" s="4">
+      <c r="D98" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C99" s="2">
         <v>6</v>
       </c>
-      <c r="D93" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C94" s="4">
+      <c r="D99" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C100" s="2">
         <v>7</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C95" s="4">
+      <c r="D100" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C101" s="2">
         <v>8</v>
       </c>
-      <c r="D95" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C96" s="4">
+      <c r="D101" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C102" s="2">
         <v>9</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C97" s="4">
+      <c r="D102" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C103" s="2">
         <v>10</v>
       </c>
-      <c r="D97" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C98" s="4">
+      <c r="D103" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C104" s="2">
         <v>11</v>
       </c>
-      <c r="D98" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C99" s="4">
+      <c r="D104" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C105" s="2">
         <v>12</v>
       </c>
-      <c r="D99" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C100" s="4">
+      <c r="D105" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C106" s="2">
         <v>13</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C101" s="4">
+      <c r="D106" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C107" s="2">
         <v>14</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C102" s="4">
+      <c r="D107" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C108" s="2">
         <v>15</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C103" s="4">
+      <c r="D108" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C109" s="2">
         <v>16</v>
       </c>
-      <c r="D103" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C104" s="4">
+      <c r="D109" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C110" s="2">
         <v>17</v>
       </c>
-      <c r="D104" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C105" s="4">
+      <c r="D110" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C111" s="2">
         <v>18</v>
       </c>
-      <c r="D105" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C106" s="4">
+      <c r="D111" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C112" s="2">
         <v>19</v>
       </c>
-      <c r="D106" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C107" s="4">
+      <c r="D112" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C113" s="2">
         <v>20</v>
       </c>
-      <c r="D107" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C108" s="4">
+      <c r="D113" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C114" s="2">
         <v>21</v>
       </c>
-      <c r="D108" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="C109" s="4">
+      <c r="D114" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C115" s="2">
         <v>22</v>
       </c>
-      <c r="D109" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B110" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C110" s="4">
+      <c r="D115" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C116" s="2">
         <v>23</v>
       </c>
-      <c r="D110" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C111" s="4">
+      <c r="D116" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C117" s="2">
         <v>24</v>
       </c>
-      <c r="D111" s="3" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C112" s="4">
+      <c r="D117" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C118" s="2">
         <v>25</v>
       </c>
-      <c r="D112" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C113" s="4">
+      <c r="D118" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C119" s="2">
         <v>26</v>
       </c>
-      <c r="D113" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4">
-      <c r="A114" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C114" s="4">
+      <c r="D119" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C120" s="2">
         <v>27</v>
       </c>
-      <c r="D114" s="3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
-      <c r="A115" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C115" s="4">
+      <c r="D120" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C121" s="2">
         <v>28</v>
       </c>
-      <c r="D115" s="3" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4">
-      <c r="A117" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C117" s="4">
+      <c r="D121" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C123" s="2">
         <v>29</v>
       </c>
-      <c r="D117" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4">
-      <c r="A118" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B118" t="s">
-        <v>183</v>
-      </c>
-      <c r="C118" s="4">
+      <c r="D123" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B124" t="s">
+        <v>193</v>
+      </c>
+      <c r="C124" s="2">
         <v>30</v>
       </c>
-      <c r="D118" s="3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4">
-      <c r="A119" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B119" t="s">
-        <v>185</v>
-      </c>
-      <c r="C119" s="4">
+      <c r="D124" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B125" t="s">
+        <v>195</v>
+      </c>
+      <c r="C125" s="2">
         <v>31</v>
       </c>
-      <c r="D119" s="3" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4">
-      <c r="A120" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B120" t="s">
-        <v>187</v>
-      </c>
-      <c r="C120" s="4">
+      <c r="D125" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B126" t="s">
+        <v>197</v>
+      </c>
+      <c r="C126" s="2">
         <v>32</v>
       </c>
-      <c r="D120" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4">
-      <c r="A121" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B121" t="s">
-        <v>189</v>
-      </c>
-      <c r="C121" s="4">
+      <c r="D126" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B127" t="s">
+        <v>199</v>
+      </c>
+      <c r="C127" s="2">
         <v>33</v>
       </c>
-      <c r="D121" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4">
-      <c r="A122" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B122" s="3" t="s">
+      <c r="D127" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C122" s="4">
+      <c r="C128" s="2">
         <v>34</v>
       </c>
-      <c r="D122" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4">
-      <c r="A123" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B123" t="s">
+      <c r="D128" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B129" t="s">
         <v>13</v>
       </c>
-      <c r="C123" s="4">
+      <c r="C129" s="2">
         <v>35</v>
       </c>
-      <c r="D123" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4">
-      <c r="A124" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B124" t="s">
+      <c r="D129" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B130" t="s">
         <v>15</v>
       </c>
-      <c r="C124" s="4">
+      <c r="C130" s="2">
         <v>36</v>
-      </c>
-      <c r="D124" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4">
-      <c r="A125" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B125" t="s">
-        <v>17</v>
-      </c>
-      <c r="C125" s="4">
-        <v>37</v>
-      </c>
-      <c r="D125" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4">
-      <c r="A126" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C126" s="4">
-        <v>38</v>
-      </c>
-      <c r="D126" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4">
-      <c r="A127" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B127" t="s">
-        <v>196</v>
-      </c>
-      <c r="C127" s="4">
-        <v>39</v>
-      </c>
-      <c r="D127" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4">
-      <c r="A128" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B128" t="s">
-        <v>198</v>
-      </c>
-      <c r="C128" s="4">
-        <v>40</v>
-      </c>
-      <c r="D128" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4">
-      <c r="A129" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B129" t="s">
-        <v>200</v>
-      </c>
-      <c r="C129" s="4">
-        <v>41</v>
-      </c>
-      <c r="D129" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4">
-      <c r="A130" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B130" t="s">
-        <v>202</v>
-      </c>
-      <c r="C130" s="4">
-        <v>42</v>
       </c>
       <c r="D130" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="131" spans="1:4">
-      <c r="A131" s="3" t="s">
+      <c r="A131" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B131" t="s">
+        <v>17</v>
+      </c>
+      <c r="C131" s="2">
+        <v>37</v>
+      </c>
+      <c r="D131" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C132" s="2">
+        <v>38</v>
+      </c>
+      <c r="D132" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B133" t="s">
+        <v>206</v>
+      </c>
+      <c r="C133" s="2">
+        <v>39</v>
+      </c>
+      <c r="D133" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B134" t="s">
+        <v>208</v>
+      </c>
+      <c r="C134" s="2">
+        <v>40</v>
+      </c>
+      <c r="D134" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>210</v>
+      </c>
+      <c r="C135" s="2">
+        <v>41</v>
+      </c>
+      <c r="D135" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B136" t="s">
+        <v>212</v>
+      </c>
+      <c r="C136" s="2">
+        <v>42</v>
+      </c>
+      <c r="D136" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C137" s="2">
+        <v>43</v>
+      </c>
+      <c r="D137" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B138" t="s">
+        <v>216</v>
+      </c>
+      <c r="C138" s="2">
+        <v>44</v>
+      </c>
+      <c r="D138" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B139" t="s">
+        <v>218</v>
+      </c>
+      <c r="C139" s="2">
+        <v>45</v>
+      </c>
+      <c r="D139" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B140" t="s">
+        <v>220</v>
+      </c>
+      <c r="C140" s="2">
+        <v>46</v>
+      </c>
+      <c r="D140" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C141" s="2">
+        <v>47</v>
+      </c>
+      <c r="D141" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C142" s="2">
+        <v>48</v>
+      </c>
+      <c r="D142" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B143" t="s">
+        <v>226</v>
+      </c>
+      <c r="C143" s="2">
+        <v>49</v>
+      </c>
+      <c r="D143" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B144" t="s">
+        <v>228</v>
+      </c>
+      <c r="C144" s="2">
+        <v>50</v>
+      </c>
+      <c r="D144" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C145" s="2">
+        <v>51</v>
+      </c>
+      <c r="D145" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B146" t="s">
+        <v>232</v>
+      </c>
+      <c r="C146" s="2">
+        <v>52</v>
+      </c>
+      <c r="D146" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B147" t="s">
+        <v>234</v>
+      </c>
+      <c r="C147" s="2">
+        <v>53</v>
+      </c>
+      <c r="D147" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B148" t="s">
+        <v>236</v>
+      </c>
+      <c r="C148" s="2">
+        <v>54</v>
+      </c>
+      <c r="D148" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B149" t="s">
+        <v>238</v>
+      </c>
+      <c r="C149" s="2">
+        <v>55</v>
+      </c>
+      <c r="D149" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C150" s="2">
+        <v>56</v>
+      </c>
+      <c r="D150" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B151" t="s">
+        <v>242</v>
+      </c>
+      <c r="C151" s="2">
+        <v>57</v>
+      </c>
+      <c r="D151" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B152" t="s">
+        <v>244</v>
+      </c>
+      <c r="C152" s="2">
+        <v>58</v>
+      </c>
+      <c r="D152" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B153" t="s">
+        <v>246</v>
+      </c>
+      <c r="C153" s="2">
+        <v>59</v>
+      </c>
+      <c r="D153" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B154" t="s">
+        <v>248</v>
+      </c>
+      <c r="C154" s="2">
+        <v>60</v>
+      </c>
+      <c r="D154" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B155" t="s">
+        <v>250</v>
+      </c>
+      <c r="C155" s="2">
+        <v>61</v>
+      </c>
+      <c r="D155" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B156" t="s">
+        <v>252</v>
+      </c>
+      <c r="C156" s="2">
+        <v>62</v>
+      </c>
+      <c r="D156" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B157" t="s">
+        <v>254</v>
+      </c>
+      <c r="C157" s="2">
+        <v>63</v>
+      </c>
+      <c r="D157" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B158" t="s">
+        <v>256</v>
+      </c>
+      <c r="C158" s="2">
+        <v>64</v>
+      </c>
+      <c r="D158" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B159" t="s">
+        <v>258</v>
+      </c>
+      <c r="C159" s="2">
+        <v>65</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B160" t="s">
+        <v>260</v>
+      </c>
+      <c r="C160" s="2">
+        <v>66</v>
+      </c>
+      <c r="D160" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B161" t="s">
+        <v>262</v>
+      </c>
+      <c r="C161" s="2">
+        <v>67</v>
+      </c>
+      <c r="D161" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B162" t="s">
+        <v>264</v>
+      </c>
+      <c r="C162" s="2">
+        <v>68</v>
+      </c>
+      <c r="D162" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B163" t="s">
+        <v>266</v>
+      </c>
+      <c r="C163" s="2">
+        <v>69</v>
+      </c>
+      <c r="D163" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B164" t="s">
+        <v>268</v>
+      </c>
+      <c r="C164" s="2">
+        <v>70</v>
+      </c>
+      <c r="D164" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C165" s="2">
+        <v>71</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C166" s="2">
+        <v>72</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B167" t="s">
+        <v>274</v>
+      </c>
+      <c r="C167" s="2">
+        <v>73</v>
+      </c>
+      <c r="D167" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B168" t="s">
+        <v>276</v>
+      </c>
+      <c r="C168" s="2">
+        <v>74</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B169" t="s">
+        <v>278</v>
+      </c>
+      <c r="C169" s="2">
+        <v>75</v>
+      </c>
+      <c r="D169" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B170" t="s">
+        <v>280</v>
+      </c>
+      <c r="C170" s="2">
+        <v>76</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B171" t="s">
+        <v>282</v>
+      </c>
+      <c r="C171" s="2">
+        <v>77</v>
+      </c>
+      <c r="D171" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B172" t="s">
+        <v>284</v>
+      </c>
+      <c r="C172" s="2">
+        <v>78</v>
+      </c>
+      <c r="D172" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B173" t="s">
+        <v>286</v>
+      </c>
+      <c r="C173" s="2">
+        <v>79</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B174" t="s">
+        <v>288</v>
+      </c>
+      <c r="C174" s="2">
+        <v>80</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B175" t="s">
+        <v>290</v>
+      </c>
+      <c r="C175" s="2">
+        <v>81</v>
+      </c>
+      <c r="D175" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B176" t="s">
+        <v>292</v>
+      </c>
+      <c r="C176" s="2">
+        <v>82</v>
+      </c>
+      <c r="D176" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C177" s="2">
+        <v>83</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B178" t="s">
+        <v>296</v>
+      </c>
+      <c r="C178" s="2">
+        <v>84</v>
+      </c>
+      <c r="D178" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B179" t="s">
+        <v>298</v>
+      </c>
+      <c r="C179" s="2">
+        <v>85</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B180" t="s">
+        <v>300</v>
+      </c>
+      <c r="C180" s="2">
+        <v>86</v>
+      </c>
+      <c r="D180" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B181" t="s">
+        <v>302</v>
+      </c>
+      <c r="C181" s="2">
+        <v>87</v>
+      </c>
+      <c r="D181" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B182" t="s">
+        <v>304</v>
+      </c>
+      <c r="C182" s="2">
+        <v>88</v>
+      </c>
+      <c r="D182" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C183" s="2">
+        <v>89</v>
+      </c>
+      <c r="D183" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C184" s="2">
+        <v>90</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B185" t="s">
+        <v>310</v>
+      </c>
+      <c r="C185" s="2">
+        <v>91</v>
+      </c>
+      <c r="D185" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="186" s="1" customFormat="1" spans="1:5">
+      <c r="A186" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B186" t="s">
+        <v>312</v>
+      </c>
+      <c r="C186" s="2">
+        <v>92</v>
+      </c>
+      <c r="D186" t="s">
+        <v>313</v>
+      </c>
+      <c r="E186"/>
+    </row>
+    <row r="187" s="1" customFormat="1" spans="1:5">
+      <c r="A187" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B187" t="s">
+        <v>314</v>
+      </c>
+      <c r="C187" s="2">
+        <v>93</v>
+      </c>
+      <c r="D187" t="s">
+        <v>315</v>
+      </c>
+      <c r="E187"/>
+    </row>
+    <row r="188" s="1" customFormat="1" spans="1:5">
+      <c r="A188" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B188" t="s">
+        <v>316</v>
+      </c>
+      <c r="C188" s="2">
+        <v>94</v>
+      </c>
+      <c r="D188" t="s">
+        <v>317</v>
+      </c>
+      <c r="E188"/>
+    </row>
+    <row r="189" s="1" customFormat="1" spans="1:5">
+      <c r="A189" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B189" t="s">
+        <v>318</v>
+      </c>
+      <c r="C189" s="2">
+        <v>95</v>
+      </c>
+      <c r="D189" t="s">
+        <v>319</v>
+      </c>
+      <c r="E189"/>
+    </row>
+    <row r="190" s="1" customFormat="1" spans="1:5">
+      <c r="A190" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B190" t="s">
+        <v>320</v>
+      </c>
+      <c r="C190" s="2">
+        <v>96</v>
+      </c>
+      <c r="D190" t="s">
+        <v>321</v>
+      </c>
+      <c r="E190"/>
+    </row>
+    <row r="191" s="1" customFormat="1" spans="1:5">
+      <c r="A191" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B191" t="s">
+        <v>322</v>
+      </c>
+      <c r="C191" s="2">
+        <v>97</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E191"/>
+    </row>
+    <row r="192" s="1" customFormat="1" spans="1:5">
+      <c r="A192" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B192" t="s">
+        <v>324</v>
+      </c>
+      <c r="C192" s="2">
+        <v>98</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="E192"/>
+    </row>
+    <row r="193" s="1" customFormat="1" spans="1:5">
+      <c r="A193" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B193" t="s">
+        <v>326</v>
+      </c>
+      <c r="C193" s="2">
+        <v>99</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E193"/>
+    </row>
+    <row r="194" s="1" customFormat="1" spans="1:5">
+      <c r="A194" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B194" t="s">
+        <v>328</v>
+      </c>
+      <c r="C194" s="2">
+        <v>100</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="E194"/>
+    </row>
+    <row r="195" s="1" customFormat="1" spans="1:5">
+      <c r="A195" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B195" t="s">
+        <v>330</v>
+      </c>
+      <c r="C195" s="2">
+        <v>101</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="E195"/>
+    </row>
+    <row r="196" s="1" customFormat="1" spans="1:5">
+      <c r="A196" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B196" t="s">
+        <v>332</v>
+      </c>
+      <c r="C196" s="2">
+        <v>102</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E196"/>
+    </row>
+    <row r="197" s="1" customFormat="1" spans="1:5">
+      <c r="A197" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B197" t="s">
+        <v>334</v>
+      </c>
+      <c r="C197" s="2">
+        <v>103</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E197"/>
+    </row>
+    <row r="198" s="1" customFormat="1" spans="1:5">
+      <c r="A198" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B198" t="s">
+        <v>336</v>
+      </c>
+      <c r="C198" s="2">
+        <v>104</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E198"/>
+    </row>
+    <row r="199" s="1" customFormat="1" spans="1:5">
+      <c r="A199" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B199" t="s">
+        <v>338</v>
+      </c>
+      <c r="C199" s="2">
+        <v>105</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E199"/>
+    </row>
+    <row r="200" s="1" customFormat="1" spans="1:5">
+      <c r="A200" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B200" t="s">
+        <v>340</v>
+      </c>
+      <c r="C200" s="2">
+        <v>106</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E200"/>
+    </row>
+    <row r="201" s="1" customFormat="1" spans="1:5">
+      <c r="A201" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B201" t="s">
+        <v>342</v>
+      </c>
+      <c r="C201" s="2">
+        <v>107</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E201"/>
+    </row>
+    <row r="202" s="1" customFormat="1" spans="1:5">
+      <c r="A202" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B202" t="s">
+        <v>344</v>
+      </c>
+      <c r="C202" s="2">
+        <v>108</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="E202"/>
+    </row>
+    <row r="203" s="1" customFormat="1" spans="1:5">
+      <c r="A203" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B203" t="s">
+        <v>346</v>
+      </c>
+      <c r="C203" s="2">
+        <v>109</v>
+      </c>
+      <c r="D203" t="s">
+        <v>347</v>
+      </c>
+      <c r="E203"/>
+    </row>
+    <row r="204" s="1" customFormat="1" spans="1:5">
+      <c r="A204" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B204" t="s">
+        <v>348</v>
+      </c>
+      <c r="C204" s="2">
+        <v>110</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E204"/>
+    </row>
+    <row r="205" s="1" customFormat="1" spans="1:5">
+      <c r="A205" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B205" t="s">
+        <v>350</v>
+      </c>
+      <c r="C205" s="2">
+        <v>111</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="E205"/>
+    </row>
+    <row r="206" s="1" customFormat="1" spans="1:5">
+      <c r="A206" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B206" t="s">
+        <v>352</v>
+      </c>
+      <c r="C206" s="2">
+        <v>112</v>
+      </c>
+      <c r="D206" t="s">
+        <v>353</v>
+      </c>
+      <c r="E206"/>
+    </row>
+    <row r="207" s="1" customFormat="1" spans="1:5">
+      <c r="A207" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B207" t="s">
+        <v>354</v>
+      </c>
+      <c r="C207" s="2">
+        <v>113</v>
+      </c>
+      <c r="D207" t="s">
+        <v>355</v>
+      </c>
+      <c r="E207"/>
+    </row>
+    <row r="208" s="1" customFormat="1" spans="1:5">
+      <c r="A208" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B208" t="s">
+        <v>356</v>
+      </c>
+      <c r="C208" s="2">
+        <v>114</v>
+      </c>
+      <c r="D208" t="s">
+        <v>357</v>
+      </c>
+      <c r="E208"/>
+    </row>
+    <row r="209" s="1" customFormat="1" spans="1:5">
+      <c r="A209" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B209" t="s">
+        <v>358</v>
+      </c>
+      <c r="C209" s="2">
+        <v>115</v>
+      </c>
+      <c r="D209" t="s">
+        <v>359</v>
+      </c>
+      <c r="E209"/>
+    </row>
+    <row r="210" s="1" customFormat="1" spans="1:5">
+      <c r="A210" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B210" t="s">
+        <v>360</v>
+      </c>
+      <c r="C210" s="2">
+        <v>116</v>
+      </c>
+      <c r="D210" t="s">
+        <v>361</v>
+      </c>
+      <c r="E210"/>
+    </row>
+    <row r="211" s="1" customFormat="1" spans="1:5">
+      <c r="A211" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B211" t="s">
+        <v>362</v>
+      </c>
+      <c r="C211" s="2">
+        <v>117</v>
+      </c>
+      <c r="D211" t="s">
+        <v>363</v>
+      </c>
+      <c r="E211"/>
+    </row>
+    <row r="212" s="1" customFormat="1" spans="1:5">
+      <c r="A212" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B212" t="s">
+        <v>364</v>
+      </c>
+      <c r="C212" s="2">
+        <v>118</v>
+      </c>
+      <c r="D212" t="s">
+        <v>365</v>
+      </c>
+      <c r="E212"/>
+    </row>
+    <row r="213" s="1" customFormat="1" spans="1:5">
+      <c r="A213" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B213" t="s">
+        <v>366</v>
+      </c>
+      <c r="C213" s="2">
+        <v>119</v>
+      </c>
+      <c r="D213" t="s">
+        <v>367</v>
+      </c>
+      <c r="E213"/>
+    </row>
+    <row r="214" s="1" customFormat="1" spans="1:5">
+      <c r="A214" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B214" t="s">
+        <v>368</v>
+      </c>
+      <c r="C214" s="2">
+        <v>120</v>
+      </c>
+      <c r="D214" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="215" s="1" customFormat="1" spans="1:5">
+      <c r="A215" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B215" t="s">
+        <v>370</v>
+      </c>
+      <c r="C215" s="2">
+        <v>121</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="216" s="1" customFormat="1" spans="1:5">
+      <c r="A216" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B216" t="s">
+        <v>372</v>
+      </c>
+      <c r="C216" s="2">
+        <v>122</v>
+      </c>
+      <c r="D216" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="217" s="1" customFormat="1" spans="1:5">
+      <c r="A217" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C217" s="2">
+        <v>123</v>
+      </c>
+      <c r="D217" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="218" s="1" customFormat="1" spans="1:5">
+      <c r="A218" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C218" s="2">
         <v>124</v>
       </c>
-      <c r="B131" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C131" s="4">
-        <v>43</v>
-      </c>
-      <c r="D131" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4">
-      <c r="A132" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B132" t="s">
-        <v>206</v>
-      </c>
-      <c r="C132" s="4">
-        <v>44</v>
-      </c>
-      <c r="D132" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4">
-      <c r="A133" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B133" t="s">
-        <v>208</v>
-      </c>
-      <c r="C133" s="4">
-        <v>45</v>
-      </c>
-      <c r="D133" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4">
-      <c r="A134" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B134" t="s">
-        <v>210</v>
-      </c>
-      <c r="C134" s="4">
-        <v>46</v>
-      </c>
-      <c r="D134" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4">
-      <c r="A135" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="C135" s="4">
-        <v>47</v>
-      </c>
-      <c r="D135" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4">
-      <c r="A136" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B136" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="C136" s="4">
-        <v>48</v>
-      </c>
-      <c r="D136" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4">
-      <c r="A137" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B137" t="s">
-        <v>216</v>
-      </c>
-      <c r="C137" s="4">
-        <v>49</v>
-      </c>
-      <c r="D137" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4">
-      <c r="A138" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B138" t="s">
-        <v>218</v>
-      </c>
-      <c r="C138" s="4">
-        <v>50</v>
-      </c>
-      <c r="D138" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4">
-      <c r="A139" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B139" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="C139" s="4">
-        <v>51</v>
-      </c>
-      <c r="D139" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4">
-      <c r="A140" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B140" t="s">
-        <v>222</v>
-      </c>
-      <c r="C140" s="4">
-        <v>52</v>
-      </c>
-      <c r="D140" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4">
-      <c r="A141" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B141" t="s">
-        <v>224</v>
-      </c>
-      <c r="C141" s="4">
-        <v>53</v>
-      </c>
-      <c r="D141" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4">
-      <c r="A142" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B142" t="s">
-        <v>226</v>
-      </c>
-      <c r="C142" s="4">
-        <v>54</v>
-      </c>
-      <c r="D142" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4">
-      <c r="A143" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B143" t="s">
-        <v>228</v>
-      </c>
-      <c r="C143" s="4">
-        <v>55</v>
-      </c>
-      <c r="D143" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4">
-      <c r="A144" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="C144" s="4">
-        <v>56</v>
-      </c>
-      <c r="D144" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4">
-      <c r="A145" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B145" t="s">
-        <v>232</v>
-      </c>
-      <c r="C145" s="4">
-        <v>57</v>
-      </c>
-      <c r="D145" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4">
-      <c r="A146" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B146" t="s">
-        <v>234</v>
-      </c>
-      <c r="C146" s="4">
-        <v>58</v>
-      </c>
-      <c r="D146" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4">
-      <c r="A147" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B147" t="s">
-        <v>236</v>
-      </c>
-      <c r="C147" s="4">
-        <v>59</v>
-      </c>
-      <c r="D147" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4">
-      <c r="A148" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B148" t="s">
-        <v>238</v>
-      </c>
-      <c r="C148" s="4">
-        <v>60</v>
-      </c>
-      <c r="D148" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4">
-      <c r="A149" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B149" t="s">
-        <v>240</v>
-      </c>
-      <c r="C149" s="4">
-        <v>61</v>
-      </c>
-      <c r="D149" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4">
-      <c r="A150" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B150" t="s">
-        <v>242</v>
-      </c>
-      <c r="C150" s="4">
-        <v>62</v>
-      </c>
-      <c r="D150" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4">
-      <c r="A151" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B151" t="s">
-        <v>244</v>
-      </c>
-      <c r="C151" s="4">
-        <v>63</v>
-      </c>
-      <c r="D151" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4">
-      <c r="A152" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B152" t="s">
-        <v>246</v>
-      </c>
-      <c r="C152" s="4">
-        <v>64</v>
-      </c>
-      <c r="D152" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4">
-      <c r="A153" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B153" t="s">
-        <v>248</v>
-      </c>
-      <c r="C153" s="4">
-        <v>65</v>
-      </c>
-      <c r="D153" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4">
-      <c r="A154" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B154" t="s">
-        <v>250</v>
-      </c>
-      <c r="C154" s="4">
-        <v>66</v>
-      </c>
-      <c r="D154" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4">
-      <c r="A155" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B155" t="s">
-        <v>252</v>
-      </c>
-      <c r="C155" s="4">
-        <v>67</v>
-      </c>
-      <c r="D155" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4">
-      <c r="A156" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B156" t="s">
-        <v>254</v>
-      </c>
-      <c r="C156" s="4">
-        <v>68</v>
-      </c>
-      <c r="D156" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4">
-      <c r="A157" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B157" t="s">
-        <v>256</v>
-      </c>
-      <c r="C157" s="4">
-        <v>69</v>
-      </c>
-      <c r="D157" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4">
-      <c r="A158" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B158" t="s">
-        <v>258</v>
-      </c>
-      <c r="C158" s="4">
-        <v>70</v>
-      </c>
-      <c r="D158" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4">
-      <c r="A159" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="C159" s="4">
-        <v>71</v>
-      </c>
-      <c r="D159" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4">
-      <c r="A160" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="C160" s="4">
-        <v>72</v>
-      </c>
-      <c r="D160" s="3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4">
-      <c r="A161" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B161" t="s">
-        <v>264</v>
-      </c>
-      <c r="C161" s="4">
-        <v>73</v>
-      </c>
-      <c r="D161" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4">
-      <c r="A162" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B162" t="s">
-        <v>266</v>
-      </c>
-      <c r="C162" s="4">
-        <v>74</v>
-      </c>
-      <c r="D162" s="3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4">
-      <c r="A163" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B163" t="s">
-        <v>268</v>
-      </c>
-      <c r="C163" s="4">
-        <v>75</v>
-      </c>
-      <c r="D163" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4">
-      <c r="A164" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B164" t="s">
-        <v>270</v>
-      </c>
-      <c r="C164" s="4">
-        <v>76</v>
-      </c>
-      <c r="D164" s="3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4">
-      <c r="A165" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B165" t="s">
-        <v>272</v>
-      </c>
-      <c r="C165" s="4">
-        <v>77</v>
-      </c>
-      <c r="D165" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4">
-      <c r="A166" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B166" t="s">
-        <v>274</v>
-      </c>
-      <c r="C166" s="4">
-        <v>78</v>
-      </c>
-      <c r="D166" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4">
-      <c r="A167" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B167" t="s">
-        <v>276</v>
-      </c>
-      <c r="C167" s="4">
-        <v>79</v>
-      </c>
-      <c r="D167" s="3" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4">
-      <c r="A168" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B168" t="s">
-        <v>278</v>
-      </c>
-      <c r="C168" s="4">
-        <v>80</v>
-      </c>
-      <c r="D168" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4">
-      <c r="A169" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B169" t="s">
-        <v>280</v>
-      </c>
-      <c r="C169" s="4">
-        <v>81</v>
-      </c>
-      <c r="D169" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4">
-      <c r="A170" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B170" t="s">
-        <v>282</v>
-      </c>
-      <c r="C170" s="4">
-        <v>82</v>
-      </c>
-      <c r="D170" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4">
-      <c r="A171" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="C171" s="4">
-        <v>83</v>
-      </c>
-      <c r="D171" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4">
-      <c r="A172" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B172" t="s">
-        <v>286</v>
-      </c>
-      <c r="C172" s="4">
-        <v>84</v>
-      </c>
-      <c r="D172" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4">
-      <c r="A173" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B173" t="s">
-        <v>288</v>
-      </c>
-      <c r="C173" s="4">
-        <v>85</v>
-      </c>
-      <c r="D173" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4">
-      <c r="A174" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B174" t="s">
-        <v>290</v>
-      </c>
-      <c r="C174" s="4">
-        <v>86</v>
-      </c>
-      <c r="D174" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4">
-      <c r="A175" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B175" t="s">
-        <v>292</v>
-      </c>
-      <c r="C175" s="4">
-        <v>87</v>
-      </c>
-      <c r="D175" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4">
-      <c r="A176" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B176" t="s">
-        <v>294</v>
-      </c>
-      <c r="C176" s="4">
-        <v>88</v>
-      </c>
-      <c r="D176" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5">
-      <c r="A177" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B177" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="C177" s="4">
-        <v>89</v>
-      </c>
-      <c r="D177" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5">
-      <c r="A178" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B178" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="C178" s="4">
-        <v>90</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5">
-      <c r="A179" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B179" t="s">
-        <v>300</v>
-      </c>
-      <c r="C179" s="4">
-        <v>91</v>
-      </c>
-      <c r="D179" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="180" s="2" customFormat="1" spans="1:5">
-      <c r="A180" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B180" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="C180" s="9">
-        <v>92</v>
-      </c>
-      <c r="D180" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="E180" s="8"/>
-    </row>
-    <row r="181" s="2" customFormat="1" spans="1:5">
-      <c r="A181" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B181" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="C181" s="9">
-        <v>93</v>
-      </c>
-      <c r="D181" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="E181" s="8"/>
-    </row>
-    <row r="182" s="2" customFormat="1" spans="1:5">
-      <c r="A182" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B182" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="C182" s="9">
-        <v>94</v>
-      </c>
-      <c r="D182" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="E182" s="8"/>
-    </row>
-    <row r="183" s="2" customFormat="1" spans="1:5">
-      <c r="A183" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B183" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="C183" s="9">
-        <v>95</v>
-      </c>
-      <c r="D183" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E183" s="8"/>
-    </row>
-    <row r="184" s="2" customFormat="1" spans="1:5">
-      <c r="A184" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B184" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C184" s="9">
-        <v>96</v>
-      </c>
-      <c r="D184" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E184" s="8"/>
-    </row>
-    <row r="185" s="2" customFormat="1" spans="1:5">
-      <c r="A185" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B185" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="C185" s="9">
-        <v>97</v>
-      </c>
-      <c r="D185" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E185" s="8"/>
-    </row>
-    <row r="186" s="2" customFormat="1" spans="1:5">
-      <c r="A186" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B186" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="C186" s="9">
-        <v>98</v>
-      </c>
-      <c r="D186" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E186" s="8"/>
-    </row>
-    <row r="187" s="2" customFormat="1" spans="1:5">
-      <c r="A187" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B187" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="C187" s="9">
-        <v>99</v>
-      </c>
-      <c r="D187" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E187" s="8"/>
-    </row>
-    <row r="188" s="2" customFormat="1" spans="1:5">
-      <c r="A188" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B188" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="C188" s="9">
-        <v>100</v>
-      </c>
-      <c r="D188" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="E188" s="8"/>
-    </row>
-    <row r="189" s="2" customFormat="1" spans="1:5">
-      <c r="A189" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B189" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="C189" s="9">
-        <v>101</v>
-      </c>
-      <c r="D189" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E189" s="8"/>
-    </row>
-    <row r="190" s="2" customFormat="1" spans="1:5">
-      <c r="A190" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B190" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="C190" s="9">
-        <v>102</v>
-      </c>
-      <c r="D190" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="E190" s="8"/>
-    </row>
-    <row r="191" s="2" customFormat="1" spans="1:5">
-      <c r="A191" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B191" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="C191" s="9">
-        <v>103</v>
-      </c>
-      <c r="D191" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E191" s="8"/>
-    </row>
-    <row r="192" s="2" customFormat="1" spans="1:5">
-      <c r="A192" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B192" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="C192" s="9">
-        <v>104</v>
-      </c>
-      <c r="D192" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E192" s="8"/>
-    </row>
-    <row r="193" s="2" customFormat="1" spans="1:5">
-      <c r="A193" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B193" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="C193" s="9">
-        <v>105</v>
-      </c>
-      <c r="D193" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E193" s="8"/>
-    </row>
-    <row r="194" s="2" customFormat="1" spans="1:5">
-      <c r="A194" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B194" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="C194" s="9">
-        <v>106</v>
-      </c>
-      <c r="D194" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="E194" s="8"/>
-    </row>
-    <row r="195" s="2" customFormat="1" spans="1:5">
-      <c r="A195" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B195" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="C195" s="9">
-        <v>107</v>
-      </c>
-      <c r="D195" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="E195" s="8"/>
-    </row>
-    <row r="196" s="2" customFormat="1" spans="1:5">
-      <c r="A196" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B196" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="C196" s="9">
-        <v>108</v>
-      </c>
-      <c r="D196" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="E196" s="8"/>
-    </row>
-    <row r="197" s="2" customFormat="1" spans="1:5">
-      <c r="A197" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B197" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="C197" s="9">
-        <v>109</v>
-      </c>
-      <c r="D197" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="E197" s="8"/>
-    </row>
-    <row r="198" s="2" customFormat="1" spans="1:5">
-      <c r="A198" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B198" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="C198" s="9">
-        <v>110</v>
-      </c>
-      <c r="D198" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="E198" s="8"/>
-    </row>
-    <row r="199" s="2" customFormat="1" spans="1:5">
-      <c r="A199" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B199" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="C199" s="9">
-        <v>111</v>
-      </c>
-      <c r="D199" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="E199" s="8"/>
-    </row>
-    <row r="200" s="2" customFormat="1" spans="1:5">
-      <c r="A200" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B200" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="C200" s="9">
-        <v>112</v>
-      </c>
-      <c r="D200" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="E200" s="8"/>
-    </row>
-    <row r="201" s="2" customFormat="1" spans="1:5">
-      <c r="A201" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B201" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="C201" s="9">
-        <v>113</v>
-      </c>
-      <c r="D201" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="E201" s="8"/>
-    </row>
-    <row r="202" s="2" customFormat="1" spans="1:5">
-      <c r="A202" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B202" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="C202" s="9">
-        <v>114</v>
-      </c>
-      <c r="D202" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="E202" s="8"/>
-    </row>
-    <row r="203" s="2" customFormat="1" spans="1:5">
-      <c r="A203" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B203" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="C203" s="9">
-        <v>115</v>
-      </c>
-      <c r="D203" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="E203" s="8"/>
-    </row>
-    <row r="204" s="2" customFormat="1" spans="1:5">
-      <c r="A204" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B204" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="C204" s="9">
-        <v>116</v>
-      </c>
-      <c r="D204" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="E204" s="8"/>
-    </row>
-    <row r="205" s="2" customFormat="1" spans="1:5">
-      <c r="A205" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B205" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="C205" s="9">
-        <v>117</v>
-      </c>
-      <c r="D205" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="E205" s="8"/>
-    </row>
-    <row r="206" s="2" customFormat="1" spans="1:5">
-      <c r="A206" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B206" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="C206" s="9">
-        <v>118</v>
-      </c>
-      <c r="D206" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="E206" s="8"/>
-    </row>
-    <row r="207" s="2" customFormat="1" spans="1:5">
-      <c r="A207" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B207" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="C207" s="9">
-        <v>119</v>
-      </c>
-      <c r="D207" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="E207" s="8"/>
-    </row>
-    <row r="208" s="2" customFormat="1" spans="1:5">
-      <c r="A208" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B208" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="C208" s="9">
-        <v>120</v>
-      </c>
-      <c r="D208" s="8" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="209" s="2" customFormat="1" spans="1:4">
-      <c r="A209" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B209" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="C209" s="9">
-        <v>121</v>
-      </c>
-      <c r="D209" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="210" s="2" customFormat="1" spans="1:4">
-      <c r="A210" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B210" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="C210" s="9">
-        <v>122</v>
-      </c>
-      <c r="D210" s="8" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="211" s="2" customFormat="1" spans="1:4">
-      <c r="A211" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B211" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="C211" s="9">
-        <v>123</v>
-      </c>
-      <c r="D211" s="8" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="212" s="2" customFormat="1" spans="1:4">
-      <c r="A212" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B212" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="C212" s="9">
-        <v>124</v>
-      </c>
-      <c r="D212" s="8" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="213" s="2" customFormat="1" spans="1:4">
-      <c r="A213" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B213" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="C213" s="9">
+      <c r="D218" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="219" s="1" customFormat="1" spans="1:5">
+      <c r="A219" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C219" s="2">
         <v>125</v>
       </c>
-      <c r="D213" s="8" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="214" s="2" customFormat="1" spans="1:4">
-      <c r="A214" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B214" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="C214" s="9">
+      <c r="D219" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="220" s="1" customFormat="1" spans="1:5">
+      <c r="A220" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C220" s="2">
         <v>126</v>
       </c>
-      <c r="D214" s="8" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="215" s="2" customFormat="1" spans="1:4">
-      <c r="A215" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B215" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="C215" s="9">
+      <c r="D220" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="221" s="1" customFormat="1" spans="1:5">
+      <c r="A221" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C221" s="2">
         <v>127</v>
       </c>
-      <c r="D215" s="8" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="216" s="2" customFormat="1" spans="1:4">
-      <c r="A216" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B216" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="C216" s="9">
+      <c r="D221" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="222" s="1" customFormat="1" spans="1:5">
+      <c r="A222" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C222" s="2">
         <v>128</v>
       </c>
-      <c r="D216" s="8" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="217" s="2" customFormat="1" spans="1:4">
-      <c r="A217" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B217" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="C217" s="9">
+      <c r="D222" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="223" s="1" customFormat="1" spans="1:5">
+      <c r="A223" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C223" s="2">
         <v>129</v>
       </c>
-      <c r="D217" s="8" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="218" s="2" customFormat="1" spans="1:4">
-      <c r="A218" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B218" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="C218" s="9">
+      <c r="D223" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="224" s="1" customFormat="1" spans="1:5">
+      <c r="A224" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C224" s="2">
         <v>130</v>
       </c>
-      <c r="D218" s="8" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4">
-      <c r="A219" t="s">
-        <v>124</v>
-      </c>
-      <c r="B219" t="s">
-        <v>380</v>
-      </c>
-      <c r="C219" s="4">
-        <v>131</v>
-      </c>
-      <c r="D219" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4">
-      <c r="A220" t="s">
-        <v>124</v>
-      </c>
-      <c r="B220" t="s">
-        <v>382</v>
-      </c>
-      <c r="C220" s="4">
-        <v>132</v>
-      </c>
-      <c r="D220" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4">
-      <c r="A221" t="s">
-        <v>124</v>
-      </c>
-      <c r="B221" t="s">
-        <v>384</v>
-      </c>
-      <c r="C221" s="4">
-        <v>133</v>
-      </c>
-      <c r="D221" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4">
-      <c r="A222" t="s">
-        <v>124</v>
-      </c>
-      <c r="B222" t="s">
-        <v>386</v>
-      </c>
-      <c r="C222" s="4">
-        <v>134</v>
-      </c>
-      <c r="D222" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4">
-      <c r="A223" t="s">
-        <v>124</v>
-      </c>
-      <c r="B223" t="s">
-        <v>388</v>
-      </c>
-      <c r="C223" s="4">
-        <v>135</v>
-      </c>
-      <c r="D223" t="s">
+      <c r="D224" t="s">
         <v>389</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4">
-      <c r="A224" t="s">
-        <v>124</v>
-      </c>
-      <c r="B224" t="s">
-        <v>390</v>
-      </c>
-      <c r="C224" s="4">
-        <v>136</v>
-      </c>
-      <c r="D224" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B225" t="s">
-        <v>392</v>
-      </c>
-      <c r="C225" s="4">
-        <v>137</v>
+        <v>390</v>
+      </c>
+      <c r="C225" s="2">
+        <v>131</v>
       </c>
       <c r="D225" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B226" t="s">
-        <v>394</v>
-      </c>
-      <c r="C226" s="4">
-        <v>138</v>
+        <v>392</v>
+      </c>
+      <c r="C226" s="2">
+        <v>132</v>
       </c>
       <c r="D226" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B227" t="s">
-        <v>396</v>
-      </c>
-      <c r="C227" s="4">
-        <v>139</v>
+        <v>394</v>
+      </c>
+      <c r="C227" s="2">
+        <v>133</v>
       </c>
       <c r="D227" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B228" t="s">
-        <v>398</v>
-      </c>
-      <c r="C228" s="4">
-        <v>140</v>
+        <v>396</v>
+      </c>
+      <c r="C228" s="2">
+        <v>134</v>
       </c>
       <c r="D228" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B229" t="s">
-        <v>400</v>
-      </c>
-      <c r="C229" s="4">
-        <v>141</v>
+        <v>398</v>
+      </c>
+      <c r="C229" s="2">
+        <v>135</v>
       </c>
       <c r="D229" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B230" t="s">
-        <v>402</v>
-      </c>
-      <c r="C230" s="4">
-        <v>142</v>
+        <v>400</v>
+      </c>
+      <c r="C230" s="2">
+        <v>136</v>
       </c>
       <c r="D230" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B231" t="s">
-        <v>404</v>
-      </c>
-      <c r="C231" s="4">
-        <v>143</v>
+        <v>402</v>
+      </c>
+      <c r="C231" s="2">
+        <v>137</v>
       </c>
       <c r="D231" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B232" t="s">
-        <v>406</v>
-      </c>
-      <c r="C232" s="4">
-        <v>144</v>
+        <v>404</v>
+      </c>
+      <c r="C232" s="2">
+        <v>138</v>
       </c>
       <c r="D232" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B233" t="s">
-        <v>408</v>
-      </c>
-      <c r="C233" s="4">
-        <v>145</v>
+        <v>406</v>
+      </c>
+      <c r="C233" s="2">
+        <v>139</v>
       </c>
       <c r="D233" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B234" t="s">
-        <v>410</v>
-      </c>
-      <c r="C234" s="4">
-        <v>146</v>
+        <v>408</v>
+      </c>
+      <c r="C234" s="2">
+        <v>140</v>
       </c>
       <c r="D234" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>124</v>
-      </c>
-      <c r="B235" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="C235" s="4">
-        <v>147</v>
-      </c>
-      <c r="D235" s="3" t="s">
-        <v>413</v>
+        <v>134</v>
+      </c>
+      <c r="B235" t="s">
+        <v>410</v>
+      </c>
+      <c r="C235" s="2">
+        <v>141</v>
+      </c>
+      <c r="D235" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>124</v>
-      </c>
-      <c r="B236" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="C236" s="4">
-        <v>148</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>415</v>
+        <v>134</v>
+      </c>
+      <c r="B236" t="s">
+        <v>412</v>
+      </c>
+      <c r="C236" s="2">
+        <v>142</v>
+      </c>
+      <c r="D236" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>124</v>
-      </c>
-      <c r="B237" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="C237" s="4">
-        <v>149</v>
-      </c>
-      <c r="D237" s="10" t="s">
-        <v>417</v>
+        <v>134</v>
+      </c>
+      <c r="B237" t="s">
+        <v>414</v>
+      </c>
+      <c r="C237" s="2">
+        <v>143</v>
+      </c>
+      <c r="D237" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>124</v>
-      </c>
-      <c r="B238" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="C238" s="4">
-        <v>150</v>
-      </c>
-      <c r="D238" s="10" t="s">
-        <v>419</v>
+        <v>134</v>
+      </c>
+      <c r="B238" t="s">
+        <v>416</v>
+      </c>
+      <c r="C238" s="2">
+        <v>144</v>
+      </c>
+      <c r="D238" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>124</v>
-      </c>
-      <c r="B239" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B239" t="s">
+        <v>418</v>
+      </c>
+      <c r="C239" s="2">
+        <v>145</v>
+      </c>
+      <c r="D239" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" t="s">
+        <v>134</v>
+      </c>
+      <c r="B240" t="s">
         <v>420</v>
       </c>
-      <c r="C239" s="4">
+      <c r="C240" s="2">
+        <v>146</v>
+      </c>
+      <c r="D240" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" t="s">
+        <v>134</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C241" s="2">
+        <v>147</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" t="s">
+        <v>134</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C242" s="2">
+        <v>148</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" t="s">
+        <v>134</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C243" s="2">
+        <v>149</v>
+      </c>
+      <c r="D243" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" t="s">
+        <v>134</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C244" s="2">
+        <v>150</v>
+      </c>
+      <c r="D244" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" t="s">
+        <v>134</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C245" s="2">
         <v>151</v>
       </c>
-      <c r="D239" s="10" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4">
-      <c r="B240"/>
-      <c r="D240"/>
-    </row>
-    <row r="241" spans="1:4">
-      <c r="B241"/>
-      <c r="D241"/>
-    </row>
-    <row r="242" spans="1:4">
-      <c r="B242"/>
-      <c r="D242"/>
-    </row>
-    <row r="243" spans="1:4">
-      <c r="B243"/>
-      <c r="D243"/>
-    </row>
-    <row r="244" spans="1:4">
-      <c r="A244" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B244" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="C244" s="4">
-        <v>1111</v>
-      </c>
-      <c r="D244"/>
-    </row>
-    <row r="245" spans="1:4">
-      <c r="A245" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B245" t="s">
-        <v>423</v>
-      </c>
-      <c r="C245" s="4">
-        <v>1112</v>
-      </c>
-      <c r="D245"/>
+      <c r="D245" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="246" spans="1:4">
-      <c r="A246" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B246" t="s">
-        <v>424</v>
-      </c>
-      <c r="C246" s="4">
-        <v>1113</v>
-      </c>
+      <c r="B246"/>
       <c r="D246"/>
     </row>
     <row r="247" spans="1:4">
@@ -5450,15 +5484,39 @@
       <c r="D249"/>
     </row>
     <row r="250" spans="1:4">
-      <c r="B250"/>
+      <c r="A250" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C250" s="2">
+        <v>1111</v>
+      </c>
       <c r="D250"/>
     </row>
     <row r="251" spans="1:4">
-      <c r="B251"/>
+      <c r="A251" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B251" t="s">
+        <v>433</v>
+      </c>
+      <c r="C251" s="2">
+        <v>1112</v>
+      </c>
       <c r="D251"/>
     </row>
     <row r="252" spans="1:4">
-      <c r="B252"/>
+      <c r="A252" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B252" t="s">
+        <v>434</v>
+      </c>
+      <c r="C252" s="2">
+        <v>1113</v>
+      </c>
       <c r="D252"/>
     </row>
     <row r="253" spans="1:4">
@@ -5509,242 +5567,266 @@
       <c r="B264"/>
       <c r="D264"/>
     </row>
+    <row r="265" spans="1:4">
+      <c r="B265"/>
+      <c r="D265"/>
+    </row>
     <row r="266" spans="1:4">
-      <c r="A266" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="B266" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="C266" s="4">
+      <c r="B266"/>
+      <c r="D266"/>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="B267"/>
+      <c r="D267"/>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="B268"/>
+      <c r="D268"/>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="B269"/>
+      <c r="D269"/>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="B270"/>
+      <c r="D270"/>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C272" s="2">
         <v>1</v>
       </c>
-      <c r="D266" s="3" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4">
-      <c r="A267" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="B267" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="C267" s="4">
+      <c r="D272" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C273" s="2">
         <v>2</v>
       </c>
-      <c r="D267" s="3" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4">
-      <c r="A268" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="B268" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="C268" s="4">
+      <c r="D273" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C274" s="2">
         <v>3</v>
       </c>
-      <c r="D268" s="3" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4">
-      <c r="A269" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="B269" s="4" t="s">
+      <c r="D274" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B275" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C269" s="4">
+      <c r="C275" s="2">
         <v>4</v>
       </c>
-      <c r="D269" s="3" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4">
-      <c r="A270" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="B270" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="C270" s="4">
+      <c r="D275" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C276" s="2">
         <v>5</v>
       </c>
-      <c r="D270" s="3" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4">
-      <c r="A271" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="B271" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="C271" s="4">
+      <c r="D276" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C277" s="2">
         <v>6</v>
       </c>
-      <c r="D271" s="3" t="s">
+      <c r="D277" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" s="1" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="272" spans="1:4">
-      <c r="A272" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="B272" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="C272" s="4">
+      <c r="B278" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C278" s="2">
         <v>7</v>
       </c>
-      <c r="D272" s="3" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4">
-      <c r="A273" t="s">
-        <v>425</v>
-      </c>
-      <c r="B273" t="s">
-        <v>15</v>
-      </c>
-      <c r="C273" s="4">
-        <v>8</v>
-      </c>
-      <c r="D273" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4">
-      <c r="A274" t="s">
-        <v>425</v>
-      </c>
-      <c r="B274" t="s">
-        <v>439</v>
-      </c>
-      <c r="C274" s="4">
-        <v>9</v>
-      </c>
-      <c r="D274" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4">
-      <c r="A275" t="s">
-        <v>425</v>
-      </c>
-      <c r="B275" t="s">
-        <v>441</v>
-      </c>
-      <c r="C275" s="4">
-        <v>10</v>
-      </c>
-      <c r="D275" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4">
-      <c r="A276" t="s">
-        <v>425</v>
-      </c>
-      <c r="B276" t="s">
-        <v>443</v>
-      </c>
-      <c r="C276" s="4">
-        <v>11</v>
-      </c>
-      <c r="D276" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="277" spans="1:4">
-      <c r="A277" t="s">
-        <v>445</v>
-      </c>
-      <c r="B277" t="s">
-        <v>446</v>
-      </c>
-      <c r="C277" s="4">
-        <v>1</v>
-      </c>
-      <c r="D277" t="s">
+      <c r="D278" s="1" t="s">
         <v>447</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4">
-      <c r="A278" t="s">
-        <v>445</v>
-      </c>
-      <c r="B278" t="s">
-        <v>448</v>
-      </c>
-      <c r="C278" s="4">
-        <v>2</v>
-      </c>
-      <c r="D278" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="B279" t="s">
-        <v>450</v>
-      </c>
-      <c r="C279" s="4">
-        <v>3</v>
+        <v>15</v>
+      </c>
+      <c r="C279" s="2">
+        <v>8</v>
       </c>
       <c r="D279" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>452</v>
+        <v>435</v>
       </c>
       <c r="B280" t="s">
-        <v>453</v>
-      </c>
-      <c r="C280" s="4">
-        <v>1</v>
+        <v>449</v>
+      </c>
+      <c r="C280" s="2">
+        <v>9</v>
       </c>
       <c r="D280" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
+        <v>435</v>
+      </c>
+      <c r="B281" t="s">
+        <v>451</v>
+      </c>
+      <c r="C281" s="2">
+        <v>10</v>
+      </c>
+      <c r="D281" t="s">
         <v>452</v>
-      </c>
-      <c r="B281" t="s">
-        <v>455</v>
-      </c>
-      <c r="C281" s="4">
-        <v>2</v>
-      </c>
-      <c r="D281" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>452</v>
+        <v>435</v>
       </c>
       <c r="B282" t="s">
+        <v>453</v>
+      </c>
+      <c r="C282" s="2">
+        <v>11</v>
+      </c>
+      <c r="D282" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" t="s">
+        <v>455</v>
+      </c>
+      <c r="B283" t="s">
+        <v>456</v>
+      </c>
+      <c r="C283" s="2">
+        <v>1</v>
+      </c>
+      <c r="D283" t="s">
         <v>457</v>
       </c>
-      <c r="C282" s="4">
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" t="s">
+        <v>455</v>
+      </c>
+      <c r="B284" t="s">
+        <v>458</v>
+      </c>
+      <c r="C284" s="2">
+        <v>2</v>
+      </c>
+      <c r="D284" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" t="s">
+        <v>455</v>
+      </c>
+      <c r="B285" t="s">
+        <v>460</v>
+      </c>
+      <c r="C285" s="2">
         <v>3</v>
       </c>
-      <c r="D282" t="s">
-        <v>458</v>
+      <c r="D285" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" t="s">
+        <v>462</v>
+      </c>
+      <c r="B286" t="s">
+        <v>463</v>
+      </c>
+      <c r="C286" s="2">
+        <v>1</v>
+      </c>
+      <c r="D286" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" t="s">
+        <v>462</v>
+      </c>
+      <c r="B287" t="s">
+        <v>465</v>
+      </c>
+      <c r="C287" s="2">
+        <v>2</v>
+      </c>
+      <c r="D287" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" t="s">
+        <v>462</v>
+      </c>
+      <c r="B288" t="s">
+        <v>467</v>
+      </c>
+      <c r="C288" s="2">
+        <v>3</v>
+      </c>
+      <c r="D288" t="s">
+        <v>468</v>
       </c>
     </row>
   </sheetData>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="13170" windowHeight="10470"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="490">
   <si>
     <t>Enum</t>
   </si>
@@ -1330,6 +1330,12 @@
     <t>比牌时,自己的牌型顺位提高</t>
   </si>
   <si>
+    <t>GiantPotion</t>
+  </si>
+  <si>
+    <t>巨人药剂</t>
+  </si>
+  <si>
     <t>MaxHp</t>
   </si>
   <si>
@@ -1397,6 +1403,63 @@
   </si>
   <si>
     <t>单次比牌造成伤害达到指定值</t>
+  </si>
+  <si>
+    <t>亮出对子次数</t>
+  </si>
+  <si>
+    <t>Failure</t>
+  </si>
+  <si>
+    <t>比牌负于对手次数</t>
+  </si>
+  <si>
+    <t>Defeat</t>
+  </si>
+  <si>
+    <t>比牌战胜对手次数</t>
+  </si>
+  <si>
+    <t>LuxuryGoods</t>
+  </si>
+  <si>
+    <t>奢侈品</t>
+  </si>
+  <si>
+    <t>Angel</t>
+  </si>
+  <si>
+    <t>天使</t>
+  </si>
+  <si>
+    <t>DeathNum</t>
+  </si>
+  <si>
+    <t>死亡次数</t>
+  </si>
+  <si>
+    <t>Perspective</t>
+  </si>
+  <si>
+    <t>使用透视次数</t>
+  </si>
+  <si>
+    <t>OneDamage</t>
+  </si>
+  <si>
+    <t>单次打出的伤害</t>
+  </si>
+  <si>
+    <t>NumberOfCoinsOwned</t>
+  </si>
+  <si>
+    <t>战斗时拥有金币数量</t>
+  </si>
+  <si>
+    <t>CriticalNum</t>
+  </si>
+  <si>
+    <t>触发暴击次数</t>
   </si>
   <si>
     <t>GuideTriggerType</t>
@@ -1604,12 +1667,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1930,7 +1999,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -1954,16 +2023,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -1972,96 +2041,108 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2412,12 +2493,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:E288"/>
+  <dimension ref="A4:E299"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16.7416666666667" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.7" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.05833333333333" style="2" customWidth="1"/>
+    <col min="3" max="3" width="7.05833333333333" style="3" customWidth="1"/>
     <col min="4" max="4" width="31.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="34.75" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1" customWidth="1"/>
@@ -2430,7 +2511,7 @@
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
@@ -2444,7 +2525,7 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -2458,7 +2539,7 @@
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -2472,7 +2553,7 @@
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -2486,7 +2567,7 @@
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -2500,7 +2581,7 @@
       <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -2514,7 +2595,7 @@
       <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -2528,7 +2609,7 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="3">
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -2542,7 +2623,7 @@
       <c r="B14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="3">
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -2556,7 +2637,7 @@
       <c r="B16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="3">
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -2570,7 +2651,7 @@
       <c r="B17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="3">
         <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -2584,7 +2665,7 @@
       <c r="B19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="3">
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -2598,7 +2679,7 @@
       <c r="B20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="3">
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -2612,7 +2693,7 @@
       <c r="B21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="3">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -2626,7 +2707,7 @@
       <c r="B22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="3">
         <v>4</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -2640,7 +2721,7 @@
       <c r="B39" t="s">
         <v>36</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="3">
         <v>1</v>
       </c>
       <c r="D39" t="s">
@@ -2654,7 +2735,7 @@
       <c r="B40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="3">
         <v>2</v>
       </c>
       <c r="D40" t="s">
@@ -2668,7 +2749,7 @@
       <c r="B41" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="3">
         <v>3</v>
       </c>
       <c r="D41" t="s">
@@ -2682,7 +2763,7 @@
       <c r="B42" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="3">
         <v>4</v>
       </c>
       <c r="D42" t="s">
@@ -2696,7 +2777,7 @@
       <c r="B43" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="3">
         <v>5</v>
       </c>
       <c r="D43" t="s">
@@ -2710,7 +2791,7 @@
       <c r="B44" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="3">
         <v>6</v>
       </c>
       <c r="D44" s="1" t="s">
@@ -2724,7 +2805,7 @@
       <c r="B45" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="3">
         <v>7</v>
       </c>
       <c r="D45" s="1" t="s">
@@ -2738,7 +2819,7 @@
       <c r="B46" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="3">
         <v>8</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -2752,7 +2833,7 @@
       <c r="B47" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="3">
         <v>9</v>
       </c>
       <c r="D47" s="1" t="s">
@@ -2766,7 +2847,7 @@
       <c r="B48" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" s="3">
         <v>10</v>
       </c>
       <c r="D48" s="1" t="s">
@@ -2780,7 +2861,7 @@
       <c r="B49" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="2">
+      <c r="C49" s="3">
         <v>11</v>
       </c>
       <c r="D49" s="1" t="s">
@@ -2794,7 +2875,7 @@
       <c r="B50" t="s">
         <v>58</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50" s="3">
         <v>12</v>
       </c>
       <c r="D50" t="s">
@@ -2808,7 +2889,7 @@
       <c r="B51" t="s">
         <v>60</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="3">
         <v>13</v>
       </c>
       <c r="D51" t="s">
@@ -2822,7 +2903,7 @@
       <c r="B52" t="s">
         <v>62</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52" s="3">
         <v>14</v>
       </c>
       <c r="D52" t="s">
@@ -2836,7 +2917,7 @@
       <c r="B53" t="s">
         <v>64</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" s="3">
         <v>15</v>
       </c>
       <c r="D53" t="s">
@@ -2850,7 +2931,7 @@
       <c r="B54" t="s">
         <v>66</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" s="3">
         <v>16</v>
       </c>
       <c r="D54" t="s">
@@ -2864,7 +2945,7 @@
       <c r="B55" t="s">
         <v>68</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" s="3">
         <v>17</v>
       </c>
       <c r="D55" t="s">
@@ -2878,7 +2959,7 @@
       <c r="B56" t="s">
         <v>70</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C56" s="3">
         <v>18</v>
       </c>
       <c r="D56" t="s">
@@ -2892,7 +2973,7 @@
       <c r="B57" t="s">
         <v>72</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C57" s="3">
         <v>19</v>
       </c>
       <c r="D57" t="s">
@@ -2906,7 +2987,7 @@
       <c r="B58" t="s">
         <v>74</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C58" s="3">
         <v>20</v>
       </c>
       <c r="D58" t="s">
@@ -2920,7 +3001,7 @@
       <c r="B59" t="s">
         <v>76</v>
       </c>
-      <c r="C59" s="2">
+      <c r="C59" s="3">
         <v>21</v>
       </c>
       <c r="D59" t="s">
@@ -2934,7 +3015,7 @@
       <c r="B60" t="s">
         <v>78</v>
       </c>
-      <c r="C60" s="2">
+      <c r="C60" s="3">
         <v>22</v>
       </c>
       <c r="D60" t="s">
@@ -2948,7 +3029,7 @@
       <c r="B61" t="s">
         <v>80</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C61" s="3">
         <v>23</v>
       </c>
       <c r="D61" t="s">
@@ -2962,7 +3043,7 @@
       <c r="B62" t="s">
         <v>82</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C62" s="3">
         <v>24</v>
       </c>
       <c r="D62" t="s">
@@ -2976,7 +3057,7 @@
       <c r="B63" t="s">
         <v>84</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C63" s="3">
         <v>25</v>
       </c>
       <c r="D63" t="s">
@@ -2990,7 +3071,7 @@
       <c r="B64" t="s">
         <v>86</v>
       </c>
-      <c r="C64" s="2">
+      <c r="C64" s="3">
         <v>26</v>
       </c>
       <c r="D64" t="s">
@@ -3004,7 +3085,7 @@
       <c r="B65" t="s">
         <v>88</v>
       </c>
-      <c r="C65" s="2">
+      <c r="C65" s="3">
         <v>27</v>
       </c>
       <c r="D65" t="s">
@@ -3018,7 +3099,7 @@
       <c r="B66" t="s">
         <v>90</v>
       </c>
-      <c r="C66" s="2">
+      <c r="C66" s="3">
         <v>28</v>
       </c>
       <c r="D66" t="s">
@@ -3032,7 +3113,7 @@
       <c r="B67" t="s">
         <v>92</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C67" s="3">
         <v>29</v>
       </c>
       <c r="D67" t="s">
@@ -3046,7 +3127,7 @@
       <c r="B68" t="s">
         <v>94</v>
       </c>
-      <c r="C68" s="2">
+      <c r="C68" s="3">
         <v>30</v>
       </c>
       <c r="D68" t="s">
@@ -3060,7 +3141,7 @@
       <c r="B69" t="s">
         <v>96</v>
       </c>
-      <c r="C69" s="2">
+      <c r="C69" s="3">
         <v>31</v>
       </c>
       <c r="D69" t="s">
@@ -3074,7 +3155,7 @@
       <c r="B70" t="s">
         <v>98</v>
       </c>
-      <c r="C70" s="2">
+      <c r="C70" s="3">
         <v>32</v>
       </c>
       <c r="D70" t="s">
@@ -3088,7 +3169,7 @@
       <c r="B71" t="s">
         <v>100</v>
       </c>
-      <c r="C71" s="2">
+      <c r="C71" s="3">
         <v>33</v>
       </c>
       <c r="D71" t="s">
@@ -3102,7 +3183,7 @@
       <c r="B72" t="s">
         <v>102</v>
       </c>
-      <c r="C72" s="2">
+      <c r="C72" s="3">
         <v>34</v>
       </c>
       <c r="D72" t="s">
@@ -3116,7 +3197,7 @@
       <c r="B73" t="s">
         <v>104</v>
       </c>
-      <c r="C73" s="2">
+      <c r="C73" s="3">
         <v>35</v>
       </c>
       <c r="D73" t="s">
@@ -3130,7 +3211,7 @@
       <c r="B74" t="s">
         <v>106</v>
       </c>
-      <c r="C74" s="2">
+      <c r="C74" s="3">
         <v>36</v>
       </c>
       <c r="D74" t="s">
@@ -3144,7 +3225,7 @@
       <c r="B75" t="s">
         <v>108</v>
       </c>
-      <c r="C75" s="2">
+      <c r="C75" s="3">
         <v>37</v>
       </c>
       <c r="D75" t="s">
@@ -3158,7 +3239,7 @@
       <c r="B76" t="s">
         <v>110</v>
       </c>
-      <c r="C76" s="2">
+      <c r="C76" s="3">
         <v>38</v>
       </c>
       <c r="D76" t="s">
@@ -3172,7 +3253,7 @@
       <c r="B77" t="s">
         <v>112</v>
       </c>
-      <c r="C77" s="2">
+      <c r="C77" s="3">
         <v>39</v>
       </c>
       <c r="D77" t="s">
@@ -3186,7 +3267,7 @@
       <c r="B78" t="s">
         <v>114</v>
       </c>
-      <c r="C78" s="2">
+      <c r="C78" s="3">
         <v>40</v>
       </c>
       <c r="D78" t="s">
@@ -3200,7 +3281,7 @@
       <c r="B79" t="s">
         <v>116</v>
       </c>
-      <c r="C79" s="2">
+      <c r="C79" s="3">
         <v>41</v>
       </c>
       <c r="D79" t="s">
@@ -3214,7 +3295,7 @@
       <c r="B80" t="s">
         <v>118</v>
       </c>
-      <c r="C80" s="2">
+      <c r="C80" s="3">
         <v>42</v>
       </c>
       <c r="D80" t="s">
@@ -3228,7 +3309,7 @@
       <c r="B81" t="s">
         <v>120</v>
       </c>
-      <c r="C81" s="2">
+      <c r="C81" s="3">
         <v>43</v>
       </c>
       <c r="D81" t="s">
@@ -3242,7 +3323,7 @@
       <c r="B82" t="s">
         <v>122</v>
       </c>
-      <c r="C82" s="2">
+      <c r="C82" s="3">
         <v>44</v>
       </c>
       <c r="D82" t="s">
@@ -3256,7 +3337,7 @@
       <c r="B83" t="s">
         <v>124</v>
       </c>
-      <c r="C83" s="2">
+      <c r="C83" s="3">
         <v>45</v>
       </c>
       <c r="D83" t="s">
@@ -3270,7 +3351,7 @@
       <c r="B84" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C84" s="2">
+      <c r="C84" s="3">
         <v>46</v>
       </c>
       <c r="D84" t="s">
@@ -3284,7 +3365,7 @@
       <c r="B85" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C85" s="2">
+      <c r="C85" s="3">
         <v>47</v>
       </c>
       <c r="D85" t="s">
@@ -3298,7 +3379,7 @@
       <c r="B86" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C86" s="2">
+      <c r="C86" s="3">
         <v>48</v>
       </c>
       <c r="D86" t="s">
@@ -3312,7 +3393,7 @@
       <c r="B87" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C87" s="2">
+      <c r="C87" s="3">
         <v>49</v>
       </c>
       <c r="D87" t="s">
@@ -3322,7 +3403,7 @@
     <row r="88" customFormat="1" spans="1:4">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
-      <c r="C88" s="2"/>
+      <c r="C88" s="3"/>
       <c r="D88" s="1"/>
     </row>
     <row r="94" spans="1:4">
@@ -3332,7 +3413,7 @@
       <c r="B94" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C94" s="2">
+      <c r="C94" s="3">
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
@@ -3346,7 +3427,7 @@
       <c r="B95" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C95" s="2">
+      <c r="C95" s="3">
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
@@ -3360,7 +3441,7 @@
       <c r="B96" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C96" s="2">
+      <c r="C96" s="3">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
@@ -3371,10 +3452,10 @@
       <c r="A97" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B97" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C97" s="2">
+      <c r="C97" s="3">
         <v>4</v>
       </c>
       <c r="D97" s="1" t="s">
@@ -3385,10 +3466,10 @@
       <c r="A98" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="B98" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C98" s="2">
+      <c r="C98" s="3">
         <v>5</v>
       </c>
       <c r="D98" s="1" t="s">
@@ -3399,10 +3480,10 @@
       <c r="A99" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="B99" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C99" s="2">
+      <c r="C99" s="3">
         <v>6</v>
       </c>
       <c r="D99" s="1" t="s">
@@ -3413,10 +3494,10 @@
       <c r="A100" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B100" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C100" s="2">
+      <c r="C100" s="3">
         <v>7</v>
       </c>
       <c r="D100" s="1" t="s">
@@ -3427,10 +3508,10 @@
       <c r="A101" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="B101" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C101" s="2">
+      <c r="C101" s="3">
         <v>8</v>
       </c>
       <c r="D101" s="1" t="s">
@@ -3441,10 +3522,10 @@
       <c r="A102" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="B102" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C102" s="2">
+      <c r="C102" s="3">
         <v>9</v>
       </c>
       <c r="D102" s="1" t="s">
@@ -3455,10 +3536,10 @@
       <c r="A103" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="B103" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C103" s="2">
+      <c r="C103" s="3">
         <v>10</v>
       </c>
       <c r="D103" s="1" t="s">
@@ -3469,10 +3550,10 @@
       <c r="A104" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="B104" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C104" s="2">
+      <c r="C104" s="3">
         <v>11</v>
       </c>
       <c r="D104" s="1" t="s">
@@ -3483,10 +3564,10 @@
       <c r="A105" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="B105" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C105" s="2">
+      <c r="C105" s="3">
         <v>12</v>
       </c>
       <c r="D105" s="1" t="s">
@@ -3497,10 +3578,10 @@
       <c r="A106" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="B106" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C106" s="2">
+      <c r="C106" s="3">
         <v>13</v>
       </c>
       <c r="D106" s="1" t="s">
@@ -3511,10 +3592,10 @@
       <c r="A107" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="B107" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C107" s="2">
+      <c r="C107" s="3">
         <v>14</v>
       </c>
       <c r="D107" s="1" t="s">
@@ -3525,10 +3606,10 @@
       <c r="A108" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="B108" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C108" s="2">
+      <c r="C108" s="3">
         <v>15</v>
       </c>
       <c r="D108" s="1" t="s">
@@ -3542,7 +3623,7 @@
       <c r="B109" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C109" s="2">
+      <c r="C109" s="3">
         <v>16</v>
       </c>
       <c r="D109" s="1" t="s">
@@ -3553,10 +3634,10 @@
       <c r="A110" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B110" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C110" s="2">
+      <c r="C110" s="3">
         <v>17</v>
       </c>
       <c r="D110" s="1" t="s">
@@ -3570,7 +3651,7 @@
       <c r="B111" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C111" s="2">
+      <c r="C111" s="3">
         <v>18</v>
       </c>
       <c r="D111" s="1" t="s">
@@ -3581,10 +3662,10 @@
       <c r="A112" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B112" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C112" s="2">
+      <c r="C112" s="3">
         <v>19</v>
       </c>
       <c r="D112" s="1" t="s">
@@ -3598,7 +3679,7 @@
       <c r="B113" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C113" s="2">
+      <c r="C113" s="3">
         <v>20</v>
       </c>
       <c r="D113" s="1" t="s">
@@ -3612,7 +3693,7 @@
       <c r="B114" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C114" s="2">
+      <c r="C114" s="3">
         <v>21</v>
       </c>
       <c r="D114" s="1" t="s">
@@ -3623,10 +3704,10 @@
       <c r="A115" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B115" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C115" s="2">
+      <c r="C115" s="3">
         <v>22</v>
       </c>
       <c r="D115" s="1" t="s">
@@ -3637,10 +3718,10 @@
       <c r="A116" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B116" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C116" s="2">
+      <c r="C116" s="3">
         <v>23</v>
       </c>
       <c r="D116" s="1" t="s">
@@ -3654,7 +3735,7 @@
       <c r="B117" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C117" s="2">
+      <c r="C117" s="3">
         <v>24</v>
       </c>
       <c r="D117" s="1" t="s">
@@ -3668,7 +3749,7 @@
       <c r="B118" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C118" s="2">
+      <c r="C118" s="3">
         <v>25</v>
       </c>
       <c r="D118" s="1" t="s">
@@ -3682,7 +3763,7 @@
       <c r="B119" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C119" s="2">
+      <c r="C119" s="3">
         <v>26</v>
       </c>
       <c r="D119" s="1" t="s">
@@ -3696,7 +3777,7 @@
       <c r="B120" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C120" s="2">
+      <c r="C120" s="3">
         <v>27</v>
       </c>
       <c r="D120" s="1" t="s">
@@ -3710,25 +3791,39 @@
       <c r="B121" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C121" s="2">
+      <c r="C121" s="3">
         <v>28</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>190</v>
       </c>
     </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C122" s="3">
+        <v>29</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
     <row r="123" spans="1:4">
       <c r="A123" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C123" s="2">
-        <v>29</v>
+      <c r="B123" t="s">
+        <v>193</v>
+      </c>
+      <c r="C123" s="3">
+        <v>30</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3736,13 +3831,13 @@
         <v>134</v>
       </c>
       <c r="B124" t="s">
-        <v>193</v>
-      </c>
-      <c r="C124" s="2">
-        <v>30</v>
+        <v>195</v>
+      </c>
+      <c r="C124" s="3">
+        <v>31</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3750,13 +3845,13 @@
         <v>134</v>
       </c>
       <c r="B125" t="s">
-        <v>195</v>
-      </c>
-      <c r="C125" s="2">
-        <v>31</v>
+        <v>197</v>
+      </c>
+      <c r="C125" s="3">
+        <v>32</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3764,41 +3859,41 @@
         <v>134</v>
       </c>
       <c r="B126" t="s">
-        <v>197</v>
-      </c>
-      <c r="C126" s="2">
-        <v>32</v>
+        <v>199</v>
+      </c>
+      <c r="C126" s="3">
+        <v>33</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B127" t="s">
-        <v>199</v>
-      </c>
-      <c r="C127" s="2">
-        <v>33</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>200</v>
+      <c r="B127" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C127" s="3">
+        <v>34</v>
+      </c>
+      <c r="D127" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C128" s="2">
-        <v>34</v>
+      <c r="B128" t="s">
+        <v>13</v>
+      </c>
+      <c r="C128" s="3">
+        <v>35</v>
       </c>
       <c r="D128" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3806,13 +3901,13 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>13</v>
-      </c>
-      <c r="C129" s="2">
-        <v>35</v>
+        <v>15</v>
+      </c>
+      <c r="C129" s="3">
+        <v>36</v>
       </c>
       <c r="D129" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3820,41 +3915,41 @@
         <v>134</v>
       </c>
       <c r="B130" t="s">
-        <v>15</v>
-      </c>
-      <c r="C130" s="2">
-        <v>36</v>
+        <v>17</v>
+      </c>
+      <c r="C130" s="3">
+        <v>37</v>
       </c>
       <c r="D130" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B131" t="s">
-        <v>17</v>
-      </c>
-      <c r="C131" s="2">
-        <v>37</v>
+      <c r="B131" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C131" s="3">
+        <v>38</v>
       </c>
       <c r="D131" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B132" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C132" s="2">
-        <v>38</v>
+      <c r="B132" t="s">
+        <v>206</v>
+      </c>
+      <c r="C132" s="3">
+        <v>39</v>
       </c>
       <c r="D132" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3862,13 +3957,13 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>206</v>
-      </c>
-      <c r="C133" s="2">
-        <v>39</v>
+        <v>208</v>
+      </c>
+      <c r="C133" s="3">
+        <v>40</v>
       </c>
       <c r="D133" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3876,13 +3971,13 @@
         <v>134</v>
       </c>
       <c r="B134" t="s">
-        <v>208</v>
-      </c>
-      <c r="C134" s="2">
-        <v>40</v>
+        <v>210</v>
+      </c>
+      <c r="C134" s="3">
+        <v>41</v>
       </c>
       <c r="D134" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3890,41 +3985,41 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>210</v>
-      </c>
-      <c r="C135" s="2">
-        <v>41</v>
+        <v>212</v>
+      </c>
+      <c r="C135" s="3">
+        <v>42</v>
       </c>
       <c r="D135" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B136" t="s">
-        <v>212</v>
-      </c>
-      <c r="C136" s="2">
-        <v>42</v>
+      <c r="B136" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C136" s="3">
+        <v>43</v>
       </c>
       <c r="D136" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C137" s="2">
-        <v>43</v>
+      <c r="B137" t="s">
+        <v>216</v>
+      </c>
+      <c r="C137" s="3">
+        <v>44</v>
       </c>
       <c r="D137" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3932,13 +4027,13 @@
         <v>134</v>
       </c>
       <c r="B138" t="s">
-        <v>216</v>
-      </c>
-      <c r="C138" s="2">
-        <v>44</v>
+        <v>218</v>
+      </c>
+      <c r="C138" s="3">
+        <v>45</v>
       </c>
       <c r="D138" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3946,55 +4041,55 @@
         <v>134</v>
       </c>
       <c r="B139" t="s">
-        <v>218</v>
-      </c>
-      <c r="C139" s="2">
-        <v>45</v>
+        <v>220</v>
+      </c>
+      <c r="C139" s="3">
+        <v>46</v>
       </c>
       <c r="D139" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B140" t="s">
-        <v>220</v>
-      </c>
-      <c r="C140" s="2">
-        <v>46</v>
+      <c r="B140" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C140" s="3">
+        <v>47</v>
       </c>
       <c r="D140" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B141" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C141" s="2">
-        <v>47</v>
+      <c r="B141" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C141" s="3">
+        <v>48</v>
       </c>
       <c r="D141" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C142" s="2">
-        <v>48</v>
+      <c r="B142" t="s">
+        <v>226</v>
+      </c>
+      <c r="C142" s="3">
+        <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4002,41 +4097,41 @@
         <v>134</v>
       </c>
       <c r="B143" t="s">
-        <v>226</v>
-      </c>
-      <c r="C143" s="2">
-        <v>49</v>
+        <v>228</v>
+      </c>
+      <c r="C143" s="3">
+        <v>50</v>
       </c>
       <c r="D143" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B144" t="s">
-        <v>228</v>
-      </c>
-      <c r="C144" s="2">
-        <v>50</v>
+      <c r="B144" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C144" s="3">
+        <v>51</v>
       </c>
       <c r="D144" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B145" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="C145" s="2">
-        <v>51</v>
+      <c r="B145" t="s">
+        <v>232</v>
+      </c>
+      <c r="C145" s="3">
+        <v>52</v>
       </c>
       <c r="D145" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4044,13 +4139,13 @@
         <v>134</v>
       </c>
       <c r="B146" t="s">
-        <v>232</v>
-      </c>
-      <c r="C146" s="2">
-        <v>52</v>
+        <v>234</v>
+      </c>
+      <c r="C146" s="3">
+        <v>53</v>
       </c>
       <c r="D146" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4058,13 +4153,13 @@
         <v>134</v>
       </c>
       <c r="B147" t="s">
-        <v>234</v>
-      </c>
-      <c r="C147" s="2">
-        <v>53</v>
+        <v>236</v>
+      </c>
+      <c r="C147" s="3">
+        <v>54</v>
       </c>
       <c r="D147" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4072,41 +4167,41 @@
         <v>134</v>
       </c>
       <c r="B148" t="s">
-        <v>236</v>
-      </c>
-      <c r="C148" s="2">
-        <v>54</v>
+        <v>238</v>
+      </c>
+      <c r="C148" s="3">
+        <v>55</v>
       </c>
       <c r="D148" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B149" t="s">
-        <v>238</v>
-      </c>
-      <c r="C149" s="2">
-        <v>55</v>
+      <c r="B149" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C149" s="3">
+        <v>56</v>
       </c>
       <c r="D149" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B150" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C150" s="2">
-        <v>56</v>
+      <c r="B150" t="s">
+        <v>242</v>
+      </c>
+      <c r="C150" s="3">
+        <v>57</v>
       </c>
       <c r="D150" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4114,13 +4209,13 @@
         <v>134</v>
       </c>
       <c r="B151" t="s">
-        <v>242</v>
-      </c>
-      <c r="C151" s="2">
-        <v>57</v>
+        <v>244</v>
+      </c>
+      <c r="C151" s="3">
+        <v>58</v>
       </c>
       <c r="D151" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4128,13 +4223,13 @@
         <v>134</v>
       </c>
       <c r="B152" t="s">
-        <v>244</v>
-      </c>
-      <c r="C152" s="2">
-        <v>58</v>
+        <v>246</v>
+      </c>
+      <c r="C152" s="3">
+        <v>59</v>
       </c>
       <c r="D152" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4142,13 +4237,13 @@
         <v>134</v>
       </c>
       <c r="B153" t="s">
-        <v>246</v>
-      </c>
-      <c r="C153" s="2">
-        <v>59</v>
+        <v>248</v>
+      </c>
+      <c r="C153" s="3">
+        <v>60</v>
       </c>
       <c r="D153" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4156,13 +4251,13 @@
         <v>134</v>
       </c>
       <c r="B154" t="s">
-        <v>248</v>
-      </c>
-      <c r="C154" s="2">
-        <v>60</v>
+        <v>250</v>
+      </c>
+      <c r="C154" s="3">
+        <v>61</v>
       </c>
       <c r="D154" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4170,13 +4265,13 @@
         <v>134</v>
       </c>
       <c r="B155" t="s">
-        <v>250</v>
-      </c>
-      <c r="C155" s="2">
-        <v>61</v>
+        <v>252</v>
+      </c>
+      <c r="C155" s="3">
+        <v>62</v>
       </c>
       <c r="D155" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4184,13 +4279,13 @@
         <v>134</v>
       </c>
       <c r="B156" t="s">
-        <v>252</v>
-      </c>
-      <c r="C156" s="2">
-        <v>62</v>
+        <v>254</v>
+      </c>
+      <c r="C156" s="3">
+        <v>63</v>
       </c>
       <c r="D156" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4198,13 +4293,13 @@
         <v>134</v>
       </c>
       <c r="B157" t="s">
-        <v>254</v>
-      </c>
-      <c r="C157" s="2">
-        <v>63</v>
+        <v>256</v>
+      </c>
+      <c r="C157" s="3">
+        <v>64</v>
       </c>
       <c r="D157" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4212,13 +4307,13 @@
         <v>134</v>
       </c>
       <c r="B158" t="s">
-        <v>256</v>
-      </c>
-      <c r="C158" s="2">
-        <v>64</v>
-      </c>
-      <c r="D158" t="s">
-        <v>257</v>
+        <v>258</v>
+      </c>
+      <c r="C158" s="3">
+        <v>65</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4226,13 +4321,13 @@
         <v>134</v>
       </c>
       <c r="B159" t="s">
-        <v>258</v>
-      </c>
-      <c r="C159" s="2">
-        <v>65</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
+      </c>
+      <c r="C159" s="3">
+        <v>66</v>
+      </c>
+      <c r="D159" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4240,13 +4335,13 @@
         <v>134</v>
       </c>
       <c r="B160" t="s">
-        <v>260</v>
-      </c>
-      <c r="C160" s="2">
-        <v>66</v>
+        <v>262</v>
+      </c>
+      <c r="C160" s="3">
+        <v>67</v>
       </c>
       <c r="D160" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4254,13 +4349,13 @@
         <v>134</v>
       </c>
       <c r="B161" t="s">
-        <v>262</v>
-      </c>
-      <c r="C161" s="2">
-        <v>67</v>
+        <v>264</v>
+      </c>
+      <c r="C161" s="3">
+        <v>68</v>
       </c>
       <c r="D161" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4268,13 +4363,13 @@
         <v>134</v>
       </c>
       <c r="B162" t="s">
-        <v>264</v>
-      </c>
-      <c r="C162" s="2">
-        <v>68</v>
+        <v>266</v>
+      </c>
+      <c r="C162" s="3">
+        <v>69</v>
       </c>
       <c r="D162" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4282,27 +4377,27 @@
         <v>134</v>
       </c>
       <c r="B163" t="s">
-        <v>266</v>
-      </c>
-      <c r="C163" s="2">
-        <v>69</v>
+        <v>268</v>
+      </c>
+      <c r="C163" s="3">
+        <v>70</v>
       </c>
       <c r="D163" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B164" t="s">
-        <v>268</v>
-      </c>
-      <c r="C164" s="2">
-        <v>70</v>
-      </c>
-      <c r="D164" t="s">
-        <v>269</v>
+      <c r="B164" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C164" s="3">
+        <v>71</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4310,27 +4405,27 @@
         <v>134</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C165" s="2">
-        <v>71</v>
+        <v>272</v>
+      </c>
+      <c r="C165" s="3">
+        <v>72</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C166" s="2">
-        <v>72</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>273</v>
+      <c r="B166" t="s">
+        <v>274</v>
+      </c>
+      <c r="C166" s="3">
+        <v>73</v>
+      </c>
+      <c r="D166" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4338,13 +4433,13 @@
         <v>134</v>
       </c>
       <c r="B167" t="s">
-        <v>274</v>
-      </c>
-      <c r="C167" s="2">
-        <v>73</v>
-      </c>
-      <c r="D167" t="s">
-        <v>275</v>
+        <v>276</v>
+      </c>
+      <c r="C167" s="3">
+        <v>74</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4352,13 +4447,13 @@
         <v>134</v>
       </c>
       <c r="B168" t="s">
-        <v>276</v>
-      </c>
-      <c r="C168" s="2">
-        <v>74</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
+      </c>
+      <c r="C168" s="3">
+        <v>75</v>
+      </c>
+      <c r="D168" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4366,13 +4461,13 @@
         <v>134</v>
       </c>
       <c r="B169" t="s">
-        <v>278</v>
-      </c>
-      <c r="C169" s="2">
-        <v>75</v>
-      </c>
-      <c r="D169" t="s">
-        <v>279</v>
+        <v>280</v>
+      </c>
+      <c r="C169" s="3">
+        <v>76</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4380,13 +4475,13 @@
         <v>134</v>
       </c>
       <c r="B170" t="s">
-        <v>280</v>
-      </c>
-      <c r="C170" s="2">
-        <v>76</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
+      </c>
+      <c r="C170" s="3">
+        <v>77</v>
+      </c>
+      <c r="D170" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4394,13 +4489,13 @@
         <v>134</v>
       </c>
       <c r="B171" t="s">
-        <v>282</v>
-      </c>
-      <c r="C171" s="2">
-        <v>77</v>
+        <v>284</v>
+      </c>
+      <c r="C171" s="3">
+        <v>78</v>
       </c>
       <c r="D171" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4408,13 +4503,13 @@
         <v>134</v>
       </c>
       <c r="B172" t="s">
-        <v>284</v>
-      </c>
-      <c r="C172" s="2">
-        <v>78</v>
-      </c>
-      <c r="D172" t="s">
-        <v>285</v>
+        <v>286</v>
+      </c>
+      <c r="C172" s="3">
+        <v>79</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4422,13 +4517,13 @@
         <v>134</v>
       </c>
       <c r="B173" t="s">
-        <v>286</v>
-      </c>
-      <c r="C173" s="2">
-        <v>79</v>
+        <v>288</v>
+      </c>
+      <c r="C173" s="3">
+        <v>80</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4436,13 +4531,13 @@
         <v>134</v>
       </c>
       <c r="B174" t="s">
-        <v>288</v>
-      </c>
-      <c r="C174" s="2">
-        <v>80</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
+      </c>
+      <c r="C174" s="3">
+        <v>81</v>
+      </c>
+      <c r="D174" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4450,41 +4545,41 @@
         <v>134</v>
       </c>
       <c r="B175" t="s">
-        <v>290</v>
-      </c>
-      <c r="C175" s="2">
-        <v>81</v>
+        <v>292</v>
+      </c>
+      <c r="C175" s="3">
+        <v>82</v>
       </c>
       <c r="D175" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B176" t="s">
-        <v>292</v>
-      </c>
-      <c r="C176" s="2">
-        <v>82</v>
-      </c>
-      <c r="D176" t="s">
-        <v>293</v>
+      <c r="B176" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C176" s="3">
+        <v>83</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B177" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C177" s="2">
-        <v>83</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>295</v>
+      <c r="B177" t="s">
+        <v>296</v>
+      </c>
+      <c r="C177" s="3">
+        <v>84</v>
+      </c>
+      <c r="D177" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -4492,13 +4587,13 @@
         <v>134</v>
       </c>
       <c r="B178" t="s">
-        <v>296</v>
-      </c>
-      <c r="C178" s="2">
-        <v>84</v>
-      </c>
-      <c r="D178" t="s">
-        <v>297</v>
+        <v>298</v>
+      </c>
+      <c r="C178" s="3">
+        <v>85</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -4506,13 +4601,13 @@
         <v>134</v>
       </c>
       <c r="B179" t="s">
-        <v>298</v>
-      </c>
-      <c r="C179" s="2">
-        <v>85</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
+      </c>
+      <c r="C179" s="3">
+        <v>86</v>
+      </c>
+      <c r="D179" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -4520,13 +4615,13 @@
         <v>134</v>
       </c>
       <c r="B180" t="s">
-        <v>300</v>
-      </c>
-      <c r="C180" s="2">
-        <v>86</v>
+        <v>302</v>
+      </c>
+      <c r="C180" s="3">
+        <v>87</v>
       </c>
       <c r="D180" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -4534,83 +4629,84 @@
         <v>134</v>
       </c>
       <c r="B181" t="s">
-        <v>302</v>
-      </c>
-      <c r="C181" s="2">
-        <v>87</v>
+        <v>304</v>
+      </c>
+      <c r="C181" s="3">
+        <v>88</v>
       </c>
       <c r="D181" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B182" t="s">
-        <v>304</v>
-      </c>
-      <c r="C182" s="2">
-        <v>88</v>
+      <c r="B182" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C182" s="3">
+        <v>89</v>
       </c>
       <c r="D182" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B183" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C183" s="2">
-        <v>89</v>
-      </c>
-      <c r="D183" t="s">
-        <v>307</v>
+      <c r="B183" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C183" s="3">
+        <v>90</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B184" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="C184" s="2">
-        <v>90</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5">
+      <c r="B184" t="s">
+        <v>310</v>
+      </c>
+      <c r="C184" s="3">
+        <v>91</v>
+      </c>
+      <c r="D184" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="185" s="1" customFormat="1" spans="1:5">
       <c r="A185" s="1" t="s">
         <v>134</v>
       </c>
       <c r="B185" t="s">
-        <v>310</v>
-      </c>
-      <c r="C185" s="2">
-        <v>91</v>
+        <v>312</v>
+      </c>
+      <c r="C185" s="3">
+        <v>92</v>
       </c>
       <c r="D185" t="s">
-        <v>311</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="E185"/>
     </row>
     <row r="186" s="1" customFormat="1" spans="1:5">
       <c r="A186" s="1" t="s">
         <v>134</v>
       </c>
       <c r="B186" t="s">
-        <v>312</v>
-      </c>
-      <c r="C186" s="2">
-        <v>92</v>
+        <v>314</v>
+      </c>
+      <c r="C186" s="3">
+        <v>93</v>
       </c>
       <c r="D186" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E186"/>
     </row>
@@ -4619,13 +4715,13 @@
         <v>134</v>
       </c>
       <c r="B187" t="s">
-        <v>314</v>
-      </c>
-      <c r="C187" s="2">
-        <v>93</v>
+        <v>316</v>
+      </c>
+      <c r="C187" s="3">
+        <v>94</v>
       </c>
       <c r="D187" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E187"/>
     </row>
@@ -4634,13 +4730,13 @@
         <v>134</v>
       </c>
       <c r="B188" t="s">
-        <v>316</v>
-      </c>
-      <c r="C188" s="2">
-        <v>94</v>
+        <v>318</v>
+      </c>
+      <c r="C188" s="3">
+        <v>95</v>
       </c>
       <c r="D188" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E188"/>
     </row>
@@ -4649,13 +4745,13 @@
         <v>134</v>
       </c>
       <c r="B189" t="s">
-        <v>318</v>
-      </c>
-      <c r="C189" s="2">
-        <v>95</v>
+        <v>320</v>
+      </c>
+      <c r="C189" s="3">
+        <v>96</v>
       </c>
       <c r="D189" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E189"/>
     </row>
@@ -4664,13 +4760,13 @@
         <v>134</v>
       </c>
       <c r="B190" t="s">
-        <v>320</v>
-      </c>
-      <c r="C190" s="2">
-        <v>96</v>
-      </c>
-      <c r="D190" t="s">
-        <v>321</v>
+        <v>322</v>
+      </c>
+      <c r="C190" s="3">
+        <v>97</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>323</v>
       </c>
       <c r="E190"/>
     </row>
@@ -4679,13 +4775,13 @@
         <v>134</v>
       </c>
       <c r="B191" t="s">
-        <v>322</v>
-      </c>
-      <c r="C191" s="2">
-        <v>97</v>
+        <v>324</v>
+      </c>
+      <c r="C191" s="3">
+        <v>98</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E191"/>
     </row>
@@ -4694,13 +4790,13 @@
         <v>134</v>
       </c>
       <c r="B192" t="s">
-        <v>324</v>
-      </c>
-      <c r="C192" s="2">
-        <v>98</v>
+        <v>326</v>
+      </c>
+      <c r="C192" s="3">
+        <v>99</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E192"/>
     </row>
@@ -4709,13 +4805,13 @@
         <v>134</v>
       </c>
       <c r="B193" t="s">
-        <v>326</v>
-      </c>
-      <c r="C193" s="2">
-        <v>99</v>
+        <v>328</v>
+      </c>
+      <c r="C193" s="3">
+        <v>100</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E193"/>
     </row>
@@ -4724,13 +4820,13 @@
         <v>134</v>
       </c>
       <c r="B194" t="s">
-        <v>328</v>
-      </c>
-      <c r="C194" s="2">
-        <v>100</v>
+        <v>330</v>
+      </c>
+      <c r="C194" s="3">
+        <v>101</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E194"/>
     </row>
@@ -4739,13 +4835,13 @@
         <v>134</v>
       </c>
       <c r="B195" t="s">
-        <v>330</v>
-      </c>
-      <c r="C195" s="2">
-        <v>101</v>
+        <v>332</v>
+      </c>
+      <c r="C195" s="3">
+        <v>102</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E195"/>
     </row>
@@ -4754,13 +4850,13 @@
         <v>134</v>
       </c>
       <c r="B196" t="s">
-        <v>332</v>
-      </c>
-      <c r="C196" s="2">
-        <v>102</v>
+        <v>334</v>
+      </c>
+      <c r="C196" s="3">
+        <v>103</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E196"/>
     </row>
@@ -4769,13 +4865,13 @@
         <v>134</v>
       </c>
       <c r="B197" t="s">
-        <v>334</v>
-      </c>
-      <c r="C197" s="2">
-        <v>103</v>
+        <v>336</v>
+      </c>
+      <c r="C197" s="3">
+        <v>104</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E197"/>
     </row>
@@ -4784,13 +4880,13 @@
         <v>134</v>
       </c>
       <c r="B198" t="s">
-        <v>336</v>
-      </c>
-      <c r="C198" s="2">
-        <v>104</v>
+        <v>338</v>
+      </c>
+      <c r="C198" s="3">
+        <v>105</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E198"/>
     </row>
@@ -4799,13 +4895,13 @@
         <v>134</v>
       </c>
       <c r="B199" t="s">
-        <v>338</v>
-      </c>
-      <c r="C199" s="2">
-        <v>105</v>
+        <v>340</v>
+      </c>
+      <c r="C199" s="3">
+        <v>106</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E199"/>
     </row>
@@ -4814,13 +4910,13 @@
         <v>134</v>
       </c>
       <c r="B200" t="s">
-        <v>340</v>
-      </c>
-      <c r="C200" s="2">
-        <v>106</v>
+        <v>342</v>
+      </c>
+      <c r="C200" s="3">
+        <v>107</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E200"/>
     </row>
@@ -4829,13 +4925,13 @@
         <v>134</v>
       </c>
       <c r="B201" t="s">
-        <v>342</v>
-      </c>
-      <c r="C201" s="2">
-        <v>107</v>
+        <v>344</v>
+      </c>
+      <c r="C201" s="3">
+        <v>108</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E201"/>
     </row>
@@ -4844,13 +4940,13 @@
         <v>134</v>
       </c>
       <c r="B202" t="s">
-        <v>344</v>
-      </c>
-      <c r="C202" s="2">
-        <v>108</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
+      </c>
+      <c r="C202" s="3">
+        <v>109</v>
+      </c>
+      <c r="D202" t="s">
+        <v>347</v>
       </c>
       <c r="E202"/>
     </row>
@@ -4859,13 +4955,13 @@
         <v>134</v>
       </c>
       <c r="B203" t="s">
-        <v>346</v>
-      </c>
-      <c r="C203" s="2">
-        <v>109</v>
-      </c>
-      <c r="D203" t="s">
-        <v>347</v>
+        <v>348</v>
+      </c>
+      <c r="C203" s="3">
+        <v>110</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>349</v>
       </c>
       <c r="E203"/>
     </row>
@@ -4874,13 +4970,13 @@
         <v>134</v>
       </c>
       <c r="B204" t="s">
-        <v>348</v>
-      </c>
-      <c r="C204" s="2">
-        <v>110</v>
+        <v>350</v>
+      </c>
+      <c r="C204" s="3">
+        <v>111</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E204"/>
     </row>
@@ -4889,13 +4985,13 @@
         <v>134</v>
       </c>
       <c r="B205" t="s">
-        <v>350</v>
-      </c>
-      <c r="C205" s="2">
-        <v>111</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
+      </c>
+      <c r="C205" s="3">
+        <v>112</v>
+      </c>
+      <c r="D205" t="s">
+        <v>353</v>
       </c>
       <c r="E205"/>
     </row>
@@ -4904,13 +5000,13 @@
         <v>134</v>
       </c>
       <c r="B206" t="s">
-        <v>352</v>
-      </c>
-      <c r="C206" s="2">
-        <v>112</v>
+        <v>354</v>
+      </c>
+      <c r="C206" s="3">
+        <v>113</v>
       </c>
       <c r="D206" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E206"/>
     </row>
@@ -4919,13 +5015,13 @@
         <v>134</v>
       </c>
       <c r="B207" t="s">
-        <v>354</v>
-      </c>
-      <c r="C207" s="2">
-        <v>113</v>
+        <v>356</v>
+      </c>
+      <c r="C207" s="3">
+        <v>114</v>
       </c>
       <c r="D207" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E207"/>
     </row>
@@ -4934,13 +5030,13 @@
         <v>134</v>
       </c>
       <c r="B208" t="s">
-        <v>356</v>
-      </c>
-      <c r="C208" s="2">
-        <v>114</v>
+        <v>358</v>
+      </c>
+      <c r="C208" s="3">
+        <v>115</v>
       </c>
       <c r="D208" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E208"/>
     </row>
@@ -4949,13 +5045,13 @@
         <v>134</v>
       </c>
       <c r="B209" t="s">
-        <v>358</v>
-      </c>
-      <c r="C209" s="2">
-        <v>115</v>
+        <v>360</v>
+      </c>
+      <c r="C209" s="3">
+        <v>116</v>
       </c>
       <c r="D209" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E209"/>
     </row>
@@ -4964,13 +5060,13 @@
         <v>134</v>
       </c>
       <c r="B210" t="s">
-        <v>360</v>
-      </c>
-      <c r="C210" s="2">
-        <v>116</v>
+        <v>362</v>
+      </c>
+      <c r="C210" s="3">
+        <v>117</v>
       </c>
       <c r="D210" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E210"/>
     </row>
@@ -4979,13 +5075,13 @@
         <v>134</v>
       </c>
       <c r="B211" t="s">
-        <v>362</v>
-      </c>
-      <c r="C211" s="2">
-        <v>117</v>
+        <v>364</v>
+      </c>
+      <c r="C211" s="3">
+        <v>118</v>
       </c>
       <c r="D211" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E211"/>
     </row>
@@ -4994,13 +5090,13 @@
         <v>134</v>
       </c>
       <c r="B212" t="s">
-        <v>364</v>
-      </c>
-      <c r="C212" s="2">
-        <v>118</v>
+        <v>366</v>
+      </c>
+      <c r="C212" s="3">
+        <v>119</v>
       </c>
       <c r="D212" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E212"/>
     </row>
@@ -5009,28 +5105,27 @@
         <v>134</v>
       </c>
       <c r="B213" t="s">
-        <v>366</v>
-      </c>
-      <c r="C213" s="2">
-        <v>119</v>
+        <v>368</v>
+      </c>
+      <c r="C213" s="3">
+        <v>120</v>
       </c>
       <c r="D213" t="s">
-        <v>367</v>
-      </c>
-      <c r="E213"/>
+        <v>369</v>
+      </c>
     </row>
     <row r="214" s="1" customFormat="1" spans="1:5">
       <c r="A214" s="1" t="s">
         <v>134</v>
       </c>
       <c r="B214" t="s">
-        <v>368</v>
-      </c>
-      <c r="C214" s="2">
-        <v>120</v>
-      </c>
-      <c r="D214" t="s">
-        <v>369</v>
+        <v>370</v>
+      </c>
+      <c r="C214" s="3">
+        <v>121</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="215" s="1" customFormat="1" spans="1:5">
@@ -5038,139 +5133,139 @@
         <v>134</v>
       </c>
       <c r="B215" t="s">
-        <v>370</v>
-      </c>
-      <c r="C215" s="2">
-        <v>121</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
+      </c>
+      <c r="C215" s="3">
+        <v>122</v>
+      </c>
+      <c r="D215" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="216" s="1" customFormat="1" spans="1:5">
       <c r="A216" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B216" t="s">
-        <v>372</v>
-      </c>
-      <c r="C216" s="2">
-        <v>122</v>
+      <c r="B216" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C216" s="3">
+        <v>123</v>
       </c>
       <c r="D216" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="217" s="1" customFormat="1" spans="1:5">
       <c r="A217" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B217" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C217" s="2">
-        <v>123</v>
+      <c r="B217" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C217" s="3">
+        <v>124</v>
       </c>
       <c r="D217" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="218" s="1" customFormat="1" spans="1:5">
       <c r="A218" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B218" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="C218" s="2">
-        <v>124</v>
+      <c r="B218" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C218" s="3">
+        <v>125</v>
       </c>
       <c r="D218" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="219" s="1" customFormat="1" spans="1:5">
       <c r="A219" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B219" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="C219" s="2">
-        <v>125</v>
+      <c r="B219" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C219" s="3">
+        <v>126</v>
       </c>
       <c r="D219" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="220" s="1" customFormat="1" spans="1:5">
       <c r="A220" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B220" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="C220" s="2">
-        <v>126</v>
+      <c r="B220" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C220" s="3">
+        <v>127</v>
       </c>
       <c r="D220" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="221" s="1" customFormat="1" spans="1:5">
       <c r="A221" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B221" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="C221" s="2">
-        <v>127</v>
+      <c r="B221" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C221" s="3">
+        <v>128</v>
       </c>
       <c r="D221" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="222" s="1" customFormat="1" spans="1:5">
       <c r="A222" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B222" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="C222" s="2">
-        <v>128</v>
+      <c r="B222" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C222" s="3">
+        <v>129</v>
       </c>
       <c r="D222" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="223" s="1" customFormat="1" spans="1:5">
       <c r="A223" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B223" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="C223" s="2">
-        <v>129</v>
+      <c r="B223" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="C223" s="3">
+        <v>130</v>
       </c>
       <c r="D223" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="224" s="1" customFormat="1" spans="1:5">
-      <c r="A224" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C224" s="2">
-        <v>130</v>
+        <v>389</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" t="s">
+        <v>134</v>
+      </c>
+      <c r="B224" t="s">
+        <v>390</v>
+      </c>
+      <c r="C224" s="3">
+        <v>131</v>
       </c>
       <c r="D224" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5178,13 +5273,13 @@
         <v>134</v>
       </c>
       <c r="B225" t="s">
-        <v>390</v>
-      </c>
-      <c r="C225" s="2">
-        <v>131</v>
+        <v>392</v>
+      </c>
+      <c r="C225" s="3">
+        <v>132</v>
       </c>
       <c r="D225" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5192,13 +5287,13 @@
         <v>134</v>
       </c>
       <c r="B226" t="s">
-        <v>392</v>
-      </c>
-      <c r="C226" s="2">
-        <v>132</v>
+        <v>394</v>
+      </c>
+      <c r="C226" s="3">
+        <v>133</v>
       </c>
       <c r="D226" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5206,13 +5301,13 @@
         <v>134</v>
       </c>
       <c r="B227" t="s">
-        <v>394</v>
-      </c>
-      <c r="C227" s="2">
-        <v>133</v>
+        <v>396</v>
+      </c>
+      <c r="C227" s="3">
+        <v>134</v>
       </c>
       <c r="D227" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5220,13 +5315,13 @@
         <v>134</v>
       </c>
       <c r="B228" t="s">
-        <v>396</v>
-      </c>
-      <c r="C228" s="2">
-        <v>134</v>
+        <v>398</v>
+      </c>
+      <c r="C228" s="3">
+        <v>135</v>
       </c>
       <c r="D228" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5234,13 +5329,13 @@
         <v>134</v>
       </c>
       <c r="B229" t="s">
-        <v>398</v>
-      </c>
-      <c r="C229" s="2">
-        <v>135</v>
+        <v>400</v>
+      </c>
+      <c r="C229" s="3">
+        <v>136</v>
       </c>
       <c r="D229" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5248,13 +5343,13 @@
         <v>134</v>
       </c>
       <c r="B230" t="s">
-        <v>400</v>
-      </c>
-      <c r="C230" s="2">
-        <v>136</v>
+        <v>402</v>
+      </c>
+      <c r="C230" s="3">
+        <v>137</v>
       </c>
       <c r="D230" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5262,13 +5357,13 @@
         <v>134</v>
       </c>
       <c r="B231" t="s">
-        <v>402</v>
-      </c>
-      <c r="C231" s="2">
-        <v>137</v>
+        <v>404</v>
+      </c>
+      <c r="C231" s="3">
+        <v>138</v>
       </c>
       <c r="D231" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5276,13 +5371,13 @@
         <v>134</v>
       </c>
       <c r="B232" t="s">
-        <v>404</v>
-      </c>
-      <c r="C232" s="2">
-        <v>138</v>
+        <v>406</v>
+      </c>
+      <c r="C232" s="3">
+        <v>139</v>
       </c>
       <c r="D232" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5290,13 +5385,13 @@
         <v>134</v>
       </c>
       <c r="B233" t="s">
-        <v>406</v>
-      </c>
-      <c r="C233" s="2">
-        <v>139</v>
+        <v>408</v>
+      </c>
+      <c r="C233" s="3">
+        <v>140</v>
       </c>
       <c r="D233" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5304,13 +5399,13 @@
         <v>134</v>
       </c>
       <c r="B234" t="s">
-        <v>408</v>
-      </c>
-      <c r="C234" s="2">
-        <v>140</v>
+        <v>410</v>
+      </c>
+      <c r="C234" s="3">
+        <v>141</v>
       </c>
       <c r="D234" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5318,13 +5413,13 @@
         <v>134</v>
       </c>
       <c r="B235" t="s">
-        <v>410</v>
-      </c>
-      <c r="C235" s="2">
-        <v>141</v>
+        <v>412</v>
+      </c>
+      <c r="C235" s="3">
+        <v>142</v>
       </c>
       <c r="D235" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5332,13 +5427,13 @@
         <v>134</v>
       </c>
       <c r="B236" t="s">
-        <v>412</v>
-      </c>
-      <c r="C236" s="2">
-        <v>142</v>
+        <v>414</v>
+      </c>
+      <c r="C236" s="3">
+        <v>143</v>
       </c>
       <c r="D236" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5346,13 +5441,13 @@
         <v>134</v>
       </c>
       <c r="B237" t="s">
-        <v>414</v>
-      </c>
-      <c r="C237" s="2">
-        <v>143</v>
+        <v>416</v>
+      </c>
+      <c r="C237" s="3">
+        <v>144</v>
       </c>
       <c r="D237" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5360,13 +5455,13 @@
         <v>134</v>
       </c>
       <c r="B238" t="s">
-        <v>416</v>
-      </c>
-      <c r="C238" s="2">
-        <v>144</v>
+        <v>418</v>
+      </c>
+      <c r="C238" s="3">
+        <v>145</v>
       </c>
       <c r="D238" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5374,69 +5469,69 @@
         <v>134</v>
       </c>
       <c r="B239" t="s">
-        <v>418</v>
-      </c>
-      <c r="C239" s="2">
-        <v>145</v>
+        <v>420</v>
+      </c>
+      <c r="C239" s="3">
+        <v>146</v>
       </c>
       <c r="D239" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
         <v>134</v>
       </c>
-      <c r="B240" t="s">
-        <v>420</v>
-      </c>
-      <c r="C240" s="2">
-        <v>146</v>
-      </c>
-      <c r="D240" t="s">
-        <v>421</v>
+      <c r="B240" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C240" s="3">
+        <v>147</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
         <v>134</v>
       </c>
-      <c r="B241" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="C241" s="2">
-        <v>147</v>
+      <c r="B241" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C241" s="3">
+        <v>148</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
         <v>134</v>
       </c>
-      <c r="B242" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="C242" s="2">
-        <v>148</v>
-      </c>
-      <c r="D242" s="1" t="s">
-        <v>425</v>
+      <c r="B242" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C242" s="3">
+        <v>149</v>
+      </c>
+      <c r="D242" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
         <v>134</v>
       </c>
-      <c r="B243" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="C243" s="2">
-        <v>149</v>
+      <c r="B243" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C243" s="3">
+        <v>150</v>
       </c>
       <c r="D243" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5444,27 +5539,27 @@
         <v>134</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C244" s="2">
-        <v>150</v>
+        <v>430</v>
+      </c>
+      <c r="C244" s="3">
+        <v>151</v>
       </c>
       <c r="D244" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
         <v>134</v>
       </c>
-      <c r="B245" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C245" s="2">
-        <v>151</v>
-      </c>
-      <c r="D245" t="s">
-        <v>431</v>
+      <c r="B245" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="C245" s="3">
+        <v>152</v>
+      </c>
+      <c r="D245" s="4" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5480,18 +5575,26 @@
       <c r="D248"/>
     </row>
     <row r="249" spans="1:4">
-      <c r="B249"/>
+      <c r="A249" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C249" s="3">
+        <v>1111</v>
+      </c>
       <c r="D249"/>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B250" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="C250" s="2">
-        <v>1111</v>
+      <c r="B250" t="s">
+        <v>435</v>
+      </c>
+      <c r="C250" s="3">
+        <v>1112</v>
       </c>
       <c r="D250"/>
     </row>
@@ -5500,23 +5603,15 @@
         <v>134</v>
       </c>
       <c r="B251" t="s">
-        <v>433</v>
-      </c>
-      <c r="C251" s="2">
-        <v>1112</v>
+        <v>436</v>
+      </c>
+      <c r="C251" s="3">
+        <v>1113</v>
       </c>
       <c r="D251"/>
     </row>
     <row r="252" spans="1:4">
-      <c r="A252" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B252" t="s">
-        <v>434</v>
-      </c>
-      <c r="C252" s="2">
-        <v>1113</v>
-      </c>
+      <c r="B252"/>
       <c r="D252"/>
     </row>
     <row r="253" spans="1:4">
@@ -5587,246 +5682,392 @@
       <c r="B269"/>
       <c r="D269"/>
     </row>
-    <row r="270" spans="1:4">
-      <c r="B270"/>
-      <c r="D270"/>
+    <row r="271" spans="1:4">
+      <c r="A271" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C271" s="3">
+        <v>1</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="B272" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="C272" s="2">
-        <v>1</v>
+        <v>437</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C272" s="3">
+        <v>2</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="C273" s="2">
-        <v>2</v>
+        <v>437</v>
+      </c>
+      <c r="B273" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C273" s="3">
+        <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="274" spans="1:4">
       <c r="A274" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="C274" s="2">
-        <v>3</v>
+        <v>437</v>
+      </c>
+      <c r="B274" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C274" s="3">
+        <v>4</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="275" spans="1:4">
       <c r="A275" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="B275" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C275" s="2">
-        <v>4</v>
+        <v>437</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="C275" s="3">
+        <v>5</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="276" spans="1:4">
       <c r="A276" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="B276" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="C276" s="2">
-        <v>5</v>
+        <v>437</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C276" s="3">
+        <v>6</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="277" spans="1:4">
       <c r="A277" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="B277" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="C277" s="2">
-        <v>6</v>
+        <v>437</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C277" s="3">
+        <v>7</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="278" spans="1:4">
-      <c r="A278" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="C278" s="2">
-        <v>7</v>
-      </c>
-      <c r="D278" s="1" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4">
-      <c r="A279" t="s">
-        <v>435</v>
-      </c>
-      <c r="B279" t="s">
+      <c r="A278" t="s">
+        <v>437</v>
+      </c>
+      <c r="B278" t="s">
         <v>15</v>
       </c>
-      <c r="C279" s="2">
+      <c r="C278" s="3">
         <v>8</v>
       </c>
-      <c r="D279" t="s">
-        <v>448</v>
+      <c r="D278" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="279" s="2" customFormat="1" spans="1:4">
+      <c r="A279" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C279" s="6">
+        <v>9</v>
+      </c>
+      <c r="D279" s="5" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B280" t="s">
-        <v>449</v>
-      </c>
-      <c r="C280" s="2">
-        <v>9</v>
+        <v>453</v>
+      </c>
+      <c r="C280" s="3">
+        <v>10</v>
       </c>
       <c r="D280" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B281" t="s">
-        <v>451</v>
-      </c>
-      <c r="C281" s="2">
-        <v>10</v>
+        <v>455</v>
+      </c>
+      <c r="C281" s="3">
+        <v>11</v>
       </c>
       <c r="D281" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4">
-      <c r="A282" t="s">
-        <v>435</v>
-      </c>
-      <c r="B282" t="s">
-        <v>453</v>
-      </c>
-      <c r="C282" s="2">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="282" s="2" customFormat="1" spans="1:4">
+      <c r="A282" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B282" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D282" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4">
-      <c r="A283" t="s">
-        <v>455</v>
-      </c>
-      <c r="B283" t="s">
-        <v>456</v>
-      </c>
-      <c r="C283" s="2">
+      <c r="C282" s="6">
+        <v>12</v>
+      </c>
+      <c r="D282" s="5" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="283" s="2" customFormat="1" spans="1:4">
+      <c r="A283" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C283" s="6">
+        <v>13</v>
+      </c>
+      <c r="D283" s="5" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="284" s="2" customFormat="1" spans="1:4">
+      <c r="A284" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="C284" s="6">
+        <v>14</v>
+      </c>
+      <c r="D284" s="5" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="285" s="2" customFormat="1" spans="1:4">
+      <c r="A285" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B285" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="C285" s="6">
+        <v>15</v>
+      </c>
+      <c r="D285" s="5" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="286" s="2" customFormat="1" spans="1:4">
+      <c r="A286" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="C286" s="6">
+        <v>16</v>
+      </c>
+      <c r="D286" s="5" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="287" s="2" customFormat="1" spans="1:4">
+      <c r="A287" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B287" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="C287" s="6">
+        <v>17</v>
+      </c>
+      <c r="D287" s="5" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="288" s="2" customFormat="1" spans="1:4">
+      <c r="A288" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="C288" s="6">
+        <v>18</v>
+      </c>
+      <c r="D288" s="5" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="289" s="2" customFormat="1" spans="1:4">
+      <c r="A289" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="C289" s="6">
+        <v>19</v>
+      </c>
+      <c r="D289" s="5" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="290" s="2" customFormat="1" spans="1:4">
+      <c r="A290" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="C290" s="6">
+        <v>20</v>
+      </c>
+      <c r="D290" s="5" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="291" s="2" customFormat="1" spans="1:4">
+      <c r="A291" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="C291" s="6">
+        <v>21</v>
+      </c>
+      <c r="D291" s="5" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292"/>
+      <c r="B292"/>
+      <c r="D292"/>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293"/>
+      <c r="B293"/>
+      <c r="D293"/>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" t="s">
+        <v>476</v>
+      </c>
+      <c r="B294" t="s">
+        <v>477</v>
+      </c>
+      <c r="C294" s="3">
         <v>1</v>
       </c>
-      <c r="D283" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4">
-      <c r="A284" t="s">
-        <v>455</v>
-      </c>
-      <c r="B284" t="s">
-        <v>458</v>
-      </c>
-      <c r="C284" s="2">
+      <c r="D294" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" t="s">
+        <v>476</v>
+      </c>
+      <c r="B295" t="s">
+        <v>479</v>
+      </c>
+      <c r="C295" s="3">
         <v>2</v>
       </c>
-      <c r="D284" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4">
-      <c r="A285" t="s">
-        <v>455</v>
-      </c>
-      <c r="B285" t="s">
-        <v>460</v>
-      </c>
-      <c r="C285" s="2">
+      <c r="D295" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" t="s">
+        <v>476</v>
+      </c>
+      <c r="B296" t="s">
+        <v>481</v>
+      </c>
+      <c r="C296" s="3">
         <v>3</v>
       </c>
-      <c r="D285" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4">
-      <c r="A286" t="s">
-        <v>462</v>
-      </c>
-      <c r="B286" t="s">
-        <v>463</v>
-      </c>
-      <c r="C286" s="2">
+      <c r="D296" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" t="s">
+        <v>483</v>
+      </c>
+      <c r="B297" t="s">
+        <v>484</v>
+      </c>
+      <c r="C297" s="3">
         <v>1</v>
       </c>
-      <c r="D286" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4">
-      <c r="A287" t="s">
-        <v>462</v>
-      </c>
-      <c r="B287" t="s">
-        <v>465</v>
-      </c>
-      <c r="C287" s="2">
+      <c r="D297" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" t="s">
+        <v>483</v>
+      </c>
+      <c r="B298" t="s">
+        <v>486</v>
+      </c>
+      <c r="C298" s="3">
         <v>2</v>
       </c>
-      <c r="D287" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4">
-      <c r="A288" t="s">
-        <v>462</v>
-      </c>
-      <c r="B288" t="s">
-        <v>467</v>
-      </c>
-      <c r="C288" s="2">
+      <c r="D298" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" t="s">
+        <v>483</v>
+      </c>
+      <c r="B299" t="s">
+        <v>488</v>
+      </c>
+      <c r="C299" s="3">
         <v>3</v>
       </c>
-      <c r="D288" t="s">
-        <v>468</v>
+      <c r="D299" t="s">
+        <v>489</v>
       </c>
     </row>
   </sheetData>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="13170" windowHeight="10470"/>
+    <workbookView windowWidth="13170" windowHeight="11550"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="492">
   <si>
     <t>Enum</t>
   </si>
@@ -1334,6 +1334,12 @@
   </si>
   <si>
     <t>巨人药剂</t>
+  </si>
+  <si>
+    <t>CardProvideAttack</t>
+  </si>
+  <si>
+    <t>卡牌提供攻击力</t>
   </si>
   <si>
     <t>MaxHp</t>
@@ -2123,11 +2129,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -2138,6 +2147,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2493,12 +2508,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:E299"/>
+  <dimension ref="A4:E300"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16.7416666666667" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.7" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.05833333333333" style="3" customWidth="1"/>
+    <col min="3" max="3" width="7.05833333333333" style="4" customWidth="1"/>
     <col min="4" max="4" width="31.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="34.75" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1" customWidth="1"/>
@@ -2511,7 +2526,7 @@
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
@@ -2525,7 +2540,7 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="4">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -2539,7 +2554,7 @@
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="4">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -2553,7 +2568,7 @@
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="4">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -2567,7 +2582,7 @@
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="4">
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -2581,7 +2596,7 @@
       <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="4">
         <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -2595,7 +2610,7 @@
       <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="4">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -2609,7 +2624,7 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="4">
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -2623,7 +2638,7 @@
       <c r="B14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="4">
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -2637,7 +2652,7 @@
       <c r="B16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="4">
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -2651,7 +2666,7 @@
       <c r="B17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="4">
         <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -2665,7 +2680,7 @@
       <c r="B19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="4">
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -2679,7 +2694,7 @@
       <c r="B20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="4">
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -2693,7 +2708,7 @@
       <c r="B21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="4">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -2707,7 +2722,7 @@
       <c r="B22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="4">
         <v>4</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -2721,7 +2736,7 @@
       <c r="B39" t="s">
         <v>36</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="4">
         <v>1</v>
       </c>
       <c r="D39" t="s">
@@ -2735,7 +2750,7 @@
       <c r="B40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="4">
         <v>2</v>
       </c>
       <c r="D40" t="s">
@@ -2749,7 +2764,7 @@
       <c r="B41" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="4">
         <v>3</v>
       </c>
       <c r="D41" t="s">
@@ -2763,7 +2778,7 @@
       <c r="B42" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="4">
         <v>4</v>
       </c>
       <c r="D42" t="s">
@@ -2777,7 +2792,7 @@
       <c r="B43" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="4">
         <v>5</v>
       </c>
       <c r="D43" t="s">
@@ -2791,7 +2806,7 @@
       <c r="B44" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="4">
         <v>6</v>
       </c>
       <c r="D44" s="1" t="s">
@@ -2805,7 +2820,7 @@
       <c r="B45" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="4">
         <v>7</v>
       </c>
       <c r="D45" s="1" t="s">
@@ -2819,7 +2834,7 @@
       <c r="B46" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="4">
         <v>8</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -2833,7 +2848,7 @@
       <c r="B47" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="4">
         <v>9</v>
       </c>
       <c r="D47" s="1" t="s">
@@ -2847,7 +2862,7 @@
       <c r="B48" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="4">
         <v>10</v>
       </c>
       <c r="D48" s="1" t="s">
@@ -2861,7 +2876,7 @@
       <c r="B49" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="4">
         <v>11</v>
       </c>
       <c r="D49" s="1" t="s">
@@ -2875,7 +2890,7 @@
       <c r="B50" t="s">
         <v>58</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="4">
         <v>12</v>
       </c>
       <c r="D50" t="s">
@@ -2889,7 +2904,7 @@
       <c r="B51" t="s">
         <v>60</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="4">
         <v>13</v>
       </c>
       <c r="D51" t="s">
@@ -2903,7 +2918,7 @@
       <c r="B52" t="s">
         <v>62</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C52" s="4">
         <v>14</v>
       </c>
       <c r="D52" t="s">
@@ -2917,7 +2932,7 @@
       <c r="B53" t="s">
         <v>64</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53" s="4">
         <v>15</v>
       </c>
       <c r="D53" t="s">
@@ -2931,7 +2946,7 @@
       <c r="B54" t="s">
         <v>66</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C54" s="4">
         <v>16</v>
       </c>
       <c r="D54" t="s">
@@ -2945,7 +2960,7 @@
       <c r="B55" t="s">
         <v>68</v>
       </c>
-      <c r="C55" s="3">
+      <c r="C55" s="4">
         <v>17</v>
       </c>
       <c r="D55" t="s">
@@ -2959,7 +2974,7 @@
       <c r="B56" t="s">
         <v>70</v>
       </c>
-      <c r="C56" s="3">
+      <c r="C56" s="4">
         <v>18</v>
       </c>
       <c r="D56" t="s">
@@ -2973,7 +2988,7 @@
       <c r="B57" t="s">
         <v>72</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57" s="4">
         <v>19</v>
       </c>
       <c r="D57" t="s">
@@ -2987,7 +3002,7 @@
       <c r="B58" t="s">
         <v>74</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="4">
         <v>20</v>
       </c>
       <c r="D58" t="s">
@@ -3001,7 +3016,7 @@
       <c r="B59" t="s">
         <v>76</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="4">
         <v>21</v>
       </c>
       <c r="D59" t="s">
@@ -3015,7 +3030,7 @@
       <c r="B60" t="s">
         <v>78</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60" s="4">
         <v>22</v>
       </c>
       <c r="D60" t="s">
@@ -3029,7 +3044,7 @@
       <c r="B61" t="s">
         <v>80</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="4">
         <v>23</v>
       </c>
       <c r="D61" t="s">
@@ -3043,7 +3058,7 @@
       <c r="B62" t="s">
         <v>82</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62" s="4">
         <v>24</v>
       </c>
       <c r="D62" t="s">
@@ -3057,7 +3072,7 @@
       <c r="B63" t="s">
         <v>84</v>
       </c>
-      <c r="C63" s="3">
+      <c r="C63" s="4">
         <v>25</v>
       </c>
       <c r="D63" t="s">
@@ -3071,7 +3086,7 @@
       <c r="B64" t="s">
         <v>86</v>
       </c>
-      <c r="C64" s="3">
+      <c r="C64" s="4">
         <v>26</v>
       </c>
       <c r="D64" t="s">
@@ -3085,7 +3100,7 @@
       <c r="B65" t="s">
         <v>88</v>
       </c>
-      <c r="C65" s="3">
+      <c r="C65" s="4">
         <v>27</v>
       </c>
       <c r="D65" t="s">
@@ -3099,7 +3114,7 @@
       <c r="B66" t="s">
         <v>90</v>
       </c>
-      <c r="C66" s="3">
+      <c r="C66" s="4">
         <v>28</v>
       </c>
       <c r="D66" t="s">
@@ -3113,7 +3128,7 @@
       <c r="B67" t="s">
         <v>92</v>
       </c>
-      <c r="C67" s="3">
+      <c r="C67" s="4">
         <v>29</v>
       </c>
       <c r="D67" t="s">
@@ -3127,7 +3142,7 @@
       <c r="B68" t="s">
         <v>94</v>
       </c>
-      <c r="C68" s="3">
+      <c r="C68" s="4">
         <v>30</v>
       </c>
       <c r="D68" t="s">
@@ -3141,7 +3156,7 @@
       <c r="B69" t="s">
         <v>96</v>
       </c>
-      <c r="C69" s="3">
+      <c r="C69" s="4">
         <v>31</v>
       </c>
       <c r="D69" t="s">
@@ -3155,7 +3170,7 @@
       <c r="B70" t="s">
         <v>98</v>
       </c>
-      <c r="C70" s="3">
+      <c r="C70" s="4">
         <v>32</v>
       </c>
       <c r="D70" t="s">
@@ -3169,7 +3184,7 @@
       <c r="B71" t="s">
         <v>100</v>
       </c>
-      <c r="C71" s="3">
+      <c r="C71" s="4">
         <v>33</v>
       </c>
       <c r="D71" t="s">
@@ -3183,7 +3198,7 @@
       <c r="B72" t="s">
         <v>102</v>
       </c>
-      <c r="C72" s="3">
+      <c r="C72" s="4">
         <v>34</v>
       </c>
       <c r="D72" t="s">
@@ -3197,7 +3212,7 @@
       <c r="B73" t="s">
         <v>104</v>
       </c>
-      <c r="C73" s="3">
+      <c r="C73" s="4">
         <v>35</v>
       </c>
       <c r="D73" t="s">
@@ -3211,7 +3226,7 @@
       <c r="B74" t="s">
         <v>106</v>
       </c>
-      <c r="C74" s="3">
+      <c r="C74" s="4">
         <v>36</v>
       </c>
       <c r="D74" t="s">
@@ -3225,7 +3240,7 @@
       <c r="B75" t="s">
         <v>108</v>
       </c>
-      <c r="C75" s="3">
+      <c r="C75" s="4">
         <v>37</v>
       </c>
       <c r="D75" t="s">
@@ -3239,7 +3254,7 @@
       <c r="B76" t="s">
         <v>110</v>
       </c>
-      <c r="C76" s="3">
+      <c r="C76" s="4">
         <v>38</v>
       </c>
       <c r="D76" t="s">
@@ -3253,7 +3268,7 @@
       <c r="B77" t="s">
         <v>112</v>
       </c>
-      <c r="C77" s="3">
+      <c r="C77" s="4">
         <v>39</v>
       </c>
       <c r="D77" t="s">
@@ -3267,7 +3282,7 @@
       <c r="B78" t="s">
         <v>114</v>
       </c>
-      <c r="C78" s="3">
+      <c r="C78" s="4">
         <v>40</v>
       </c>
       <c r="D78" t="s">
@@ -3281,7 +3296,7 @@
       <c r="B79" t="s">
         <v>116</v>
       </c>
-      <c r="C79" s="3">
+      <c r="C79" s="4">
         <v>41</v>
       </c>
       <c r="D79" t="s">
@@ -3295,7 +3310,7 @@
       <c r="B80" t="s">
         <v>118</v>
       </c>
-      <c r="C80" s="3">
+      <c r="C80" s="4">
         <v>42</v>
       </c>
       <c r="D80" t="s">
@@ -3309,7 +3324,7 @@
       <c r="B81" t="s">
         <v>120</v>
       </c>
-      <c r="C81" s="3">
+      <c r="C81" s="4">
         <v>43</v>
       </c>
       <c r="D81" t="s">
@@ -3323,7 +3338,7 @@
       <c r="B82" t="s">
         <v>122</v>
       </c>
-      <c r="C82" s="3">
+      <c r="C82" s="4">
         <v>44</v>
       </c>
       <c r="D82" t="s">
@@ -3337,7 +3352,7 @@
       <c r="B83" t="s">
         <v>124</v>
       </c>
-      <c r="C83" s="3">
+      <c r="C83" s="4">
         <v>45</v>
       </c>
       <c r="D83" t="s">
@@ -3351,7 +3366,7 @@
       <c r="B84" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C84" s="3">
+      <c r="C84" s="4">
         <v>46</v>
       </c>
       <c r="D84" t="s">
@@ -3365,7 +3380,7 @@
       <c r="B85" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C85" s="3">
+      <c r="C85" s="4">
         <v>47</v>
       </c>
       <c r="D85" t="s">
@@ -3379,7 +3394,7 @@
       <c r="B86" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C86" s="3">
+      <c r="C86" s="4">
         <v>48</v>
       </c>
       <c r="D86" t="s">
@@ -3393,7 +3408,7 @@
       <c r="B87" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C87" s="3">
+      <c r="C87" s="4">
         <v>49</v>
       </c>
       <c r="D87" t="s">
@@ -3403,7 +3418,7 @@
     <row r="88" customFormat="1" spans="1:4">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
-      <c r="C88" s="3"/>
+      <c r="C88" s="4"/>
       <c r="D88" s="1"/>
     </row>
     <row r="94" spans="1:4">
@@ -3413,7 +3428,7 @@
       <c r="B94" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C94" s="3">
+      <c r="C94" s="4">
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
@@ -3427,7 +3442,7 @@
       <c r="B95" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C95" s="3">
+      <c r="C95" s="4">
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
@@ -3441,7 +3456,7 @@
       <c r="B96" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C96" s="3">
+      <c r="C96" s="4">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
@@ -3452,10 +3467,10 @@
       <c r="A97" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C97" s="3">
+      <c r="C97" s="4">
         <v>4</v>
       </c>
       <c r="D97" s="1" t="s">
@@ -3466,10 +3481,10 @@
       <c r="A98" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C98" s="3">
+      <c r="C98" s="4">
         <v>5</v>
       </c>
       <c r="D98" s="1" t="s">
@@ -3480,10 +3495,10 @@
       <c r="A99" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C99" s="3">
+      <c r="C99" s="4">
         <v>6</v>
       </c>
       <c r="D99" s="1" t="s">
@@ -3494,10 +3509,10 @@
       <c r="A100" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C100" s="3">
+      <c r="C100" s="4">
         <v>7</v>
       </c>
       <c r="D100" s="1" t="s">
@@ -3508,10 +3523,10 @@
       <c r="A101" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C101" s="3">
+      <c r="C101" s="4">
         <v>8</v>
       </c>
       <c r="D101" s="1" t="s">
@@ -3522,10 +3537,10 @@
       <c r="A102" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="B102" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C102" s="3">
+      <c r="C102" s="4">
         <v>9</v>
       </c>
       <c r="D102" s="1" t="s">
@@ -3536,10 +3551,10 @@
       <c r="A103" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C103" s="3">
+      <c r="C103" s="4">
         <v>10</v>
       </c>
       <c r="D103" s="1" t="s">
@@ -3550,10 +3565,10 @@
       <c r="A104" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B104" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C104" s="3">
+      <c r="C104" s="4">
         <v>11</v>
       </c>
       <c r="D104" s="1" t="s">
@@ -3564,10 +3579,10 @@
       <c r="A105" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B105" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C105" s="3">
+      <c r="C105" s="4">
         <v>12</v>
       </c>
       <c r="D105" s="1" t="s">
@@ -3578,10 +3593,10 @@
       <c r="A106" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C106" s="3">
+      <c r="C106" s="4">
         <v>13</v>
       </c>
       <c r="D106" s="1" t="s">
@@ -3592,10 +3607,10 @@
       <c r="A107" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B107" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C107" s="3">
+      <c r="C107" s="4">
         <v>14</v>
       </c>
       <c r="D107" s="1" t="s">
@@ -3606,10 +3621,10 @@
       <c r="A108" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B108" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C108" s="3">
+      <c r="C108" s="4">
         <v>15</v>
       </c>
       <c r="D108" s="1" t="s">
@@ -3623,7 +3638,7 @@
       <c r="B109" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C109" s="3">
+      <c r="C109" s="4">
         <v>16</v>
       </c>
       <c r="D109" s="1" t="s">
@@ -3634,10 +3649,10 @@
       <c r="A110" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="B110" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="C110" s="3">
+      <c r="C110" s="4">
         <v>17</v>
       </c>
       <c r="D110" s="1" t="s">
@@ -3651,7 +3666,7 @@
       <c r="B111" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C111" s="3">
+      <c r="C111" s="4">
         <v>18</v>
       </c>
       <c r="D111" s="1" t="s">
@@ -3662,10 +3677,10 @@
       <c r="A112" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B112" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C112" s="3">
+      <c r="C112" s="4">
         <v>19</v>
       </c>
       <c r="D112" s="1" t="s">
@@ -3679,7 +3694,7 @@
       <c r="B113" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C113" s="3">
+      <c r="C113" s="4">
         <v>20</v>
       </c>
       <c r="D113" s="1" t="s">
@@ -3693,7 +3708,7 @@
       <c r="B114" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C114" s="3">
+      <c r="C114" s="4">
         <v>21</v>
       </c>
       <c r="D114" s="1" t="s">
@@ -3704,10 +3719,10 @@
       <c r="A115" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B115" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C115" s="3">
+      <c r="C115" s="4">
         <v>22</v>
       </c>
       <c r="D115" s="1" t="s">
@@ -3718,10 +3733,10 @@
       <c r="A116" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="B116" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="C116" s="3">
+      <c r="C116" s="4">
         <v>23</v>
       </c>
       <c r="D116" s="1" t="s">
@@ -3735,7 +3750,7 @@
       <c r="B117" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C117" s="3">
+      <c r="C117" s="4">
         <v>24</v>
       </c>
       <c r="D117" s="1" t="s">
@@ -3749,7 +3764,7 @@
       <c r="B118" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C118" s="3">
+      <c r="C118" s="4">
         <v>25</v>
       </c>
       <c r="D118" s="1" t="s">
@@ -3763,7 +3778,7 @@
       <c r="B119" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C119" s="3">
+      <c r="C119" s="4">
         <v>26</v>
       </c>
       <c r="D119" s="1" t="s">
@@ -3777,7 +3792,7 @@
       <c r="B120" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C120" s="3">
+      <c r="C120" s="4">
         <v>27</v>
       </c>
       <c r="D120" s="1" t="s">
@@ -3791,7 +3806,7 @@
       <c r="B121" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C121" s="3">
+      <c r="C121" s="4">
         <v>28</v>
       </c>
       <c r="D121" s="1" t="s">
@@ -3805,7 +3820,7 @@
       <c r="B122" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C122" s="3">
+      <c r="C122" s="4">
         <v>29</v>
       </c>
       <c r="D122" s="1" t="s">
@@ -3819,7 +3834,7 @@
       <c r="B123" t="s">
         <v>193</v>
       </c>
-      <c r="C123" s="3">
+      <c r="C123" s="4">
         <v>30</v>
       </c>
       <c r="D123" s="1" t="s">
@@ -3833,7 +3848,7 @@
       <c r="B124" t="s">
         <v>195</v>
       </c>
-      <c r="C124" s="3">
+      <c r="C124" s="4">
         <v>31</v>
       </c>
       <c r="D124" s="1" t="s">
@@ -3847,7 +3862,7 @@
       <c r="B125" t="s">
         <v>197</v>
       </c>
-      <c r="C125" s="3">
+      <c r="C125" s="4">
         <v>32</v>
       </c>
       <c r="D125" s="1" t="s">
@@ -3861,7 +3876,7 @@
       <c r="B126" t="s">
         <v>199</v>
       </c>
-      <c r="C126" s="3">
+      <c r="C126" s="4">
         <v>33</v>
       </c>
       <c r="D126" s="1" t="s">
@@ -3875,7 +3890,7 @@
       <c r="B127" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C127" s="3">
+      <c r="C127" s="4">
         <v>34</v>
       </c>
       <c r="D127" t="s">
@@ -3889,7 +3904,7 @@
       <c r="B128" t="s">
         <v>13</v>
       </c>
-      <c r="C128" s="3">
+      <c r="C128" s="4">
         <v>35</v>
       </c>
       <c r="D128" t="s">
@@ -3903,7 +3918,7 @@
       <c r="B129" t="s">
         <v>15</v>
       </c>
-      <c r="C129" s="3">
+      <c r="C129" s="4">
         <v>36</v>
       </c>
       <c r="D129" t="s">
@@ -3917,7 +3932,7 @@
       <c r="B130" t="s">
         <v>17</v>
       </c>
-      <c r="C130" s="3">
+      <c r="C130" s="4">
         <v>37</v>
       </c>
       <c r="D130" t="s">
@@ -3928,10 +3943,10 @@
       <c r="A131" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B131" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C131" s="3">
+      <c r="C131" s="4">
         <v>38</v>
       </c>
       <c r="D131" t="s">
@@ -3945,7 +3960,7 @@
       <c r="B132" t="s">
         <v>206</v>
       </c>
-      <c r="C132" s="3">
+      <c r="C132" s="4">
         <v>39</v>
       </c>
       <c r="D132" t="s">
@@ -3959,7 +3974,7 @@
       <c r="B133" t="s">
         <v>208</v>
       </c>
-      <c r="C133" s="3">
+      <c r="C133" s="4">
         <v>40</v>
       </c>
       <c r="D133" t="s">
@@ -3973,7 +3988,7 @@
       <c r="B134" t="s">
         <v>210</v>
       </c>
-      <c r="C134" s="3">
+      <c r="C134" s="4">
         <v>41</v>
       </c>
       <c r="D134" t="s">
@@ -3987,7 +4002,7 @@
       <c r="B135" t="s">
         <v>212</v>
       </c>
-      <c r="C135" s="3">
+      <c r="C135" s="4">
         <v>42</v>
       </c>
       <c r="D135" t="s">
@@ -4001,7 +4016,7 @@
       <c r="B136" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C136" s="3">
+      <c r="C136" s="4">
         <v>43</v>
       </c>
       <c r="D136" t="s">
@@ -4015,7 +4030,7 @@
       <c r="B137" t="s">
         <v>216</v>
       </c>
-      <c r="C137" s="3">
+      <c r="C137" s="4">
         <v>44</v>
       </c>
       <c r="D137" t="s">
@@ -4029,7 +4044,7 @@
       <c r="B138" t="s">
         <v>218</v>
       </c>
-      <c r="C138" s="3">
+      <c r="C138" s="4">
         <v>45</v>
       </c>
       <c r="D138" t="s">
@@ -4043,7 +4058,7 @@
       <c r="B139" t="s">
         <v>220</v>
       </c>
-      <c r="C139" s="3">
+      <c r="C139" s="4">
         <v>46</v>
       </c>
       <c r="D139" t="s">
@@ -4054,10 +4069,10 @@
       <c r="A140" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="B140" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="C140" s="3">
+      <c r="C140" s="4">
         <v>47</v>
       </c>
       <c r="D140" t="s">
@@ -4068,10 +4083,10 @@
       <c r="A141" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C141" s="3">
+      <c r="C141" s="4">
         <v>48</v>
       </c>
       <c r="D141" t="s">
@@ -4085,7 +4100,7 @@
       <c r="B142" t="s">
         <v>226</v>
       </c>
-      <c r="C142" s="3">
+      <c r="C142" s="4">
         <v>49</v>
       </c>
       <c r="D142" t="s">
@@ -4099,7 +4114,7 @@
       <c r="B143" t="s">
         <v>228</v>
       </c>
-      <c r="C143" s="3">
+      <c r="C143" s="4">
         <v>50</v>
       </c>
       <c r="D143" t="s">
@@ -4110,10 +4125,10 @@
       <c r="A144" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B144" s="3" t="s">
+      <c r="B144" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="C144" s="3">
+      <c r="C144" s="4">
         <v>51</v>
       </c>
       <c r="D144" t="s">
@@ -4127,7 +4142,7 @@
       <c r="B145" t="s">
         <v>232</v>
       </c>
-      <c r="C145" s="3">
+      <c r="C145" s="4">
         <v>52</v>
       </c>
       <c r="D145" t="s">
@@ -4141,7 +4156,7 @@
       <c r="B146" t="s">
         <v>234</v>
       </c>
-      <c r="C146" s="3">
+      <c r="C146" s="4">
         <v>53</v>
       </c>
       <c r="D146" t="s">
@@ -4155,7 +4170,7 @@
       <c r="B147" t="s">
         <v>236</v>
       </c>
-      <c r="C147" s="3">
+      <c r="C147" s="4">
         <v>54</v>
       </c>
       <c r="D147" t="s">
@@ -4169,7 +4184,7 @@
       <c r="B148" t="s">
         <v>238</v>
       </c>
-      <c r="C148" s="3">
+      <c r="C148" s="4">
         <v>55</v>
       </c>
       <c r="D148" t="s">
@@ -4180,10 +4195,10 @@
       <c r="A149" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="B149" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="C149" s="3">
+      <c r="C149" s="4">
         <v>56</v>
       </c>
       <c r="D149" t="s">
@@ -4197,7 +4212,7 @@
       <c r="B150" t="s">
         <v>242</v>
       </c>
-      <c r="C150" s="3">
+      <c r="C150" s="4">
         <v>57</v>
       </c>
       <c r="D150" t="s">
@@ -4211,7 +4226,7 @@
       <c r="B151" t="s">
         <v>244</v>
       </c>
-      <c r="C151" s="3">
+      <c r="C151" s="4">
         <v>58</v>
       </c>
       <c r="D151" t="s">
@@ -4225,7 +4240,7 @@
       <c r="B152" t="s">
         <v>246</v>
       </c>
-      <c r="C152" s="3">
+      <c r="C152" s="4">
         <v>59</v>
       </c>
       <c r="D152" t="s">
@@ -4239,7 +4254,7 @@
       <c r="B153" t="s">
         <v>248</v>
       </c>
-      <c r="C153" s="3">
+      <c r="C153" s="4">
         <v>60</v>
       </c>
       <c r="D153" t="s">
@@ -4253,7 +4268,7 @@
       <c r="B154" t="s">
         <v>250</v>
       </c>
-      <c r="C154" s="3">
+      <c r="C154" s="4">
         <v>61</v>
       </c>
       <c r="D154" t="s">
@@ -4267,7 +4282,7 @@
       <c r="B155" t="s">
         <v>252</v>
       </c>
-      <c r="C155" s="3">
+      <c r="C155" s="4">
         <v>62</v>
       </c>
       <c r="D155" t="s">
@@ -4281,7 +4296,7 @@
       <c r="B156" t="s">
         <v>254</v>
       </c>
-      <c r="C156" s="3">
+      <c r="C156" s="4">
         <v>63</v>
       </c>
       <c r="D156" t="s">
@@ -4295,7 +4310,7 @@
       <c r="B157" t="s">
         <v>256</v>
       </c>
-      <c r="C157" s="3">
+      <c r="C157" s="4">
         <v>64</v>
       </c>
       <c r="D157" t="s">
@@ -4309,7 +4324,7 @@
       <c r="B158" t="s">
         <v>258</v>
       </c>
-      <c r="C158" s="3">
+      <c r="C158" s="4">
         <v>65</v>
       </c>
       <c r="D158" s="1" t="s">
@@ -4323,7 +4338,7 @@
       <c r="B159" t="s">
         <v>260</v>
       </c>
-      <c r="C159" s="3">
+      <c r="C159" s="4">
         <v>66</v>
       </c>
       <c r="D159" t="s">
@@ -4337,7 +4352,7 @@
       <c r="B160" t="s">
         <v>262</v>
       </c>
-      <c r="C160" s="3">
+      <c r="C160" s="4">
         <v>67</v>
       </c>
       <c r="D160" t="s">
@@ -4351,7 +4366,7 @@
       <c r="B161" t="s">
         <v>264</v>
       </c>
-      <c r="C161" s="3">
+      <c r="C161" s="4">
         <v>68</v>
       </c>
       <c r="D161" t="s">
@@ -4365,7 +4380,7 @@
       <c r="B162" t="s">
         <v>266</v>
       </c>
-      <c r="C162" s="3">
+      <c r="C162" s="4">
         <v>69</v>
       </c>
       <c r="D162" t="s">
@@ -4379,7 +4394,7 @@
       <c r="B163" t="s">
         <v>268</v>
       </c>
-      <c r="C163" s="3">
+      <c r="C163" s="4">
         <v>70</v>
       </c>
       <c r="D163" t="s">
@@ -4393,7 +4408,7 @@
       <c r="B164" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C164" s="3">
+      <c r="C164" s="4">
         <v>71</v>
       </c>
       <c r="D164" s="1" t="s">
@@ -4407,7 +4422,7 @@
       <c r="B165" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C165" s="3">
+      <c r="C165" s="4">
         <v>72</v>
       </c>
       <c r="D165" s="1" t="s">
@@ -4421,7 +4436,7 @@
       <c r="B166" t="s">
         <v>274</v>
       </c>
-      <c r="C166" s="3">
+      <c r="C166" s="4">
         <v>73</v>
       </c>
       <c r="D166" t="s">
@@ -4435,7 +4450,7 @@
       <c r="B167" t="s">
         <v>276</v>
       </c>
-      <c r="C167" s="3">
+      <c r="C167" s="4">
         <v>74</v>
       </c>
       <c r="D167" s="1" t="s">
@@ -4449,7 +4464,7 @@
       <c r="B168" t="s">
         <v>278</v>
       </c>
-      <c r="C168" s="3">
+      <c r="C168" s="4">
         <v>75</v>
       </c>
       <c r="D168" t="s">
@@ -4463,7 +4478,7 @@
       <c r="B169" t="s">
         <v>280</v>
       </c>
-      <c r="C169" s="3">
+      <c r="C169" s="4">
         <v>76</v>
       </c>
       <c r="D169" s="1" t="s">
@@ -4477,7 +4492,7 @@
       <c r="B170" t="s">
         <v>282</v>
       </c>
-      <c r="C170" s="3">
+      <c r="C170" s="4">
         <v>77</v>
       </c>
       <c r="D170" t="s">
@@ -4491,7 +4506,7 @@
       <c r="B171" t="s">
         <v>284</v>
       </c>
-      <c r="C171" s="3">
+      <c r="C171" s="4">
         <v>78</v>
       </c>
       <c r="D171" t="s">
@@ -4505,7 +4520,7 @@
       <c r="B172" t="s">
         <v>286</v>
       </c>
-      <c r="C172" s="3">
+      <c r="C172" s="4">
         <v>79</v>
       </c>
       <c r="D172" s="1" t="s">
@@ -4519,7 +4534,7 @@
       <c r="B173" t="s">
         <v>288</v>
       </c>
-      <c r="C173" s="3">
+      <c r="C173" s="4">
         <v>80</v>
       </c>
       <c r="D173" s="1" t="s">
@@ -4533,7 +4548,7 @@
       <c r="B174" t="s">
         <v>290</v>
       </c>
-      <c r="C174" s="3">
+      <c r="C174" s="4">
         <v>81</v>
       </c>
       <c r="D174" t="s">
@@ -4547,7 +4562,7 @@
       <c r="B175" t="s">
         <v>292</v>
       </c>
-      <c r="C175" s="3">
+      <c r="C175" s="4">
         <v>82</v>
       </c>
       <c r="D175" t="s">
@@ -4558,10 +4573,10 @@
       <c r="A176" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B176" s="3" t="s">
+      <c r="B176" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="C176" s="3">
+      <c r="C176" s="4">
         <v>83</v>
       </c>
       <c r="D176" s="1" t="s">
@@ -4575,7 +4590,7 @@
       <c r="B177" t="s">
         <v>296</v>
       </c>
-      <c r="C177" s="3">
+      <c r="C177" s="4">
         <v>84</v>
       </c>
       <c r="D177" t="s">
@@ -4589,7 +4604,7 @@
       <c r="B178" t="s">
         <v>298</v>
       </c>
-      <c r="C178" s="3">
+      <c r="C178" s="4">
         <v>85</v>
       </c>
       <c r="D178" s="1" t="s">
@@ -4603,7 +4618,7 @@
       <c r="B179" t="s">
         <v>300</v>
       </c>
-      <c r="C179" s="3">
+      <c r="C179" s="4">
         <v>86</v>
       </c>
       <c r="D179" t="s">
@@ -4617,7 +4632,7 @@
       <c r="B180" t="s">
         <v>302</v>
       </c>
-      <c r="C180" s="3">
+      <c r="C180" s="4">
         <v>87</v>
       </c>
       <c r="D180" t="s">
@@ -4631,7 +4646,7 @@
       <c r="B181" t="s">
         <v>304</v>
       </c>
-      <c r="C181" s="3">
+      <c r="C181" s="4">
         <v>88</v>
       </c>
       <c r="D181" t="s">
@@ -4642,10 +4657,10 @@
       <c r="A182" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B182" s="3" t="s">
+      <c r="B182" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="C182" s="3">
+      <c r="C182" s="4">
         <v>89</v>
       </c>
       <c r="D182" t="s">
@@ -4656,10 +4671,10 @@
       <c r="A183" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B183" s="3" t="s">
+      <c r="B183" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C183" s="3">
+      <c r="C183" s="4">
         <v>90</v>
       </c>
       <c r="D183" s="1" t="s">
@@ -4673,7 +4688,7 @@
       <c r="B184" t="s">
         <v>310</v>
       </c>
-      <c r="C184" s="3">
+      <c r="C184" s="4">
         <v>91</v>
       </c>
       <c r="D184" t="s">
@@ -4687,7 +4702,7 @@
       <c r="B185" t="s">
         <v>312</v>
       </c>
-      <c r="C185" s="3">
+      <c r="C185" s="4">
         <v>92</v>
       </c>
       <c r="D185" t="s">
@@ -4702,7 +4717,7 @@
       <c r="B186" t="s">
         <v>314</v>
       </c>
-      <c r="C186" s="3">
+      <c r="C186" s="4">
         <v>93</v>
       </c>
       <c r="D186" t="s">
@@ -4717,7 +4732,7 @@
       <c r="B187" t="s">
         <v>316</v>
       </c>
-      <c r="C187" s="3">
+      <c r="C187" s="4">
         <v>94</v>
       </c>
       <c r="D187" t="s">
@@ -4732,7 +4747,7 @@
       <c r="B188" t="s">
         <v>318</v>
       </c>
-      <c r="C188" s="3">
+      <c r="C188" s="4">
         <v>95</v>
       </c>
       <c r="D188" t="s">
@@ -4747,7 +4762,7 @@
       <c r="B189" t="s">
         <v>320</v>
       </c>
-      <c r="C189" s="3">
+      <c r="C189" s="4">
         <v>96</v>
       </c>
       <c r="D189" t="s">
@@ -4762,7 +4777,7 @@
       <c r="B190" t="s">
         <v>322</v>
       </c>
-      <c r="C190" s="3">
+      <c r="C190" s="4">
         <v>97</v>
       </c>
       <c r="D190" s="1" t="s">
@@ -4777,7 +4792,7 @@
       <c r="B191" t="s">
         <v>324</v>
       </c>
-      <c r="C191" s="3">
+      <c r="C191" s="4">
         <v>98</v>
       </c>
       <c r="D191" s="1" t="s">
@@ -4792,7 +4807,7 @@
       <c r="B192" t="s">
         <v>326</v>
       </c>
-      <c r="C192" s="3">
+      <c r="C192" s="4">
         <v>99</v>
       </c>
       <c r="D192" s="1" t="s">
@@ -4807,7 +4822,7 @@
       <c r="B193" t="s">
         <v>328</v>
       </c>
-      <c r="C193" s="3">
+      <c r="C193" s="4">
         <v>100</v>
       </c>
       <c r="D193" s="1" t="s">
@@ -4822,7 +4837,7 @@
       <c r="B194" t="s">
         <v>330</v>
       </c>
-      <c r="C194" s="3">
+      <c r="C194" s="4">
         <v>101</v>
       </c>
       <c r="D194" s="1" t="s">
@@ -4837,7 +4852,7 @@
       <c r="B195" t="s">
         <v>332</v>
       </c>
-      <c r="C195" s="3">
+      <c r="C195" s="4">
         <v>102</v>
       </c>
       <c r="D195" s="1" t="s">
@@ -4852,7 +4867,7 @@
       <c r="B196" t="s">
         <v>334</v>
       </c>
-      <c r="C196" s="3">
+      <c r="C196" s="4">
         <v>103</v>
       </c>
       <c r="D196" s="1" t="s">
@@ -4867,7 +4882,7 @@
       <c r="B197" t="s">
         <v>336</v>
       </c>
-      <c r="C197" s="3">
+      <c r="C197" s="4">
         <v>104</v>
       </c>
       <c r="D197" s="1" t="s">
@@ -4882,7 +4897,7 @@
       <c r="B198" t="s">
         <v>338</v>
       </c>
-      <c r="C198" s="3">
+      <c r="C198" s="4">
         <v>105</v>
       </c>
       <c r="D198" s="1" t="s">
@@ -4897,7 +4912,7 @@
       <c r="B199" t="s">
         <v>340</v>
       </c>
-      <c r="C199" s="3">
+      <c r="C199" s="4">
         <v>106</v>
       </c>
       <c r="D199" s="1" t="s">
@@ -4912,7 +4927,7 @@
       <c r="B200" t="s">
         <v>342</v>
       </c>
-      <c r="C200" s="3">
+      <c r="C200" s="4">
         <v>107</v>
       </c>
       <c r="D200" s="1" t="s">
@@ -4927,7 +4942,7 @@
       <c r="B201" t="s">
         <v>344</v>
       </c>
-      <c r="C201" s="3">
+      <c r="C201" s="4">
         <v>108</v>
       </c>
       <c r="D201" s="1" t="s">
@@ -4942,7 +4957,7 @@
       <c r="B202" t="s">
         <v>346</v>
       </c>
-      <c r="C202" s="3">
+      <c r="C202" s="4">
         <v>109</v>
       </c>
       <c r="D202" t="s">
@@ -4957,7 +4972,7 @@
       <c r="B203" t="s">
         <v>348</v>
       </c>
-      <c r="C203" s="3">
+      <c r="C203" s="4">
         <v>110</v>
       </c>
       <c r="D203" s="1" t="s">
@@ -4972,7 +4987,7 @@
       <c r="B204" t="s">
         <v>350</v>
       </c>
-      <c r="C204" s="3">
+      <c r="C204" s="4">
         <v>111</v>
       </c>
       <c r="D204" s="1" t="s">
@@ -4987,7 +5002,7 @@
       <c r="B205" t="s">
         <v>352</v>
       </c>
-      <c r="C205" s="3">
+      <c r="C205" s="4">
         <v>112</v>
       </c>
       <c r="D205" t="s">
@@ -5002,7 +5017,7 @@
       <c r="B206" t="s">
         <v>354</v>
       </c>
-      <c r="C206" s="3">
+      <c r="C206" s="4">
         <v>113</v>
       </c>
       <c r="D206" t="s">
@@ -5017,7 +5032,7 @@
       <c r="B207" t="s">
         <v>356</v>
       </c>
-      <c r="C207" s="3">
+      <c r="C207" s="4">
         <v>114</v>
       </c>
       <c r="D207" t="s">
@@ -5032,7 +5047,7 @@
       <c r="B208" t="s">
         <v>358</v>
       </c>
-      <c r="C208" s="3">
+      <c r="C208" s="4">
         <v>115</v>
       </c>
       <c r="D208" t="s">
@@ -5047,7 +5062,7 @@
       <c r="B209" t="s">
         <v>360</v>
       </c>
-      <c r="C209" s="3">
+      <c r="C209" s="4">
         <v>116</v>
       </c>
       <c r="D209" t="s">
@@ -5062,7 +5077,7 @@
       <c r="B210" t="s">
         <v>362</v>
       </c>
-      <c r="C210" s="3">
+      <c r="C210" s="4">
         <v>117</v>
       </c>
       <c r="D210" t="s">
@@ -5077,7 +5092,7 @@
       <c r="B211" t="s">
         <v>364</v>
       </c>
-      <c r="C211" s="3">
+      <c r="C211" s="4">
         <v>118</v>
       </c>
       <c r="D211" t="s">
@@ -5092,7 +5107,7 @@
       <c r="B212" t="s">
         <v>366</v>
       </c>
-      <c r="C212" s="3">
+      <c r="C212" s="4">
         <v>119</v>
       </c>
       <c r="D212" t="s">
@@ -5107,7 +5122,7 @@
       <c r="B213" t="s">
         <v>368</v>
       </c>
-      <c r="C213" s="3">
+      <c r="C213" s="4">
         <v>120</v>
       </c>
       <c r="D213" t="s">
@@ -5121,7 +5136,7 @@
       <c r="B214" t="s">
         <v>370</v>
       </c>
-      <c r="C214" s="3">
+      <c r="C214" s="4">
         <v>121</v>
       </c>
       <c r="D214" s="1" t="s">
@@ -5135,7 +5150,7 @@
       <c r="B215" t="s">
         <v>372</v>
       </c>
-      <c r="C215" s="3">
+      <c r="C215" s="4">
         <v>122</v>
       </c>
       <c r="D215" t="s">
@@ -5146,10 +5161,10 @@
       <c r="A216" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B216" s="3" t="s">
+      <c r="B216" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="C216" s="3">
+      <c r="C216" s="4">
         <v>123</v>
       </c>
       <c r="D216" t="s">
@@ -5160,10 +5175,10 @@
       <c r="A217" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B217" s="3" t="s">
+      <c r="B217" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="C217" s="3">
+      <c r="C217" s="4">
         <v>124</v>
       </c>
       <c r="D217" t="s">
@@ -5174,10 +5189,10 @@
       <c r="A218" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B218" s="3" t="s">
+      <c r="B218" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="C218" s="3">
+      <c r="C218" s="4">
         <v>125</v>
       </c>
       <c r="D218" t="s">
@@ -5188,10 +5203,10 @@
       <c r="A219" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B219" s="3" t="s">
+      <c r="B219" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="C219" s="3">
+      <c r="C219" s="4">
         <v>126</v>
       </c>
       <c r="D219" t="s">
@@ -5202,10 +5217,10 @@
       <c r="A220" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B220" s="3" t="s">
+      <c r="B220" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="C220" s="3">
+      <c r="C220" s="4">
         <v>127</v>
       </c>
       <c r="D220" t="s">
@@ -5216,10 +5231,10 @@
       <c r="A221" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B221" s="3" t="s">
+      <c r="B221" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="C221" s="3">
+      <c r="C221" s="4">
         <v>128</v>
       </c>
       <c r="D221" t="s">
@@ -5230,10 +5245,10 @@
       <c r="A222" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B222" s="3" t="s">
+      <c r="B222" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="C222" s="3">
+      <c r="C222" s="4">
         <v>129</v>
       </c>
       <c r="D222" t="s">
@@ -5244,10 +5259,10 @@
       <c r="A223" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B223" s="3" t="s">
+      <c r="B223" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="C223" s="3">
+      <c r="C223" s="4">
         <v>130</v>
       </c>
       <c r="D223" t="s">
@@ -5261,7 +5276,7 @@
       <c r="B224" t="s">
         <v>390</v>
       </c>
-      <c r="C224" s="3">
+      <c r="C224" s="4">
         <v>131</v>
       </c>
       <c r="D224" t="s">
@@ -5275,7 +5290,7 @@
       <c r="B225" t="s">
         <v>392</v>
       </c>
-      <c r="C225" s="3">
+      <c r="C225" s="4">
         <v>132</v>
       </c>
       <c r="D225" t="s">
@@ -5289,7 +5304,7 @@
       <c r="B226" t="s">
         <v>394</v>
       </c>
-      <c r="C226" s="3">
+      <c r="C226" s="4">
         <v>133</v>
       </c>
       <c r="D226" t="s">
@@ -5303,7 +5318,7 @@
       <c r="B227" t="s">
         <v>396</v>
       </c>
-      <c r="C227" s="3">
+      <c r="C227" s="4">
         <v>134</v>
       </c>
       <c r="D227" t="s">
@@ -5317,7 +5332,7 @@
       <c r="B228" t="s">
         <v>398</v>
       </c>
-      <c r="C228" s="3">
+      <c r="C228" s="4">
         <v>135</v>
       </c>
       <c r="D228" t="s">
@@ -5331,7 +5346,7 @@
       <c r="B229" t="s">
         <v>400</v>
       </c>
-      <c r="C229" s="3">
+      <c r="C229" s="4">
         <v>136</v>
       </c>
       <c r="D229" t="s">
@@ -5345,7 +5360,7 @@
       <c r="B230" t="s">
         <v>402</v>
       </c>
-      <c r="C230" s="3">
+      <c r="C230" s="4">
         <v>137</v>
       </c>
       <c r="D230" t="s">
@@ -5359,7 +5374,7 @@
       <c r="B231" t="s">
         <v>404</v>
       </c>
-      <c r="C231" s="3">
+      <c r="C231" s="4">
         <v>138</v>
       </c>
       <c r="D231" t="s">
@@ -5373,7 +5388,7 @@
       <c r="B232" t="s">
         <v>406</v>
       </c>
-      <c r="C232" s="3">
+      <c r="C232" s="4">
         <v>139</v>
       </c>
       <c r="D232" t="s">
@@ -5387,7 +5402,7 @@
       <c r="B233" t="s">
         <v>408</v>
       </c>
-      <c r="C233" s="3">
+      <c r="C233" s="4">
         <v>140</v>
       </c>
       <c r="D233" t="s">
@@ -5401,7 +5416,7 @@
       <c r="B234" t="s">
         <v>410</v>
       </c>
-      <c r="C234" s="3">
+      <c r="C234" s="4">
         <v>141</v>
       </c>
       <c r="D234" t="s">
@@ -5415,7 +5430,7 @@
       <c r="B235" t="s">
         <v>412</v>
       </c>
-      <c r="C235" s="3">
+      <c r="C235" s="4">
         <v>142</v>
       </c>
       <c r="D235" t="s">
@@ -5429,7 +5444,7 @@
       <c r="B236" t="s">
         <v>414</v>
       </c>
-      <c r="C236" s="3">
+      <c r="C236" s="4">
         <v>143</v>
       </c>
       <c r="D236" t="s">
@@ -5443,7 +5458,7 @@
       <c r="B237" t="s">
         <v>416</v>
       </c>
-      <c r="C237" s="3">
+      <c r="C237" s="4">
         <v>144</v>
       </c>
       <c r="D237" t="s">
@@ -5457,7 +5472,7 @@
       <c r="B238" t="s">
         <v>418</v>
       </c>
-      <c r="C238" s="3">
+      <c r="C238" s="4">
         <v>145</v>
       </c>
       <c r="D238" t="s">
@@ -5471,7 +5486,7 @@
       <c r="B239" t="s">
         <v>420</v>
       </c>
-      <c r="C239" s="3">
+      <c r="C239" s="4">
         <v>146</v>
       </c>
       <c r="D239" t="s">
@@ -5482,10 +5497,10 @@
       <c r="A240" t="s">
         <v>134</v>
       </c>
-      <c r="B240" s="3" t="s">
+      <c r="B240" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="C240" s="3">
+      <c r="C240" s="4">
         <v>147</v>
       </c>
       <c r="D240" s="1" t="s">
@@ -5496,10 +5511,10 @@
       <c r="A241" t="s">
         <v>134</v>
       </c>
-      <c r="B241" s="3" t="s">
+      <c r="B241" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="C241" s="3">
+      <c r="C241" s="4">
         <v>148</v>
       </c>
       <c r="D241" s="1" t="s">
@@ -5510,10 +5525,10 @@
       <c r="A242" t="s">
         <v>134</v>
       </c>
-      <c r="B242" s="3" t="s">
+      <c r="B242" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="C242" s="3">
+      <c r="C242" s="4">
         <v>149</v>
       </c>
       <c r="D242" t="s">
@@ -5527,7 +5542,7 @@
       <c r="B243" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C243" s="3">
+      <c r="C243" s="4">
         <v>150</v>
       </c>
       <c r="D243" t="s">
@@ -5541,7 +5556,7 @@
       <c r="B244" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C244" s="3">
+      <c r="C244" s="4">
         <v>151</v>
       </c>
       <c r="D244" t="s">
@@ -5552,19 +5567,29 @@
       <c r="A245" t="s">
         <v>134</v>
       </c>
-      <c r="B245" s="4" t="s">
+      <c r="B245" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="C245" s="3">
+      <c r="C245" s="4">
         <v>152</v>
       </c>
-      <c r="D245" s="4" t="s">
+      <c r="D245" s="5" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="246" spans="1:4">
-      <c r="B246"/>
-      <c r="D246"/>
+    <row r="246" s="2" customFormat="1" spans="1:4">
+      <c r="A246" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B246" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="C246" s="4">
+        <v>153</v>
+      </c>
+      <c r="D246" s="6" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="247" spans="1:4">
       <c r="B247"/>
@@ -5575,26 +5600,18 @@
       <c r="D248"/>
     </row>
     <row r="249" spans="1:4">
-      <c r="A249" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B249" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="C249" s="3">
-        <v>1111</v>
-      </c>
+      <c r="B249"/>
       <c r="D249"/>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B250" t="s">
-        <v>435</v>
-      </c>
-      <c r="C250" s="3">
-        <v>1112</v>
+      <c r="B250" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C250" s="4">
+        <v>1111</v>
       </c>
       <c r="D250"/>
     </row>
@@ -5603,15 +5620,23 @@
         <v>134</v>
       </c>
       <c r="B251" t="s">
-        <v>436</v>
-      </c>
-      <c r="C251" s="3">
+        <v>437</v>
+      </c>
+      <c r="C251" s="4">
+        <v>1112</v>
+      </c>
+      <c r="D251"/>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B252" t="s">
+        <v>438</v>
+      </c>
+      <c r="C252" s="4">
         <v>1113</v>
       </c>
-      <c r="D251"/>
-    </row>
-    <row r="252" spans="1:4">
-      <c r="B252"/>
       <c r="D252"/>
     </row>
     <row r="253" spans="1:4">
@@ -5682,29 +5707,19 @@
       <c r="B269"/>
       <c r="D269"/>
     </row>
-    <row r="271" spans="1:4">
-      <c r="A271" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="B271" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C271" s="3">
-        <v>1</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>439</v>
-      </c>
+    <row r="270" spans="1:4">
+      <c r="B270"/>
+      <c r="D270"/>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="B272" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C272" s="3">
-        <v>2</v>
+      <c r="C272" s="4">
+        <v>1</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>441</v>
@@ -5712,13 +5727,13 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="B273" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="B273" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="C273" s="3">
-        <v>3</v>
+      <c r="C273" s="4">
+        <v>2</v>
       </c>
       <c r="D273" s="1" t="s">
         <v>443</v>
@@ -5726,41 +5741,41 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="B274" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C274" s="3">
-        <v>4</v>
+        <v>439</v>
+      </c>
+      <c r="B274" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C274" s="4">
+        <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="275" spans="1:4">
       <c r="A275" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="B275" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="C275" s="3">
-        <v>5</v>
+        <v>439</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C275" s="4">
+        <v>4</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="276" spans="1:4">
       <c r="A276" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="B276" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="C276" s="3">
-        <v>6</v>
+        <v>439</v>
+      </c>
+      <c r="B276" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="C276" s="4">
+        <v>5</v>
       </c>
       <c r="D276" s="1" t="s">
         <v>447</v>
@@ -5768,218 +5783,227 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="B277" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="B277" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="C277" s="3">
-        <v>7</v>
+      <c r="C277" s="4">
+        <v>6</v>
       </c>
       <c r="D277" s="1" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="278" spans="1:4">
-      <c r="A278" t="s">
-        <v>437</v>
-      </c>
-      <c r="B278" t="s">
+      <c r="A278" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B278" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="C278" s="4">
+        <v>7</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" t="s">
+        <v>439</v>
+      </c>
+      <c r="B279" t="s">
         <v>15</v>
       </c>
-      <c r="C278" s="3">
+      <c r="C279" s="4">
         <v>8</v>
       </c>
-      <c r="D278" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="279" s="2" customFormat="1" spans="1:4">
-      <c r="A279" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="B279" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="C279" s="6">
+      <c r="D279" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="280" s="3" customFormat="1" spans="1:4">
+      <c r="A280" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="B280" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="C280" s="9">
         <v>9</v>
       </c>
-      <c r="D279" s="5" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4">
-      <c r="A280" t="s">
-        <v>437</v>
-      </c>
-      <c r="B280" t="s">
-        <v>453</v>
-      </c>
-      <c r="C280" s="3">
-        <v>10</v>
-      </c>
-      <c r="D280" t="s">
+      <c r="D280" s="8" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B281" t="s">
         <v>455</v>
       </c>
-      <c r="C281" s="3">
-        <v>11</v>
+      <c r="C281" s="4">
+        <v>10</v>
       </c>
       <c r="D281" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="282" s="2" customFormat="1" spans="1:4">
-      <c r="A282" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="B282" s="5" t="s">
+    <row r="282" spans="1:4">
+      <c r="A282" t="s">
+        <v>439</v>
+      </c>
+      <c r="B282" t="s">
+        <v>457</v>
+      </c>
+      <c r="C282" s="4">
         <v>11</v>
       </c>
-      <c r="C282" s="6">
+      <c r="D282" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="283" s="3" customFormat="1" spans="1:4">
+      <c r="A283" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="B283" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C283" s="9">
         <v>12</v>
       </c>
-      <c r="D282" s="5" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="283" s="2" customFormat="1" spans="1:4">
-      <c r="A283" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="B283" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="C283" s="6">
+      <c r="D283" s="8" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="284" s="3" customFormat="1" spans="1:4">
+      <c r="A284" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="B284" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="C284" s="9">
         <v>13</v>
       </c>
-      <c r="D283" s="5" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="284" s="2" customFormat="1" spans="1:4">
-      <c r="A284" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="B284" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="C284" s="6">
+      <c r="D284" s="8" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="285" s="3" customFormat="1" spans="1:4">
+      <c r="A285" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="B285" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="C285" s="9">
         <v>14</v>
       </c>
-      <c r="D284" s="5" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="285" s="2" customFormat="1" spans="1:4">
-      <c r="A285" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="B285" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="C285" s="6">
+      <c r="D285" s="8" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="286" s="3" customFormat="1" spans="1:4">
+      <c r="A286" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="B286" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="C286" s="9">
         <v>15</v>
       </c>
-      <c r="D285" s="5" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="286" s="2" customFormat="1" spans="1:4">
-      <c r="A286" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="B286" s="6" t="s">
-        <v>464</v>
-      </c>
-      <c r="C286" s="6">
+      <c r="D286" s="8" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="287" s="3" customFormat="1" spans="1:4">
+      <c r="A287" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="B287" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="C287" s="9">
         <v>16</v>
       </c>
-      <c r="D286" s="5" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="287" s="2" customFormat="1" spans="1:4">
-      <c r="A287" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="B287" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="C287" s="6">
+      <c r="D287" s="8" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="288" s="3" customFormat="1" spans="1:4">
+      <c r="A288" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="B288" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="C288" s="9">
         <v>17</v>
       </c>
-      <c r="D287" s="5" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="288" s="2" customFormat="1" spans="1:4">
-      <c r="A288" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="B288" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="C288" s="6">
+      <c r="D288" s="8" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="289" s="3" customFormat="1" spans="1:4">
+      <c r="A289" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="B289" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="C289" s="9">
         <v>18</v>
       </c>
-      <c r="D288" s="5" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="289" s="2" customFormat="1" spans="1:4">
-      <c r="A289" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="B289" s="6" t="s">
-        <v>470</v>
-      </c>
-      <c r="C289" s="6">
+      <c r="D289" s="8" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="290" s="3" customFormat="1" spans="1:4">
+      <c r="A290" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="B290" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="C290" s="9">
         <v>19</v>
       </c>
-      <c r="D289" s="5" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="290" s="2" customFormat="1" spans="1:4">
-      <c r="A290" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="B290" s="6" t="s">
-        <v>472</v>
-      </c>
-      <c r="C290" s="6">
+      <c r="D290" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="291" s="3" customFormat="1" spans="1:4">
+      <c r="A291" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="B291" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="C291" s="9">
         <v>20</v>
       </c>
-      <c r="D290" s="5" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="291" s="2" customFormat="1" spans="1:4">
-      <c r="A291" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="B291" s="6" t="s">
-        <v>474</v>
-      </c>
-      <c r="C291" s="6">
+      <c r="D291" s="8" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="292" s="3" customFormat="1" spans="1:4">
+      <c r="A292" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="B292" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="C292" s="9">
         <v>21</v>
       </c>
-      <c r="D291" s="5" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4">
-      <c r="A292"/>
-      <c r="B292"/>
-      <c r="D292"/>
+      <c r="D292" s="8" t="s">
+        <v>477</v>
+      </c>
     </row>
     <row r="293" spans="1:4">
       <c r="A293"/>
@@ -5987,28 +6011,19 @@
       <c r="D293"/>
     </row>
     <row r="294" spans="1:4">
-      <c r="A294" t="s">
-        <v>476</v>
-      </c>
-      <c r="B294" t="s">
-        <v>477</v>
-      </c>
-      <c r="C294" s="3">
-        <v>1</v>
-      </c>
-      <c r="D294" t="s">
-        <v>478</v>
-      </c>
+      <c r="A294"/>
+      <c r="B294"/>
+      <c r="D294"/>
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B295" t="s">
         <v>479</v>
       </c>
-      <c r="C295" s="3">
-        <v>2</v>
+      <c r="C295" s="4">
+        <v>1</v>
       </c>
       <c r="D295" t="s">
         <v>480</v>
@@ -6016,13 +6031,13 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B296" t="s">
         <v>481</v>
       </c>
-      <c r="C296" s="3">
-        <v>3</v>
+      <c r="C296" s="4">
+        <v>2</v>
       </c>
       <c r="D296" t="s">
         <v>482</v>
@@ -6030,27 +6045,27 @@
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
+        <v>478</v>
+      </c>
+      <c r="B297" t="s">
         <v>483</v>
       </c>
-      <c r="B297" t="s">
+      <c r="C297" s="4">
+        <v>3</v>
+      </c>
+      <c r="D297" t="s">
         <v>484</v>
-      </c>
-      <c r="C297" s="3">
-        <v>1</v>
-      </c>
-      <c r="D297" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B298" t="s">
         <v>486</v>
       </c>
-      <c r="C298" s="3">
-        <v>2</v>
+      <c r="C298" s="4">
+        <v>1</v>
       </c>
       <c r="D298" t="s">
         <v>487</v>
@@ -6058,16 +6073,30 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B299" t="s">
         <v>488</v>
       </c>
-      <c r="C299" s="3">
-        <v>3</v>
+      <c r="C299" s="4">
+        <v>2</v>
       </c>
       <c r="D299" t="s">
         <v>489</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" t="s">
+        <v>485</v>
+      </c>
+      <c r="B300" t="s">
+        <v>490</v>
+      </c>
+      <c r="C300" s="4">
+        <v>3</v>
+      </c>
+      <c r="D300" t="s">
+        <v>491</v>
       </c>
     </row>
   </sheetData>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="493">
   <si>
     <t>Enum</t>
   </si>
@@ -1466,6 +1466,9 @@
   </si>
   <si>
     <t>触发暴击次数</t>
+  </si>
+  <si>
+    <t>三花聚顶</t>
   </si>
   <si>
     <t>GuideTriggerType</t>
@@ -2129,7 +2132,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2142,6 +2145,9 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2149,13 +2155,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2508,12 +2508,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:E300"/>
+  <dimension ref="A4:E301"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16.7416666666667" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.7" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.05833333333333" style="4" customWidth="1"/>
+    <col min="3" max="3" width="7.05833333333333" style="5" customWidth="1"/>
     <col min="4" max="4" width="31.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="34.75" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1" customWidth="1"/>
@@ -2526,7 +2526,7 @@
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
@@ -2540,7 +2540,7 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="5">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -2554,7 +2554,7 @@
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -2568,7 +2568,7 @@
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="5">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -2582,7 +2582,7 @@
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -2596,7 +2596,7 @@
       <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -2610,7 +2610,7 @@
       <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="5">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -2624,7 +2624,7 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="5">
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -2638,7 +2638,7 @@
       <c r="B14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -2652,7 +2652,7 @@
       <c r="B16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="5">
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -2666,7 +2666,7 @@
       <c r="B17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="5">
         <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -2680,7 +2680,7 @@
       <c r="B19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="5">
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -2694,7 +2694,7 @@
       <c r="B20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="5">
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -2708,7 +2708,7 @@
       <c r="B21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="5">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -2722,7 +2722,7 @@
       <c r="B22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="5">
         <v>4</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -2736,7 +2736,7 @@
       <c r="B39" t="s">
         <v>36</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="5">
         <v>1</v>
       </c>
       <c r="D39" t="s">
@@ -2750,7 +2750,7 @@
       <c r="B40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="5">
         <v>2</v>
       </c>
       <c r="D40" t="s">
@@ -2764,7 +2764,7 @@
       <c r="B41" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="5">
         <v>3</v>
       </c>
       <c r="D41" t="s">
@@ -2778,7 +2778,7 @@
       <c r="B42" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="5">
         <v>4</v>
       </c>
       <c r="D42" t="s">
@@ -2792,7 +2792,7 @@
       <c r="B43" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="5">
         <v>5</v>
       </c>
       <c r="D43" t="s">
@@ -2806,7 +2806,7 @@
       <c r="B44" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="5">
         <v>6</v>
       </c>
       <c r="D44" s="1" t="s">
@@ -2820,7 +2820,7 @@
       <c r="B45" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="5">
         <v>7</v>
       </c>
       <c r="D45" s="1" t="s">
@@ -2834,7 +2834,7 @@
       <c r="B46" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="5">
         <v>8</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -2848,7 +2848,7 @@
       <c r="B47" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="5">
         <v>9</v>
       </c>
       <c r="D47" s="1" t="s">
@@ -2862,7 +2862,7 @@
       <c r="B48" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="5">
         <v>10</v>
       </c>
       <c r="D48" s="1" t="s">
@@ -2876,7 +2876,7 @@
       <c r="B49" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="5">
         <v>11</v>
       </c>
       <c r="D49" s="1" t="s">
@@ -2890,7 +2890,7 @@
       <c r="B50" t="s">
         <v>58</v>
       </c>
-      <c r="C50" s="4">
+      <c r="C50" s="5">
         <v>12</v>
       </c>
       <c r="D50" t="s">
@@ -2904,7 +2904,7 @@
       <c r="B51" t="s">
         <v>60</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C51" s="5">
         <v>13</v>
       </c>
       <c r="D51" t="s">
@@ -2918,7 +2918,7 @@
       <c r="B52" t="s">
         <v>62</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="5">
         <v>14</v>
       </c>
       <c r="D52" t="s">
@@ -2932,7 +2932,7 @@
       <c r="B53" t="s">
         <v>64</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="5">
         <v>15</v>
       </c>
       <c r="D53" t="s">
@@ -2946,7 +2946,7 @@
       <c r="B54" t="s">
         <v>66</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54" s="5">
         <v>16</v>
       </c>
       <c r="D54" t="s">
@@ -2960,7 +2960,7 @@
       <c r="B55" t="s">
         <v>68</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="5">
         <v>17</v>
       </c>
       <c r="D55" t="s">
@@ -2974,7 +2974,7 @@
       <c r="B56" t="s">
         <v>70</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="5">
         <v>18</v>
       </c>
       <c r="D56" t="s">
@@ -2988,7 +2988,7 @@
       <c r="B57" t="s">
         <v>72</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C57" s="5">
         <v>19</v>
       </c>
       <c r="D57" t="s">
@@ -3002,7 +3002,7 @@
       <c r="B58" t="s">
         <v>74</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="5">
         <v>20</v>
       </c>
       <c r="D58" t="s">
@@ -3016,7 +3016,7 @@
       <c r="B59" t="s">
         <v>76</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59" s="5">
         <v>21</v>
       </c>
       <c r="D59" t="s">
@@ -3030,7 +3030,7 @@
       <c r="B60" t="s">
         <v>78</v>
       </c>
-      <c r="C60" s="4">
+      <c r="C60" s="5">
         <v>22</v>
       </c>
       <c r="D60" t="s">
@@ -3044,7 +3044,7 @@
       <c r="B61" t="s">
         <v>80</v>
       </c>
-      <c r="C61" s="4">
+      <c r="C61" s="5">
         <v>23</v>
       </c>
       <c r="D61" t="s">
@@ -3058,7 +3058,7 @@
       <c r="B62" t="s">
         <v>82</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C62" s="5">
         <v>24</v>
       </c>
       <c r="D62" t="s">
@@ -3072,7 +3072,7 @@
       <c r="B63" t="s">
         <v>84</v>
       </c>
-      <c r="C63" s="4">
+      <c r="C63" s="5">
         <v>25</v>
       </c>
       <c r="D63" t="s">
@@ -3086,7 +3086,7 @@
       <c r="B64" t="s">
         <v>86</v>
       </c>
-      <c r="C64" s="4">
+      <c r="C64" s="5">
         <v>26</v>
       </c>
       <c r="D64" t="s">
@@ -3100,7 +3100,7 @@
       <c r="B65" t="s">
         <v>88</v>
       </c>
-      <c r="C65" s="4">
+      <c r="C65" s="5">
         <v>27</v>
       </c>
       <c r="D65" t="s">
@@ -3114,7 +3114,7 @@
       <c r="B66" t="s">
         <v>90</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C66" s="5">
         <v>28</v>
       </c>
       <c r="D66" t="s">
@@ -3128,7 +3128,7 @@
       <c r="B67" t="s">
         <v>92</v>
       </c>
-      <c r="C67" s="4">
+      <c r="C67" s="5">
         <v>29</v>
       </c>
       <c r="D67" t="s">
@@ -3142,7 +3142,7 @@
       <c r="B68" t="s">
         <v>94</v>
       </c>
-      <c r="C68" s="4">
+      <c r="C68" s="5">
         <v>30</v>
       </c>
       <c r="D68" t="s">
@@ -3156,7 +3156,7 @@
       <c r="B69" t="s">
         <v>96</v>
       </c>
-      <c r="C69" s="4">
+      <c r="C69" s="5">
         <v>31</v>
       </c>
       <c r="D69" t="s">
@@ -3170,7 +3170,7 @@
       <c r="B70" t="s">
         <v>98</v>
       </c>
-      <c r="C70" s="4">
+      <c r="C70" s="5">
         <v>32</v>
       </c>
       <c r="D70" t="s">
@@ -3184,7 +3184,7 @@
       <c r="B71" t="s">
         <v>100</v>
       </c>
-      <c r="C71" s="4">
+      <c r="C71" s="5">
         <v>33</v>
       </c>
       <c r="D71" t="s">
@@ -3198,7 +3198,7 @@
       <c r="B72" t="s">
         <v>102</v>
       </c>
-      <c r="C72" s="4">
+      <c r="C72" s="5">
         <v>34</v>
       </c>
       <c r="D72" t="s">
@@ -3212,7 +3212,7 @@
       <c r="B73" t="s">
         <v>104</v>
       </c>
-      <c r="C73" s="4">
+      <c r="C73" s="5">
         <v>35</v>
       </c>
       <c r="D73" t="s">
@@ -3226,7 +3226,7 @@
       <c r="B74" t="s">
         <v>106</v>
       </c>
-      <c r="C74" s="4">
+      <c r="C74" s="5">
         <v>36</v>
       </c>
       <c r="D74" t="s">
@@ -3240,7 +3240,7 @@
       <c r="B75" t="s">
         <v>108</v>
       </c>
-      <c r="C75" s="4">
+      <c r="C75" s="5">
         <v>37</v>
       </c>
       <c r="D75" t="s">
@@ -3254,7 +3254,7 @@
       <c r="B76" t="s">
         <v>110</v>
       </c>
-      <c r="C76" s="4">
+      <c r="C76" s="5">
         <v>38</v>
       </c>
       <c r="D76" t="s">
@@ -3268,7 +3268,7 @@
       <c r="B77" t="s">
         <v>112</v>
       </c>
-      <c r="C77" s="4">
+      <c r="C77" s="5">
         <v>39</v>
       </c>
       <c r="D77" t="s">
@@ -3282,7 +3282,7 @@
       <c r="B78" t="s">
         <v>114</v>
       </c>
-      <c r="C78" s="4">
+      <c r="C78" s="5">
         <v>40</v>
       </c>
       <c r="D78" t="s">
@@ -3296,7 +3296,7 @@
       <c r="B79" t="s">
         <v>116</v>
       </c>
-      <c r="C79" s="4">
+      <c r="C79" s="5">
         <v>41</v>
       </c>
       <c r="D79" t="s">
@@ -3310,7 +3310,7 @@
       <c r="B80" t="s">
         <v>118</v>
       </c>
-      <c r="C80" s="4">
+      <c r="C80" s="5">
         <v>42</v>
       </c>
       <c r="D80" t="s">
@@ -3324,7 +3324,7 @@
       <c r="B81" t="s">
         <v>120</v>
       </c>
-      <c r="C81" s="4">
+      <c r="C81" s="5">
         <v>43</v>
       </c>
       <c r="D81" t="s">
@@ -3338,7 +3338,7 @@
       <c r="B82" t="s">
         <v>122</v>
       </c>
-      <c r="C82" s="4">
+      <c r="C82" s="5">
         <v>44</v>
       </c>
       <c r="D82" t="s">
@@ -3352,7 +3352,7 @@
       <c r="B83" t="s">
         <v>124</v>
       </c>
-      <c r="C83" s="4">
+      <c r="C83" s="5">
         <v>45</v>
       </c>
       <c r="D83" t="s">
@@ -3366,7 +3366,7 @@
       <c r="B84" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C84" s="4">
+      <c r="C84" s="5">
         <v>46</v>
       </c>
       <c r="D84" t="s">
@@ -3380,7 +3380,7 @@
       <c r="B85" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C85" s="4">
+      <c r="C85" s="5">
         <v>47</v>
       </c>
       <c r="D85" t="s">
@@ -3394,7 +3394,7 @@
       <c r="B86" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C86" s="4">
+      <c r="C86" s="5">
         <v>48</v>
       </c>
       <c r="D86" t="s">
@@ -3408,7 +3408,7 @@
       <c r="B87" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C87" s="4">
+      <c r="C87" s="5">
         <v>49</v>
       </c>
       <c r="D87" t="s">
@@ -3418,7 +3418,7 @@
     <row r="88" customFormat="1" spans="1:4">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
-      <c r="C88" s="4"/>
+      <c r="C88" s="5"/>
       <c r="D88" s="1"/>
     </row>
     <row r="94" spans="1:4">
@@ -3428,7 +3428,7 @@
       <c r="B94" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C94" s="4">
+      <c r="C94" s="5">
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
@@ -3442,7 +3442,7 @@
       <c r="B95" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C95" s="4">
+      <c r="C95" s="5">
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
@@ -3456,7 +3456,7 @@
       <c r="B96" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C96" s="4">
+      <c r="C96" s="5">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
@@ -3467,10 +3467,10 @@
       <c r="A97" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C97" s="4">
+      <c r="C97" s="5">
         <v>4</v>
       </c>
       <c r="D97" s="1" t="s">
@@ -3481,10 +3481,10 @@
       <c r="A98" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C98" s="4">
+      <c r="C98" s="5">
         <v>5</v>
       </c>
       <c r="D98" s="1" t="s">
@@ -3495,10 +3495,10 @@
       <c r="A99" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C99" s="4">
+      <c r="C99" s="5">
         <v>6</v>
       </c>
       <c r="D99" s="1" t="s">
@@ -3509,10 +3509,10 @@
       <c r="A100" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="C100" s="4">
+      <c r="C100" s="5">
         <v>7</v>
       </c>
       <c r="D100" s="1" t="s">
@@ -3523,10 +3523,10 @@
       <c r="A101" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B101" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C101" s="4">
+      <c r="C101" s="5">
         <v>8</v>
       </c>
       <c r="D101" s="1" t="s">
@@ -3537,10 +3537,10 @@
       <c r="A102" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C102" s="4">
+      <c r="C102" s="5">
         <v>9</v>
       </c>
       <c r="D102" s="1" t="s">
@@ -3551,10 +3551,10 @@
       <c r="A103" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B103" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C103" s="4">
+      <c r="C103" s="5">
         <v>10</v>
       </c>
       <c r="D103" s="1" t="s">
@@ -3565,10 +3565,10 @@
       <c r="A104" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B104" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="C104" s="4">
+      <c r="C104" s="5">
         <v>11</v>
       </c>
       <c r="D104" s="1" t="s">
@@ -3579,10 +3579,10 @@
       <c r="A105" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B105" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C105" s="4">
+      <c r="C105" s="5">
         <v>12</v>
       </c>
       <c r="D105" s="1" t="s">
@@ -3593,10 +3593,10 @@
       <c r="A106" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B106" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="C106" s="4">
+      <c r="C106" s="5">
         <v>13</v>
       </c>
       <c r="D106" s="1" t="s">
@@ -3607,10 +3607,10 @@
       <c r="A107" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B107" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C107" s="4">
+      <c r="C107" s="5">
         <v>14</v>
       </c>
       <c r="D107" s="1" t="s">
@@ -3621,10 +3621,10 @@
       <c r="A108" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B108" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C108" s="4">
+      <c r="C108" s="5">
         <v>15</v>
       </c>
       <c r="D108" s="1" t="s">
@@ -3638,7 +3638,7 @@
       <c r="B109" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C109" s="4">
+      <c r="C109" s="5">
         <v>16</v>
       </c>
       <c r="D109" s="1" t="s">
@@ -3649,10 +3649,10 @@
       <c r="A110" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B110" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C110" s="4">
+      <c r="C110" s="5">
         <v>17</v>
       </c>
       <c r="D110" s="1" t="s">
@@ -3666,7 +3666,7 @@
       <c r="B111" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C111" s="4">
+      <c r="C111" s="5">
         <v>18</v>
       </c>
       <c r="D111" s="1" t="s">
@@ -3677,10 +3677,10 @@
       <c r="A112" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B112" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C112" s="4">
+      <c r="C112" s="5">
         <v>19</v>
       </c>
       <c r="D112" s="1" t="s">
@@ -3694,7 +3694,7 @@
       <c r="B113" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C113" s="4">
+      <c r="C113" s="5">
         <v>20</v>
       </c>
       <c r="D113" s="1" t="s">
@@ -3708,7 +3708,7 @@
       <c r="B114" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C114" s="4">
+      <c r="C114" s="5">
         <v>21</v>
       </c>
       <c r="D114" s="1" t="s">
@@ -3719,10 +3719,10 @@
       <c r="A115" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="B115" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="C115" s="4">
+      <c r="C115" s="5">
         <v>22</v>
       </c>
       <c r="D115" s="1" t="s">
@@ -3733,10 +3733,10 @@
       <c r="A116" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C116" s="4">
+      <c r="C116" s="5">
         <v>23</v>
       </c>
       <c r="D116" s="1" t="s">
@@ -3750,7 +3750,7 @@
       <c r="B117" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C117" s="4">
+      <c r="C117" s="5">
         <v>24</v>
       </c>
       <c r="D117" s="1" t="s">
@@ -3764,7 +3764,7 @@
       <c r="B118" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C118" s="4">
+      <c r="C118" s="5">
         <v>25</v>
       </c>
       <c r="D118" s="1" t="s">
@@ -3778,7 +3778,7 @@
       <c r="B119" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C119" s="4">
+      <c r="C119" s="5">
         <v>26</v>
       </c>
       <c r="D119" s="1" t="s">
@@ -3792,7 +3792,7 @@
       <c r="B120" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C120" s="4">
+      <c r="C120" s="5">
         <v>27</v>
       </c>
       <c r="D120" s="1" t="s">
@@ -3806,7 +3806,7 @@
       <c r="B121" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C121" s="4">
+      <c r="C121" s="5">
         <v>28</v>
       </c>
       <c r="D121" s="1" t="s">
@@ -3820,7 +3820,7 @@
       <c r="B122" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C122" s="4">
+      <c r="C122" s="5">
         <v>29</v>
       </c>
       <c r="D122" s="1" t="s">
@@ -3834,7 +3834,7 @@
       <c r="B123" t="s">
         <v>193</v>
       </c>
-      <c r="C123" s="4">
+      <c r="C123" s="5">
         <v>30</v>
       </c>
       <c r="D123" s="1" t="s">
@@ -3848,7 +3848,7 @@
       <c r="B124" t="s">
         <v>195</v>
       </c>
-      <c r="C124" s="4">
+      <c r="C124" s="5">
         <v>31</v>
       </c>
       <c r="D124" s="1" t="s">
@@ -3862,7 +3862,7 @@
       <c r="B125" t="s">
         <v>197</v>
       </c>
-      <c r="C125" s="4">
+      <c r="C125" s="5">
         <v>32</v>
       </c>
       <c r="D125" s="1" t="s">
@@ -3876,7 +3876,7 @@
       <c r="B126" t="s">
         <v>199</v>
       </c>
-      <c r="C126" s="4">
+      <c r="C126" s="5">
         <v>33</v>
       </c>
       <c r="D126" s="1" t="s">
@@ -3890,7 +3890,7 @@
       <c r="B127" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C127" s="4">
+      <c r="C127" s="5">
         <v>34</v>
       </c>
       <c r="D127" t="s">
@@ -3904,7 +3904,7 @@
       <c r="B128" t="s">
         <v>13</v>
       </c>
-      <c r="C128" s="4">
+      <c r="C128" s="5">
         <v>35</v>
       </c>
       <c r="D128" t="s">
@@ -3918,7 +3918,7 @@
       <c r="B129" t="s">
         <v>15</v>
       </c>
-      <c r="C129" s="4">
+      <c r="C129" s="5">
         <v>36</v>
       </c>
       <c r="D129" t="s">
@@ -3932,7 +3932,7 @@
       <c r="B130" t="s">
         <v>17</v>
       </c>
-      <c r="C130" s="4">
+      <c r="C130" s="5">
         <v>37</v>
       </c>
       <c r="D130" t="s">
@@ -3943,10 +3943,10 @@
       <c r="A131" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B131" s="4" t="s">
+      <c r="B131" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C131" s="4">
+      <c r="C131" s="5">
         <v>38</v>
       </c>
       <c r="D131" t="s">
@@ -3960,7 +3960,7 @@
       <c r="B132" t="s">
         <v>206</v>
       </c>
-      <c r="C132" s="4">
+      <c r="C132" s="5">
         <v>39</v>
       </c>
       <c r="D132" t="s">
@@ -3974,7 +3974,7 @@
       <c r="B133" t="s">
         <v>208</v>
       </c>
-      <c r="C133" s="4">
+      <c r="C133" s="5">
         <v>40</v>
       </c>
       <c r="D133" t="s">
@@ -3988,7 +3988,7 @@
       <c r="B134" t="s">
         <v>210</v>
       </c>
-      <c r="C134" s="4">
+      <c r="C134" s="5">
         <v>41</v>
       </c>
       <c r="D134" t="s">
@@ -4002,7 +4002,7 @@
       <c r="B135" t="s">
         <v>212</v>
       </c>
-      <c r="C135" s="4">
+      <c r="C135" s="5">
         <v>42</v>
       </c>
       <c r="D135" t="s">
@@ -4016,7 +4016,7 @@
       <c r="B136" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C136" s="4">
+      <c r="C136" s="5">
         <v>43</v>
       </c>
       <c r="D136" t="s">
@@ -4030,7 +4030,7 @@
       <c r="B137" t="s">
         <v>216</v>
       </c>
-      <c r="C137" s="4">
+      <c r="C137" s="5">
         <v>44</v>
       </c>
       <c r="D137" t="s">
@@ -4044,7 +4044,7 @@
       <c r="B138" t="s">
         <v>218</v>
       </c>
-      <c r="C138" s="4">
+      <c r="C138" s="5">
         <v>45</v>
       </c>
       <c r="D138" t="s">
@@ -4058,7 +4058,7 @@
       <c r="B139" t="s">
         <v>220</v>
       </c>
-      <c r="C139" s="4">
+      <c r="C139" s="5">
         <v>46</v>
       </c>
       <c r="D139" t="s">
@@ -4069,10 +4069,10 @@
       <c r="A140" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B140" s="4" t="s">
+      <c r="B140" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="C140" s="4">
+      <c r="C140" s="5">
         <v>47</v>
       </c>
       <c r="D140" t="s">
@@ -4083,10 +4083,10 @@
       <c r="A141" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B141" s="4" t="s">
+      <c r="B141" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="C141" s="4">
+      <c r="C141" s="5">
         <v>48</v>
       </c>
       <c r="D141" t="s">
@@ -4100,7 +4100,7 @@
       <c r="B142" t="s">
         <v>226</v>
       </c>
-      <c r="C142" s="4">
+      <c r="C142" s="5">
         <v>49</v>
       </c>
       <c r="D142" t="s">
@@ -4114,7 +4114,7 @@
       <c r="B143" t="s">
         <v>228</v>
       </c>
-      <c r="C143" s="4">
+      <c r="C143" s="5">
         <v>50</v>
       </c>
       <c r="D143" t="s">
@@ -4125,10 +4125,10 @@
       <c r="A144" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B144" s="4" t="s">
+      <c r="B144" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="C144" s="4">
+      <c r="C144" s="5">
         <v>51</v>
       </c>
       <c r="D144" t="s">
@@ -4142,7 +4142,7 @@
       <c r="B145" t="s">
         <v>232</v>
       </c>
-      <c r="C145" s="4">
+      <c r="C145" s="5">
         <v>52</v>
       </c>
       <c r="D145" t="s">
@@ -4156,7 +4156,7 @@
       <c r="B146" t="s">
         <v>234</v>
       </c>
-      <c r="C146" s="4">
+      <c r="C146" s="5">
         <v>53</v>
       </c>
       <c r="D146" t="s">
@@ -4170,7 +4170,7 @@
       <c r="B147" t="s">
         <v>236</v>
       </c>
-      <c r="C147" s="4">
+      <c r="C147" s="5">
         <v>54</v>
       </c>
       <c r="D147" t="s">
@@ -4184,7 +4184,7 @@
       <c r="B148" t="s">
         <v>238</v>
       </c>
-      <c r="C148" s="4">
+      <c r="C148" s="5">
         <v>55</v>
       </c>
       <c r="D148" t="s">
@@ -4195,10 +4195,10 @@
       <c r="A149" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B149" s="4" t="s">
+      <c r="B149" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="C149" s="4">
+      <c r="C149" s="5">
         <v>56</v>
       </c>
       <c r="D149" t="s">
@@ -4212,7 +4212,7 @@
       <c r="B150" t="s">
         <v>242</v>
       </c>
-      <c r="C150" s="4">
+      <c r="C150" s="5">
         <v>57</v>
       </c>
       <c r="D150" t="s">
@@ -4226,7 +4226,7 @@
       <c r="B151" t="s">
         <v>244</v>
       </c>
-      <c r="C151" s="4">
+      <c r="C151" s="5">
         <v>58</v>
       </c>
       <c r="D151" t="s">
@@ -4240,7 +4240,7 @@
       <c r="B152" t="s">
         <v>246</v>
       </c>
-      <c r="C152" s="4">
+      <c r="C152" s="5">
         <v>59</v>
       </c>
       <c r="D152" t="s">
@@ -4254,7 +4254,7 @@
       <c r="B153" t="s">
         <v>248</v>
       </c>
-      <c r="C153" s="4">
+      <c r="C153" s="5">
         <v>60</v>
       </c>
       <c r="D153" t="s">
@@ -4268,7 +4268,7 @@
       <c r="B154" t="s">
         <v>250</v>
       </c>
-      <c r="C154" s="4">
+      <c r="C154" s="5">
         <v>61</v>
       </c>
       <c r="D154" t="s">
@@ -4282,7 +4282,7 @@
       <c r="B155" t="s">
         <v>252</v>
       </c>
-      <c r="C155" s="4">
+      <c r="C155" s="5">
         <v>62</v>
       </c>
       <c r="D155" t="s">
@@ -4296,7 +4296,7 @@
       <c r="B156" t="s">
         <v>254</v>
       </c>
-      <c r="C156" s="4">
+      <c r="C156" s="5">
         <v>63</v>
       </c>
       <c r="D156" t="s">
@@ -4310,7 +4310,7 @@
       <c r="B157" t="s">
         <v>256</v>
       </c>
-      <c r="C157" s="4">
+      <c r="C157" s="5">
         <v>64</v>
       </c>
       <c r="D157" t="s">
@@ -4324,7 +4324,7 @@
       <c r="B158" t="s">
         <v>258</v>
       </c>
-      <c r="C158" s="4">
+      <c r="C158" s="5">
         <v>65</v>
       </c>
       <c r="D158" s="1" t="s">
@@ -4338,7 +4338,7 @@
       <c r="B159" t="s">
         <v>260</v>
       </c>
-      <c r="C159" s="4">
+      <c r="C159" s="5">
         <v>66</v>
       </c>
       <c r="D159" t="s">
@@ -4352,7 +4352,7 @@
       <c r="B160" t="s">
         <v>262</v>
       </c>
-      <c r="C160" s="4">
+      <c r="C160" s="5">
         <v>67</v>
       </c>
       <c r="D160" t="s">
@@ -4366,7 +4366,7 @@
       <c r="B161" t="s">
         <v>264</v>
       </c>
-      <c r="C161" s="4">
+      <c r="C161" s="5">
         <v>68</v>
       </c>
       <c r="D161" t="s">
@@ -4380,7 +4380,7 @@
       <c r="B162" t="s">
         <v>266</v>
       </c>
-      <c r="C162" s="4">
+      <c r="C162" s="5">
         <v>69</v>
       </c>
       <c r="D162" t="s">
@@ -4394,7 +4394,7 @@
       <c r="B163" t="s">
         <v>268</v>
       </c>
-      <c r="C163" s="4">
+      <c r="C163" s="5">
         <v>70</v>
       </c>
       <c r="D163" t="s">
@@ -4408,7 +4408,7 @@
       <c r="B164" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C164" s="4">
+      <c r="C164" s="5">
         <v>71</v>
       </c>
       <c r="D164" s="1" t="s">
@@ -4422,7 +4422,7 @@
       <c r="B165" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C165" s="4">
+      <c r="C165" s="5">
         <v>72</v>
       </c>
       <c r="D165" s="1" t="s">
@@ -4436,7 +4436,7 @@
       <c r="B166" t="s">
         <v>274</v>
       </c>
-      <c r="C166" s="4">
+      <c r="C166" s="5">
         <v>73</v>
       </c>
       <c r="D166" t="s">
@@ -4450,7 +4450,7 @@
       <c r="B167" t="s">
         <v>276</v>
       </c>
-      <c r="C167" s="4">
+      <c r="C167" s="5">
         <v>74</v>
       </c>
       <c r="D167" s="1" t="s">
@@ -4464,7 +4464,7 @@
       <c r="B168" t="s">
         <v>278</v>
       </c>
-      <c r="C168" s="4">
+      <c r="C168" s="5">
         <v>75</v>
       </c>
       <c r="D168" t="s">
@@ -4478,7 +4478,7 @@
       <c r="B169" t="s">
         <v>280</v>
       </c>
-      <c r="C169" s="4">
+      <c r="C169" s="5">
         <v>76</v>
       </c>
       <c r="D169" s="1" t="s">
@@ -4492,7 +4492,7 @@
       <c r="B170" t="s">
         <v>282</v>
       </c>
-      <c r="C170" s="4">
+      <c r="C170" s="5">
         <v>77</v>
       </c>
       <c r="D170" t="s">
@@ -4506,7 +4506,7 @@
       <c r="B171" t="s">
         <v>284</v>
       </c>
-      <c r="C171" s="4">
+      <c r="C171" s="5">
         <v>78</v>
       </c>
       <c r="D171" t="s">
@@ -4520,7 +4520,7 @@
       <c r="B172" t="s">
         <v>286</v>
       </c>
-      <c r="C172" s="4">
+      <c r="C172" s="5">
         <v>79</v>
       </c>
       <c r="D172" s="1" t="s">
@@ -4534,7 +4534,7 @@
       <c r="B173" t="s">
         <v>288</v>
       </c>
-      <c r="C173" s="4">
+      <c r="C173" s="5">
         <v>80</v>
       </c>
       <c r="D173" s="1" t="s">
@@ -4548,7 +4548,7 @@
       <c r="B174" t="s">
         <v>290</v>
       </c>
-      <c r="C174" s="4">
+      <c r="C174" s="5">
         <v>81</v>
       </c>
       <c r="D174" t="s">
@@ -4562,7 +4562,7 @@
       <c r="B175" t="s">
         <v>292</v>
       </c>
-      <c r="C175" s="4">
+      <c r="C175" s="5">
         <v>82</v>
       </c>
       <c r="D175" t="s">
@@ -4573,10 +4573,10 @@
       <c r="A176" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B176" s="4" t="s">
+      <c r="B176" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="C176" s="4">
+      <c r="C176" s="5">
         <v>83</v>
       </c>
       <c r="D176" s="1" t="s">
@@ -4590,7 +4590,7 @@
       <c r="B177" t="s">
         <v>296</v>
       </c>
-      <c r="C177" s="4">
+      <c r="C177" s="5">
         <v>84</v>
       </c>
       <c r="D177" t="s">
@@ -4604,7 +4604,7 @@
       <c r="B178" t="s">
         <v>298</v>
       </c>
-      <c r="C178" s="4">
+      <c r="C178" s="5">
         <v>85</v>
       </c>
       <c r="D178" s="1" t="s">
@@ -4618,7 +4618,7 @@
       <c r="B179" t="s">
         <v>300</v>
       </c>
-      <c r="C179" s="4">
+      <c r="C179" s="5">
         <v>86</v>
       </c>
       <c r="D179" t="s">
@@ -4632,7 +4632,7 @@
       <c r="B180" t="s">
         <v>302</v>
       </c>
-      <c r="C180" s="4">
+      <c r="C180" s="5">
         <v>87</v>
       </c>
       <c r="D180" t="s">
@@ -4646,7 +4646,7 @@
       <c r="B181" t="s">
         <v>304</v>
       </c>
-      <c r="C181" s="4">
+      <c r="C181" s="5">
         <v>88</v>
       </c>
       <c r="D181" t="s">
@@ -4657,10 +4657,10 @@
       <c r="A182" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B182" s="4" t="s">
+      <c r="B182" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="C182" s="4">
+      <c r="C182" s="5">
         <v>89</v>
       </c>
       <c r="D182" t="s">
@@ -4671,10 +4671,10 @@
       <c r="A183" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B183" s="4" t="s">
+      <c r="B183" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="C183" s="4">
+      <c r="C183" s="5">
         <v>90</v>
       </c>
       <c r="D183" s="1" t="s">
@@ -4688,7 +4688,7 @@
       <c r="B184" t="s">
         <v>310</v>
       </c>
-      <c r="C184" s="4">
+      <c r="C184" s="5">
         <v>91</v>
       </c>
       <c r="D184" t="s">
@@ -4702,7 +4702,7 @@
       <c r="B185" t="s">
         <v>312</v>
       </c>
-      <c r="C185" s="4">
+      <c r="C185" s="5">
         <v>92</v>
       </c>
       <c r="D185" t="s">
@@ -4717,7 +4717,7 @@
       <c r="B186" t="s">
         <v>314</v>
       </c>
-      <c r="C186" s="4">
+      <c r="C186" s="5">
         <v>93</v>
       </c>
       <c r="D186" t="s">
@@ -4732,7 +4732,7 @@
       <c r="B187" t="s">
         <v>316</v>
       </c>
-      <c r="C187" s="4">
+      <c r="C187" s="5">
         <v>94</v>
       </c>
       <c r="D187" t="s">
@@ -4747,7 +4747,7 @@
       <c r="B188" t="s">
         <v>318</v>
       </c>
-      <c r="C188" s="4">
+      <c r="C188" s="5">
         <v>95</v>
       </c>
       <c r="D188" t="s">
@@ -4762,7 +4762,7 @@
       <c r="B189" t="s">
         <v>320</v>
       </c>
-      <c r="C189" s="4">
+      <c r="C189" s="5">
         <v>96</v>
       </c>
       <c r="D189" t="s">
@@ -4777,7 +4777,7 @@
       <c r="B190" t="s">
         <v>322</v>
       </c>
-      <c r="C190" s="4">
+      <c r="C190" s="5">
         <v>97</v>
       </c>
       <c r="D190" s="1" t="s">
@@ -4792,7 +4792,7 @@
       <c r="B191" t="s">
         <v>324</v>
       </c>
-      <c r="C191" s="4">
+      <c r="C191" s="5">
         <v>98</v>
       </c>
       <c r="D191" s="1" t="s">
@@ -4807,7 +4807,7 @@
       <c r="B192" t="s">
         <v>326</v>
       </c>
-      <c r="C192" s="4">
+      <c r="C192" s="5">
         <v>99</v>
       </c>
       <c r="D192" s="1" t="s">
@@ -4822,7 +4822,7 @@
       <c r="B193" t="s">
         <v>328</v>
       </c>
-      <c r="C193" s="4">
+      <c r="C193" s="5">
         <v>100</v>
       </c>
       <c r="D193" s="1" t="s">
@@ -4837,7 +4837,7 @@
       <c r="B194" t="s">
         <v>330</v>
       </c>
-      <c r="C194" s="4">
+      <c r="C194" s="5">
         <v>101</v>
       </c>
       <c r="D194" s="1" t="s">
@@ -4852,7 +4852,7 @@
       <c r="B195" t="s">
         <v>332</v>
       </c>
-      <c r="C195" s="4">
+      <c r="C195" s="5">
         <v>102</v>
       </c>
       <c r="D195" s="1" t="s">
@@ -4867,7 +4867,7 @@
       <c r="B196" t="s">
         <v>334</v>
       </c>
-      <c r="C196" s="4">
+      <c r="C196" s="5">
         <v>103</v>
       </c>
       <c r="D196" s="1" t="s">
@@ -4882,7 +4882,7 @@
       <c r="B197" t="s">
         <v>336</v>
       </c>
-      <c r="C197" s="4">
+      <c r="C197" s="5">
         <v>104</v>
       </c>
       <c r="D197" s="1" t="s">
@@ -4897,7 +4897,7 @@
       <c r="B198" t="s">
         <v>338</v>
       </c>
-      <c r="C198" s="4">
+      <c r="C198" s="5">
         <v>105</v>
       </c>
       <c r="D198" s="1" t="s">
@@ -4912,7 +4912,7 @@
       <c r="B199" t="s">
         <v>340</v>
       </c>
-      <c r="C199" s="4">
+      <c r="C199" s="5">
         <v>106</v>
       </c>
       <c r="D199" s="1" t="s">
@@ -4927,7 +4927,7 @@
       <c r="B200" t="s">
         <v>342</v>
       </c>
-      <c r="C200" s="4">
+      <c r="C200" s="5">
         <v>107</v>
       </c>
       <c r="D200" s="1" t="s">
@@ -4942,7 +4942,7 @@
       <c r="B201" t="s">
         <v>344</v>
       </c>
-      <c r="C201" s="4">
+      <c r="C201" s="5">
         <v>108</v>
       </c>
       <c r="D201" s="1" t="s">
@@ -4957,7 +4957,7 @@
       <c r="B202" t="s">
         <v>346</v>
       </c>
-      <c r="C202" s="4">
+      <c r="C202" s="5">
         <v>109</v>
       </c>
       <c r="D202" t="s">
@@ -4972,7 +4972,7 @@
       <c r="B203" t="s">
         <v>348</v>
       </c>
-      <c r="C203" s="4">
+      <c r="C203" s="5">
         <v>110</v>
       </c>
       <c r="D203" s="1" t="s">
@@ -4987,7 +4987,7 @@
       <c r="B204" t="s">
         <v>350</v>
       </c>
-      <c r="C204" s="4">
+      <c r="C204" s="5">
         <v>111</v>
       </c>
       <c r="D204" s="1" t="s">
@@ -5002,7 +5002,7 @@
       <c r="B205" t="s">
         <v>352</v>
       </c>
-      <c r="C205" s="4">
+      <c r="C205" s="5">
         <v>112</v>
       </c>
       <c r="D205" t="s">
@@ -5017,7 +5017,7 @@
       <c r="B206" t="s">
         <v>354</v>
       </c>
-      <c r="C206" s="4">
+      <c r="C206" s="5">
         <v>113</v>
       </c>
       <c r="D206" t="s">
@@ -5032,7 +5032,7 @@
       <c r="B207" t="s">
         <v>356</v>
       </c>
-      <c r="C207" s="4">
+      <c r="C207" s="5">
         <v>114</v>
       </c>
       <c r="D207" t="s">
@@ -5047,7 +5047,7 @@
       <c r="B208" t="s">
         <v>358</v>
       </c>
-      <c r="C208" s="4">
+      <c r="C208" s="5">
         <v>115</v>
       </c>
       <c r="D208" t="s">
@@ -5062,7 +5062,7 @@
       <c r="B209" t="s">
         <v>360</v>
       </c>
-      <c r="C209" s="4">
+      <c r="C209" s="5">
         <v>116</v>
       </c>
       <c r="D209" t="s">
@@ -5077,7 +5077,7 @@
       <c r="B210" t="s">
         <v>362</v>
       </c>
-      <c r="C210" s="4">
+      <c r="C210" s="5">
         <v>117</v>
       </c>
       <c r="D210" t="s">
@@ -5092,7 +5092,7 @@
       <c r="B211" t="s">
         <v>364</v>
       </c>
-      <c r="C211" s="4">
+      <c r="C211" s="5">
         <v>118</v>
       </c>
       <c r="D211" t="s">
@@ -5107,7 +5107,7 @@
       <c r="B212" t="s">
         <v>366</v>
       </c>
-      <c r="C212" s="4">
+      <c r="C212" s="5">
         <v>119</v>
       </c>
       <c r="D212" t="s">
@@ -5122,7 +5122,7 @@
       <c r="B213" t="s">
         <v>368</v>
       </c>
-      <c r="C213" s="4">
+      <c r="C213" s="5">
         <v>120</v>
       </c>
       <c r="D213" t="s">
@@ -5136,7 +5136,7 @@
       <c r="B214" t="s">
         <v>370</v>
       </c>
-      <c r="C214" s="4">
+      <c r="C214" s="5">
         <v>121</v>
       </c>
       <c r="D214" s="1" t="s">
@@ -5150,7 +5150,7 @@
       <c r="B215" t="s">
         <v>372</v>
       </c>
-      <c r="C215" s="4">
+      <c r="C215" s="5">
         <v>122</v>
       </c>
       <c r="D215" t="s">
@@ -5161,10 +5161,10 @@
       <c r="A216" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B216" s="4" t="s">
+      <c r="B216" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="C216" s="4">
+      <c r="C216" s="5">
         <v>123</v>
       </c>
       <c r="D216" t="s">
@@ -5175,10 +5175,10 @@
       <c r="A217" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B217" s="4" t="s">
+      <c r="B217" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="C217" s="4">
+      <c r="C217" s="5">
         <v>124</v>
       </c>
       <c r="D217" t="s">
@@ -5189,10 +5189,10 @@
       <c r="A218" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B218" s="4" t="s">
+      <c r="B218" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="C218" s="4">
+      <c r="C218" s="5">
         <v>125</v>
       </c>
       <c r="D218" t="s">
@@ -5203,10 +5203,10 @@
       <c r="A219" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B219" s="4" t="s">
+      <c r="B219" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="C219" s="4">
+      <c r="C219" s="5">
         <v>126</v>
       </c>
       <c r="D219" t="s">
@@ -5217,10 +5217,10 @@
       <c r="A220" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B220" s="4" t="s">
+      <c r="B220" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="C220" s="4">
+      <c r="C220" s="5">
         <v>127</v>
       </c>
       <c r="D220" t="s">
@@ -5231,10 +5231,10 @@
       <c r="A221" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B221" s="4" t="s">
+      <c r="B221" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="C221" s="4">
+      <c r="C221" s="5">
         <v>128</v>
       </c>
       <c r="D221" t="s">
@@ -5245,10 +5245,10 @@
       <c r="A222" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B222" s="4" t="s">
+      <c r="B222" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="C222" s="4">
+      <c r="C222" s="5">
         <v>129</v>
       </c>
       <c r="D222" t="s">
@@ -5259,10 +5259,10 @@
       <c r="A223" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B223" s="4" t="s">
+      <c r="B223" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="C223" s="4">
+      <c r="C223" s="5">
         <v>130</v>
       </c>
       <c r="D223" t="s">
@@ -5276,7 +5276,7 @@
       <c r="B224" t="s">
         <v>390</v>
       </c>
-      <c r="C224" s="4">
+      <c r="C224" s="5">
         <v>131</v>
       </c>
       <c r="D224" t="s">
@@ -5290,7 +5290,7 @@
       <c r="B225" t="s">
         <v>392</v>
       </c>
-      <c r="C225" s="4">
+      <c r="C225" s="5">
         <v>132</v>
       </c>
       <c r="D225" t="s">
@@ -5304,7 +5304,7 @@
       <c r="B226" t="s">
         <v>394</v>
       </c>
-      <c r="C226" s="4">
+      <c r="C226" s="5">
         <v>133</v>
       </c>
       <c r="D226" t="s">
@@ -5318,7 +5318,7 @@
       <c r="B227" t="s">
         <v>396</v>
       </c>
-      <c r="C227" s="4">
+      <c r="C227" s="5">
         <v>134</v>
       </c>
       <c r="D227" t="s">
@@ -5332,7 +5332,7 @@
       <c r="B228" t="s">
         <v>398</v>
       </c>
-      <c r="C228" s="4">
+      <c r="C228" s="5">
         <v>135</v>
       </c>
       <c r="D228" t="s">
@@ -5346,7 +5346,7 @@
       <c r="B229" t="s">
         <v>400</v>
       </c>
-      <c r="C229" s="4">
+      <c r="C229" s="5">
         <v>136</v>
       </c>
       <c r="D229" t="s">
@@ -5360,7 +5360,7 @@
       <c r="B230" t="s">
         <v>402</v>
       </c>
-      <c r="C230" s="4">
+      <c r="C230" s="5">
         <v>137</v>
       </c>
       <c r="D230" t="s">
@@ -5374,7 +5374,7 @@
       <c r="B231" t="s">
         <v>404</v>
       </c>
-      <c r="C231" s="4">
+      <c r="C231" s="5">
         <v>138</v>
       </c>
       <c r="D231" t="s">
@@ -5388,7 +5388,7 @@
       <c r="B232" t="s">
         <v>406</v>
       </c>
-      <c r="C232" s="4">
+      <c r="C232" s="5">
         <v>139</v>
       </c>
       <c r="D232" t="s">
@@ -5402,7 +5402,7 @@
       <c r="B233" t="s">
         <v>408</v>
       </c>
-      <c r="C233" s="4">
+      <c r="C233" s="5">
         <v>140</v>
       </c>
       <c r="D233" t="s">
@@ -5416,7 +5416,7 @@
       <c r="B234" t="s">
         <v>410</v>
       </c>
-      <c r="C234" s="4">
+      <c r="C234" s="5">
         <v>141</v>
       </c>
       <c r="D234" t="s">
@@ -5430,7 +5430,7 @@
       <c r="B235" t="s">
         <v>412</v>
       </c>
-      <c r="C235" s="4">
+      <c r="C235" s="5">
         <v>142</v>
       </c>
       <c r="D235" t="s">
@@ -5444,7 +5444,7 @@
       <c r="B236" t="s">
         <v>414</v>
       </c>
-      <c r="C236" s="4">
+      <c r="C236" s="5">
         <v>143</v>
       </c>
       <c r="D236" t="s">
@@ -5458,7 +5458,7 @@
       <c r="B237" t="s">
         <v>416</v>
       </c>
-      <c r="C237" s="4">
+      <c r="C237" s="5">
         <v>144</v>
       </c>
       <c r="D237" t="s">
@@ -5472,7 +5472,7 @@
       <c r="B238" t="s">
         <v>418</v>
       </c>
-      <c r="C238" s="4">
+      <c r="C238" s="5">
         <v>145</v>
       </c>
       <c r="D238" t="s">
@@ -5486,7 +5486,7 @@
       <c r="B239" t="s">
         <v>420</v>
       </c>
-      <c r="C239" s="4">
+      <c r="C239" s="5">
         <v>146</v>
       </c>
       <c r="D239" t="s">
@@ -5497,10 +5497,10 @@
       <c r="A240" t="s">
         <v>134</v>
       </c>
-      <c r="B240" s="4" t="s">
+      <c r="B240" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="C240" s="4">
+      <c r="C240" s="5">
         <v>147</v>
       </c>
       <c r="D240" s="1" t="s">
@@ -5511,10 +5511,10 @@
       <c r="A241" t="s">
         <v>134</v>
       </c>
-      <c r="B241" s="4" t="s">
+      <c r="B241" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="C241" s="4">
+      <c r="C241" s="5">
         <v>148</v>
       </c>
       <c r="D241" s="1" t="s">
@@ -5525,10 +5525,10 @@
       <c r="A242" t="s">
         <v>134</v>
       </c>
-      <c r="B242" s="4" t="s">
+      <c r="B242" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="C242" s="4">
+      <c r="C242" s="5">
         <v>149</v>
       </c>
       <c r="D242" t="s">
@@ -5542,7 +5542,7 @@
       <c r="B243" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C243" s="4">
+      <c r="C243" s="5">
         <v>150</v>
       </c>
       <c r="D243" t="s">
@@ -5556,7 +5556,7 @@
       <c r="B244" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C244" s="4">
+      <c r="C244" s="5">
         <v>151</v>
       </c>
       <c r="D244" t="s">
@@ -5567,13 +5567,13 @@
       <c r="A245" t="s">
         <v>134</v>
       </c>
-      <c r="B245" s="5" t="s">
+      <c r="B245" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="C245" s="4">
+      <c r="C245" s="5">
         <v>152</v>
       </c>
-      <c r="D245" s="5" t="s">
+      <c r="D245" s="6" t="s">
         <v>433</v>
       </c>
     </row>
@@ -5584,7 +5584,7 @@
       <c r="B246" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="C246" s="4">
+      <c r="C246" s="5">
         <v>153</v>
       </c>
       <c r="D246" s="6" t="s">
@@ -5607,10 +5607,10 @@
       <c r="A250" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B250" s="4" t="s">
+      <c r="B250" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="C250" s="4">
+      <c r="C250" s="5">
         <v>1111</v>
       </c>
       <c r="D250"/>
@@ -5622,7 +5622,7 @@
       <c r="B251" t="s">
         <v>437</v>
       </c>
-      <c r="C251" s="4">
+      <c r="C251" s="5">
         <v>1112</v>
       </c>
       <c r="D251"/>
@@ -5634,7 +5634,7 @@
       <c r="B252" t="s">
         <v>438</v>
       </c>
-      <c r="C252" s="4">
+      <c r="C252" s="5">
         <v>1113</v>
       </c>
       <c r="D252"/>
@@ -5718,7 +5718,7 @@
       <c r="B272" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C272" s="4">
+      <c r="C272" s="5">
         <v>1</v>
       </c>
       <c r="D272" s="1" t="s">
@@ -5729,10 +5729,10 @@
       <c r="A273" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B273" s="4" t="s">
+      <c r="B273" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="C273" s="4">
+      <c r="C273" s="5">
         <v>2</v>
       </c>
       <c r="D273" s="1" t="s">
@@ -5743,10 +5743,10 @@
       <c r="A274" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B274" s="4" t="s">
+      <c r="B274" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="C274" s="4">
+      <c r="C274" s="5">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
@@ -5757,10 +5757,10 @@
       <c r="A275" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B275" s="4" t="s">
+      <c r="B275" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C275" s="4">
+      <c r="C275" s="5">
         <v>4</v>
       </c>
       <c r="D275" s="1" t="s">
@@ -5771,10 +5771,10 @@
       <c r="A276" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B276" s="4" t="s">
+      <c r="B276" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="C276" s="4">
+      <c r="C276" s="5">
         <v>5</v>
       </c>
       <c r="D276" s="1" t="s">
@@ -5785,10 +5785,10 @@
       <c r="A277" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B277" s="4" t="s">
+      <c r="B277" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="C277" s="4">
+      <c r="C277" s="5">
         <v>6</v>
       </c>
       <c r="D277" s="1" t="s">
@@ -5799,10 +5799,10 @@
       <c r="A278" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B278" s="4" t="s">
+      <c r="B278" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="C278" s="4">
+      <c r="C278" s="5">
         <v>7</v>
       </c>
       <c r="D278" s="1" t="s">
@@ -5816,7 +5816,7 @@
       <c r="B279" t="s">
         <v>15</v>
       </c>
-      <c r="C279" s="4">
+      <c r="C279" s="5">
         <v>8</v>
       </c>
       <c r="D279" t="s">
@@ -5824,16 +5824,16 @@
       </c>
     </row>
     <row r="280" s="3" customFormat="1" spans="1:4">
-      <c r="A280" s="8" t="s">
+      <c r="A280" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="B280" s="8" t="s">
+      <c r="B280" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="C280" s="9">
+      <c r="C280" s="8">
         <v>9</v>
       </c>
-      <c r="D280" s="8" t="s">
+      <c r="D280" s="4" t="s">
         <v>454</v>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       <c r="B281" t="s">
         <v>455</v>
       </c>
-      <c r="C281" s="4">
+      <c r="C281" s="5">
         <v>10</v>
       </c>
       <c r="D281" t="s">
@@ -5858,7 +5858,7 @@
       <c r="B282" t="s">
         <v>457</v>
       </c>
-      <c r="C282" s="4">
+      <c r="C282" s="5">
         <v>11</v>
       </c>
       <c r="D282" t="s">
@@ -5866,149 +5866,158 @@
       </c>
     </row>
     <row r="283" s="3" customFormat="1" spans="1:4">
-      <c r="A283" s="8" t="s">
+      <c r="A283" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="B283" s="8" t="s">
+      <c r="B283" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C283" s="9">
+      <c r="C283" s="8">
         <v>12</v>
       </c>
-      <c r="D283" s="8" t="s">
+      <c r="D283" s="4" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="284" s="3" customFormat="1" spans="1:4">
-      <c r="A284" s="8" t="s">
+      <c r="A284" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="B284" s="9" t="s">
+      <c r="B284" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="C284" s="9">
+      <c r="C284" s="8">
         <v>13</v>
       </c>
-      <c r="D284" s="8" t="s">
+      <c r="D284" s="4" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="285" s="3" customFormat="1" spans="1:4">
-      <c r="A285" s="8" t="s">
+      <c r="A285" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="B285" s="9" t="s">
+      <c r="B285" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="C285" s="9">
+      <c r="C285" s="8">
         <v>14</v>
       </c>
-      <c r="D285" s="8" t="s">
+      <c r="D285" s="4" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="286" s="3" customFormat="1" spans="1:4">
-      <c r="A286" s="8" t="s">
+      <c r="A286" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="B286" s="9" t="s">
+      <c r="B286" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="C286" s="9">
+      <c r="C286" s="8">
         <v>15</v>
       </c>
-      <c r="D286" s="8" t="s">
+      <c r="D286" s="4" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="287" s="3" customFormat="1" spans="1:4">
-      <c r="A287" s="8" t="s">
+      <c r="A287" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="B287" s="9" t="s">
+      <c r="B287" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="C287" s="9">
+      <c r="C287" s="8">
         <v>16</v>
       </c>
-      <c r="D287" s="8" t="s">
+      <c r="D287" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="288" s="3" customFormat="1" spans="1:4">
-      <c r="A288" s="8" t="s">
+      <c r="A288" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="B288" s="9" t="s">
+      <c r="B288" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="C288" s="9">
+      <c r="C288" s="8">
         <v>17</v>
       </c>
-      <c r="D288" s="8" t="s">
+      <c r="D288" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="289" s="3" customFormat="1" spans="1:4">
-      <c r="A289" s="8" t="s">
+      <c r="A289" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="B289" s="9" t="s">
+      <c r="B289" s="8" t="s">
         <v>470</v>
       </c>
-      <c r="C289" s="9">
+      <c r="C289" s="8">
         <v>18</v>
       </c>
-      <c r="D289" s="8" t="s">
+      <c r="D289" s="4" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="290" s="3" customFormat="1" spans="1:4">
-      <c r="A290" s="8" t="s">
+      <c r="A290" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="B290" s="9" t="s">
+      <c r="B290" s="8" t="s">
         <v>472</v>
       </c>
-      <c r="C290" s="9">
+      <c r="C290" s="8">
         <v>19</v>
       </c>
-      <c r="D290" s="8" t="s">
+      <c r="D290" s="4" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="291" s="3" customFormat="1" spans="1:4">
-      <c r="A291" s="8" t="s">
+      <c r="A291" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="B291" s="9" t="s">
+      <c r="B291" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="C291" s="9">
+      <c r="C291" s="8">
         <v>20</v>
       </c>
-      <c r="D291" s="8" t="s">
+      <c r="D291" s="4" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="292" s="3" customFormat="1" spans="1:4">
-      <c r="A292" s="8" t="s">
+      <c r="A292" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="B292" s="9" t="s">
+      <c r="B292" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="C292" s="9">
+      <c r="C292" s="8">
         <v>21</v>
       </c>
-      <c r="D292" s="8" t="s">
+      <c r="D292" s="4" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="293" spans="1:4">
-      <c r="A293"/>
-      <c r="B293"/>
-      <c r="D293"/>
+    <row r="293" s="4" customFormat="1" spans="1:4">
+      <c r="A293" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="B293" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C293" s="8">
+        <v>22</v>
+      </c>
+      <c r="D293" s="4" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="294" spans="1:4">
       <c r="A294"/>
@@ -6016,87 +6025,92 @@
       <c r="D294"/>
     </row>
     <row r="295" spans="1:4">
-      <c r="A295" t="s">
-        <v>478</v>
-      </c>
-      <c r="B295" t="s">
-        <v>479</v>
-      </c>
-      <c r="C295" s="4">
-        <v>1</v>
-      </c>
-      <c r="D295" t="s">
-        <v>480</v>
-      </c>
+      <c r="A295"/>
+      <c r="B295"/>
+      <c r="D295"/>
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B296" t="s">
+        <v>480</v>
+      </c>
+      <c r="C296" s="5">
+        <v>1</v>
+      </c>
+      <c r="D296" t="s">
         <v>481</v>
-      </c>
-      <c r="C296" s="4">
-        <v>2</v>
-      </c>
-      <c r="D296" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B297" t="s">
+        <v>482</v>
+      </c>
+      <c r="C297" s="5">
+        <v>2</v>
+      </c>
+      <c r="D297" t="s">
         <v>483</v>
-      </c>
-      <c r="C297" s="4">
-        <v>3</v>
-      </c>
-      <c r="D297" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
+        <v>479</v>
+      </c>
+      <c r="B298" t="s">
+        <v>484</v>
+      </c>
+      <c r="C298" s="5">
+        <v>3</v>
+      </c>
+      <c r="D298" t="s">
         <v>485</v>
-      </c>
-      <c r="B298" t="s">
-        <v>486</v>
-      </c>
-      <c r="C298" s="4">
-        <v>1</v>
-      </c>
-      <c r="D298" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B299" t="s">
+        <v>487</v>
+      </c>
+      <c r="C299" s="5">
+        <v>1</v>
+      </c>
+      <c r="D299" t="s">
         <v>488</v>
-      </c>
-      <c r="C299" s="4">
-        <v>2</v>
-      </c>
-      <c r="D299" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B300" t="s">
+        <v>489</v>
+      </c>
+      <c r="C300" s="5">
+        <v>2</v>
+      </c>
+      <c r="D300" t="s">
         <v>490</v>
       </c>
-      <c r="C300" s="4">
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" t="s">
+        <v>486</v>
+      </c>
+      <c r="B301" t="s">
+        <v>491</v>
+      </c>
+      <c r="C301" s="5">
         <v>3</v>
       </c>
-      <c r="D300" t="s">
-        <v>491</v>
+      <c r="D301" t="s">
+        <v>492</v>
       </c>
     </row>
   </sheetData>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="13170" windowHeight="11550"/>
+    <workbookView windowWidth="14715" windowHeight="11025"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="495">
   <si>
     <t>Enum</t>
   </si>
@@ -56,6 +56,12 @@
   </si>
   <si>
     <t>Boss</t>
+  </si>
+  <si>
+    <t>Elite</t>
+  </si>
+  <si>
+    <t>精英敌人</t>
   </si>
   <si>
     <t>HandType</t>
@@ -2132,14 +2138,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -2149,12 +2152,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2508,12 +2505,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:E301"/>
+  <dimension ref="A4:E302"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16.7416666666667" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.7" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.05833333333333" style="5" customWidth="1"/>
+    <col min="3" max="3" width="7.05833333333333" style="4" customWidth="1"/>
     <col min="4" max="4" width="31.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="34.75" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1" customWidth="1"/>
@@ -2526,7 +2523,7 @@
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
@@ -2540,7 +2537,7 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -2554,36 +2551,36 @@
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C8" s="4">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
         <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="5">
-        <v>2</v>
+      <c r="C10" s="4">
+        <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>12</v>
@@ -2591,13 +2588,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="5">
-        <v>4</v>
+      <c r="C11" s="4">
+        <v>2</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>14</v>
@@ -2605,13 +2602,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="5">
-        <v>3</v>
+      <c r="C12" s="4">
+        <v>4</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>16</v>
@@ -2619,13 +2616,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="5">
-        <v>5</v>
+      <c r="C13" s="4">
+        <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>18</v>
@@ -2633,69 +2630,69 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="5">
-        <v>6</v>
+      <c r="C14" s="4">
+        <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C15" s="4">
+        <v>6</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C16" s="5">
-        <v>1</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="5">
-        <v>2</v>
+      <c r="C17" s="4">
+        <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
+    <row r="18" spans="1:4">
+      <c r="A18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C18" s="4">
+        <v>2</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="C19" s="5">
-        <v>1</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="5">
-        <v>2</v>
+      <c r="C20" s="4">
+        <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>30</v>
@@ -2703,13 +2700,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="5">
-        <v>3</v>
+      <c r="C21" s="4">
+        <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>32</v>
@@ -2717,41 +2714,41 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="5">
-        <v>4</v>
+      <c r="C22" s="4">
+        <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="1" t="s">
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C23" s="4">
+        <v>4</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C39" s="5">
-        <v>1</v>
-      </c>
-      <c r="D39" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="5">
-        <v>2</v>
+      <c r="C40" s="4">
+        <v>1</v>
       </c>
       <c r="D40" t="s">
         <v>39</v>
@@ -2759,13 +2756,13 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="5">
-        <v>3</v>
+      <c r="C41" s="4">
+        <v>2</v>
       </c>
       <c r="D41" t="s">
         <v>41</v>
@@ -2773,13 +2770,13 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="5">
-        <v>4</v>
+      <c r="C42" s="4">
+        <v>3</v>
       </c>
       <c r="D42" t="s">
         <v>43</v>
@@ -2787,13 +2784,13 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="5">
-        <v>5</v>
+      <c r="C43" s="4">
+        <v>4</v>
       </c>
       <c r="D43" t="s">
         <v>45</v>
@@ -2801,27 +2798,27 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="5">
-        <v>6</v>
-      </c>
-      <c r="D44" s="1" t="s">
+      <c r="C44" s="4">
+        <v>5</v>
+      </c>
+      <c r="D44" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C45" s="5">
-        <v>7</v>
+      <c r="C45" s="4">
+        <v>6</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>49</v>
@@ -2829,13 +2826,13 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="5">
-        <v>8</v>
+      <c r="C46" s="4">
+        <v>7</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>51</v>
@@ -2843,13 +2840,13 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C47" s="5">
-        <v>9</v>
+      <c r="C47" s="4">
+        <v>8</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>53</v>
@@ -2857,13 +2854,13 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="5">
-        <v>10</v>
+      <c r="C48" s="4">
+        <v>9</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>55</v>
@@ -2871,41 +2868,41 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="5">
-        <v>11</v>
+      <c r="C49" s="4">
+        <v>10</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" t="s">
-        <v>35</v>
-      </c>
-      <c r="B50" t="s">
+      <c r="A50" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C50" s="5">
-        <v>12</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="C50" s="4">
+        <v>11</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B51" t="s">
         <v>60</v>
       </c>
-      <c r="C51" s="5">
-        <v>13</v>
+      <c r="C51" s="4">
+        <v>12</v>
       </c>
       <c r="D51" t="s">
         <v>61</v>
@@ -2913,13 +2910,13 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B52" t="s">
         <v>62</v>
       </c>
-      <c r="C52" s="5">
-        <v>14</v>
+      <c r="C52" s="4">
+        <v>13</v>
       </c>
       <c r="D52" t="s">
         <v>63</v>
@@ -2927,13 +2924,13 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B53" t="s">
         <v>64</v>
       </c>
-      <c r="C53" s="5">
-        <v>15</v>
+      <c r="C53" s="4">
+        <v>14</v>
       </c>
       <c r="D53" t="s">
         <v>65</v>
@@ -2941,13 +2938,13 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B54" t="s">
         <v>66</v>
       </c>
-      <c r="C54" s="5">
-        <v>16</v>
+      <c r="C54" s="4">
+        <v>15</v>
       </c>
       <c r="D54" t="s">
         <v>67</v>
@@ -2955,13 +2952,13 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B55" t="s">
         <v>68</v>
       </c>
-      <c r="C55" s="5">
-        <v>17</v>
+      <c r="C55" s="4">
+        <v>16</v>
       </c>
       <c r="D55" t="s">
         <v>69</v>
@@ -2969,13 +2966,13 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B56" t="s">
         <v>70</v>
       </c>
-      <c r="C56" s="5">
-        <v>18</v>
+      <c r="C56" s="4">
+        <v>17</v>
       </c>
       <c r="D56" t="s">
         <v>71</v>
@@ -2983,13 +2980,13 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B57" t="s">
         <v>72</v>
       </c>
-      <c r="C57" s="5">
-        <v>19</v>
+      <c r="C57" s="4">
+        <v>18</v>
       </c>
       <c r="D57" t="s">
         <v>73</v>
@@ -2997,13 +2994,13 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B58" t="s">
         <v>74</v>
       </c>
-      <c r="C58" s="5">
-        <v>20</v>
+      <c r="C58" s="4">
+        <v>19</v>
       </c>
       <c r="D58" t="s">
         <v>75</v>
@@ -3011,13 +3008,13 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B59" t="s">
         <v>76</v>
       </c>
-      <c r="C59" s="5">
-        <v>21</v>
+      <c r="C59" s="4">
+        <v>20</v>
       </c>
       <c r="D59" t="s">
         <v>77</v>
@@ -3025,13 +3022,13 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B60" t="s">
         <v>78</v>
       </c>
-      <c r="C60" s="5">
-        <v>22</v>
+      <c r="C60" s="4">
+        <v>21</v>
       </c>
       <c r="D60" t="s">
         <v>79</v>
@@ -3039,13 +3036,13 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B61" t="s">
         <v>80</v>
       </c>
-      <c r="C61" s="5">
-        <v>23</v>
+      <c r="C61" s="4">
+        <v>22</v>
       </c>
       <c r="D61" t="s">
         <v>81</v>
@@ -3053,13 +3050,13 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B62" t="s">
         <v>82</v>
       </c>
-      <c r="C62" s="5">
-        <v>24</v>
+      <c r="C62" s="4">
+        <v>23</v>
       </c>
       <c r="D62" t="s">
         <v>83</v>
@@ -3067,13 +3064,13 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B63" t="s">
         <v>84</v>
       </c>
-      <c r="C63" s="5">
-        <v>25</v>
+      <c r="C63" s="4">
+        <v>24</v>
       </c>
       <c r="D63" t="s">
         <v>85</v>
@@ -3081,13 +3078,13 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B64" t="s">
         <v>86</v>
       </c>
-      <c r="C64" s="5">
-        <v>26</v>
+      <c r="C64" s="4">
+        <v>25</v>
       </c>
       <c r="D64" t="s">
         <v>87</v>
@@ -3095,13 +3092,13 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B65" t="s">
         <v>88</v>
       </c>
-      <c r="C65" s="5">
-        <v>27</v>
+      <c r="C65" s="4">
+        <v>26</v>
       </c>
       <c r="D65" t="s">
         <v>89</v>
@@ -3109,13 +3106,13 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B66" t="s">
         <v>90</v>
       </c>
-      <c r="C66" s="5">
-        <v>28</v>
+      <c r="C66" s="4">
+        <v>27</v>
       </c>
       <c r="D66" t="s">
         <v>91</v>
@@ -3123,13 +3120,13 @@
     </row>
     <row r="67" s="1" customFormat="1" spans="1:4">
       <c r="A67" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B67" t="s">
         <v>92</v>
       </c>
-      <c r="C67" s="5">
-        <v>29</v>
+      <c r="C67" s="4">
+        <v>28</v>
       </c>
       <c r="D67" t="s">
         <v>93</v>
@@ -3137,13 +3134,13 @@
     </row>
     <row r="68" s="1" customFormat="1" spans="1:4">
       <c r="A68" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B68" t="s">
         <v>94</v>
       </c>
-      <c r="C68" s="5">
-        <v>30</v>
+      <c r="C68" s="4">
+        <v>29</v>
       </c>
       <c r="D68" t="s">
         <v>95</v>
@@ -3151,13 +3148,13 @@
     </row>
     <row r="69" s="1" customFormat="1" spans="1:4">
       <c r="A69" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B69" t="s">
         <v>96</v>
       </c>
-      <c r="C69" s="5">
-        <v>31</v>
+      <c r="C69" s="4">
+        <v>30</v>
       </c>
       <c r="D69" t="s">
         <v>97</v>
@@ -3165,13 +3162,13 @@
     </row>
     <row r="70" s="1" customFormat="1" spans="1:4">
       <c r="A70" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B70" t="s">
         <v>98</v>
       </c>
-      <c r="C70" s="5">
-        <v>32</v>
+      <c r="C70" s="4">
+        <v>31</v>
       </c>
       <c r="D70" t="s">
         <v>99</v>
@@ -3179,13 +3176,13 @@
     </row>
     <row r="71" s="1" customFormat="1" spans="1:4">
       <c r="A71" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B71" t="s">
         <v>100</v>
       </c>
-      <c r="C71" s="5">
-        <v>33</v>
+      <c r="C71" s="4">
+        <v>32</v>
       </c>
       <c r="D71" t="s">
         <v>101</v>
@@ -3193,13 +3190,13 @@
     </row>
     <row r="72" s="1" customFormat="1" spans="1:4">
       <c r="A72" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B72" t="s">
         <v>102</v>
       </c>
-      <c r="C72" s="5">
-        <v>34</v>
+      <c r="C72" s="4">
+        <v>33</v>
       </c>
       <c r="D72" t="s">
         <v>103</v>
@@ -3207,13 +3204,13 @@
     </row>
     <row r="73" s="1" customFormat="1" spans="1:4">
       <c r="A73" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B73" t="s">
         <v>104</v>
       </c>
-      <c r="C73" s="5">
-        <v>35</v>
+      <c r="C73" s="4">
+        <v>34</v>
       </c>
       <c r="D73" t="s">
         <v>105</v>
@@ -3221,13 +3218,13 @@
     </row>
     <row r="74" s="1" customFormat="1" spans="1:4">
       <c r="A74" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B74" t="s">
         <v>106</v>
       </c>
-      <c r="C74" s="5">
-        <v>36</v>
+      <c r="C74" s="4">
+        <v>35</v>
       </c>
       <c r="D74" t="s">
         <v>107</v>
@@ -3235,13 +3232,13 @@
     </row>
     <row r="75" s="1" customFormat="1" spans="1:4">
       <c r="A75" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B75" t="s">
         <v>108</v>
       </c>
-      <c r="C75" s="5">
-        <v>37</v>
+      <c r="C75" s="4">
+        <v>36</v>
       </c>
       <c r="D75" t="s">
         <v>109</v>
@@ -3249,13 +3246,13 @@
     </row>
     <row r="76" s="1" customFormat="1" spans="1:4">
       <c r="A76" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B76" t="s">
         <v>110</v>
       </c>
-      <c r="C76" s="5">
-        <v>38</v>
+      <c r="C76" s="4">
+        <v>37</v>
       </c>
       <c r="D76" t="s">
         <v>111</v>
@@ -3263,13 +3260,13 @@
     </row>
     <row r="77" s="1" customFormat="1" spans="1:4">
       <c r="A77" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B77" t="s">
         <v>112</v>
       </c>
-      <c r="C77" s="5">
-        <v>39</v>
+      <c r="C77" s="4">
+        <v>38</v>
       </c>
       <c r="D77" t="s">
         <v>113</v>
@@ -3277,13 +3274,13 @@
     </row>
     <row r="78" s="1" customFormat="1" spans="1:4">
       <c r="A78" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B78" t="s">
         <v>114</v>
       </c>
-      <c r="C78" s="5">
-        <v>40</v>
+      <c r="C78" s="4">
+        <v>39</v>
       </c>
       <c r="D78" t="s">
         <v>115</v>
@@ -3291,13 +3288,13 @@
     </row>
     <row r="79" s="1" customFormat="1" spans="1:4">
       <c r="A79" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B79" t="s">
         <v>116</v>
       </c>
-      <c r="C79" s="5">
-        <v>41</v>
+      <c r="C79" s="4">
+        <v>40</v>
       </c>
       <c r="D79" t="s">
         <v>117</v>
@@ -3305,13 +3302,13 @@
     </row>
     <row r="80" s="1" customFormat="1" spans="1:4">
       <c r="A80" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B80" t="s">
         <v>118</v>
       </c>
-      <c r="C80" s="5">
-        <v>42</v>
+      <c r="C80" s="4">
+        <v>41</v>
       </c>
       <c r="D80" t="s">
         <v>119</v>
@@ -3319,13 +3316,13 @@
     </row>
     <row r="81" s="1" customFormat="1" spans="1:4">
       <c r="A81" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B81" t="s">
         <v>120</v>
       </c>
-      <c r="C81" s="5">
-        <v>43</v>
+      <c r="C81" s="4">
+        <v>42</v>
       </c>
       <c r="D81" t="s">
         <v>121</v>
@@ -3333,117 +3330,111 @@
     </row>
     <row r="82" s="1" customFormat="1" spans="1:4">
       <c r="A82" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B82" t="s">
         <v>122</v>
       </c>
-      <c r="C82" s="5">
-        <v>44</v>
+      <c r="C82" s="4">
+        <v>43</v>
       </c>
       <c r="D82" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="83" customFormat="1" spans="1:4">
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B83" t="s">
         <v>124</v>
       </c>
-      <c r="C83" s="5">
-        <v>45</v>
+      <c r="C83" s="4">
+        <v>44</v>
       </c>
       <c r="D83" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="84" customFormat="1" spans="1:4">
+    <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>35</v>
-      </c>
-      <c r="B84" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B84" t="s">
         <v>126</v>
       </c>
-      <c r="C84" s="5">
-        <v>46</v>
+      <c r="C84" s="4">
+        <v>45</v>
       </c>
       <c r="D84" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="85" customFormat="1" spans="1:4">
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C85" s="5">
-        <v>47</v>
+      <c r="C85" s="4">
+        <v>46</v>
       </c>
       <c r="D85" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="86" customFormat="1" spans="1:4">
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C86" s="5">
-        <v>48</v>
+      <c r="C86" s="4">
+        <v>47</v>
       </c>
       <c r="D86" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="87" customFormat="1" spans="1:4">
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C87" s="5">
-        <v>49</v>
+      <c r="C87" s="4">
+        <v>48</v>
       </c>
       <c r="D87" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="88" customFormat="1" spans="1:4">
-      <c r="A88" s="1"/>
-      <c r="B88" s="1"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="1"/>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94" s="1" t="s">
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
+        <v>37</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C88" s="4">
+        <v>49</v>
+      </c>
+      <c r="D88" t="s">
         <v>135</v>
-      </c>
-      <c r="C94" s="5">
-        <v>1</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C95" s="5">
-        <v>2</v>
+      <c r="C95" s="4">
+        <v>1</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>138</v>
@@ -3451,13 +3442,13 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C96" s="5">
-        <v>3</v>
+      <c r="C96" s="4">
+        <v>2</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>140</v>
@@ -3465,13 +3456,13 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B97" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C97" s="5">
-        <v>4</v>
+      <c r="C97" s="4">
+        <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>142</v>
@@ -3479,13 +3470,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B98" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B98" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C98" s="5">
-        <v>5</v>
+      <c r="C98" s="4">
+        <v>4</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>144</v>
@@ -3493,13 +3484,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B99" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B99" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C99" s="5">
-        <v>6</v>
+      <c r="C99" s="4">
+        <v>5</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>146</v>
@@ -3507,13 +3498,13 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B100" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B100" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C100" s="5">
-        <v>7</v>
+      <c r="C100" s="4">
+        <v>6</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>148</v>
@@ -3521,13 +3512,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B101" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B101" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C101" s="5">
-        <v>8</v>
+      <c r="C101" s="4">
+        <v>7</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>150</v>
@@ -3535,13 +3526,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B102" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B102" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C102" s="5">
-        <v>9</v>
+      <c r="C102" s="4">
+        <v>8</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>152</v>
@@ -3549,13 +3540,13 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B103" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B103" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C103" s="5">
-        <v>10</v>
+      <c r="C103" s="4">
+        <v>9</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>154</v>
@@ -3563,13 +3554,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B104" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B104" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C104" s="5">
-        <v>11</v>
+      <c r="C104" s="4">
+        <v>10</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>156</v>
@@ -3577,13 +3568,13 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B105" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B105" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C105" s="5">
-        <v>12</v>
+      <c r="C105" s="4">
+        <v>11</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>158</v>
@@ -3591,13 +3582,13 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B106" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B106" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C106" s="5">
-        <v>13</v>
+      <c r="C106" s="4">
+        <v>12</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>160</v>
@@ -3605,13 +3596,13 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B107" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B107" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C107" s="5">
-        <v>14</v>
+      <c r="C107" s="4">
+        <v>13</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>162</v>
@@ -3619,13 +3610,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B108" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B108" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C108" s="5">
-        <v>15</v>
+      <c r="C108" s="4">
+        <v>14</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>164</v>
@@ -3633,13 +3624,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B109" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B109" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C109" s="5">
-        <v>16</v>
+      <c r="C109" s="4">
+        <v>15</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>166</v>
@@ -3647,13 +3638,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B110" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C110" s="5">
-        <v>17</v>
+      <c r="C110" s="4">
+        <v>16</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>168</v>
@@ -3661,13 +3652,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B111" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B111" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C111" s="5">
-        <v>18</v>
+      <c r="C111" s="4">
+        <v>17</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>170</v>
@@ -3675,13 +3666,13 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B112" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C112" s="5">
-        <v>19</v>
+      <c r="C112" s="4">
+        <v>18</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>172</v>
@@ -3689,13 +3680,13 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B113" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B113" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C113" s="5">
-        <v>20</v>
+      <c r="C113" s="4">
+        <v>19</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>174</v>
@@ -3703,13 +3694,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C114" s="5">
-        <v>21</v>
+      <c r="C114" s="4">
+        <v>20</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>176</v>
@@ -3717,13 +3708,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B115" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C115" s="5">
-        <v>22</v>
+      <c r="C115" s="4">
+        <v>21</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>178</v>
@@ -3731,13 +3722,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B116" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B116" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="C116" s="5">
-        <v>23</v>
+      <c r="C116" s="4">
+        <v>22</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>180</v>
@@ -3745,13 +3736,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B117" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B117" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C117" s="5">
-        <v>24</v>
+      <c r="C117" s="4">
+        <v>23</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>182</v>
@@ -3759,13 +3750,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C118" s="5">
-        <v>25</v>
+      <c r="C118" s="4">
+        <v>24</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>184</v>
@@ -3773,13 +3764,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C119" s="5">
-        <v>26</v>
+      <c r="C119" s="4">
+        <v>25</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>186</v>
@@ -3787,13 +3778,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C120" s="5">
-        <v>27</v>
+      <c r="C120" s="4">
+        <v>26</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>188</v>
@@ -3801,13 +3792,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C121" s="5">
-        <v>28</v>
+      <c r="C121" s="4">
+        <v>27</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>190</v>
@@ -3815,13 +3806,13 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C122" s="5">
-        <v>29</v>
+      <c r="C122" s="4">
+        <v>28</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>192</v>
@@ -3829,13 +3820,13 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B123" t="s">
+        <v>136</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C123" s="5">
-        <v>30</v>
+      <c r="C123" s="4">
+        <v>29</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>194</v>
@@ -3843,13 +3834,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B124" t="s">
         <v>195</v>
       </c>
-      <c r="C124" s="5">
-        <v>31</v>
+      <c r="C124" s="4">
+        <v>30</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>196</v>
@@ -3857,13 +3848,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B125" t="s">
         <v>197</v>
       </c>
-      <c r="C125" s="5">
-        <v>32</v>
+      <c r="C125" s="4">
+        <v>31</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>198</v>
@@ -3871,13 +3862,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B126" t="s">
         <v>199</v>
       </c>
-      <c r="C126" s="5">
-        <v>33</v>
+      <c r="C126" s="4">
+        <v>32</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>200</v>
@@ -3885,83 +3876,83 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C127" s="5">
-        <v>34</v>
-      </c>
-      <c r="D127" t="s">
+        <v>136</v>
+      </c>
+      <c r="B127" t="s">
         <v>201</v>
+      </c>
+      <c r="C127" s="4">
+        <v>33</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B128" t="s">
+        <v>136</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C128" s="5">
-        <v>35</v>
+      <c r="C128" s="4">
+        <v>34</v>
       </c>
       <c r="D128" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B129" t="s">
         <v>15</v>
       </c>
-      <c r="C129" s="5">
-        <v>36</v>
+      <c r="C129" s="4">
+        <v>35</v>
       </c>
       <c r="D129" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B130" t="s">
         <v>17</v>
       </c>
-      <c r="C130" s="5">
-        <v>37</v>
+      <c r="C130" s="4">
+        <v>36</v>
       </c>
       <c r="D130" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B131" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B131" t="s">
         <v>19</v>
       </c>
-      <c r="C131" s="5">
-        <v>38</v>
+      <c r="C131" s="4">
+        <v>37</v>
       </c>
       <c r="D131" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B132" t="s">
-        <v>206</v>
-      </c>
-      <c r="C132" s="5">
-        <v>39</v>
+        <v>136</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C132" s="4">
+        <v>38</v>
       </c>
       <c r="D132" t="s">
         <v>207</v>
@@ -3969,13 +3960,13 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B133" t="s">
         <v>208</v>
       </c>
-      <c r="C133" s="5">
-        <v>40</v>
+      <c r="C133" s="4">
+        <v>39</v>
       </c>
       <c r="D133" t="s">
         <v>209</v>
@@ -3983,13 +3974,13 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B134" t="s">
         <v>210</v>
       </c>
-      <c r="C134" s="5">
-        <v>41</v>
+      <c r="C134" s="4">
+        <v>40</v>
       </c>
       <c r="D134" t="s">
         <v>211</v>
@@ -3997,13 +3988,13 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B135" t="s">
         <v>212</v>
       </c>
-      <c r="C135" s="5">
-        <v>42</v>
+      <c r="C135" s="4">
+        <v>41</v>
       </c>
       <c r="D135" t="s">
         <v>213</v>
@@ -4011,13 +4002,13 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B136" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B136" t="s">
         <v>214</v>
       </c>
-      <c r="C136" s="5">
-        <v>43</v>
+      <c r="C136" s="4">
+        <v>42</v>
       </c>
       <c r="D136" t="s">
         <v>215</v>
@@ -4025,13 +4016,13 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B137" t="s">
+        <v>136</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C137" s="5">
-        <v>44</v>
+      <c r="C137" s="4">
+        <v>43</v>
       </c>
       <c r="D137" t="s">
         <v>217</v>
@@ -4039,13 +4030,13 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B138" t="s">
         <v>218</v>
       </c>
-      <c r="C138" s="5">
-        <v>45</v>
+      <c r="C138" s="4">
+        <v>44</v>
       </c>
       <c r="D138" t="s">
         <v>219</v>
@@ -4053,13 +4044,13 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B139" t="s">
         <v>220</v>
       </c>
-      <c r="C139" s="5">
-        <v>46</v>
+      <c r="C139" s="4">
+        <v>45</v>
       </c>
       <c r="D139" t="s">
         <v>221</v>
@@ -4067,13 +4058,13 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B140" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B140" t="s">
         <v>222</v>
       </c>
-      <c r="C140" s="5">
-        <v>47</v>
+      <c r="C140" s="4">
+        <v>46</v>
       </c>
       <c r="D140" t="s">
         <v>223</v>
@@ -4081,13 +4072,13 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B141" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B141" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C141" s="5">
-        <v>48</v>
+      <c r="C141" s="4">
+        <v>47</v>
       </c>
       <c r="D141" t="s">
         <v>225</v>
@@ -4095,13 +4086,13 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B142" t="s">
+        <v>136</v>
+      </c>
+      <c r="B142" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="C142" s="5">
-        <v>49</v>
+      <c r="C142" s="4">
+        <v>48</v>
       </c>
       <c r="D142" t="s">
         <v>227</v>
@@ -4109,13 +4100,13 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B143" t="s">
         <v>228</v>
       </c>
-      <c r="C143" s="5">
-        <v>50</v>
+      <c r="C143" s="4">
+        <v>49</v>
       </c>
       <c r="D143" t="s">
         <v>229</v>
@@ -4123,13 +4114,13 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B144" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B144" t="s">
         <v>230</v>
       </c>
-      <c r="C144" s="5">
-        <v>51</v>
+      <c r="C144" s="4">
+        <v>50</v>
       </c>
       <c r="D144" t="s">
         <v>231</v>
@@ -4137,13 +4128,13 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B145" t="s">
+        <v>136</v>
+      </c>
+      <c r="B145" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C145" s="5">
-        <v>52</v>
+      <c r="C145" s="4">
+        <v>51</v>
       </c>
       <c r="D145" t="s">
         <v>233</v>
@@ -4151,13 +4142,13 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B146" t="s">
         <v>234</v>
       </c>
-      <c r="C146" s="5">
-        <v>53</v>
+      <c r="C146" s="4">
+        <v>52</v>
       </c>
       <c r="D146" t="s">
         <v>235</v>
@@ -4165,13 +4156,13 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B147" t="s">
         <v>236</v>
       </c>
-      <c r="C147" s="5">
-        <v>54</v>
+      <c r="C147" s="4">
+        <v>53</v>
       </c>
       <c r="D147" t="s">
         <v>237</v>
@@ -4179,13 +4170,13 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B148" t="s">
         <v>238</v>
       </c>
-      <c r="C148" s="5">
-        <v>55</v>
+      <c r="C148" s="4">
+        <v>54</v>
       </c>
       <c r="D148" t="s">
         <v>239</v>
@@ -4193,13 +4184,13 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B149" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B149" t="s">
         <v>240</v>
       </c>
-      <c r="C149" s="5">
-        <v>56</v>
+      <c r="C149" s="4">
+        <v>55</v>
       </c>
       <c r="D149" t="s">
         <v>241</v>
@@ -4207,13 +4198,13 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B150" t="s">
+        <v>136</v>
+      </c>
+      <c r="B150" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C150" s="5">
-        <v>57</v>
+      <c r="C150" s="4">
+        <v>56</v>
       </c>
       <c r="D150" t="s">
         <v>243</v>
@@ -4221,13 +4212,13 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B151" t="s">
         <v>244</v>
       </c>
-      <c r="C151" s="5">
-        <v>58</v>
+      <c r="C151" s="4">
+        <v>57</v>
       </c>
       <c r="D151" t="s">
         <v>245</v>
@@ -4235,13 +4226,13 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B152" t="s">
         <v>246</v>
       </c>
-      <c r="C152" s="5">
-        <v>59</v>
+      <c r="C152" s="4">
+        <v>58</v>
       </c>
       <c r="D152" t="s">
         <v>247</v>
@@ -4249,13 +4240,13 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B153" t="s">
         <v>248</v>
       </c>
-      <c r="C153" s="5">
-        <v>60</v>
+      <c r="C153" s="4">
+        <v>59</v>
       </c>
       <c r="D153" t="s">
         <v>249</v>
@@ -4263,13 +4254,13 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B154" t="s">
         <v>250</v>
       </c>
-      <c r="C154" s="5">
-        <v>61</v>
+      <c r="C154" s="4">
+        <v>60</v>
       </c>
       <c r="D154" t="s">
         <v>251</v>
@@ -4277,13 +4268,13 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B155" t="s">
         <v>252</v>
       </c>
-      <c r="C155" s="5">
-        <v>62</v>
+      <c r="C155" s="4">
+        <v>61</v>
       </c>
       <c r="D155" t="s">
         <v>253</v>
@@ -4291,13 +4282,13 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B156" t="s">
         <v>254</v>
       </c>
-      <c r="C156" s="5">
-        <v>63</v>
+      <c r="C156" s="4">
+        <v>62</v>
       </c>
       <c r="D156" t="s">
         <v>255</v>
@@ -4305,13 +4296,13 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B157" t="s">
         <v>256</v>
       </c>
-      <c r="C157" s="5">
-        <v>64</v>
+      <c r="C157" s="4">
+        <v>63</v>
       </c>
       <c r="D157" t="s">
         <v>257</v>
@@ -4319,41 +4310,41 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B158" t="s">
         <v>258</v>
       </c>
-      <c r="C158" s="5">
-        <v>65</v>
-      </c>
-      <c r="D158" s="1" t="s">
+      <c r="C158" s="4">
+        <v>64</v>
+      </c>
+      <c r="D158" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B159" t="s">
         <v>260</v>
       </c>
-      <c r="C159" s="5">
-        <v>66</v>
-      </c>
-      <c r="D159" t="s">
+      <c r="C159" s="4">
+        <v>65</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B160" t="s">
         <v>262</v>
       </c>
-      <c r="C160" s="5">
-        <v>67</v>
+      <c r="C160" s="4">
+        <v>66</v>
       </c>
       <c r="D160" t="s">
         <v>263</v>
@@ -4361,13 +4352,13 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B161" t="s">
         <v>264</v>
       </c>
-      <c r="C161" s="5">
-        <v>68</v>
+      <c r="C161" s="4">
+        <v>67</v>
       </c>
       <c r="D161" t="s">
         <v>265</v>
@@ -4375,13 +4366,13 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B162" t="s">
         <v>266</v>
       </c>
-      <c r="C162" s="5">
-        <v>69</v>
+      <c r="C162" s="4">
+        <v>68</v>
       </c>
       <c r="D162" t="s">
         <v>267</v>
@@ -4389,13 +4380,13 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B163" t="s">
         <v>268</v>
       </c>
-      <c r="C163" s="5">
-        <v>70</v>
+      <c r="C163" s="4">
+        <v>69</v>
       </c>
       <c r="D163" t="s">
         <v>269</v>
@@ -4403,27 +4394,27 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B164" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B164" t="s">
         <v>270</v>
       </c>
-      <c r="C164" s="5">
-        <v>71</v>
-      </c>
-      <c r="D164" s="1" t="s">
+      <c r="C164" s="4">
+        <v>70</v>
+      </c>
+      <c r="D164" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C165" s="5">
-        <v>72</v>
+      <c r="C165" s="4">
+        <v>71</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>273</v>
@@ -4431,83 +4422,83 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B166" t="s">
+        <v>136</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C166" s="5">
-        <v>73</v>
-      </c>
-      <c r="D166" t="s">
+      <c r="C166" s="4">
+        <v>72</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B167" t="s">
         <v>276</v>
       </c>
-      <c r="C167" s="5">
-        <v>74</v>
-      </c>
-      <c r="D167" s="1" t="s">
+      <c r="C167" s="4">
+        <v>73</v>
+      </c>
+      <c r="D167" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B168" t="s">
         <v>278</v>
       </c>
-      <c r="C168" s="5">
-        <v>75</v>
-      </c>
-      <c r="D168" t="s">
+      <c r="C168" s="4">
+        <v>74</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B169" t="s">
         <v>280</v>
       </c>
-      <c r="C169" s="5">
-        <v>76</v>
-      </c>
-      <c r="D169" s="1" t="s">
+      <c r="C169" s="4">
+        <v>75</v>
+      </c>
+      <c r="D169" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B170" t="s">
         <v>282</v>
       </c>
-      <c r="C170" s="5">
-        <v>77</v>
-      </c>
-      <c r="D170" t="s">
+      <c r="C170" s="4">
+        <v>76</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B171" t="s">
         <v>284</v>
       </c>
-      <c r="C171" s="5">
-        <v>78</v>
+      <c r="C171" s="4">
+        <v>77</v>
       </c>
       <c r="D171" t="s">
         <v>285</v>
@@ -4515,27 +4506,27 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B172" t="s">
         <v>286</v>
       </c>
-      <c r="C172" s="5">
-        <v>79</v>
-      </c>
-      <c r="D172" s="1" t="s">
+      <c r="C172" s="4">
+        <v>78</v>
+      </c>
+      <c r="D172" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B173" t="s">
         <v>288</v>
       </c>
-      <c r="C173" s="5">
-        <v>80</v>
+      <c r="C173" s="4">
+        <v>79</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>289</v>
@@ -4543,27 +4534,27 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B174" t="s">
         <v>290</v>
       </c>
-      <c r="C174" s="5">
-        <v>81</v>
-      </c>
-      <c r="D174" t="s">
+      <c r="C174" s="4">
+        <v>80</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B175" t="s">
         <v>292</v>
       </c>
-      <c r="C175" s="5">
-        <v>82</v>
+      <c r="C175" s="4">
+        <v>81</v>
       </c>
       <c r="D175" t="s">
         <v>293</v>
@@ -4571,69 +4562,69 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B176" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B176" t="s">
         <v>294</v>
       </c>
-      <c r="C176" s="5">
-        <v>83</v>
-      </c>
-      <c r="D176" s="1" t="s">
+      <c r="C176" s="4">
+        <v>82</v>
+      </c>
+      <c r="D176" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B177" t="s">
+        <v>136</v>
+      </c>
+      <c r="B177" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="C177" s="5">
-        <v>84</v>
-      </c>
-      <c r="D177" t="s">
+      <c r="C177" s="4">
+        <v>83</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B178" t="s">
         <v>298</v>
       </c>
-      <c r="C178" s="5">
-        <v>85</v>
-      </c>
-      <c r="D178" s="1" t="s">
+      <c r="C178" s="4">
+        <v>84</v>
+      </c>
+      <c r="D178" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B179" t="s">
         <v>300</v>
       </c>
-      <c r="C179" s="5">
-        <v>86</v>
-      </c>
-      <c r="D179" t="s">
+      <c r="C179" s="4">
+        <v>85</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B180" t="s">
         <v>302</v>
       </c>
-      <c r="C180" s="5">
-        <v>87</v>
+      <c r="C180" s="4">
+        <v>86</v>
       </c>
       <c r="D180" t="s">
         <v>303</v>
@@ -4641,13 +4632,13 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B181" t="s">
         <v>304</v>
       </c>
-      <c r="C181" s="5">
-        <v>88</v>
+      <c r="C181" s="4">
+        <v>87</v>
       </c>
       <c r="D181" t="s">
         <v>305</v>
@@ -4655,13 +4646,13 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B182" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B182" t="s">
         <v>306</v>
       </c>
-      <c r="C182" s="5">
-        <v>89</v>
+      <c r="C182" s="4">
+        <v>88</v>
       </c>
       <c r="D182" t="s">
         <v>307</v>
@@ -4669,56 +4660,55 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B183" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B183" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C183" s="5">
-        <v>90</v>
-      </c>
-      <c r="D183" s="1" t="s">
+      <c r="C183" s="4">
+        <v>89</v>
+      </c>
+      <c r="D183" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B184" t="s">
+        <v>136</v>
+      </c>
+      <c r="B184" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C184" s="5">
-        <v>91</v>
-      </c>
-      <c r="D184" t="s">
+      <c r="C184" s="4">
+        <v>90</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="185" s="1" customFormat="1" spans="1:5">
       <c r="A185" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B185" t="s">
         <v>312</v>
       </c>
-      <c r="C185" s="5">
-        <v>92</v>
+      <c r="C185" s="4">
+        <v>91</v>
       </c>
       <c r="D185" t="s">
         <v>313</v>
       </c>
-      <c r="E185"/>
     </row>
     <row r="186" s="1" customFormat="1" spans="1:5">
       <c r="A186" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B186" t="s">
         <v>314</v>
       </c>
-      <c r="C186" s="5">
-        <v>93</v>
+      <c r="C186" s="4">
+        <v>92</v>
       </c>
       <c r="D186" t="s">
         <v>315</v>
@@ -4727,13 +4717,13 @@
     </row>
     <row r="187" s="1" customFormat="1" spans="1:5">
       <c r="A187" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B187" t="s">
         <v>316</v>
       </c>
-      <c r="C187" s="5">
-        <v>94</v>
+      <c r="C187" s="4">
+        <v>93</v>
       </c>
       <c r="D187" t="s">
         <v>317</v>
@@ -4742,13 +4732,13 @@
     </row>
     <row r="188" s="1" customFormat="1" spans="1:5">
       <c r="A188" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B188" t="s">
         <v>318</v>
       </c>
-      <c r="C188" s="5">
-        <v>95</v>
+      <c r="C188" s="4">
+        <v>94</v>
       </c>
       <c r="D188" t="s">
         <v>319</v>
@@ -4757,13 +4747,13 @@
     </row>
     <row r="189" s="1" customFormat="1" spans="1:5">
       <c r="A189" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B189" t="s">
         <v>320</v>
       </c>
-      <c r="C189" s="5">
-        <v>96</v>
+      <c r="C189" s="4">
+        <v>95</v>
       </c>
       <c r="D189" t="s">
         <v>321</v>
@@ -4772,28 +4762,28 @@
     </row>
     <row r="190" s="1" customFormat="1" spans="1:5">
       <c r="A190" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B190" t="s">
         <v>322</v>
       </c>
-      <c r="C190" s="5">
-        <v>97</v>
-      </c>
-      <c r="D190" s="1" t="s">
+      <c r="C190" s="4">
+        <v>96</v>
+      </c>
+      <c r="D190" t="s">
         <v>323</v>
       </c>
       <c r="E190"/>
     </row>
     <row r="191" s="1" customFormat="1" spans="1:5">
       <c r="A191" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B191" t="s">
         <v>324</v>
       </c>
-      <c r="C191" s="5">
-        <v>98</v>
+      <c r="C191" s="4">
+        <v>97</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>325</v>
@@ -4802,13 +4792,13 @@
     </row>
     <row r="192" s="1" customFormat="1" spans="1:5">
       <c r="A192" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B192" t="s">
         <v>326</v>
       </c>
-      <c r="C192" s="5">
-        <v>99</v>
+      <c r="C192" s="4">
+        <v>98</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>327</v>
@@ -4817,13 +4807,13 @@
     </row>
     <row r="193" s="1" customFormat="1" spans="1:5">
       <c r="A193" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B193" t="s">
         <v>328</v>
       </c>
-      <c r="C193" s="5">
-        <v>100</v>
+      <c r="C193" s="4">
+        <v>99</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>329</v>
@@ -4832,13 +4822,13 @@
     </row>
     <row r="194" s="1" customFormat="1" spans="1:5">
       <c r="A194" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B194" t="s">
         <v>330</v>
       </c>
-      <c r="C194" s="5">
-        <v>101</v>
+      <c r="C194" s="4">
+        <v>100</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>331</v>
@@ -4847,13 +4837,13 @@
     </row>
     <row r="195" s="1" customFormat="1" spans="1:5">
       <c r="A195" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B195" t="s">
         <v>332</v>
       </c>
-      <c r="C195" s="5">
-        <v>102</v>
+      <c r="C195" s="4">
+        <v>101</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>333</v>
@@ -4862,13 +4852,13 @@
     </row>
     <row r="196" s="1" customFormat="1" spans="1:5">
       <c r="A196" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B196" t="s">
         <v>334</v>
       </c>
-      <c r="C196" s="5">
-        <v>103</v>
+      <c r="C196" s="4">
+        <v>102</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>335</v>
@@ -4877,13 +4867,13 @@
     </row>
     <row r="197" s="1" customFormat="1" spans="1:5">
       <c r="A197" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B197" t="s">
         <v>336</v>
       </c>
-      <c r="C197" s="5">
-        <v>104</v>
+      <c r="C197" s="4">
+        <v>103</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>337</v>
@@ -4892,13 +4882,13 @@
     </row>
     <row r="198" s="1" customFormat="1" spans="1:5">
       <c r="A198" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B198" t="s">
         <v>338</v>
       </c>
-      <c r="C198" s="5">
-        <v>105</v>
+      <c r="C198" s="4">
+        <v>104</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>339</v>
@@ -4907,13 +4897,13 @@
     </row>
     <row r="199" s="1" customFormat="1" spans="1:5">
       <c r="A199" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B199" t="s">
         <v>340</v>
       </c>
-      <c r="C199" s="5">
-        <v>106</v>
+      <c r="C199" s="4">
+        <v>105</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>341</v>
@@ -4922,13 +4912,13 @@
     </row>
     <row r="200" s="1" customFormat="1" spans="1:5">
       <c r="A200" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B200" t="s">
         <v>342</v>
       </c>
-      <c r="C200" s="5">
-        <v>107</v>
+      <c r="C200" s="4">
+        <v>106</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>343</v>
@@ -4937,13 +4927,13 @@
     </row>
     <row r="201" s="1" customFormat="1" spans="1:5">
       <c r="A201" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B201" t="s">
         <v>344</v>
       </c>
-      <c r="C201" s="5">
-        <v>108</v>
+      <c r="C201" s="4">
+        <v>107</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>345</v>
@@ -4952,43 +4942,43 @@
     </row>
     <row r="202" s="1" customFormat="1" spans="1:5">
       <c r="A202" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B202" t="s">
         <v>346</v>
       </c>
-      <c r="C202" s="5">
-        <v>109</v>
-      </c>
-      <c r="D202" t="s">
+      <c r="C202" s="4">
+        <v>108</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>347</v>
       </c>
       <c r="E202"/>
     </row>
     <row r="203" s="1" customFormat="1" spans="1:5">
       <c r="A203" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B203" t="s">
         <v>348</v>
       </c>
-      <c r="C203" s="5">
-        <v>110</v>
-      </c>
-      <c r="D203" s="1" t="s">
+      <c r="C203" s="4">
+        <v>109</v>
+      </c>
+      <c r="D203" t="s">
         <v>349</v>
       </c>
       <c r="E203"/>
     </row>
     <row r="204" s="1" customFormat="1" spans="1:5">
       <c r="A204" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B204" t="s">
         <v>350</v>
       </c>
-      <c r="C204" s="5">
-        <v>111</v>
+      <c r="C204" s="4">
+        <v>110</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>351</v>
@@ -4997,28 +4987,28 @@
     </row>
     <row r="205" s="1" customFormat="1" spans="1:5">
       <c r="A205" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B205" t="s">
         <v>352</v>
       </c>
-      <c r="C205" s="5">
-        <v>112</v>
-      </c>
-      <c r="D205" t="s">
+      <c r="C205" s="4">
+        <v>111</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>353</v>
       </c>
       <c r="E205"/>
     </row>
     <row r="206" s="1" customFormat="1" spans="1:5">
       <c r="A206" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B206" t="s">
         <v>354</v>
       </c>
-      <c r="C206" s="5">
-        <v>113</v>
+      <c r="C206" s="4">
+        <v>112</v>
       </c>
       <c r="D206" t="s">
         <v>355</v>
@@ -5027,13 +5017,13 @@
     </row>
     <row r="207" s="1" customFormat="1" spans="1:5">
       <c r="A207" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B207" t="s">
         <v>356</v>
       </c>
-      <c r="C207" s="5">
-        <v>114</v>
+      <c r="C207" s="4">
+        <v>113</v>
       </c>
       <c r="D207" t="s">
         <v>357</v>
@@ -5042,13 +5032,13 @@
     </row>
     <row r="208" s="1" customFormat="1" spans="1:5">
       <c r="A208" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B208" t="s">
         <v>358</v>
       </c>
-      <c r="C208" s="5">
-        <v>115</v>
+      <c r="C208" s="4">
+        <v>114</v>
       </c>
       <c r="D208" t="s">
         <v>359</v>
@@ -5057,13 +5047,13 @@
     </row>
     <row r="209" s="1" customFormat="1" spans="1:5">
       <c r="A209" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B209" t="s">
         <v>360</v>
       </c>
-      <c r="C209" s="5">
-        <v>116</v>
+      <c r="C209" s="4">
+        <v>115</v>
       </c>
       <c r="D209" t="s">
         <v>361</v>
@@ -5072,13 +5062,13 @@
     </row>
     <row r="210" s="1" customFormat="1" spans="1:5">
       <c r="A210" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B210" t="s">
         <v>362</v>
       </c>
-      <c r="C210" s="5">
-        <v>117</v>
+      <c r="C210" s="4">
+        <v>116</v>
       </c>
       <c r="D210" t="s">
         <v>363</v>
@@ -5087,13 +5077,13 @@
     </row>
     <row r="211" s="1" customFormat="1" spans="1:5">
       <c r="A211" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B211" t="s">
         <v>364</v>
       </c>
-      <c r="C211" s="5">
-        <v>118</v>
+      <c r="C211" s="4">
+        <v>117</v>
       </c>
       <c r="D211" t="s">
         <v>365</v>
@@ -5102,13 +5092,13 @@
     </row>
     <row r="212" s="1" customFormat="1" spans="1:5">
       <c r="A212" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B212" t="s">
         <v>366</v>
       </c>
-      <c r="C212" s="5">
-        <v>119</v>
+      <c r="C212" s="4">
+        <v>118</v>
       </c>
       <c r="D212" t="s">
         <v>367</v>
@@ -5117,55 +5107,56 @@
     </row>
     <row r="213" s="1" customFormat="1" spans="1:5">
       <c r="A213" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B213" t="s">
         <v>368</v>
       </c>
-      <c r="C213" s="5">
-        <v>120</v>
+      <c r="C213" s="4">
+        <v>119</v>
       </c>
       <c r="D213" t="s">
         <v>369</v>
       </c>
+      <c r="E213"/>
     </row>
     <row r="214" s="1" customFormat="1" spans="1:5">
       <c r="A214" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B214" t="s">
         <v>370</v>
       </c>
-      <c r="C214" s="5">
-        <v>121</v>
-      </c>
-      <c r="D214" s="1" t="s">
+      <c r="C214" s="4">
+        <v>120</v>
+      </c>
+      <c r="D214" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="215" s="1" customFormat="1" spans="1:5">
       <c r="A215" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B215" t="s">
         <v>372</v>
       </c>
-      <c r="C215" s="5">
-        <v>122</v>
-      </c>
-      <c r="D215" t="s">
+      <c r="C215" s="4">
+        <v>121</v>
+      </c>
+      <c r="D215" s="1" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="216" s="1" customFormat="1" spans="1:5">
       <c r="A216" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B216" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B216" t="s">
         <v>374</v>
       </c>
-      <c r="C216" s="5">
-        <v>123</v>
+      <c r="C216" s="4">
+        <v>122</v>
       </c>
       <c r="D216" t="s">
         <v>375</v>
@@ -5173,13 +5164,13 @@
     </row>
     <row r="217" s="1" customFormat="1" spans="1:5">
       <c r="A217" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B217" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B217" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="C217" s="5">
-        <v>124</v>
+      <c r="C217" s="4">
+        <v>123</v>
       </c>
       <c r="D217" t="s">
         <v>377</v>
@@ -5187,13 +5178,13 @@
     </row>
     <row r="218" s="1" customFormat="1" spans="1:5">
       <c r="A218" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B218" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B218" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="C218" s="5">
-        <v>125</v>
+      <c r="C218" s="4">
+        <v>124</v>
       </c>
       <c r="D218" t="s">
         <v>379</v>
@@ -5201,13 +5192,13 @@
     </row>
     <row r="219" s="1" customFormat="1" spans="1:5">
       <c r="A219" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B219" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B219" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="C219" s="5">
-        <v>126</v>
+      <c r="C219" s="4">
+        <v>125</v>
       </c>
       <c r="D219" t="s">
         <v>381</v>
@@ -5215,13 +5206,13 @@
     </row>
     <row r="220" s="1" customFormat="1" spans="1:5">
       <c r="A220" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B220" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B220" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="C220" s="5">
-        <v>127</v>
+      <c r="C220" s="4">
+        <v>126</v>
       </c>
       <c r="D220" t="s">
         <v>383</v>
@@ -5229,13 +5220,13 @@
     </row>
     <row r="221" s="1" customFormat="1" spans="1:5">
       <c r="A221" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B221" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B221" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="C221" s="5">
-        <v>128</v>
+      <c r="C221" s="4">
+        <v>127</v>
       </c>
       <c r="D221" t="s">
         <v>385</v>
@@ -5243,13 +5234,13 @@
     </row>
     <row r="222" s="1" customFormat="1" spans="1:5">
       <c r="A222" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B222" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B222" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="C222" s="5">
-        <v>129</v>
+      <c r="C222" s="4">
+        <v>128</v>
       </c>
       <c r="D222" t="s">
         <v>387</v>
@@ -5257,27 +5248,27 @@
     </row>
     <row r="223" s="1" customFormat="1" spans="1:5">
       <c r="A223" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B223" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B223" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="C223" s="5">
-        <v>130</v>
+      <c r="C223" s="4">
+        <v>129</v>
       </c>
       <c r="D223" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="224" spans="1:5">
-      <c r="A224" t="s">
-        <v>134</v>
-      </c>
-      <c r="B224" t="s">
+      <c r="A224" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B224" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="C224" s="5">
-        <v>131</v>
+      <c r="C224" s="4">
+        <v>130</v>
       </c>
       <c r="D224" t="s">
         <v>391</v>
@@ -5285,13 +5276,13 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B225" t="s">
         <v>392</v>
       </c>
-      <c r="C225" s="5">
-        <v>132</v>
+      <c r="C225" s="4">
+        <v>131</v>
       </c>
       <c r="D225" t="s">
         <v>393</v>
@@ -5299,13 +5290,13 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B226" t="s">
         <v>394</v>
       </c>
-      <c r="C226" s="5">
-        <v>133</v>
+      <c r="C226" s="4">
+        <v>132</v>
       </c>
       <c r="D226" t="s">
         <v>395</v>
@@ -5313,13 +5304,13 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B227" t="s">
         <v>396</v>
       </c>
-      <c r="C227" s="5">
-        <v>134</v>
+      <c r="C227" s="4">
+        <v>133</v>
       </c>
       <c r="D227" t="s">
         <v>397</v>
@@ -5327,13 +5318,13 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B228" t="s">
         <v>398</v>
       </c>
-      <c r="C228" s="5">
-        <v>135</v>
+      <c r="C228" s="4">
+        <v>134</v>
       </c>
       <c r="D228" t="s">
         <v>399</v>
@@ -5341,13 +5332,13 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B229" t="s">
         <v>400</v>
       </c>
-      <c r="C229" s="5">
-        <v>136</v>
+      <c r="C229" s="4">
+        <v>135</v>
       </c>
       <c r="D229" t="s">
         <v>401</v>
@@ -5355,13 +5346,13 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B230" t="s">
         <v>402</v>
       </c>
-      <c r="C230" s="5">
-        <v>137</v>
+      <c r="C230" s="4">
+        <v>136</v>
       </c>
       <c r="D230" t="s">
         <v>403</v>
@@ -5369,13 +5360,13 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B231" t="s">
         <v>404</v>
       </c>
-      <c r="C231" s="5">
-        <v>138</v>
+      <c r="C231" s="4">
+        <v>137</v>
       </c>
       <c r="D231" t="s">
         <v>405</v>
@@ -5383,13 +5374,13 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B232" t="s">
         <v>406</v>
       </c>
-      <c r="C232" s="5">
-        <v>139</v>
+      <c r="C232" s="4">
+        <v>138</v>
       </c>
       <c r="D232" t="s">
         <v>407</v>
@@ -5397,13 +5388,13 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B233" t="s">
         <v>408</v>
       </c>
-      <c r="C233" s="5">
-        <v>140</v>
+      <c r="C233" s="4">
+        <v>139</v>
       </c>
       <c r="D233" t="s">
         <v>409</v>
@@ -5411,13 +5402,13 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B234" t="s">
         <v>410</v>
       </c>
-      <c r="C234" s="5">
-        <v>141</v>
+      <c r="C234" s="4">
+        <v>140</v>
       </c>
       <c r="D234" t="s">
         <v>411</v>
@@ -5425,13 +5416,13 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B235" t="s">
         <v>412</v>
       </c>
-      <c r="C235" s="5">
-        <v>142</v>
+      <c r="C235" s="4">
+        <v>141</v>
       </c>
       <c r="D235" t="s">
         <v>413</v>
@@ -5439,13 +5430,13 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B236" t="s">
         <v>414</v>
       </c>
-      <c r="C236" s="5">
-        <v>143</v>
+      <c r="C236" s="4">
+        <v>142</v>
       </c>
       <c r="D236" t="s">
         <v>415</v>
@@ -5453,13 +5444,13 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B237" t="s">
         <v>416</v>
       </c>
-      <c r="C237" s="5">
-        <v>144</v>
+      <c r="C237" s="4">
+        <v>143</v>
       </c>
       <c r="D237" t="s">
         <v>417</v>
@@ -5467,13 +5458,13 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B238" t="s">
         <v>418</v>
       </c>
-      <c r="C238" s="5">
-        <v>145</v>
+      <c r="C238" s="4">
+        <v>144</v>
       </c>
       <c r="D238" t="s">
         <v>419</v>
@@ -5481,13 +5472,13 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B239" t="s">
         <v>420</v>
       </c>
-      <c r="C239" s="5">
-        <v>146</v>
+      <c r="C239" s="4">
+        <v>145</v>
       </c>
       <c r="D239" t="s">
         <v>421</v>
@@ -5495,27 +5486,27 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>134</v>
-      </c>
-      <c r="B240" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B240" t="s">
         <v>422</v>
       </c>
-      <c r="C240" s="5">
-        <v>147</v>
-      </c>
-      <c r="D240" s="1" t="s">
+      <c r="C240" s="4">
+        <v>146</v>
+      </c>
+      <c r="D240" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>134</v>
-      </c>
-      <c r="B241" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B241" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="C241" s="5">
-        <v>148</v>
+      <c r="C241" s="4">
+        <v>147</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>425</v>
@@ -5523,27 +5514,27 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>134</v>
-      </c>
-      <c r="B242" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B242" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="C242" s="5">
-        <v>149</v>
-      </c>
-      <c r="D242" t="s">
+      <c r="C242" s="4">
+        <v>148</v>
+      </c>
+      <c r="D242" s="1" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>134</v>
-      </c>
-      <c r="B243" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B243" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="C243" s="5">
-        <v>150</v>
+      <c r="C243" s="4">
+        <v>149</v>
       </c>
       <c r="D243" t="s">
         <v>429</v>
@@ -5551,13 +5542,13 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C244" s="5">
-        <v>151</v>
+      <c r="C244" s="4">
+        <v>150</v>
       </c>
       <c r="D244" t="s">
         <v>431</v>
@@ -5565,35 +5556,45 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>134</v>
-      </c>
-      <c r="B245" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C245" s="5">
+      <c r="C245" s="4">
+        <v>151</v>
+      </c>
+      <c r="D245" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="246" s="1" customFormat="1" spans="1:4">
+      <c r="A246" t="s">
+        <v>136</v>
+      </c>
+      <c r="B246" t="s">
+        <v>434</v>
+      </c>
+      <c r="C246" s="4">
         <v>152</v>
       </c>
-      <c r="D245" s="6" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="246" s="2" customFormat="1" spans="1:4">
-      <c r="A246" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B246" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="C246" s="5">
+      <c r="D246" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" t="s">
+        <v>136</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C247" s="4">
         <v>153</v>
       </c>
-      <c r="D246" s="6" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4">
-      <c r="B247"/>
-      <c r="D247"/>
+      <c r="D247" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="248" spans="1:4">
       <c r="B248"/>
@@ -5604,43 +5605,43 @@
       <c r="D249"/>
     </row>
     <row r="250" spans="1:4">
-      <c r="A250" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B250" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="C250" s="5">
-        <v>1111</v>
-      </c>
+      <c r="B250"/>
       <c r="D250"/>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B251" t="s">
-        <v>437</v>
-      </c>
-      <c r="C251" s="5">
-        <v>1112</v>
+        <v>136</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="C251" s="4">
+        <v>1111</v>
       </c>
       <c r="D251"/>
     </row>
     <row r="252" spans="1:4">
       <c r="A252" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B252" t="s">
-        <v>438</v>
-      </c>
-      <c r="C252" s="5">
+        <v>439</v>
+      </c>
+      <c r="C252" s="4">
+        <v>1112</v>
+      </c>
+      <c r="D252"/>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B253" t="s">
+        <v>440</v>
+      </c>
+      <c r="C253" s="4">
         <v>1113</v>
       </c>
-      <c r="D252"/>
-    </row>
-    <row r="253" spans="1:4">
-      <c r="B253"/>
       <c r="D253"/>
     </row>
     <row r="254" spans="1:4">
@@ -5655,85 +5656,75 @@
       <c r="B256"/>
       <c r="D256"/>
     </row>
-    <row r="257" spans="1:4">
+    <row r="257" spans="2:4">
       <c r="B257"/>
       <c r="D257"/>
     </row>
-    <row r="258" spans="1:4">
+    <row r="258" spans="2:4">
       <c r="B258"/>
       <c r="D258"/>
     </row>
-    <row r="259" spans="1:4">
+    <row r="259" spans="2:4">
       <c r="B259"/>
       <c r="D259"/>
     </row>
-    <row r="260" spans="1:4">
+    <row r="260" spans="2:4">
       <c r="B260"/>
       <c r="D260"/>
     </row>
-    <row r="261" spans="1:4">
+    <row r="261" spans="2:4">
       <c r="B261"/>
       <c r="D261"/>
     </row>
-    <row r="262" spans="1:4">
+    <row r="262" spans="2:4">
       <c r="B262"/>
       <c r="D262"/>
     </row>
-    <row r="263" spans="1:4">
+    <row r="263" spans="2:4">
       <c r="B263"/>
       <c r="D263"/>
     </row>
-    <row r="264" spans="1:4">
+    <row r="264" spans="2:4">
       <c r="B264"/>
       <c r="D264"/>
     </row>
-    <row r="265" spans="1:4">
+    <row r="265" spans="2:4">
       <c r="B265"/>
       <c r="D265"/>
     </row>
-    <row r="266" spans="1:4">
+    <row r="266" spans="2:4">
       <c r="B266"/>
       <c r="D266"/>
     </row>
-    <row r="267" spans="1:4">
+    <row r="267" spans="2:4">
       <c r="B267"/>
       <c r="D267"/>
     </row>
-    <row r="268" spans="1:4">
+    <row r="268" spans="2:4">
       <c r="B268"/>
       <c r="D268"/>
     </row>
-    <row r="269" spans="1:4">
+    <row r="269" spans="2:4">
       <c r="B269"/>
       <c r="D269"/>
     </row>
-    <row r="270" spans="1:4">
+    <row r="270" spans="2:4">
       <c r="B270"/>
       <c r="D270"/>
     </row>
-    <row r="272" spans="1:4">
-      <c r="A272" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="B272" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="C272" s="5">
-        <v>1</v>
-      </c>
-      <c r="D272" s="1" t="s">
-        <v>441</v>
-      </c>
+    <row r="271" spans="2:4">
+      <c r="B271"/>
+      <c r="D271"/>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="B273" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="B273" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C273" s="5">
-        <v>2</v>
+      <c r="C273" s="4">
+        <v>1</v>
       </c>
       <c r="D273" s="1" t="s">
         <v>443</v>
@@ -5741,13 +5732,13 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="B274" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="B274" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="C274" s="5">
-        <v>3</v>
+      <c r="C274" s="4">
+        <v>2</v>
       </c>
       <c r="D274" s="1" t="s">
         <v>445</v>
@@ -5755,41 +5746,41 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="B275" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C275" s="5">
-        <v>4</v>
+        <v>441</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="C275" s="4">
+        <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="276" spans="1:4">
       <c r="A276" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="B276" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="C276" s="5">
-        <v>5</v>
+        <v>441</v>
+      </c>
+      <c r="B276" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C276" s="4">
+        <v>4</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="277" spans="1:4">
       <c r="A277" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="B277" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="C277" s="5">
-        <v>6</v>
+        <v>441</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C277" s="4">
+        <v>5</v>
       </c>
       <c r="D277" s="1" t="s">
         <v>449</v>
@@ -5797,232 +5788,241 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="B278" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="B278" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="C278" s="5">
-        <v>7</v>
+      <c r="C278" s="4">
+        <v>6</v>
       </c>
       <c r="D278" s="1" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="279" spans="1:4">
-      <c r="A279" t="s">
-        <v>439</v>
-      </c>
-      <c r="B279" t="s">
-        <v>15</v>
-      </c>
-      <c r="C279" s="5">
+      <c r="A279" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B279" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C279" s="4">
+        <v>7</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="280" s="2" customFormat="1" spans="1:4">
+      <c r="A280" t="s">
+        <v>441</v>
+      </c>
+      <c r="B280" t="s">
+        <v>17</v>
+      </c>
+      <c r="C280" s="4">
         <v>8</v>
       </c>
-      <c r="D279" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="280" s="3" customFormat="1" spans="1:4">
-      <c r="A280" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="B280" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="C280" s="8">
+      <c r="D280" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C281" s="5">
         <v>9</v>
       </c>
-      <c r="D280" s="4" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4">
-      <c r="A281" t="s">
-        <v>439</v>
-      </c>
-      <c r="B281" t="s">
-        <v>455</v>
-      </c>
-      <c r="C281" s="5">
-        <v>10</v>
-      </c>
-      <c r="D281" t="s">
+      <c r="D281" s="3" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B282" t="s">
         <v>457</v>
       </c>
-      <c r="C282" s="5">
-        <v>11</v>
+      <c r="C282" s="4">
+        <v>10</v>
       </c>
       <c r="D282" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="283" s="3" customFormat="1" spans="1:4">
-      <c r="A283" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="B283" s="4" t="s">
+    <row r="283" s="2" customFormat="1" spans="1:4">
+      <c r="A283" t="s">
+        <v>441</v>
+      </c>
+      <c r="B283" t="s">
+        <v>459</v>
+      </c>
+      <c r="C283" s="4">
         <v>11</v>
       </c>
-      <c r="C283" s="8">
+      <c r="D283" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="284" s="2" customFormat="1" spans="1:4">
+      <c r="A284" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B284" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C284" s="5">
         <v>12</v>
       </c>
-      <c r="D283" s="4" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="284" s="3" customFormat="1" spans="1:4">
-      <c r="A284" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="B284" s="8" t="s">
-        <v>460</v>
-      </c>
-      <c r="C284" s="8">
+      <c r="D284" s="3" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="285" s="2" customFormat="1" spans="1:4">
+      <c r="A285" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B285" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="C285" s="5">
         <v>13</v>
       </c>
-      <c r="D284" s="4" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="285" s="3" customFormat="1" spans="1:4">
-      <c r="A285" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="B285" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="C285" s="8">
+      <c r="D285" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="286" s="2" customFormat="1" spans="1:4">
+      <c r="A286" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="C286" s="5">
         <v>14</v>
       </c>
-      <c r="D285" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="286" s="3" customFormat="1" spans="1:4">
-      <c r="A286" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="B286" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="C286" s="8">
+      <c r="D286" s="3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="287" s="2" customFormat="1" spans="1:4">
+      <c r="A287" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B287" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="C287" s="5">
         <v>15</v>
       </c>
-      <c r="D286" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="287" s="3" customFormat="1" spans="1:4">
-      <c r="A287" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="B287" s="8" t="s">
-        <v>466</v>
-      </c>
-      <c r="C287" s="8">
+      <c r="D287" s="3" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="288" s="2" customFormat="1" spans="1:4">
+      <c r="A288" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="C288" s="5">
         <v>16</v>
       </c>
-      <c r="D287" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="288" s="3" customFormat="1" spans="1:4">
-      <c r="A288" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="B288" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="C288" s="8">
+      <c r="D288" s="3" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="289" s="2" customFormat="1" spans="1:4">
+      <c r="A289" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="C289" s="5">
         <v>17</v>
       </c>
-      <c r="D288" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="289" s="3" customFormat="1" spans="1:4">
-      <c r="A289" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="B289" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="C289" s="8">
+      <c r="D289" s="3" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="290" s="2" customFormat="1" spans="1:4">
+      <c r="A290" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="C290" s="5">
         <v>18</v>
       </c>
-      <c r="D289" s="4" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="290" s="3" customFormat="1" spans="1:4">
-      <c r="A290" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="B290" s="8" t="s">
-        <v>472</v>
-      </c>
-      <c r="C290" s="8">
+      <c r="D290" s="3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="291" s="2" customFormat="1" spans="1:4">
+      <c r="A291" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="C291" s="5">
         <v>19</v>
       </c>
-      <c r="D290" s="4" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="291" s="3" customFormat="1" spans="1:4">
-      <c r="A291" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="B291" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="C291" s="8">
+      <c r="D291" s="3" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="292" s="2" customFormat="1" spans="1:4">
+      <c r="A292" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="C292" s="5">
         <v>20</v>
       </c>
-      <c r="D291" s="4" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="292" s="3" customFormat="1" spans="1:4">
-      <c r="A292" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="B292" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="C292" s="8">
+      <c r="D292" s="3" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="293" s="3" customFormat="1" spans="1:4">
+      <c r="A293" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="C293" s="5">
         <v>21</v>
       </c>
-      <c r="D292" s="4" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="293" s="4" customFormat="1" spans="1:4">
-      <c r="A293" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="B293" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="C293" s="8">
+      <c r="D293" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C294" s="5">
         <v>22</v>
       </c>
-      <c r="D293" s="4" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4">
-      <c r="A294"/>
-      <c r="B294"/>
-      <c r="D294"/>
+      <c r="D294" s="3" t="s">
+        <v>480</v>
+      </c>
     </row>
     <row r="295" spans="1:4">
       <c r="A295"/>
@@ -6030,28 +6030,19 @@
       <c r="D295"/>
     </row>
     <row r="296" spans="1:4">
-      <c r="A296" t="s">
-        <v>479</v>
-      </c>
-      <c r="B296" t="s">
-        <v>480</v>
-      </c>
-      <c r="C296" s="5">
-        <v>1</v>
-      </c>
-      <c r="D296" t="s">
-        <v>481</v>
-      </c>
+      <c r="A296"/>
+      <c r="B296"/>
+      <c r="D296"/>
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B297" t="s">
         <v>482</v>
       </c>
-      <c r="C297" s="5">
-        <v>2</v>
+      <c r="C297" s="4">
+        <v>1</v>
       </c>
       <c r="D297" t="s">
         <v>483</v>
@@ -6059,13 +6050,13 @@
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B298" t="s">
         <v>484</v>
       </c>
-      <c r="C298" s="5">
-        <v>3</v>
+      <c r="C298" s="4">
+        <v>2</v>
       </c>
       <c r="D298" t="s">
         <v>485</v>
@@ -6073,27 +6064,27 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
+        <v>481</v>
+      </c>
+      <c r="B299" t="s">
         <v>486</v>
       </c>
-      <c r="B299" t="s">
+      <c r="C299" s="4">
+        <v>3</v>
+      </c>
+      <c r="D299" t="s">
         <v>487</v>
-      </c>
-      <c r="C299" s="5">
-        <v>1</v>
-      </c>
-      <c r="D299" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B300" t="s">
         <v>489</v>
       </c>
-      <c r="C300" s="5">
-        <v>2</v>
+      <c r="C300" s="4">
+        <v>1</v>
       </c>
       <c r="D300" t="s">
         <v>490</v>
@@ -6101,16 +6092,30 @@
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B301" t="s">
         <v>491</v>
       </c>
-      <c r="C301" s="5">
-        <v>3</v>
+      <c r="C301" s="4">
+        <v>2</v>
       </c>
       <c r="D301" t="s">
         <v>492</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" t="s">
+        <v>488</v>
+      </c>
+      <c r="B302" t="s">
+        <v>493</v>
+      </c>
+      <c r="C302" s="4">
+        <v>3</v>
+      </c>
+      <c r="D302" t="s">
+        <v>494</v>
       </c>
     </row>
   </sheetData>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -1058,7 +1058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E304"/>
+  <dimension ref="A1:E315"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.7416666666667" customWidth="1" style="1" min="1" max="1"/>
@@ -2394,249 +2394,230 @@
         </is>
       </c>
     </row>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
+    <row r="89">
+      <c r="A89" s="0" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B89" s="0" t="inlineStr">
+        <is>
+          <t>PeekSwap</t>
+        </is>
+      </c>
+      <c r="C89" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="D89" s="0" t="inlineStr">
+        <is>
+          <t>BOSS开牌前偷看玩家手牌,弃掉自己最差的牌重抽</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B90" s="0" t="inlineStr">
+        <is>
+          <t>VengefulFlame</t>
+        </is>
+      </c>
+      <c r="C90" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="D90" s="0" t="inlineStr">
+        <is>
+          <t>玩家被点燃,每回合开始受伤,赢下比牌可压制一回合</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B91" s="0" t="inlineStr">
+        <is>
+          <t>FrostArmor</t>
+        </is>
+      </c>
+      <c r="C91" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="D91" s="0" t="inlineStr">
+        <is>
+          <t>BOSS每回合叠加冰甲吸收伤害,大伤害一击击碎</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>BloodDebt</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>53</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>BOSS每损失10%生命,造成的伤害提高,有上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B93" s="0" t="inlineStr">
+        <is>
+          <t>StoneDormancy</t>
+        </is>
+      </c>
+      <c r="C93" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="D93" s="0" t="inlineStr">
+        <is>
+          <t>BOSS开场沉睡,苏醒后攻击强化且首击加倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B94" s="0" t="inlineStr">
+        <is>
+          <t>WinLust</t>
+        </is>
+      </c>
+      <c r="C94" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="D94" s="0" t="inlineStr">
+        <is>
+          <t>BOSS赢比牌加攻,输比牌变脆</t>
+        </is>
+      </c>
+    </row>
     <row r="95">
-      <c r="A95" s="1" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>TwoCardAttack</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>数字牌2提供额外攻击力</t>
+      <c r="A95" s="0" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B95" s="0" t="inlineStr">
+        <is>
+          <t>SoulHarvest</t>
+        </is>
+      </c>
+      <c r="C95" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="D95" s="0" t="inlineStr">
+        <is>
+          <t>每回合收割玩家生命上限</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>ThreeCardAttack</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>数字牌3提供额外攻击力</t>
+      <c r="A96" s="0" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B96" s="0" t="inlineStr">
+        <is>
+          <t>ChargeSmash</t>
+        </is>
+      </c>
+      <c r="C96" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="D96" s="0" t="inlineStr">
+        <is>
+          <t>BOSS周期蓄力,赢牌则重击,输牌则被打断眩晕</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>FourCardAttack</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D97" s="1" t="inlineStr">
-        <is>
-          <t>数字牌4提供额外攻击力</t>
+      <c r="A97" s="0" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B97" s="0" t="inlineStr">
+        <is>
+          <t>MirrorHand</t>
+        </is>
+      </c>
+      <c r="C97" s="0" t="n">
+        <v>58</v>
+      </c>
+      <c r="D97" s="0" t="inlineStr">
+        <is>
+          <t>BOSS比牌顺位复制玩家上回合牌型,惩罚重复套路</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>FiveCardAttack</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D98" s="1" t="inlineStr">
-        <is>
-          <t>数字牌5提供额外攻击力</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="1" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>SixCardAttack</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>数字牌6提供额外攻击力</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="1" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>SevenCardAttack</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>数字牌7提供额外攻击力</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="1" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>EightCardAttack</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>数字牌8提供额外攻击力</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="1" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>NineCardAttack</t>
-        </is>
-      </c>
-      <c r="C102" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>数字牌9提供额外攻击力</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="1" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>TenCardAttack</t>
-        </is>
-      </c>
-      <c r="C103" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>数字牌10提供额外攻击力</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="1" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>ACardAttack</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>A牌提供额外攻击力</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="1" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>HeadCardAttack</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>人头牌提供额外攻击力</t>
-        </is>
-      </c>
-    </row>
+      <c r="A98" s="0" t="inlineStr">
+        <is>
+          <t>BossEntryType</t>
+        </is>
+      </c>
+      <c r="B98" s="0" t="inlineStr">
+        <is>
+          <t>CanopyAura</t>
+        </is>
+      </c>
+      <c r="C98" s="0" t="n">
+        <v>59</v>
+      </c>
+      <c r="D98" s="0" t="inlineStr">
+        <is>
+          <t>BOSS存活时,其他敌人受到伤害降低且造成伤害提高</t>
+        </is>
+      </c>
+    </row>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>HeroHpMax</t>
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t>TwoCardAttack</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>英雄的血量上限</t>
+          <t>数字牌2提供额外攻击力</t>
         </is>
       </c>
     </row>
@@ -2646,17 +2627,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>HeroTakeDamage</t>
+      <c r="B107" s="1" t="inlineStr">
+        <is>
+          <t>ThreeCardAttack</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>英雄承受的伤害</t>
+          <t>数字牌3提供额外攻击力</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2647,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>HeroAttack</t>
+      <c r="B108" s="1" t="inlineStr">
+        <is>
+          <t>FourCardAttack</t>
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>英雄的基础攻击力</t>
+          <t>数字牌4提供额外攻击力</t>
         </is>
       </c>
     </row>
@@ -2688,15 +2669,15 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>HeroCritical</t>
+          <t>FiveCardAttack</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>英雄的暴击率</t>
+          <t>数字牌5提供额外攻击力</t>
         </is>
       </c>
     </row>
@@ -2706,17 +2687,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>AttackBossDamage</t>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>SixCardAttack</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>对BOSS的伤害</t>
+          <t>数字牌6提供额外攻击力</t>
         </is>
       </c>
     </row>
@@ -2728,15 +2709,15 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>FirstShowCardEveryLevel</t>
+          <t>SevenCardAttack</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>每关首次亮牌后结算倍率</t>
+          <t>数字牌7提供额外攻击力</t>
         </is>
       </c>
     </row>
@@ -2746,17 +2727,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>KillingProbabilityTen</t>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>EightCardAttack</t>
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>斩杀10%血量以下非BOSS敌人的概率</t>
+          <t>数字牌8提供额外攻击力</t>
         </is>
       </c>
     </row>
@@ -2768,15 +2749,15 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>KillingBringsBackBlood</t>
+          <t>NineCardAttack</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>血量低于20%以下时,杀人回血</t>
+          <t>数字牌9提供额外攻击力</t>
         </is>
       </c>
     </row>
@@ -2786,17 +2767,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>ManyMonsterDamage</t>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>TenCardAttack</t>
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t>敌人数量大于1时,造成的伤害</t>
+          <t>数字牌10提供额外攻击力</t>
         </is>
       </c>
     </row>
@@ -2806,17 +2787,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>UsingRubbingCards</t>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>ACardAttack</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>亮牌前使用过搓牌,结算时的攻击力</t>
+          <t>A牌提供额外攻击力</t>
         </is>
       </c>
     </row>
@@ -2828,15 +2809,15 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>HeroHpReplyEveryLevelEnding</t>
+          <t>HeadCardAttack</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>每关结束后,回复的血量百分比</t>
+          <t>人头牌提供额外攻击力</t>
         </is>
       </c>
     </row>
@@ -2848,15 +2829,15 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>ProOfObtainingFundsEverySettlement</t>
+          <t>HeroHpMax</t>
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>结算时,获得额外资金的概率</t>
+          <t>英雄的血量上限</t>
         </is>
       </c>
     </row>
@@ -2866,17 +2847,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>OneMonsterDamage</t>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>HeroTakeDamage</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>只剩1名敌人时,造成的伤害</t>
+          <t>英雄承受的伤害</t>
         </is>
       </c>
     </row>
@@ -2886,17 +2867,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>HpUnderDamage</t>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>HeroAttack</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>血量低于20%时,造成的伤害</t>
+          <t>英雄的基础攻击力</t>
         </is>
       </c>
     </row>
@@ -2906,17 +2887,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>KillingProOfObtainingFunds</t>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>HeroCritical</t>
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>击杀敌人时,获得额外资金的概率</t>
+          <t>英雄的暴击率</t>
         </is>
       </c>
     </row>
@@ -2928,15 +2909,15 @@
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>InitialFunds</t>
+          <t>AttackBossDamage</t>
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>初始拥有资金</t>
+          <t>对BOSS的伤害</t>
         </is>
       </c>
     </row>
@@ -2946,17 +2927,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>ProOfExtraAttack</t>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>FirstShowCardEveryLevel</t>
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>额外造成1次10%伤害的概率</t>
+          <t>每关首次亮牌后结算倍率</t>
         </is>
       </c>
     </row>
@@ -2968,15 +2949,15 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>CardMagnification</t>
+          <t>KillingProbabilityTen</t>
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>结算时获得额外倍率</t>
+          <t>斩杀10%血量以下非BOSS敌人的概率</t>
         </is>
       </c>
     </row>
@@ -2986,17 +2967,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B124" s="0" t="inlineStr">
-        <is>
-          <t>SquarePlate</t>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>KillingBringsBackBlood</t>
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>每张方片牌在结算时提供倍率</t>
+          <t>血量低于20%以下时,杀人回血</t>
         </is>
       </c>
     </row>
@@ -3006,17 +2987,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B125" s="0" t="inlineStr">
-        <is>
-          <t>Spades</t>
+      <c r="B125" s="1" t="inlineStr">
+        <is>
+          <t>ManyMonsterDamage</t>
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>每张黑桃牌在结算时提供倍率</t>
+          <t>敌人数量大于1时,造成的伤害</t>
         </is>
       </c>
     </row>
@@ -3026,17 +3007,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B126" s="0" t="inlineStr">
-        <is>
-          <t>RedHeart</t>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t>UsingRubbingCards</t>
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>每张红心牌在结算时提供倍率</t>
+          <t>亮牌前使用过搓牌,结算时的攻击力</t>
         </is>
       </c>
     </row>
@@ -3046,17 +3027,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B127" s="0" t="inlineStr">
-        <is>
-          <t>PlumBlossom</t>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>HeroHpReplyEveryLevelEnding</t>
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>每张梅花牌在结算时提供倍率</t>
+          <t>每关结束后,回复的血量百分比</t>
         </is>
       </c>
     </row>
@@ -3066,17 +3047,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>Couplet</t>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>ProOfObtainingFundsEverySettlement</t>
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="D128" s="0" t="inlineStr">
-        <is>
-          <t>对子倍率提高</t>
+        <v>23</v>
+      </c>
+      <c r="D128" s="1" t="inlineStr">
+        <is>
+          <t>结算时,获得额外资金的概率</t>
         </is>
       </c>
     </row>
@@ -3086,17 +3067,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B129" s="0" t="inlineStr">
-        <is>
-          <t>Straight</t>
+      <c r="B129" s="1" t="inlineStr">
+        <is>
+          <t>OneMonsterDamage</t>
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="D129" s="0" t="inlineStr">
-        <is>
-          <t>顺子倍率提高</t>
+        <v>24</v>
+      </c>
+      <c r="D129" s="1" t="inlineStr">
+        <is>
+          <t>只剩1名敌人时,造成的伤害</t>
         </is>
       </c>
     </row>
@@ -3106,17 +3087,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B130" s="0" t="inlineStr">
-        <is>
-          <t>Flush</t>
+      <c r="B130" s="1" t="inlineStr">
+        <is>
+          <t>HpUnderDamage</t>
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="D130" s="0" t="inlineStr">
-        <is>
-          <t>同花倍率提高</t>
+        <v>25</v>
+      </c>
+      <c r="D130" s="1" t="inlineStr">
+        <is>
+          <t>血量低于20%时,造成的伤害</t>
         </is>
       </c>
     </row>
@@ -3126,17 +3107,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B131" s="0" t="inlineStr">
-        <is>
-          <t>StraightFlush</t>
+      <c r="B131" s="1" t="inlineStr">
+        <is>
+          <t>KillingProOfObtainingFunds</t>
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="D131" s="0" t="inlineStr">
-        <is>
-          <t>同花顺倍率提高</t>
+        <v>26</v>
+      </c>
+      <c r="D131" s="1" t="inlineStr">
+        <is>
+          <t>击杀敌人时,获得额外资金的概率</t>
         </is>
       </c>
     </row>
@@ -3146,17 +3127,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B132" s="4" t="inlineStr">
-        <is>
-          <t>Leopard</t>
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t>InitialFunds</t>
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="D132" s="0" t="inlineStr">
-        <is>
-          <t>豹子倍率提高</t>
+        <v>27</v>
+      </c>
+      <c r="D132" s="1" t="inlineStr">
+        <is>
+          <t>初始拥有资金</t>
         </is>
       </c>
     </row>
@@ -3166,17 +3147,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B133" s="0" t="inlineStr">
-        <is>
-          <t>SquarePlateAttack</t>
+      <c r="B133" s="1" t="inlineStr">
+        <is>
+          <t>ProOfExtraAttack</t>
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="D133" s="0" t="inlineStr">
-        <is>
-          <t>每张方片牌在结算时提供攻击力</t>
+        <v>28</v>
+      </c>
+      <c r="D133" s="1" t="inlineStr">
+        <is>
+          <t>额外造成1次10%伤害的概率</t>
         </is>
       </c>
     </row>
@@ -3186,17 +3167,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B134" s="0" t="inlineStr">
-        <is>
-          <t>SpadesAttack</t>
+      <c r="B134" s="1" t="inlineStr">
+        <is>
+          <t>CardMagnification</t>
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="D134" s="0" t="inlineStr">
-        <is>
-          <t>每张黑桃牌在结算时提供攻击力</t>
+        <v>29</v>
+      </c>
+      <c r="D134" s="1" t="inlineStr">
+        <is>
+          <t>结算时获得额外倍率</t>
         </is>
       </c>
     </row>
@@ -3208,15 +3189,15 @@
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>RedHeartAttack</t>
+          <t>SquarePlate</t>
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="D135" s="0" t="inlineStr">
-        <is>
-          <t>每张红心牌在结算时提供攻击力</t>
+        <v>30</v>
+      </c>
+      <c r="D135" s="1" t="inlineStr">
+        <is>
+          <t>每张方片牌在结算时提供倍率</t>
         </is>
       </c>
     </row>
@@ -3228,15 +3209,15 @@
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>PlumBlossomAttack</t>
+          <t>Spades</t>
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="D136" s="0" t="inlineStr">
-        <is>
-          <t>每张梅花牌在结算时提供攻击力</t>
+        <v>31</v>
+      </c>
+      <c r="D136" s="1" t="inlineStr">
+        <is>
+          <t>每张黑桃牌在结算时提供倍率</t>
         </is>
       </c>
     </row>
@@ -3246,17 +3227,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B137" s="1" t="inlineStr">
-        <is>
-          <t>CoupletAttack</t>
+      <c r="B137" s="0" t="inlineStr">
+        <is>
+          <t>RedHeart</t>
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="D137" s="0" t="inlineStr">
-        <is>
-          <t>对子牌型在结算时提供攻击力</t>
+        <v>32</v>
+      </c>
+      <c r="D137" s="1" t="inlineStr">
+        <is>
+          <t>每张红心牌在结算时提供倍率</t>
         </is>
       </c>
     </row>
@@ -3268,15 +3249,15 @@
       </c>
       <c r="B138" s="0" t="inlineStr">
         <is>
-          <t>StraightAttack</t>
+          <t>PlumBlossom</t>
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="D138" s="0" t="inlineStr">
-        <is>
-          <t>顺子牌型在结算时提供攻击力</t>
+        <v>33</v>
+      </c>
+      <c r="D138" s="1" t="inlineStr">
+        <is>
+          <t>每张梅花牌在结算时提供倍率</t>
         </is>
       </c>
     </row>
@@ -3286,17 +3267,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B139" s="0" t="inlineStr">
-        <is>
-          <t>FlushAttack</t>
+      <c r="B139" s="1" t="inlineStr">
+        <is>
+          <t>Couplet</t>
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D139" s="0" t="inlineStr">
         <is>
-          <t>同花牌型在结算时提供攻击力</t>
+          <t>对子倍率提高</t>
         </is>
       </c>
     </row>
@@ -3308,15 +3289,15 @@
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>StraightFlushAttack</t>
+          <t>Straight</t>
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D140" s="0" t="inlineStr">
         <is>
-          <t>同花顺牌型在结算时提供攻击力</t>
+          <t>顺子倍率提高</t>
         </is>
       </c>
     </row>
@@ -3326,17 +3307,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>LeopardAttack</t>
+      <c r="B141" s="0" t="inlineStr">
+        <is>
+          <t>Flush</t>
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D141" s="0" t="inlineStr">
         <is>
-          <t>豹子牌型在结算时提供攻击力</t>
+          <t>同花倍率提高</t>
         </is>
       </c>
     </row>
@@ -3346,17 +3327,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B142" s="4" t="inlineStr">
-        <is>
-          <t>HeroHpReplyEveryRoundEnding</t>
+      <c r="B142" s="0" t="inlineStr">
+        <is>
+          <t>StraightFlush</t>
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D142" s="0" t="inlineStr">
         <is>
-          <t>回合结束回复当前生命值</t>
+          <t>同花顺倍率提高</t>
         </is>
       </c>
     </row>
@@ -3366,17 +3347,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B143" s="0" t="inlineStr">
-        <is>
-          <t>Liability</t>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D143" s="0" t="inlineStr">
         <is>
-          <t>资金可以为负数</t>
+          <t>豹子倍率提高</t>
         </is>
       </c>
     </row>
@@ -3388,15 +3369,15 @@
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>EveryRubbingNum</t>
+          <t>SquarePlateAttack</t>
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D144" s="0" t="inlineStr">
         <is>
-          <t>每剩余1个搓牌次数,提供倍率</t>
+          <t>每张方片牌在结算时提供攻击力</t>
         </is>
       </c>
     </row>
@@ -3406,17 +3387,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B145" s="4" t="inlineStr">
-        <is>
-          <t>ProOfHeadCardFunds</t>
+      <c r="B145" s="0" t="inlineStr">
+        <is>
+          <t>SpadesAttack</t>
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D145" s="0" t="inlineStr">
         <is>
-          <t>人头牌提供1资金的概率</t>
+          <t>每张黑桃牌在结算时提供攻击力</t>
         </is>
       </c>
     </row>
@@ -3428,15 +3409,15 @@
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>RedHeartAttack</t>
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D146" s="0" t="inlineStr">
         <is>
-          <t>每有1张留在手里的每张黑桃/梅花,提供倍率</t>
+          <t>每张红心牌在结算时提供攻击力</t>
         </is>
       </c>
     </row>
@@ -3448,15 +3429,15 @@
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>Cupid</t>
+          <t>PlumBlossomAttack</t>
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D147" s="0" t="inlineStr">
         <is>
-          <t>每有1张留在手里的每张方片/红心,提供倍率</t>
+          <t>每张梅花牌在结算时提供攻击力</t>
         </is>
       </c>
     </row>
@@ -3466,17 +3447,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B148" s="0" t="inlineStr">
-        <is>
-          <t>ConsumeFundsGetAttack</t>
+      <c r="B148" s="1" t="inlineStr">
+        <is>
+          <t>CoupletAttack</t>
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D148" s="0" t="inlineStr">
         <is>
-          <t>每花费10资金,提供英雄攻击力</t>
+          <t>对子牌型在结算时提供攻击力</t>
         </is>
       </c>
     </row>
@@ -3488,15 +3469,15 @@
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>TakeDamageGetFunds</t>
+          <t>StraightAttack</t>
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D149" s="0" t="inlineStr">
         <is>
-          <t>受到伤害,提供资金</t>
+          <t>顺子牌型在结算时提供攻击力</t>
         </is>
       </c>
     </row>
@@ -3506,17 +3487,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B150" s="4" t="inlineStr">
-        <is>
-          <t>BloodSucking</t>
+      <c r="B150" s="0" t="inlineStr">
+        <is>
+          <t>FlushAttack</t>
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D150" s="0" t="inlineStr">
         <is>
-          <t>吸血效果</t>
+          <t>同花牌型在结算时提供攻击力</t>
         </is>
       </c>
     </row>
@@ -3528,15 +3509,15 @@
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>DoubleCardAttack</t>
+          <t>StraightFlushAttack</t>
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D151" s="0" t="inlineStr">
         <is>
-          <t>亮出的牌点数提供的攻击力提高</t>
+          <t>同花顺牌型在结算时提供攻击力</t>
         </is>
       </c>
     </row>
@@ -3546,17 +3527,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B152" s="0" t="inlineStr">
-        <is>
-          <t>TheSwordOfVictory</t>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>LeopardAttack</t>
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D152" s="0" t="inlineStr">
         <is>
-          <t>结算伤害时,将留在手牌上最大牌点数转化为额外攻击力</t>
+          <t>豹子牌型在结算时提供攻击力</t>
         </is>
       </c>
     </row>
@@ -3566,17 +3547,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B153" s="0" t="inlineStr">
-        <is>
-          <t>EveryUseRubbingNum</t>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>HeroHpReplyEveryRoundEnding</t>
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D153" s="0" t="inlineStr">
         <is>
-          <t>每回合内,每搓1次牌,结算时提供倍率</t>
+          <t>回合结束回复当前生命值</t>
         </is>
       </c>
     </row>
@@ -3588,15 +3569,15 @@
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>FreeShopRefresh</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D154" s="0" t="inlineStr">
         <is>
-          <t>免费商店刷新次数</t>
+          <t>资金可以为负数</t>
         </is>
       </c>
     </row>
@@ -3608,15 +3589,15 @@
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>SpecialStraight</t>
+          <t>EveryRubbingNum</t>
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D155" s="0" t="inlineStr">
         <is>
-          <t>顺子牌型可以相隔1点组成</t>
+          <t>每剩余1个搓牌次数,提供倍率</t>
         </is>
       </c>
     </row>
@@ -3626,17 +3607,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B156" s="0" t="inlineStr">
-        <is>
-          <t>SpecialEightCard</t>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>ProOfHeadCardFunds</t>
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D156" s="0" t="inlineStr">
         <is>
-          <t>亮出的每张8在结算时提供+8攻击力</t>
+          <t>人头牌提供1资金的概率</t>
         </is>
       </c>
     </row>
@@ -3648,15 +3629,15 @@
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>EvenNumberCard</t>
+          <t>Camera</t>
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D157" s="0" t="inlineStr">
         <is>
-          <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供倍率</t>
+          <t>每有1张留在手里的每张黑桃/梅花,提供倍率</t>
         </is>
       </c>
     </row>
@@ -3668,15 +3649,15 @@
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>OddNumberCard</t>
+          <t>Cupid</t>
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D158" s="0" t="inlineStr">
         <is>
-          <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供倍率</t>
+          <t>每有1张留在手里的每张方片/红心,提供倍率</t>
         </is>
       </c>
     </row>
@@ -3688,15 +3669,15 @@
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>HeadCard</t>
+          <t>ConsumeFundsGetAttack</t>
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="D159" s="1" t="inlineStr">
-        <is>
-          <t>人头牌提供额外倍率</t>
+        <v>54</v>
+      </c>
+      <c r="D159" s="0" t="inlineStr">
+        <is>
+          <t>每花费10资金,提供英雄攻击力</t>
         </is>
       </c>
     </row>
@@ -3708,15 +3689,15 @@
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>KillAfterSellingPrice</t>
+          <t>TakeDamageGetFunds</t>
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D160" s="0" t="inlineStr">
         <is>
-          <t>击杀敌人,圣物出售价格提高</t>
+          <t>受到伤害,提供资金</t>
         </is>
       </c>
     </row>
@@ -3726,17 +3707,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B161" s="0" t="inlineStr">
-        <is>
-          <t>EveryCardAttackForever</t>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>BloodSucking</t>
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D161" s="0" t="inlineStr">
         <is>
-          <t>亮出的每张牌的点数在结算时会使其提供的攻击力永久提高</t>
+          <t>吸血效果</t>
         </is>
       </c>
     </row>
@@ -3748,15 +3729,15 @@
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>SpecialNineCard</t>
+          <t>DoubleCardAttack</t>
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D162" s="0" t="inlineStr">
         <is>
-          <t>亮出的每张9在结算时提供资金</t>
+          <t>亮出的牌点数提供的攻击力提高</t>
         </is>
       </c>
     </row>
@@ -3768,15 +3749,15 @@
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>SpecialTwoThreeFive</t>
+          <t>TheSwordOfVictory</t>
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D163" s="0" t="inlineStr">
         <is>
-          <t>散排235牌型等同于豹子牌型,并且可以战胜所有牌型</t>
+          <t>结算伤害时,将留在手牌上最大牌点数转化为额外攻击力</t>
         </is>
       </c>
     </row>
@@ -3788,15 +3769,15 @@
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>SpecialFlush</t>
+          <t>EveryUseRubbingNum</t>
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D164" s="0" t="inlineStr">
         <is>
-          <t>红桃和方片视为同一花色,黑桃和梅花视为同一花色</t>
+          <t>每回合内,每搓1次牌,结算时提供倍率</t>
         </is>
       </c>
     </row>
@@ -3806,17 +3787,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B165" s="1" t="inlineStr">
-        <is>
-          <t>RubbingCardsNum</t>
+      <c r="B165" s="0" t="inlineStr">
+        <is>
+          <t>FreeShopRefresh</t>
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="D165" s="1" t="inlineStr">
-        <is>
-          <t>每回合搓牌次数</t>
+        <v>60</v>
+      </c>
+      <c r="D165" s="0" t="inlineStr">
+        <is>
+          <t>免费商店刷新次数</t>
         </is>
       </c>
     </row>
@@ -3826,17 +3807,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B166" s="1" t="inlineStr">
-        <is>
-          <t>NoSkill</t>
+      <c r="B166" s="0" t="inlineStr">
+        <is>
+          <t>SpecialStraight</t>
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="D166" s="1" t="inlineStr">
-        <is>
-          <t>结算时,所有技能都无剩余使用次数时,提供倍率</t>
+        <v>61</v>
+      </c>
+      <c r="D166" s="0" t="inlineStr">
+        <is>
+          <t>顺子牌型可以相隔1点组成</t>
         </is>
       </c>
     </row>
@@ -3848,15 +3829,15 @@
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>EveryRelic</t>
+          <t>SpecialEightCard</t>
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D167" s="0" t="inlineStr">
         <is>
-          <t>每有1个圣物,结算时提供倍率</t>
+          <t>亮出的每张8在结算时提供+8攻击力</t>
         </is>
       </c>
     </row>
@@ -3868,15 +3849,15 @@
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>NoUseRubbingEveryRubbingNum</t>
+          <t>EvenNumberCard</t>
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="D168" s="1" t="inlineStr">
-        <is>
-          <t>结算时,若未使用过搓牌,每个搓牌次数提供+6倍率</t>
+        <v>63</v>
+      </c>
+      <c r="D168" s="0" t="inlineStr">
+        <is>
+          <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供倍率</t>
         </is>
       </c>
     </row>
@@ -3888,15 +3869,15 @@
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>AllCardIsHeadCard</t>
+          <t>OddNumberCard</t>
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D169" s="0" t="inlineStr">
         <is>
-          <t>所有牌均视为人头牌</t>
+          <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供倍率</t>
         </is>
       </c>
     </row>
@@ -3908,15 +3889,15 @@
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>SpecialACard</t>
+          <t>HeadCard</t>
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>A牌在结算时提供倍率</t>
+          <t>人头牌提供额外倍率</t>
         </is>
       </c>
     </row>
@@ -3928,15 +3909,15 @@
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>AccumulatedNumOfCardType</t>
+          <t>KillAfterSellingPrice</t>
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D171" s="0" t="inlineStr">
         <is>
-          <t>亮牌时,将该牌型在本局内亮出过的次数来提供倍率</t>
+          <t>击杀敌人,圣物出售价格提高</t>
         </is>
       </c>
     </row>
@@ -3948,15 +3929,15 @@
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>ProOfUpCardType</t>
+          <t>EveryCardAttackForever</t>
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D172" s="0" t="inlineStr">
         <is>
-          <t>亮牌时,有概率将该牌型提供的倍率永久+1</t>
+          <t>亮出的每张牌的点数在结算时会使其提供的攻击力永久提高</t>
         </is>
       </c>
     </row>
@@ -3968,15 +3949,15 @@
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>RubbingCardRelic</t>
+          <t>SpecialNineCard</t>
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="D173" s="1" t="inlineStr">
-        <is>
-          <t>每使用1次搓牌,结算时该圣物永久提供倍率</t>
+        <v>68</v>
+      </c>
+      <c r="D173" s="0" t="inlineStr">
+        <is>
+          <t>亮出的每张9在结算时提供资金</t>
         </is>
       </c>
     </row>
@@ -3988,15 +3969,15 @@
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>SpecialSevenCardPro</t>
+          <t>SpecialTwoThreeFive</t>
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="D174" s="1" t="inlineStr">
-        <is>
-          <t>幸运七触发概率</t>
+        <v>69</v>
+      </c>
+      <c r="D174" s="0" t="inlineStr">
+        <is>
+          <t>散排235牌型等同于豹子牌型,并且可以战胜所有牌型</t>
         </is>
       </c>
     </row>
@@ -4008,15 +3989,15 @@
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>SpecialSevenCardAttack</t>
+          <t>SpecialFlush</t>
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D175" s="0" t="inlineStr">
         <is>
-          <t>幸运七触发时提供的攻击力</t>
+          <t>红桃和方片视为同一花色,黑桃和梅花视为同一花色</t>
         </is>
       </c>
     </row>
@@ -4026,17 +4007,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B176" s="0" t="inlineStr">
-        <is>
-          <t>SpecialSevenCard</t>
+      <c r="B176" s="1" t="inlineStr">
+        <is>
+          <t>RubbingCardsNum</t>
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>82</v>
-      </c>
-      <c r="D176" s="0" t="inlineStr">
-        <is>
-          <t>幸运七触发时提供的倍率</t>
+        <v>71</v>
+      </c>
+      <c r="D176" s="1" t="inlineStr">
+        <is>
+          <t>每回合搓牌次数</t>
         </is>
       </c>
     </row>
@@ -4046,17 +4027,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B177" s="4" t="inlineStr">
-        <is>
-          <t>HeroTakeDamagePer</t>
+      <c r="B177" s="1" t="inlineStr">
+        <is>
+          <t>NoSkill</t>
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D177" s="1" t="inlineStr">
         <is>
-          <t>英雄承受的伤害百分比</t>
+          <t>结算时,所有技能都无剩余使用次数时,提供倍率</t>
         </is>
       </c>
     </row>
@@ -4068,15 +4049,15 @@
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>EveryRelic</t>
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D178" s="0" t="inlineStr">
         <is>
-          <t>英雄造成的伤害百分比</t>
+          <t>每有1个圣物,结算时提供倍率</t>
         </is>
       </c>
     </row>
@@ -4088,15 +4069,15 @@
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>VersatilePerson</t>
+          <t>NoUseRubbingEveryRubbingNum</t>
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D179" s="1" t="inlineStr">
         <is>
-          <t>攻击时,对其他人造成百分比伤害</t>
+          <t>结算时,若未使用过搓牌,每个搓牌次数提供+6倍率</t>
         </is>
       </c>
     </row>
@@ -4108,15 +4089,15 @@
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>ExtraAttackOneTime</t>
+          <t>AllCardIsHeadCard</t>
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D180" s="0" t="inlineStr">
         <is>
-          <t>额外攻击敌人1次的概率</t>
+          <t>所有牌均视为人头牌</t>
         </is>
       </c>
     </row>
@@ -4128,15 +4109,15 @@
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
-          <t>AoeDamage</t>
+          <t>SpecialACard</t>
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="D181" s="0" t="inlineStr">
-        <is>
-          <t>攻击变成原伤害百分比的群体伤害</t>
+        <v>76</v>
+      </c>
+      <c r="D181" s="1" t="inlineStr">
+        <is>
+          <t>A牌在结算时提供倍率</t>
         </is>
       </c>
     </row>
@@ -4148,15 +4129,15 @@
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
-          <t>EpicLegendRelicProUp</t>
+          <t>AccumulatedNumOfCardType</t>
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D182" s="0" t="inlineStr">
         <is>
-          <t>史诗/传说的圣物概率提高</t>
+          <t>亮牌时,将该牌型在本局内亮出过的次数来提供倍率</t>
         </is>
       </c>
     </row>
@@ -4166,17 +4147,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B183" s="4" t="inlineStr">
-        <is>
-          <t>RelicPricePer</t>
+      <c r="B183" s="0" t="inlineStr">
+        <is>
+          <t>ProOfUpCardType</t>
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D183" s="0" t="inlineStr">
         <is>
-          <t>圣物价格百分比</t>
+          <t>亮牌时,有概率将该牌型提供的倍率永久+1</t>
         </is>
       </c>
     </row>
@@ -4186,17 +4167,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B184" s="4" t="inlineStr">
-        <is>
-          <t>GetGoldAfterLevel</t>
+      <c r="B184" s="0" t="inlineStr">
+        <is>
+          <t>RubbingCardRelic</t>
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D184" s="1" t="inlineStr">
         <is>
-          <t>每关通过后获得的金币数量百分比</t>
+          <t>每使用1次搓牌,结算时该圣物永久提供倍率</t>
         </is>
       </c>
     </row>
@@ -4208,15 +4189,15 @@
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>MissDamagePer</t>
+          <t>SpecialSevenCardPro</t>
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>91</v>
-      </c>
-      <c r="D185" s="0" t="inlineStr">
-        <is>
-          <t>免疫伤害的概率</t>
+        <v>80</v>
+      </c>
+      <c r="D185" s="1" t="inlineStr">
+        <is>
+          <t>幸运七触发概率</t>
         </is>
       </c>
     </row>
@@ -4228,18 +4209,17 @@
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
-          <t>EveryRoundGetGold</t>
+          <t>SpecialSevenCardAttack</t>
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D186" s="0" t="inlineStr">
         <is>
-          <t>每回合开始获得金币</t>
-        </is>
-      </c>
-      <c r="E186" s="0" t="n"/>
+          <t>幸运七触发时提供的攻击力</t>
+        </is>
+      </c>
     </row>
     <row r="187" customFormat="1" s="1">
       <c r="A187" s="1" t="inlineStr">
@@ -4249,18 +4229,17 @@
       </c>
       <c r="B187" s="0" t="inlineStr">
         <is>
-          <t>EveryRoundEndingGetGoldPer</t>
+          <t>SpecialSevenCard</t>
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D187" s="0" t="inlineStr">
         <is>
-          <t>每回合结束概率获得金币</t>
-        </is>
-      </c>
-      <c r="E187" s="0" t="n"/>
+          <t>幸运七触发时提供的倍率</t>
+        </is>
+      </c>
     </row>
     <row r="188" customFormat="1" s="1">
       <c r="A188" s="1" t="inlineStr">
@@ -4268,20 +4247,19 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B188" s="0" t="inlineStr">
-        <is>
-          <t>EveryRoundEndingGetCritical</t>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>HeroTakeDamagePer</t>
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="D188" s="0" t="inlineStr">
-        <is>
-          <t>暴击叠加</t>
-        </is>
-      </c>
-      <c r="E188" s="0" t="n"/>
+        <v>83</v>
+      </c>
+      <c r="D188" s="1" t="inlineStr">
+        <is>
+          <t>英雄承受的伤害百分比</t>
+        </is>
+      </c>
     </row>
     <row r="189" customFormat="1" s="1">
       <c r="A189" s="1" t="inlineStr">
@@ -4291,18 +4269,17 @@
       </c>
       <c r="B189" s="0" t="inlineStr">
         <is>
-          <t>SteppingStone</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D189" s="0" t="inlineStr">
         <is>
-          <t>亮牌大于所有人加攻击力</t>
-        </is>
-      </c>
-      <c r="E189" s="0" t="n"/>
+          <t>英雄造成的伤害百分比</t>
+        </is>
+      </c>
     </row>
     <row r="190" customFormat="1" s="1">
       <c r="A190" s="1" t="inlineStr">
@@ -4312,18 +4289,17 @@
       </c>
       <c r="B190" s="0" t="inlineStr">
         <is>
-          <t>BounceDamage</t>
+          <t>VersatilePerson</t>
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="D190" s="0" t="inlineStr">
-        <is>
-          <t>受到伤害反弹伤害</t>
-        </is>
-      </c>
-      <c r="E190" s="0" t="n"/>
+        <v>85</v>
+      </c>
+      <c r="D190" s="1" t="inlineStr">
+        <is>
+          <t>攻击时,对其他人造成百分比伤害</t>
+        </is>
+      </c>
     </row>
     <row r="191" customFormat="1" s="1">
       <c r="A191" s="1" t="inlineStr">
@@ -4333,18 +4309,17 @@
       </c>
       <c r="B191" s="0" t="inlineStr">
         <is>
-          <t>AllPeacePer</t>
+          <t>ExtraAttackOneTime</t>
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="D191" s="1" t="inlineStr">
-        <is>
-          <t>承伤或伤害降低为0的概率</t>
-        </is>
-      </c>
-      <c r="E191" s="0" t="n"/>
+        <v>86</v>
+      </c>
+      <c r="D191" s="0" t="inlineStr">
+        <is>
+          <t>额外攻击敌人1次的概率</t>
+        </is>
+      </c>
     </row>
     <row r="192" customFormat="1" s="1">
       <c r="A192" s="1" t="inlineStr">
@@ -4354,18 +4329,17 @@
       </c>
       <c r="B192" s="0" t="inlineStr">
         <is>
-          <t>DefeatGetAttack</t>
+          <t>AoeDamage</t>
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>98</v>
-      </c>
-      <c r="D192" s="1" t="inlineStr">
-        <is>
-          <t>牌小获得攻击力</t>
-        </is>
-      </c>
-      <c r="E192" s="0" t="n"/>
+        <v>87</v>
+      </c>
+      <c r="D192" s="0" t="inlineStr">
+        <is>
+          <t>攻击变成原伤害百分比的群体伤害</t>
+        </is>
+      </c>
     </row>
     <row r="193" customFormat="1" s="1">
       <c r="A193" s="1" t="inlineStr">
@@ -4375,18 +4349,17 @@
       </c>
       <c r="B193" s="0" t="inlineStr">
         <is>
-          <t>DefeatGetHpMax</t>
+          <t>EpicLegendRelicProUp</t>
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="D193" s="1" t="inlineStr">
-        <is>
-          <t>牌小获得生命上限</t>
-        </is>
-      </c>
-      <c r="E193" s="0" t="n"/>
+        <v>88</v>
+      </c>
+      <c r="D193" s="0" t="inlineStr">
+        <is>
+          <t>史诗/传说的圣物概率提高</t>
+        </is>
+      </c>
     </row>
     <row r="194" customFormat="1" s="1">
       <c r="A194" s="1" t="inlineStr">
@@ -4394,20 +4367,19 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B194" s="0" t="inlineStr">
-        <is>
-          <t>DefeatAllGetGold</t>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>RelicPricePer</t>
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D194" s="1" t="inlineStr">
-        <is>
-          <t>未造成伤害获得金币</t>
-        </is>
-      </c>
-      <c r="E194" s="0" t="n"/>
+        <v>89</v>
+      </c>
+      <c r="D194" s="0" t="inlineStr">
+        <is>
+          <t>圣物价格百分比</t>
+        </is>
+      </c>
     </row>
     <row r="195" customFormat="1" s="1">
       <c r="A195" s="1" t="inlineStr">
@@ -4415,20 +4387,19 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B195" s="0" t="inlineStr">
-        <is>
-          <t>IronRiceBowl</t>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>GetGoldAfterLevel</t>
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D195" s="1" t="inlineStr">
         <is>
-          <t>亮牌后获得金币</t>
-        </is>
-      </c>
-      <c r="E195" s="0" t="n"/>
+          <t>每关通过后获得的金币数量百分比</t>
+        </is>
+      </c>
     </row>
     <row r="196" customFormat="1" s="1">
       <c r="A196" s="1" t="inlineStr">
@@ -4438,18 +4409,17 @@
       </c>
       <c r="B196" s="0" t="inlineStr">
         <is>
-          <t>EveryRoundGetHpMax</t>
+          <t>MissDamagePer</t>
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="D196" s="1" t="inlineStr">
-        <is>
-          <t>每回合开始获得生命上限</t>
-        </is>
-      </c>
-      <c r="E196" s="0" t="n"/>
+        <v>91</v>
+      </c>
+      <c r="D196" s="0" t="inlineStr">
+        <is>
+          <t>免疫伤害的概率</t>
+        </is>
+      </c>
     </row>
     <row r="197" customFormat="1" s="1">
       <c r="A197" s="1" t="inlineStr">
@@ -4459,15 +4429,15 @@
       </c>
       <c r="B197" s="0" t="inlineStr">
         <is>
-          <t>LuckyFlush</t>
+          <t>EveryRoundGetGold</t>
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="D197" s="1" t="inlineStr">
-        <is>
-          <t>强行视敌人牌为同花</t>
+        <v>92</v>
+      </c>
+      <c r="D197" s="0" t="inlineStr">
+        <is>
+          <t>每回合开始获得金币</t>
         </is>
       </c>
       <c r="E197" s="0" t="n"/>
@@ -4480,15 +4450,15 @@
       </c>
       <c r="B198" s="0" t="inlineStr">
         <is>
-          <t>EveryRoundEndingGetEvade</t>
+          <t>EveryRoundEndingGetGoldPer</t>
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>104</v>
-      </c>
-      <c r="D198" s="1" t="inlineStr">
-        <is>
-          <t>闪避叠加</t>
+        <v>93</v>
+      </c>
+      <c r="D198" s="0" t="inlineStr">
+        <is>
+          <t>每回合结束概率获得金币</t>
         </is>
       </c>
       <c r="E198" s="0" t="n"/>
@@ -4501,15 +4471,15 @@
       </c>
       <c r="B199" s="0" t="inlineStr">
         <is>
-          <t>ThermosCup</t>
+          <t>EveryRoundEndingGetCritical</t>
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="D199" s="1" t="inlineStr">
-        <is>
-          <t>半血回血</t>
+        <v>94</v>
+      </c>
+      <c r="D199" s="0" t="inlineStr">
+        <is>
+          <t>暴击叠加</t>
         </is>
       </c>
       <c r="E199" s="0" t="n"/>
@@ -4522,15 +4492,15 @@
       </c>
       <c r="B200" s="0" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>SteppingStone</t>
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="D200" s="1" t="inlineStr">
-        <is>
-          <t>利息</t>
+        <v>95</v>
+      </c>
+      <c r="D200" s="0" t="inlineStr">
+        <is>
+          <t>亮牌大于所有人加攻击力</t>
         </is>
       </c>
       <c r="E200" s="0" t="n"/>
@@ -4543,15 +4513,15 @@
       </c>
       <c r="B201" s="0" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>BounceDamage</t>
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>107</v>
-      </c>
-      <c r="D201" s="1" t="inlineStr">
-        <is>
-          <t>搓牌次数换金币</t>
+        <v>96</v>
+      </c>
+      <c r="D201" s="0" t="inlineStr">
+        <is>
+          <t>受到伤害反弹伤害</t>
         </is>
       </c>
       <c r="E201" s="0" t="n"/>
@@ -4564,15 +4534,15 @@
       </c>
       <c r="B202" s="0" t="inlineStr">
         <is>
-          <t>DefeatAllGetGoldAndReplyHp</t>
+          <t>AllPeacePer</t>
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D202" s="1" t="inlineStr">
         <is>
-          <t>牌小获得金币和回血</t>
+          <t>承伤或伤害降低为0的概率</t>
         </is>
       </c>
       <c r="E202" s="0" t="n"/>
@@ -4585,15 +4555,15 @@
       </c>
       <c r="B203" s="0" t="inlineStr">
         <is>
-          <t>MissFirstDamage</t>
+          <t>DefeatGetAttack</t>
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>109</v>
-      </c>
-      <c r="D203" s="0" t="inlineStr">
-        <is>
-          <t>免疫第一次承伤</t>
+        <v>98</v>
+      </c>
+      <c r="D203" s="1" t="inlineStr">
+        <is>
+          <t>牌小获得攻击力</t>
         </is>
       </c>
       <c r="E203" s="0" t="n"/>
@@ -4606,15 +4576,15 @@
       </c>
       <c r="B204" s="0" t="inlineStr">
         <is>
-          <t>DefeatGetMagnification</t>
+          <t>DefeatGetHpMax</t>
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D204" s="1" t="inlineStr">
         <is>
-          <t>牌小获得倍率</t>
+          <t>牌小获得生命上限</t>
         </is>
       </c>
       <c r="E204" s="0" t="n"/>
@@ -4627,15 +4597,15 @@
       </c>
       <c r="B205" s="0" t="inlineStr">
         <is>
-          <t>LuckyStraight</t>
+          <t>DefeatAllGetGold</t>
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="D205" s="1" t="inlineStr">
         <is>
-          <t>强行视敌人牌为顺子</t>
+          <t>未造成伤害获得金币</t>
         </is>
       </c>
       <c r="E205" s="0" t="n"/>
@@ -4648,15 +4618,15 @@
       </c>
       <c r="B206" s="0" t="inlineStr">
         <is>
-          <t>ReverseResult</t>
+          <t>IronRiceBowl</t>
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>112</v>
-      </c>
-      <c r="D206" s="0" t="inlineStr">
-        <is>
-          <t>反转结果的概率</t>
+        <v>101</v>
+      </c>
+      <c r="D206" s="1" t="inlineStr">
+        <is>
+          <t>亮牌后获得金币</t>
         </is>
       </c>
       <c r="E206" s="0" t="n"/>
@@ -4669,15 +4639,15 @@
       </c>
       <c r="B207" s="0" t="inlineStr">
         <is>
-          <t>NoKillMonsterGetMagnification</t>
+          <t>EveryRoundGetHpMax</t>
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>113</v>
-      </c>
-      <c r="D207" s="0" t="inlineStr">
-        <is>
-          <t>回合内未进行击杀提高倍率</t>
+        <v>102</v>
+      </c>
+      <c r="D207" s="1" t="inlineStr">
+        <is>
+          <t>每回合开始获得生命上限</t>
         </is>
       </c>
       <c r="E207" s="0" t="n"/>
@@ -4690,15 +4660,15 @@
       </c>
       <c r="B208" s="0" t="inlineStr">
         <is>
-          <t>Revenge</t>
+          <t>LuckyFlush</t>
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>114</v>
-      </c>
-      <c r="D208" s="0" t="inlineStr">
-        <is>
-          <t>对赢过自己的怪物类型提高伤害</t>
+        <v>103</v>
+      </c>
+      <c r="D208" s="1" t="inlineStr">
+        <is>
+          <t>强行视敌人牌为同花</t>
         </is>
       </c>
       <c r="E208" s="0" t="n"/>
@@ -4711,15 +4681,15 @@
       </c>
       <c r="B209" s="0" t="inlineStr">
         <is>
-          <t>NobleBadge</t>
+          <t>EveryRoundEndingGetEvade</t>
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>115</v>
-      </c>
-      <c r="D209" s="0" t="inlineStr">
-        <is>
-          <t>半血以上得金币</t>
+        <v>104</v>
+      </c>
+      <c r="D209" s="1" t="inlineStr">
+        <is>
+          <t>闪避叠加</t>
         </is>
       </c>
       <c r="E209" s="0" t="n"/>
@@ -4732,15 +4702,15 @@
       </c>
       <c r="B210" s="0" t="inlineStr">
         <is>
-          <t>Trap</t>
+          <t>ThermosCup</t>
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>116</v>
-      </c>
-      <c r="D210" s="0" t="inlineStr">
-        <is>
-          <t>赢过自己的怪物类型降低伤害</t>
+        <v>105</v>
+      </c>
+      <c r="D210" s="1" t="inlineStr">
+        <is>
+          <t>半血回血</t>
         </is>
       </c>
       <c r="E210" s="0" t="n"/>
@@ -4753,15 +4723,15 @@
       </c>
       <c r="B211" s="0" t="inlineStr">
         <is>
-          <t>DownGrade</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>117</v>
-      </c>
-      <c r="D211" s="0" t="inlineStr">
-        <is>
-          <t>降级牌型概率</t>
+        <v>106</v>
+      </c>
+      <c r="D211" s="1" t="inlineStr">
+        <is>
+          <t>利息</t>
         </is>
       </c>
       <c r="E211" s="0" t="n"/>
@@ -4774,15 +4744,15 @@
       </c>
       <c r="B212" s="0" t="inlineStr">
         <is>
-          <t>AdmissionTicket</t>
+          <t>Abacus</t>
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="D212" s="0" t="inlineStr">
-        <is>
-          <t>额外攻击的次数</t>
+        <v>107</v>
+      </c>
+      <c r="D212" s="1" t="inlineStr">
+        <is>
+          <t>搓牌次数换金币</t>
         </is>
       </c>
       <c r="E212" s="0" t="n"/>
@@ -4795,15 +4765,15 @@
       </c>
       <c r="B213" s="0" t="inlineStr">
         <is>
-          <t>MonsterDamage</t>
+          <t>DefeatAllGetGoldAndReplyHp</t>
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>119</v>
-      </c>
-      <c r="D213" s="0" t="inlineStr">
-        <is>
-          <t>敌人伤害降低</t>
+        <v>108</v>
+      </c>
+      <c r="D213" s="1" t="inlineStr">
+        <is>
+          <t>牌小获得金币和回血</t>
         </is>
       </c>
       <c r="E213" s="0" t="n"/>
@@ -4816,17 +4786,18 @@
       </c>
       <c r="B214" s="0" t="inlineStr">
         <is>
-          <t>MissGetDamage</t>
+          <t>MissFirstDamage</t>
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D214" s="0" t="inlineStr">
         <is>
-          <t>闪避反击</t>
-        </is>
-      </c>
+          <t>免疫第一次承伤</t>
+        </is>
+      </c>
+      <c r="E214" s="0" t="n"/>
     </row>
     <row r="215" customFormat="1" s="1">
       <c r="A215" s="1" t="inlineStr">
@@ -4836,17 +4807,18 @@
       </c>
       <c r="B215" s="0" t="inlineStr">
         <is>
-          <t>LuckyCouplet</t>
+          <t>DefeatGetMagnification</t>
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D215" s="1" t="inlineStr">
         <is>
-          <t>强行视敌人牌为对子</t>
-        </is>
-      </c>
+          <t>牌小获得倍率</t>
+        </is>
+      </c>
+      <c r="E215" s="0" t="n"/>
     </row>
     <row r="216" customFormat="1" s="1">
       <c r="A216" s="1" t="inlineStr">
@@ -4856,17 +4828,18 @@
       </c>
       <c r="B216" s="0" t="inlineStr">
         <is>
-          <t>DefeatGetDamage</t>
+          <t>LuckyStraight</t>
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>122</v>
-      </c>
-      <c r="D216" s="0" t="inlineStr">
-        <is>
-          <t>每次失败提升伤害</t>
-        </is>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="D216" s="1" t="inlineStr">
+        <is>
+          <t>强行视敌人牌为顺子</t>
+        </is>
+      </c>
+      <c r="E216" s="0" t="n"/>
     </row>
     <row r="217" customFormat="1" s="1">
       <c r="A217" s="1" t="inlineStr">
@@ -4874,19 +4847,20 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B217" s="4" t="inlineStr">
-        <is>
-          <t>AstrawToClutchAt</t>
+      <c r="B217" s="0" t="inlineStr">
+        <is>
+          <t>ReverseResult</t>
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D217" s="0" t="inlineStr">
         <is>
-          <t>免死一次</t>
-        </is>
-      </c>
+          <t>反转结果的概率</t>
+        </is>
+      </c>
+      <c r="E217" s="0" t="n"/>
     </row>
     <row r="218" customFormat="1" s="1">
       <c r="A218" s="1" t="inlineStr">
@@ -4894,19 +4868,20 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B218" s="4" t="inlineStr">
-        <is>
-          <t>OneMonsterGetDamage</t>
+      <c r="B218" s="0" t="inlineStr">
+        <is>
+          <t>NoKillMonsterGetMagnification</t>
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D218" s="0" t="inlineStr">
         <is>
-          <t>孤立无援</t>
-        </is>
-      </c>
+          <t>回合内未进行击杀提高倍率</t>
+        </is>
+      </c>
+      <c r="E218" s="0" t="n"/>
     </row>
     <row r="219" customFormat="1" s="1">
       <c r="A219" s="1" t="inlineStr">
@@ -4914,19 +4889,20 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B219" s="4" t="inlineStr">
-        <is>
-          <t>CardUpGrade</t>
+      <c r="B219" s="0" t="inlineStr">
+        <is>
+          <t>Revenge</t>
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D219" s="0" t="inlineStr">
         <is>
-          <t>牌型升级</t>
-        </is>
-      </c>
+          <t>对赢过自己的怪物类型提高伤害</t>
+        </is>
+      </c>
+      <c r="E219" s="0" t="n"/>
     </row>
     <row r="220" customFormat="1" s="1">
       <c r="A220" s="1" t="inlineStr">
@@ -4934,19 +4910,20 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B220" s="4" t="inlineStr">
-        <is>
-          <t>MonsterHpMax</t>
+      <c r="B220" s="0" t="inlineStr">
+        <is>
+          <t>NobleBadge</t>
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D220" s="0" t="inlineStr">
         <is>
-          <t>敌人血量上限</t>
-        </is>
-      </c>
+          <t>半血以上得金币</t>
+        </is>
+      </c>
+      <c r="E220" s="0" t="n"/>
     </row>
     <row r="221" customFormat="1" s="1">
       <c r="A221" s="1" t="inlineStr">
@@ -4954,19 +4931,20 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B221" s="4" t="inlineStr">
-        <is>
-          <t>CriticalAoe</t>
+      <c r="B221" s="0" t="inlineStr">
+        <is>
+          <t>Trap</t>
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D221" s="0" t="inlineStr">
         <is>
-          <t>暴击触发AOE</t>
-        </is>
-      </c>
+          <t>赢过自己的怪物类型降低伤害</t>
+        </is>
+      </c>
+      <c r="E221" s="0" t="n"/>
     </row>
     <row r="222" customFormat="1" s="1">
       <c r="A222" s="1" t="inlineStr">
@@ -4974,19 +4952,20 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B222" s="4" t="inlineStr">
-        <is>
-          <t>PerspectiveNum</t>
+      <c r="B222" s="0" t="inlineStr">
+        <is>
+          <t>DownGrade</t>
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D222" s="0" t="inlineStr">
         <is>
-          <t>透视次数</t>
-        </is>
-      </c>
+          <t>降级牌型概率</t>
+        </is>
+      </c>
+      <c r="E222" s="0" t="n"/>
     </row>
     <row r="223" customFormat="1" s="1">
       <c r="A223" s="1" t="inlineStr">
@@ -4994,19 +4973,20 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B223" s="4" t="inlineStr">
-        <is>
-          <t>DamageTurnToGold</t>
+      <c r="B223" s="0" t="inlineStr">
+        <is>
+          <t>AdmissionTicket</t>
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D223" s="0" t="inlineStr">
         <is>
-          <t>伤害转为金币</t>
-        </is>
-      </c>
+          <t>额外攻击的次数</t>
+        </is>
+      </c>
+      <c r="E223" s="0" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
@@ -5014,237 +4994,238 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B224" s="4" t="inlineStr">
+      <c r="B224" s="0" t="inlineStr">
+        <is>
+          <t>MonsterDamage</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="D224" s="0" t="inlineStr">
+        <is>
+          <t>敌人伤害降低</t>
+        </is>
+      </c>
+      <c r="E224" s="0" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B225" s="0" t="inlineStr">
+        <is>
+          <t>MissGetDamage</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="D225" s="0" t="inlineStr">
+        <is>
+          <t>闪避反击</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B226" s="0" t="inlineStr">
+        <is>
+          <t>LuckyCouplet</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="n">
+        <v>121</v>
+      </c>
+      <c r="D226" s="1" t="inlineStr">
+        <is>
+          <t>强行视敌人牌为对子</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B227" s="0" t="inlineStr">
+        <is>
+          <t>DefeatGetDamage</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="n">
+        <v>122</v>
+      </c>
+      <c r="D227" s="0" t="inlineStr">
+        <is>
+          <t>每次失败提升伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>AstrawToClutchAt</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="D228" s="0" t="inlineStr">
+        <is>
+          <t>免死一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>OneMonsterGetDamage</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="n">
+        <v>124</v>
+      </c>
+      <c r="D229" s="0" t="inlineStr">
+        <is>
+          <t>孤立无援</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>CardUpGrade</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="n">
+        <v>125</v>
+      </c>
+      <c r="D230" s="0" t="inlineStr">
+        <is>
+          <t>牌型升级</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t>MonsterHpMax</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="n">
+        <v>126</v>
+      </c>
+      <c r="D231" s="0" t="inlineStr">
+        <is>
+          <t>敌人血量上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
+          <t>CriticalAoe</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="D232" s="0" t="inlineStr">
+        <is>
+          <t>暴击触发AOE</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t>PerspectiveNum</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="n">
+        <v>128</v>
+      </c>
+      <c r="D233" s="0" t="inlineStr">
+        <is>
+          <t>透视次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t>DamageTurnToGold</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="D234" s="0" t="inlineStr">
+        <is>
+          <t>伤害转为金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
         <is>
           <t>GapDamage</t>
         </is>
       </c>
-      <c r="C224" s="4" t="n">
+      <c r="C235" s="4" t="n">
         <v>130</v>
       </c>
-      <c r="D224" s="0" t="inlineStr">
+      <c r="D235" s="0" t="inlineStr">
         <is>
           <t>差距胶囊</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="0" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B225" s="0" t="inlineStr">
-        <is>
-          <t>UseDamageMul</t>
-        </is>
-      </c>
-      <c r="C225" s="4" t="n">
-        <v>131</v>
-      </c>
-      <c r="D225" s="0" t="inlineStr">
-        <is>
-          <t>消耗品:本次比牌造成的伤害提高(倍率)</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="0" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B226" s="0" t="inlineStr">
-        <is>
-          <t>UseDamageFixed</t>
-        </is>
-      </c>
-      <c r="C226" s="4" t="n">
-        <v>132</v>
-      </c>
-      <c r="D226" s="0" t="inlineStr">
-        <is>
-          <t>消耗品:本次比牌造成的固定伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="0" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B227" s="0" t="inlineStr">
-        <is>
-          <t>HandTypeMagUp</t>
-        </is>
-      </c>
-      <c r="C227" s="4" t="n">
-        <v>133</v>
-      </c>
-      <c r="D227" s="0" t="inlineStr">
-        <is>
-          <t>消耗品:指定牌型的倍率永久提高(参数:牌型|数值)</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="0" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B228" s="0" t="inlineStr">
-        <is>
-          <t>RandomHandTypeMagUp</t>
-        </is>
-      </c>
-      <c r="C228" s="4" t="n">
-        <v>134</v>
-      </c>
-      <c r="D228" s="0" t="inlineStr">
-        <is>
-          <t>消耗品:随机若干牌型的倍率永久提高(参数:数值|数量)</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="0" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B229" s="0" t="inlineStr">
-        <is>
-          <t>HealHpPercent</t>
-        </is>
-      </c>
-      <c r="C229" s="4" t="n">
-        <v>135</v>
-      </c>
-      <c r="D229" s="0" t="inlineStr">
-        <is>
-          <t>消耗品:立即回复百分比最大生命</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="0" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B230" s="0" t="inlineStr">
-        <is>
-          <t>MaxHpUpAndHeal</t>
-        </is>
-      </c>
-      <c r="C230" s="4" t="n">
-        <v>136</v>
-      </c>
-      <c r="D230" s="0" t="inlineStr">
-        <is>
-          <t>消耗品:永久提高生命上限并立即回复同量生命</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="0" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B231" s="0" t="inlineStr">
-        <is>
-          <t>LossRampDamage</t>
-        </is>
-      </c>
-      <c r="C231" s="4" t="n">
-        <v>137</v>
-      </c>
-      <c r="D231" s="0" t="inlineStr">
-        <is>
-          <t>每输1次比牌提高伤害,有上限</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="0" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B232" s="0" t="inlineStr">
-        <is>
-          <t>WinHeal</t>
-        </is>
-      </c>
-      <c r="C232" s="4" t="n">
-        <v>138</v>
-      </c>
-      <c r="D232" s="0" t="inlineStr">
-        <is>
-          <t>比牌获胜后回复生命</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="0" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B233" s="0" t="inlineStr">
-        <is>
-          <t>NextShopDiscount</t>
-        </is>
-      </c>
-      <c r="C233" s="4" t="n">
-        <v>139</v>
-      </c>
-      <c r="D233" s="0" t="inlineStr">
-        <is>
-          <t>消耗品:下一次商店所有商品折扣</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="0" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B234" s="0" t="inlineStr">
-        <is>
-          <t>RemoveBossEntry</t>
-        </is>
-      </c>
-      <c r="C234" s="4" t="n">
-        <v>140</v>
-      </c>
-      <c r="D234" s="0" t="inlineStr">
-        <is>
-          <t>消耗品:移除本关1条BOSS词缀</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="0" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B235" s="0" t="inlineStr">
-        <is>
-          <t>FirstLeopardGold</t>
-        </is>
-      </c>
-      <c r="C235" s="4" t="n">
-        <v>141</v>
-      </c>
-      <c r="D235" s="0" t="inlineStr">
-        <is>
-          <t>本局首次亮出豹子时获得金币</t>
         </is>
       </c>
     </row>
@@ -5256,15 +5237,15 @@
       </c>
       <c r="B236" s="0" t="inlineStr">
         <is>
-          <t>LevelWinDamageUp</t>
+          <t>UseDamageMul</t>
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D236" s="0" t="inlineStr">
         <is>
-          <t>本关内比牌获胜伤害提高</t>
+          <t>消耗品:本次比牌造成的伤害提高(倍率)</t>
         </is>
       </c>
     </row>
@@ -5276,15 +5257,15 @@
       </c>
       <c r="B237" s="0" t="inlineStr">
         <is>
-          <t>LevelHpMaxUp</t>
+          <t>UseDamageFixed</t>
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D237" s="0" t="inlineStr">
         <is>
-          <t>本关内生命上限提高并立即回复</t>
+          <t>消耗品:本次比牌造成的固定伤害</t>
         </is>
       </c>
     </row>
@@ -5296,15 +5277,15 @@
       </c>
       <c r="B238" s="0" t="inlineStr">
         <is>
-          <t>GoldPerLevelClear</t>
+          <t>HandTypeMagUp</t>
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D238" s="0" t="inlineStr">
         <is>
-          <t>每通过1关获得固定金币</t>
+          <t>消耗品:指定牌型的倍率永久提高(参数:牌型|数值)</t>
         </is>
       </c>
     </row>
@@ -5316,15 +5297,15 @@
       </c>
       <c r="B239" s="0" t="inlineStr">
         <is>
-          <t>UseRoundNullify</t>
+          <t>RandomHandTypeMagUp</t>
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="D239" s="0" t="inlineStr">
         <is>
-          <t>消耗品:本次比牌受到的伤害为0并回复生命(参数:免伤标记|回复%)</t>
+          <t>消耗品:随机若干牌型的倍率永久提高(参数:数值|数量)</t>
         </is>
       </c>
     </row>
@@ -5336,15 +5317,15 @@
       </c>
       <c r="B240" s="0" t="inlineStr">
         <is>
-          <t>GoldDamageScale</t>
+          <t>HealHpPercent</t>
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D240" s="0" t="inlineStr">
         <is>
-          <t>按持有金币提高伤害(参数:每N金|+M%|上限%)</t>
+          <t>消耗品:立即回复百分比最大生命</t>
         </is>
       </c>
     </row>
@@ -5354,17 +5335,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B241" s="4" t="inlineStr">
-        <is>
-          <t>EpicRelicPro</t>
+      <c r="B241" s="0" t="inlineStr">
+        <is>
+          <t>MaxHpUpAndHeal</t>
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>147</v>
-      </c>
-      <c r="D241" s="1" t="inlineStr">
-        <is>
-          <t>商店中出现史诗品质圣物的概率提高</t>
+        <v>136</v>
+      </c>
+      <c r="D241" s="0" t="inlineStr">
+        <is>
+          <t>消耗品:永久提高生命上限并立即回复同量生命</t>
         </is>
       </c>
     </row>
@@ -5374,17 +5355,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B242" s="4" t="inlineStr">
-        <is>
-          <t>LegendRelicPro</t>
+      <c r="B242" s="0" t="inlineStr">
+        <is>
+          <t>LossRampDamage</t>
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>148</v>
-      </c>
-      <c r="D242" s="1" t="inlineStr">
-        <is>
-          <t>商店中出现传说品质圣物的概率提高</t>
+        <v>137</v>
+      </c>
+      <c r="D242" s="0" t="inlineStr">
+        <is>
+          <t>每输1次比牌提高伤害,有上限</t>
         </is>
       </c>
     </row>
@@ -5394,17 +5375,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B243" s="4" t="inlineStr">
-        <is>
-          <t>RelicNumMax</t>
+      <c r="B243" s="0" t="inlineStr">
+        <is>
+          <t>WinHeal</t>
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D243" s="0" t="inlineStr">
         <is>
-          <t>允许携带的圣物容量提高</t>
+          <t>比牌获胜后回复生命</t>
         </is>
       </c>
     </row>
@@ -5414,17 +5395,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B244" s="1" t="inlineStr">
-        <is>
-          <t>ReduceLevel</t>
+      <c r="B244" s="0" t="inlineStr">
+        <is>
+          <t>NextShopDiscount</t>
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D244" s="0" t="inlineStr">
         <is>
-          <t>比牌时,对方的牌型顺位降低</t>
+          <t>消耗品:下一次商店所有商品折扣</t>
         </is>
       </c>
     </row>
@@ -5434,17 +5415,17 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B245" s="1" t="inlineStr">
-        <is>
-          <t>UpLevel</t>
+      <c r="B245" s="0" t="inlineStr">
+        <is>
+          <t>RemoveBossEntry</t>
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="D245" s="0" t="inlineStr">
         <is>
-          <t>比牌时,自己的牌型顺位提高</t>
+          <t>消耗品:移除本关1条BOSS词缀</t>
         </is>
       </c>
     </row>
@@ -5456,15 +5437,15 @@
       </c>
       <c r="B246" s="0" t="inlineStr">
         <is>
-          <t>GiantPotion</t>
+          <t>FirstLeopardGold</t>
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="D246" s="0" t="inlineStr">
         <is>
-          <t>巨人药剂</t>
+          <t>本局首次亮出豹子时获得金币</t>
         </is>
       </c>
     </row>
@@ -5474,131 +5455,239 @@
           <t>MechanismType</t>
         </is>
       </c>
-      <c r="B247" s="4" t="inlineStr">
+      <c r="B247" s="0" t="inlineStr">
+        <is>
+          <t>LevelWinDamageUp</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="D247" s="0" t="inlineStr">
+        <is>
+          <t>本关内比牌获胜伤害提高</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="0" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B248" s="0" t="inlineStr">
+        <is>
+          <t>LevelHpMaxUp</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="n">
+        <v>143</v>
+      </c>
+      <c r="D248" s="0" t="inlineStr">
+        <is>
+          <t>本关内生命上限提高并立即回复</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="0" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B249" s="0" t="inlineStr">
+        <is>
+          <t>GoldPerLevelClear</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="n">
+        <v>144</v>
+      </c>
+      <c r="D249" s="0" t="inlineStr">
+        <is>
+          <t>每通过1关获得固定金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="0" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B250" s="0" t="inlineStr">
+        <is>
+          <t>UseRoundNullify</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="D250" s="0" t="inlineStr">
+        <is>
+          <t>消耗品:本次比牌受到的伤害为0并回复生命(参数:免伤标记|回复%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="0" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B251" s="0" t="inlineStr">
+        <is>
+          <t>GoldDamageScale</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="n">
+        <v>146</v>
+      </c>
+      <c r="D251" s="0" t="inlineStr">
+        <is>
+          <t>按持有金币提高伤害(参数:每N金|+M%|上限%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="0" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>EpicRelicPro</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="n">
+        <v>147</v>
+      </c>
+      <c r="D252" s="1" t="inlineStr">
+        <is>
+          <t>商店中出现史诗品质圣物的概率提高</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="0" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B253" s="4" t="inlineStr">
+        <is>
+          <t>LegendRelicPro</t>
+        </is>
+      </c>
+      <c r="C253" s="4" t="n">
+        <v>148</v>
+      </c>
+      <c r="D253" s="1" t="inlineStr">
+        <is>
+          <t>商店中出现传说品质圣物的概率提高</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="0" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="inlineStr">
+        <is>
+          <t>RelicNumMax</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="n">
+        <v>149</v>
+      </c>
+      <c r="D254" s="0" t="inlineStr">
+        <is>
+          <t>允许携带的圣物容量提高</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="0" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B255" s="1" t="inlineStr">
+        <is>
+          <t>ReduceLevel</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="D255" s="0" t="inlineStr">
+        <is>
+          <t>比牌时,对方的牌型顺位降低</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="0" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B256" s="1" t="inlineStr">
+        <is>
+          <t>UpLevel</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="n">
+        <v>151</v>
+      </c>
+      <c r="D256" s="0" t="inlineStr">
+        <is>
+          <t>比牌时,自己的牌型顺位提高</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="0" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B257" s="0" t="inlineStr">
+        <is>
+          <t>GiantPotion</t>
+        </is>
+      </c>
+      <c r="C257" s="4" t="n">
+        <v>152</v>
+      </c>
+      <c r="D257" s="0" t="inlineStr">
+        <is>
+          <t>巨人药剂</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="0" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="inlineStr">
         <is>
           <t>CardProvideAttack</t>
         </is>
       </c>
-      <c r="C247" s="4" t="n">
+      <c r="C258" s="4" t="n">
         <v>153</v>
       </c>
-      <c r="D247" s="0" t="inlineStr">
+      <c r="D258" s="0" t="inlineStr">
         <is>
           <t>卡牌提供攻击力</t>
         </is>
       </c>
-    </row>
-    <row r="248">
-      <c r="B248" s="0" t="n"/>
-      <c r="D248" s="0" t="n"/>
-    </row>
-    <row r="249">
-      <c r="B249" s="0" t="n"/>
-      <c r="D249" s="0" t="n"/>
-    </row>
-    <row r="250">
-      <c r="B250" s="0" t="n"/>
-      <c r="D250" s="0" t="n"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="1" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B251" s="4" t="inlineStr">
-        <is>
-          <t>MaxHp</t>
-        </is>
-      </c>
-      <c r="C251" s="4" t="n">
-        <v>1111</v>
-      </c>
-      <c r="D251" s="0" t="n"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="1" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B252" s="0" t="inlineStr">
-        <is>
-          <t>EveryRoundHpUp</t>
-        </is>
-      </c>
-      <c r="C252" s="4" t="n">
-        <v>1112</v>
-      </c>
-      <c r="D252" s="0" t="n"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B253" s="0" t="inlineStr">
-        <is>
-          <t>TwoThreeFive</t>
-        </is>
-      </c>
-      <c r="C253" s="4" t="n">
-        <v>1113</v>
-      </c>
-      <c r="D253" s="0" t="n"/>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>KillingGetGold</t>
-        </is>
-      </c>
-      <c r="C254" t="n">
-        <v>1114</v>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>每击杀敌人,英雄额外获得金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>KillingGetAttack</t>
-        </is>
-      </c>
-      <c r="C255" t="n">
-        <v>1115</v>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>每击杀敌人,英雄永久提高攻击力</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="B256" s="0" t="n"/>
-      <c r="D256" s="0" t="n"/>
-    </row>
-    <row r="257">
-      <c r="B257" s="0" t="n"/>
-      <c r="D257" s="0" t="n"/>
-    </row>
-    <row r="258">
-      <c r="B258" s="0" t="n"/>
-      <c r="D258" s="0" t="n"/>
     </row>
     <row r="259">
       <c r="B259" s="0" t="n"/>
@@ -5613,24 +5702,92 @@
       <c r="D261" s="0" t="n"/>
     </row>
     <row r="262">
-      <c r="B262" s="0" t="n"/>
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B262" s="4" t="inlineStr">
+        <is>
+          <t>MaxHp</t>
+        </is>
+      </c>
+      <c r="C262" s="4" t="n">
+        <v>1111</v>
+      </c>
       <c r="D262" s="0" t="n"/>
     </row>
     <row r="263">
-      <c r="B263" s="0" t="n"/>
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B263" s="0" t="inlineStr">
+        <is>
+          <t>EveryRoundHpUp</t>
+        </is>
+      </c>
+      <c r="C263" s="4" t="n">
+        <v>1112</v>
+      </c>
       <c r="D263" s="0" t="n"/>
     </row>
     <row r="264">
-      <c r="B264" s="0" t="n"/>
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B264" s="0" t="inlineStr">
+        <is>
+          <t>TwoThreeFive</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="n">
+        <v>1113</v>
+      </c>
       <c r="D264" s="0" t="n"/>
     </row>
     <row r="265">
-      <c r="B265" s="0" t="n"/>
-      <c r="D265" s="0" t="n"/>
+      <c r="A265" s="0" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B265" s="0" t="inlineStr">
+        <is>
+          <t>KillingGetGold</t>
+        </is>
+      </c>
+      <c r="C265" s="0" t="n">
+        <v>1114</v>
+      </c>
+      <c r="D265" s="0" t="inlineStr">
+        <is>
+          <t>每击杀敌人,英雄额外获得金币</t>
+        </is>
+      </c>
     </row>
     <row r="266">
-      <c r="B266" s="0" t="n"/>
-      <c r="D266" s="0" t="n"/>
+      <c r="A266" s="0" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B266" s="0" t="inlineStr">
+        <is>
+          <t>KillingGetAttack</t>
+        </is>
+      </c>
+      <c r="C266" s="0" t="n">
+        <v>1115</v>
+      </c>
+      <c r="D266" s="0" t="inlineStr">
+        <is>
+          <t>每击杀敌人,英雄永久提高攻击力</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="B267" s="0" t="n"/>
@@ -5660,384 +5817,208 @@
       <c r="B273" s="0" t="n"/>
       <c r="D273" s="0" t="n"/>
     </row>
-    <row r="274"/>
+    <row r="274">
+      <c r="B274" s="0" t="n"/>
+      <c r="D274" s="0" t="n"/>
+    </row>
     <row r="275">
-      <c r="A275" s="1" t="inlineStr">
+      <c r="B275" s="0" t="n"/>
+      <c r="D275" s="0" t="n"/>
+    </row>
+    <row r="276">
+      <c r="B276" s="0" t="n"/>
+      <c r="D276" s="0" t="n"/>
+    </row>
+    <row r="277">
+      <c r="B277" s="0" t="n"/>
+      <c r="D277" s="0" t="n"/>
+    </row>
+    <row r="278">
+      <c r="B278" s="0" t="n"/>
+      <c r="D278" s="0" t="n"/>
+    </row>
+    <row r="279">
+      <c r="B279" s="0" t="n"/>
+      <c r="D279" s="0" t="n"/>
+    </row>
+    <row r="280" customFormat="1" s="2">
+      <c r="B280" s="0" t="n"/>
+      <c r="D280" s="0" t="n"/>
+    </row>
+    <row r="281">
+      <c r="B281" s="0" t="n"/>
+      <c r="D281" s="0" t="n"/>
+    </row>
+    <row r="282">
+      <c r="B282" s="0" t="n"/>
+      <c r="D282" s="0" t="n"/>
+    </row>
+    <row r="283" customFormat="1" s="2">
+      <c r="B283" s="0" t="n"/>
+      <c r="D283" s="0" t="n"/>
+    </row>
+    <row r="284" customFormat="1" s="2">
+      <c r="B284" s="0" t="n"/>
+      <c r="D284" s="0" t="n"/>
+    </row>
+    <row r="285" customFormat="1" s="2"/>
+    <row r="286" customFormat="1" s="2">
+      <c r="A286" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B275" s="1" t="inlineStr">
+      <c r="B286" s="1" t="inlineStr">
         <is>
           <t>KillMonster</t>
         </is>
       </c>
-      <c r="C275" s="4" t="n">
+      <c r="C286" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D275" s="1" t="inlineStr">
+      <c r="D286" s="1" t="inlineStr">
         <is>
           <t>杀敌</t>
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" s="1" t="inlineStr">
+    <row r="287" customFormat="1" s="2">
+      <c r="A287" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B276" s="4" t="inlineStr">
+      <c r="B287" s="4" t="inlineStr">
         <is>
           <t>ShuffleCard</t>
         </is>
       </c>
-      <c r="C276" s="4" t="n">
+      <c r="C287" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D276" s="1" t="inlineStr">
+      <c r="D287" s="1" t="inlineStr">
         <is>
           <t>搓牌</t>
         </is>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" s="1" t="inlineStr">
+    <row r="288" customFormat="1" s="2">
+      <c r="A288" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B277" s="4" t="inlineStr">
+      <c r="B288" s="4" t="inlineStr">
         <is>
           <t>RefreshStore</t>
         </is>
       </c>
-      <c r="C277" s="4" t="n">
+      <c r="C288" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D277" s="1" t="inlineStr">
+      <c r="D288" s="1" t="inlineStr">
         <is>
           <t>刷新商店</t>
         </is>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" s="1" t="inlineStr">
+    <row r="289" customFormat="1" s="2">
+      <c r="A289" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B278" s="4" t="inlineStr">
+      <c r="B289" s="4" t="inlineStr">
         <is>
           <t>Straight</t>
         </is>
       </c>
-      <c r="C278" s="4" t="n">
+      <c r="C289" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D278" s="1" t="inlineStr">
+      <c r="D289" s="1" t="inlineStr">
         <is>
           <t>亮出顺子</t>
         </is>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" s="1" t="inlineStr">
+    <row r="290" customFormat="1" s="2">
+      <c r="A290" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B279" s="4" t="inlineStr">
+      <c r="B290" s="4" t="inlineStr">
         <is>
           <t>TwoThreeFive</t>
         </is>
       </c>
-      <c r="C279" s="4" t="n">
+      <c r="C290" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D279" s="1" t="inlineStr">
+      <c r="D290" s="1" t="inlineStr">
         <is>
           <t>亮出散牌235</t>
         </is>
       </c>
     </row>
-    <row r="280" customFormat="1" s="2">
-      <c r="A280" s="1" t="inlineStr">
+    <row r="291" customFormat="1" s="2">
+      <c r="A291" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B280" s="4" t="inlineStr">
+      <c r="B291" s="4" t="inlineStr">
         <is>
           <t>ShuffleCardAndVictory</t>
         </is>
       </c>
-      <c r="C280" s="4" t="n">
+      <c r="C291" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D280" s="1" t="inlineStr">
+      <c r="D291" s="1" t="inlineStr">
         <is>
           <t>搓牌并战胜对手</t>
         </is>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" s="1" t="inlineStr">
+    <row r="292" customFormat="1" s="2">
+      <c r="A292" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B281" s="4" t="inlineStr">
+      <c r="B292" s="4" t="inlineStr">
         <is>
           <t>Seven</t>
         </is>
       </c>
-      <c r="C281" s="4" t="n">
+      <c r="C292" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D281" s="1" t="inlineStr">
+      <c r="D292" s="1" t="inlineStr">
         <is>
           <t>亮出数字牌7</t>
         </is>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" s="0" t="inlineStr">
+    <row r="293" customFormat="1" s="3">
+      <c r="A293" s="0" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B282" s="0" t="inlineStr">
+      <c r="B293" s="0" t="inlineStr">
         <is>
           <t>Flush</t>
         </is>
       </c>
-      <c r="C282" s="4" t="n">
+      <c r="C293" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D282" s="0" t="inlineStr">
+      <c r="D293" s="0" t="inlineStr">
         <is>
           <t>亮出同花</t>
-        </is>
-      </c>
-    </row>
-    <row r="283" customFormat="1" s="2">
-      <c r="A283" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B283" s="3" t="inlineStr">
-        <is>
-          <t>ClearDifficulty</t>
-        </is>
-      </c>
-      <c r="C283" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D283" s="3" t="inlineStr">
-        <is>
-          <t>通关指定难度</t>
-        </is>
-      </c>
-    </row>
-    <row r="284" customFormat="1" s="2">
-      <c r="A284" s="0" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B284" s="0" t="inlineStr">
-        <is>
-          <t>AccumulateGold</t>
-        </is>
-      </c>
-      <c r="C284" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D284" s="0" t="inlineStr">
-        <is>
-          <t>累计获得金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="285" customFormat="1" s="2">
-      <c r="A285" s="0" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B285" s="0" t="inlineStr">
-        <is>
-          <t>SingleDamage</t>
-        </is>
-      </c>
-      <c r="C285" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D285" s="0" t="inlineStr">
-        <is>
-          <t>单次比牌造成伤害达到指定值</t>
-        </is>
-      </c>
-    </row>
-    <row r="286" customFormat="1" s="2">
-      <c r="A286" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B286" s="3" t="inlineStr">
-        <is>
-          <t>Couplet</t>
-        </is>
-      </c>
-      <c r="C286" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D286" s="3" t="inlineStr">
-        <is>
-          <t>亮出对子次数</t>
-        </is>
-      </c>
-    </row>
-    <row r="287" customFormat="1" s="2">
-      <c r="A287" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B287" s="5" t="inlineStr">
-        <is>
-          <t>Failure</t>
-        </is>
-      </c>
-      <c r="C287" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="D287" s="3" t="inlineStr">
-        <is>
-          <t>比牌负于对手次数</t>
-        </is>
-      </c>
-    </row>
-    <row r="288" customFormat="1" s="2">
-      <c r="A288" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B288" s="5" t="inlineStr">
-        <is>
-          <t>Defeat</t>
-        </is>
-      </c>
-      <c r="C288" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="D288" s="3" t="inlineStr">
-        <is>
-          <t>比牌战胜对手次数</t>
-        </is>
-      </c>
-    </row>
-    <row r="289" customFormat="1" s="2">
-      <c r="A289" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B289" s="5" t="inlineStr">
-        <is>
-          <t>LuxuryGoods</t>
-        </is>
-      </c>
-      <c r="C289" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D289" s="3" t="inlineStr">
-        <is>
-          <t>奢侈品</t>
-        </is>
-      </c>
-    </row>
-    <row r="290" customFormat="1" s="2">
-      <c r="A290" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B290" s="5" t="inlineStr">
-        <is>
-          <t>Angel</t>
-        </is>
-      </c>
-      <c r="C290" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="D290" s="3" t="inlineStr">
-        <is>
-          <t>天使</t>
-        </is>
-      </c>
-    </row>
-    <row r="291" customFormat="1" s="2">
-      <c r="A291" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B291" s="5" t="inlineStr">
-        <is>
-          <t>DeathNum</t>
-        </is>
-      </c>
-      <c r="C291" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="D291" s="3" t="inlineStr">
-        <is>
-          <t>死亡次数</t>
-        </is>
-      </c>
-    </row>
-    <row r="292" customFormat="1" s="2">
-      <c r="A292" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B292" s="5" t="inlineStr">
-        <is>
-          <t>Perspective</t>
-        </is>
-      </c>
-      <c r="C292" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="D292" s="3" t="inlineStr">
-        <is>
-          <t>使用透视次数</t>
-        </is>
-      </c>
-    </row>
-    <row r="293" customFormat="1" s="3">
-      <c r="A293" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B293" s="5" t="inlineStr">
-        <is>
-          <t>OneDamage</t>
-        </is>
-      </c>
-      <c r="C293" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="D293" s="3" t="inlineStr">
-        <is>
-          <t>单次打出的伤害</t>
         </is>
       </c>
     </row>
@@ -6047,185 +6028,405 @@
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B294" s="5" t="inlineStr">
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>ClearDifficulty</t>
+        </is>
+      </c>
+      <c r="C294" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
+          <t>通关指定难度</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="0" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B295" s="0" t="inlineStr">
+        <is>
+          <t>AccumulateGold</t>
+        </is>
+      </c>
+      <c r="C295" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D295" s="0" t="inlineStr">
+        <is>
+          <t>累计获得金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="0" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B296" s="0" t="inlineStr">
+        <is>
+          <t>SingleDamage</t>
+        </is>
+      </c>
+      <c r="C296" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D296" s="0" t="inlineStr">
+        <is>
+          <t>单次比牌造成伤害达到指定值</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>Couplet</t>
+        </is>
+      </c>
+      <c r="C297" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D297" s="3" t="inlineStr">
+        <is>
+          <t>亮出对子次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B298" s="5" t="inlineStr">
+        <is>
+          <t>Failure</t>
+        </is>
+      </c>
+      <c r="C298" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D298" s="3" t="inlineStr">
+        <is>
+          <t>比牌负于对手次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B299" s="5" t="inlineStr">
+        <is>
+          <t>Defeat</t>
+        </is>
+      </c>
+      <c r="C299" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D299" s="3" t="inlineStr">
+        <is>
+          <t>比牌战胜对手次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B300" s="5" t="inlineStr">
+        <is>
+          <t>LuxuryGoods</t>
+        </is>
+      </c>
+      <c r="C300" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D300" s="3" t="inlineStr">
+        <is>
+          <t>奢侈品</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B301" s="5" t="inlineStr">
+        <is>
+          <t>Angel</t>
+        </is>
+      </c>
+      <c r="C301" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D301" s="3" t="inlineStr">
+        <is>
+          <t>天使</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B302" s="5" t="inlineStr">
+        <is>
+          <t>DeathNum</t>
+        </is>
+      </c>
+      <c r="C302" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="D302" s="3" t="inlineStr">
+        <is>
+          <t>死亡次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B303" s="5" t="inlineStr">
+        <is>
+          <t>Perspective</t>
+        </is>
+      </c>
+      <c r="C303" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="D303" s="3" t="inlineStr">
+        <is>
+          <t>使用透视次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B304" s="5" t="inlineStr">
+        <is>
+          <t>OneDamage</t>
+        </is>
+      </c>
+      <c r="C304" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>单次打出的伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B305" s="5" t="inlineStr">
         <is>
           <t>NumberOfCoinsOwned</t>
         </is>
       </c>
-      <c r="C294" s="5" t="n">
+      <c r="C305" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D294" s="3" t="inlineStr">
+      <c r="D305" s="3" t="inlineStr">
         <is>
           <t>战斗时拥有金币数量</t>
         </is>
       </c>
     </row>
-    <row r="295">
-      <c r="A295" s="3" t="inlineStr">
+    <row r="306">
+      <c r="A306" s="3" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B295" s="5" t="inlineStr">
+      <c r="B306" s="5" t="inlineStr">
         <is>
           <t>CriticalNum</t>
         </is>
       </c>
-      <c r="C295" s="5" t="n">
+      <c r="C306" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="D295" s="3" t="inlineStr">
+      <c r="D306" s="3" t="inlineStr">
         <is>
           <t>触发暴击次数</t>
         </is>
       </c>
     </row>
-    <row r="296">
-      <c r="A296" s="3" t="inlineStr">
+    <row r="307">
+      <c r="A307" s="3" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B296" s="5" t="inlineStr">
+      <c r="B307" s="5" t="inlineStr">
         <is>
           <t>ThreeCardAttack</t>
         </is>
       </c>
-      <c r="C296" s="5" t="n">
+      <c r="C307" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="D296" s="3" t="inlineStr">
+      <c r="D307" s="3" t="inlineStr">
         <is>
           <t>三花聚顶</t>
         </is>
       </c>
     </row>
-    <row r="297">
-      <c r="A297" s="0" t="n"/>
-      <c r="B297" s="0" t="n"/>
-      <c r="D297" s="0" t="n"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="0" t="n"/>
-      <c r="B298" s="0" t="n"/>
-      <c r="D298" s="0" t="n"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="0" t="inlineStr">
+    <row r="308">
+      <c r="A308" s="0" t="n"/>
+      <c r="B308" s="0" t="n"/>
+      <c r="D308" s="0" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="0" t="n"/>
+      <c r="B309" s="0" t="n"/>
+      <c r="D309" s="0" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="0" t="inlineStr">
         <is>
           <t>GuideTriggerType</t>
         </is>
       </c>
-      <c r="B299" s="0" t="inlineStr">
+      <c r="B310" s="0" t="inlineStr">
         <is>
           <t>ScreenOpen</t>
         </is>
       </c>
-      <c r="C299" s="4" t="n">
+      <c r="C310" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D299" s="0" t="inlineStr">
+      <c r="D310" s="0" t="inlineStr">
         <is>
           <t>界面打开时触发</t>
         </is>
       </c>
     </row>
-    <row r="300">
-      <c r="A300" s="0" t="inlineStr">
+    <row r="311">
+      <c r="A311" s="0" t="inlineStr">
         <is>
           <t>GuideTriggerType</t>
         </is>
       </c>
-      <c r="B300" s="0" t="inlineStr">
+      <c r="B311" s="0" t="inlineStr">
         <is>
           <t>GamePhase</t>
         </is>
       </c>
-      <c r="C300" s="4" t="n">
+      <c r="C311" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D300" s="0" t="inlineStr">
+      <c r="D311" s="0" t="inlineStr">
         <is>
           <t>对局阶段变化时触发</t>
         </is>
       </c>
     </row>
-    <row r="301">
-      <c r="A301" s="0" t="inlineStr">
+    <row r="312">
+      <c r="A312" s="0" t="inlineStr">
         <is>
           <t>GuideTriggerType</t>
         </is>
       </c>
-      <c r="B301" s="0" t="inlineStr">
+      <c r="B312" s="0" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="C301" s="4" t="n">
+      <c r="C312" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D301" s="0" t="inlineStr">
+      <c r="D312" s="0" t="inlineStr">
         <is>
           <t>代码手动触发</t>
         </is>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" s="0" t="inlineStr">
+    <row r="313">
+      <c r="A313" s="0" t="inlineStr">
         <is>
           <t>GuideStepType</t>
         </is>
       </c>
-      <c r="B302" s="0" t="inlineStr">
+      <c r="B313" s="0" t="inlineStr">
         <is>
           <t>Click</t>
         </is>
       </c>
-      <c r="C302" s="4" t="n">
+      <c r="C313" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D302" s="0" t="inlineStr">
+      <c r="D313" s="0" t="inlineStr">
         <is>
           <t>点击高亮目标后推进</t>
         </is>
       </c>
     </row>
-    <row r="303">
-      <c r="A303" s="0" t="inlineStr">
+    <row r="314">
+      <c r="A314" s="0" t="inlineStr">
         <is>
           <t>GuideStepType</t>
         </is>
       </c>
-      <c r="B303" s="0" t="inlineStr">
+      <c r="B314" s="0" t="inlineStr">
         <is>
           <t>Wait</t>
         </is>
       </c>
-      <c r="C303" s="4" t="n">
+      <c r="C314" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D303" s="0" t="inlineStr">
+      <c r="D314" s="0" t="inlineStr">
         <is>
           <t>等待代码处理器完成后推进</t>
         </is>
       </c>
     </row>
-    <row r="304">
-      <c r="A304" s="0" t="inlineStr">
+    <row r="315">
+      <c r="A315" s="0" t="inlineStr">
         <is>
           <t>GuideStepType</t>
         </is>
       </c>
-      <c r="B304" s="0" t="inlineStr">
+      <c r="B315" s="0" t="inlineStr">
         <is>
           <t>Dialog</t>
         </is>
       </c>
-      <c r="C304" s="4" t="n">
+      <c r="C315" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D304" s="0" t="inlineStr">
+      <c r="D315" s="0" t="inlineStr">
         <is>
           <t>点击气泡下一步后推进</t>
         </is>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -1058,7 +1058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E315"/>
+  <dimension ref="A1:E330"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.7416666666667" customWidth="1" style="1" min="1" max="1"/>
@@ -2455,20 +2455,20 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="0" t="inlineStr">
         <is>
           <t>BossEntryType</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="0" t="inlineStr">
         <is>
           <t>BloodDebt</t>
         </is>
       </c>
-      <c r="C92" t="n">
+      <c r="C92" s="0" t="n">
         <v>53</v>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D92" s="0" t="inlineStr">
         <is>
           <t>BOSS每损失10%生命,造成的伤害提高,有上限</t>
         </is>
@@ -5690,132 +5690,304 @@
       </c>
     </row>
     <row r="259">
-      <c r="B259" s="0" t="n"/>
-      <c r="D259" s="0" t="n"/>
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>SelfDestroyPerRound</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>154</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>回合结束后,有概率摧毁此圣物(参数:概率)</t>
+        </is>
+      </c>
     </row>
     <row r="260">
-      <c r="B260" s="0" t="n"/>
-      <c r="D260" s="0" t="n"/>
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>SelfMultWinLose</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>155</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>比牌胜利后自身倍率+X,失败后-X(参数:胜利加成|失败扣除)</t>
+        </is>
+      </c>
     </row>
     <row r="261">
-      <c r="B261" s="0" t="n"/>
-      <c r="D261" s="0" t="n"/>
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>UseConsumableGetMult</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>156</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>每使用1次消耗类圣物,永久倍率+X</t>
+        </is>
+      </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B262" s="4" t="inlineStr">
-        <is>
-          <t>MaxHp</t>
-        </is>
-      </c>
-      <c r="C262" s="4" t="n">
-        <v>1111</v>
-      </c>
-      <c r="D262" s="0" t="n"/>
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>UseConsumableGetAttack</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>157</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>每使用1次消耗类圣物,永久攻击+X</t>
+        </is>
+      </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B263" s="0" t="inlineStr">
-        <is>
-          <t>EveryRoundHpUp</t>
-        </is>
-      </c>
-      <c r="C263" s="4" t="n">
-        <v>1112</v>
-      </c>
-      <c r="D263" s="0" t="n"/>
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>SummonConsumable</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>158</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>亮出同花顺时,随机生成1个消耗品圣物(需圣物栏有空位)</t>
+        </is>
+      </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B264" s="0" t="inlineStr">
-        <is>
-          <t>TwoThreeFive</t>
-        </is>
-      </c>
-      <c r="C264" s="4" t="n">
-        <v>1113</v>
-      </c>
-      <c r="D264" s="0" t="n"/>
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>UnshownRankMult</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>159</v>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>留在手牌中的指定点数牌每张提供倍率(参数:点数A=14/K=13/Q=12/J=11|倍率)</t>
+        </is>
+      </c>
     </row>
     <row r="265">
-      <c r="A265" s="0" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B265" s="0" t="inlineStr">
-        <is>
-          <t>KillingGetGold</t>
-        </is>
-      </c>
-      <c r="C265" s="0" t="n">
-        <v>1114</v>
-      </c>
-      <c r="D265" s="0" t="inlineStr">
-        <is>
-          <t>每击杀敌人,英雄额外获得金币</t>
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>CopyRandomRelic</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>160</v>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>每回合随机复制1个其他已拥有圣物的能力</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="0" t="inlineStr">
-        <is>
-          <t>MechanismType</t>
-        </is>
-      </c>
-      <c r="B266" s="0" t="inlineStr">
-        <is>
-          <t>KillingGetAttack</t>
-        </is>
-      </c>
-      <c r="C266" s="0" t="n">
-        <v>1115</v>
-      </c>
-      <c r="D266" s="0" t="inlineStr">
-        <is>
-          <t>每击杀敌人,英雄永久提高攻击力</t>
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>DamagePerLevelEntry</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>161</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>本关每存在1条关卡机制,造成的伤害提高(参数:百分比)</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="B267" s="0" t="n"/>
-      <c r="D267" s="0" t="n"/>
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>PeekSteal</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>162</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>使用透视时,随机抽走该敌人1张手牌,与自己点数最小的1张交换</t>
+        </is>
+      </c>
     </row>
     <row r="268">
-      <c r="B268" s="0" t="n"/>
-      <c r="D268" s="0" t="n"/>
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>SelfDecayAttack</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>163</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>提供攻击力,每次比牌后衰减(参数:初始攻击|每次衰减)</t>
+        </is>
+      </c>
     </row>
     <row r="269">
-      <c r="B269" s="0" t="n"/>
-      <c r="D269" s="0" t="n"/>
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>SelfDecayMult</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>164</v>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>提供倍率,每次比牌后衰减(参数:初始倍率|每次衰减)</t>
+        </is>
+      </c>
     </row>
     <row r="270">
-      <c r="B270" s="0" t="n"/>
-      <c r="D270" s="0" t="n"/>
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>FixedTypeCountMult</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>165</v>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>指定牌型每亮出1次,结算倍率+X(参数:牌型Level,豹子=6|倍率)</t>
+        </is>
+      </c>
     </row>
     <row r="271">
-      <c r="B271" s="0" t="n"/>
-      <c r="D271" s="0" t="n"/>
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>ShopRefreshGetMult</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>166</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>商店每刷新1次,自身倍率+X</t>
+        </is>
+      </c>
     </row>
     <row r="272">
-      <c r="B272" s="0" t="n"/>
-      <c r="D272" s="0" t="n"/>
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>LuckyDouble</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>167</v>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>使你所有圣物中概率类数值翻倍</t>
+        </is>
+      </c>
     </row>
     <row r="273">
-      <c r="B273" s="0" t="n"/>
-      <c r="D273" s="0" t="n"/>
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>WildAce</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>168</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>你的A可当作任意花色与任意点数使用</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="B274" s="0" t="n"/>
@@ -5830,24 +6002,92 @@
       <c r="D276" s="0" t="n"/>
     </row>
     <row r="277">
-      <c r="B277" s="0" t="n"/>
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
+          <t>MaxHp</t>
+        </is>
+      </c>
+      <c r="C277" s="4" t="n">
+        <v>1111</v>
+      </c>
       <c r="D277" s="0" t="n"/>
     </row>
     <row r="278">
-      <c r="B278" s="0" t="n"/>
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B278" s="0" t="inlineStr">
+        <is>
+          <t>EveryRoundHpUp</t>
+        </is>
+      </c>
+      <c r="C278" s="4" t="n">
+        <v>1112</v>
+      </c>
       <c r="D278" s="0" t="n"/>
     </row>
     <row r="279">
-      <c r="B279" s="0" t="n"/>
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B279" s="0" t="inlineStr">
+        <is>
+          <t>TwoThreeFive</t>
+        </is>
+      </c>
+      <c r="C279" s="4" t="n">
+        <v>1113</v>
+      </c>
       <c r="D279" s="0" t="n"/>
     </row>
     <row r="280" customFormat="1" s="2">
-      <c r="B280" s="0" t="n"/>
-      <c r="D280" s="0" t="n"/>
+      <c r="A280" s="0" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B280" s="0" t="inlineStr">
+        <is>
+          <t>KillingGetGold</t>
+        </is>
+      </c>
+      <c r="C280" s="0" t="n">
+        <v>1114</v>
+      </c>
+      <c r="D280" s="0" t="inlineStr">
+        <is>
+          <t>每击杀敌人,英雄额外获得金币</t>
+        </is>
+      </c>
     </row>
     <row r="281">
-      <c r="B281" s="0" t="n"/>
-      <c r="D281" s="0" t="n"/>
+      <c r="A281" s="0" t="inlineStr">
+        <is>
+          <t>MechanismType</t>
+        </is>
+      </c>
+      <c r="B281" s="0" t="inlineStr">
+        <is>
+          <t>KillingGetAttack</t>
+        </is>
+      </c>
+      <c r="C281" s="0" t="n">
+        <v>1115</v>
+      </c>
+      <c r="D281" s="0" t="inlineStr">
+        <is>
+          <t>每击杀敌人,英雄永久提高攻击力</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="B282" s="0" t="n"/>
@@ -5861,572 +6101,632 @@
       <c r="B284" s="0" t="n"/>
       <c r="D284" s="0" t="n"/>
     </row>
-    <row r="285" customFormat="1" s="2"/>
+    <row r="285" customFormat="1" s="2">
+      <c r="B285" s="0" t="n"/>
+      <c r="D285" s="0" t="n"/>
+    </row>
     <row r="286" customFormat="1" s="2">
-      <c r="A286" s="1" t="inlineStr">
+      <c r="B286" s="0" t="n"/>
+      <c r="D286" s="0" t="n"/>
+    </row>
+    <row r="287" customFormat="1" s="2">
+      <c r="B287" s="0" t="n"/>
+      <c r="D287" s="0" t="n"/>
+    </row>
+    <row r="288" customFormat="1" s="2">
+      <c r="B288" s="0" t="n"/>
+      <c r="D288" s="0" t="n"/>
+    </row>
+    <row r="289" customFormat="1" s="2">
+      <c r="B289" s="0" t="n"/>
+      <c r="D289" s="0" t="n"/>
+    </row>
+    <row r="290" customFormat="1" s="2">
+      <c r="B290" s="0" t="n"/>
+      <c r="D290" s="0" t="n"/>
+    </row>
+    <row r="291" customFormat="1" s="2">
+      <c r="B291" s="0" t="n"/>
+      <c r="D291" s="0" t="n"/>
+    </row>
+    <row r="292" customFormat="1" s="2">
+      <c r="B292" s="0" t="n"/>
+      <c r="D292" s="0" t="n"/>
+    </row>
+    <row r="293" customFormat="1" s="3">
+      <c r="B293" s="0" t="n"/>
+      <c r="D293" s="0" t="n"/>
+    </row>
+    <row r="294">
+      <c r="B294" s="0" t="n"/>
+      <c r="D294" s="0" t="n"/>
+    </row>
+    <row r="295">
+      <c r="B295" s="0" t="n"/>
+      <c r="D295" s="0" t="n"/>
+    </row>
+    <row r="296">
+      <c r="B296" s="0" t="n"/>
+      <c r="D296" s="0" t="n"/>
+    </row>
+    <row r="297">
+      <c r="B297" s="0" t="n"/>
+      <c r="D297" s="0" t="n"/>
+    </row>
+    <row r="298">
+      <c r="B298" s="0" t="n"/>
+      <c r="D298" s="0" t="n"/>
+    </row>
+    <row r="299">
+      <c r="B299" s="0" t="n"/>
+      <c r="D299" s="0" t="n"/>
+    </row>
+    <row r="300"/>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B286" s="1" t="inlineStr">
+      <c r="B301" s="1" t="inlineStr">
         <is>
           <t>KillMonster</t>
         </is>
       </c>
-      <c r="C286" s="4" t="n">
+      <c r="C301" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D286" s="1" t="inlineStr">
+      <c r="D301" s="1" t="inlineStr">
         <is>
           <t>杀敌</t>
         </is>
       </c>
     </row>
-    <row r="287" customFormat="1" s="2">
-      <c r="A287" s="1" t="inlineStr">
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B287" s="4" t="inlineStr">
+      <c r="B302" s="4" t="inlineStr">
         <is>
           <t>ShuffleCard</t>
         </is>
       </c>
-      <c r="C287" s="4" t="n">
+      <c r="C302" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D287" s="1" t="inlineStr">
+      <c r="D302" s="1" t="inlineStr">
         <is>
           <t>搓牌</t>
         </is>
       </c>
     </row>
-    <row r="288" customFormat="1" s="2">
-      <c r="A288" s="1" t="inlineStr">
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B288" s="4" t="inlineStr">
+      <c r="B303" s="4" t="inlineStr">
         <is>
           <t>RefreshStore</t>
         </is>
       </c>
-      <c r="C288" s="4" t="n">
+      <c r="C303" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D288" s="1" t="inlineStr">
+      <c r="D303" s="1" t="inlineStr">
         <is>
           <t>刷新商店</t>
         </is>
       </c>
     </row>
-    <row r="289" customFormat="1" s="2">
-      <c r="A289" s="1" t="inlineStr">
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B289" s="4" t="inlineStr">
+      <c r="B304" s="4" t="inlineStr">
         <is>
           <t>Straight</t>
         </is>
       </c>
-      <c r="C289" s="4" t="n">
+      <c r="C304" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D289" s="1" t="inlineStr">
+      <c r="D304" s="1" t="inlineStr">
         <is>
           <t>亮出顺子</t>
         </is>
       </c>
     </row>
-    <row r="290" customFormat="1" s="2">
-      <c r="A290" s="1" t="inlineStr">
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B290" s="4" t="inlineStr">
+      <c r="B305" s="4" t="inlineStr">
         <is>
           <t>TwoThreeFive</t>
         </is>
       </c>
-      <c r="C290" s="4" t="n">
+      <c r="C305" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D290" s="1" t="inlineStr">
+      <c r="D305" s="1" t="inlineStr">
         <is>
           <t>亮出散牌235</t>
         </is>
       </c>
     </row>
-    <row r="291" customFormat="1" s="2">
-      <c r="A291" s="1" t="inlineStr">
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B291" s="4" t="inlineStr">
+      <c r="B306" s="4" t="inlineStr">
         <is>
           <t>ShuffleCardAndVictory</t>
         </is>
       </c>
-      <c r="C291" s="4" t="n">
+      <c r="C306" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D291" s="1" t="inlineStr">
+      <c r="D306" s="1" t="inlineStr">
         <is>
           <t>搓牌并战胜对手</t>
         </is>
       </c>
     </row>
-    <row r="292" customFormat="1" s="2">
-      <c r="A292" s="1" t="inlineStr">
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B292" s="4" t="inlineStr">
+      <c r="B307" s="4" t="inlineStr">
         <is>
           <t>Seven</t>
         </is>
       </c>
-      <c r="C292" s="4" t="n">
+      <c r="C307" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D292" s="1" t="inlineStr">
+      <c r="D307" s="1" t="inlineStr">
         <is>
           <t>亮出数字牌7</t>
         </is>
       </c>
     </row>
-    <row r="293" customFormat="1" s="3">
-      <c r="A293" s="0" t="inlineStr">
+    <row r="308">
+      <c r="A308" s="0" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B293" s="0" t="inlineStr">
+      <c r="B308" s="0" t="inlineStr">
         <is>
           <t>Flush</t>
         </is>
       </c>
-      <c r="C293" s="4" t="n">
+      <c r="C308" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D293" s="0" t="inlineStr">
+      <c r="D308" s="0" t="inlineStr">
         <is>
           <t>亮出同花</t>
         </is>
       </c>
     </row>
-    <row r="294">
-      <c r="A294" s="3" t="inlineStr">
+    <row r="309">
+      <c r="A309" s="3" t="inlineStr">
         <is>
           <t>ContidionType</t>
         </is>
       </c>
-      <c r="B294" s="3" t="inlineStr">
+      <c r="B309" s="3" t="inlineStr">
         <is>
           <t>ClearDifficulty</t>
         </is>
       </c>
-      <c r="C294" s="5" t="n">
+      <c r="C309" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D294" s="3" t="inlineStr">
+      <c r="D309" s="3" t="inlineStr">
         <is>
           <t>通关指定难度</t>
         </is>
       </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="0" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B295" s="0" t="inlineStr">
-        <is>
-          <t>AccumulateGold</t>
-        </is>
-      </c>
-      <c r="C295" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D295" s="0" t="inlineStr">
-        <is>
-          <t>累计获得金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="0" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B296" s="0" t="inlineStr">
-        <is>
-          <t>SingleDamage</t>
-        </is>
-      </c>
-      <c r="C296" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D296" s="0" t="inlineStr">
-        <is>
-          <t>单次比牌造成伤害达到指定值</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B297" s="3" t="inlineStr">
-        <is>
-          <t>Couplet</t>
-        </is>
-      </c>
-      <c r="C297" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D297" s="3" t="inlineStr">
-        <is>
-          <t>亮出对子次数</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B298" s="5" t="inlineStr">
-        <is>
-          <t>Failure</t>
-        </is>
-      </c>
-      <c r="C298" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="D298" s="3" t="inlineStr">
-        <is>
-          <t>比牌负于对手次数</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B299" s="5" t="inlineStr">
-        <is>
-          <t>Defeat</t>
-        </is>
-      </c>
-      <c r="C299" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="D299" s="3" t="inlineStr">
-        <is>
-          <t>比牌战胜对手次数</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B300" s="5" t="inlineStr">
-        <is>
-          <t>LuxuryGoods</t>
-        </is>
-      </c>
-      <c r="C300" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D300" s="3" t="inlineStr">
-        <is>
-          <t>奢侈品</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B301" s="5" t="inlineStr">
-        <is>
-          <t>Angel</t>
-        </is>
-      </c>
-      <c r="C301" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="D301" s="3" t="inlineStr">
-        <is>
-          <t>天使</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B302" s="5" t="inlineStr">
-        <is>
-          <t>DeathNum</t>
-        </is>
-      </c>
-      <c r="C302" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="D302" s="3" t="inlineStr">
-        <is>
-          <t>死亡次数</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B303" s="5" t="inlineStr">
-        <is>
-          <t>Perspective</t>
-        </is>
-      </c>
-      <c r="C303" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="D303" s="3" t="inlineStr">
-        <is>
-          <t>使用透视次数</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B304" s="5" t="inlineStr">
-        <is>
-          <t>OneDamage</t>
-        </is>
-      </c>
-      <c r="C304" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="D304" s="3" t="inlineStr">
-        <is>
-          <t>单次打出的伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B305" s="5" t="inlineStr">
-        <is>
-          <t>NumberOfCoinsOwned</t>
-        </is>
-      </c>
-      <c r="C305" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D305" s="3" t="inlineStr">
-        <is>
-          <t>战斗时拥有金币数量</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B306" s="5" t="inlineStr">
-        <is>
-          <t>CriticalNum</t>
-        </is>
-      </c>
-      <c r="C306" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="D306" s="3" t="inlineStr">
-        <is>
-          <t>触发暴击次数</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="3" t="inlineStr">
-        <is>
-          <t>ContidionType</t>
-        </is>
-      </c>
-      <c r="B307" s="5" t="inlineStr">
-        <is>
-          <t>ThreeCardAttack</t>
-        </is>
-      </c>
-      <c r="C307" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="D307" s="3" t="inlineStr">
-        <is>
-          <t>三花聚顶</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="0" t="n"/>
-      <c r="B308" s="0" t="n"/>
-      <c r="D308" s="0" t="n"/>
-    </row>
-    <row r="309">
-      <c r="A309" s="0" t="n"/>
-      <c r="B309" s="0" t="n"/>
-      <c r="D309" s="0" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="0" t="inlineStr">
         <is>
-          <t>GuideTriggerType</t>
+          <t>ContidionType</t>
         </is>
       </c>
       <c r="B310" s="0" t="inlineStr">
         <is>
-          <t>ScreenOpen</t>
+          <t>AccumulateGold</t>
         </is>
       </c>
       <c r="C310" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D310" s="0" t="inlineStr">
         <is>
-          <t>界面打开时触发</t>
+          <t>累计获得金币</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="0" t="inlineStr">
         <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B311" s="0" t="inlineStr">
+        <is>
+          <t>SingleDamage</t>
+        </is>
+      </c>
+      <c r="C311" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D311" s="0" t="inlineStr">
+        <is>
+          <t>单次比牌造成伤害达到指定值</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>Couplet</t>
+        </is>
+      </c>
+      <c r="C312" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>亮出对子次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B313" s="5" t="inlineStr">
+        <is>
+          <t>Failure</t>
+        </is>
+      </c>
+      <c r="C313" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D313" s="3" t="inlineStr">
+        <is>
+          <t>比牌负于对手次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B314" s="5" t="inlineStr">
+        <is>
+          <t>Defeat</t>
+        </is>
+      </c>
+      <c r="C314" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>比牌战胜对手次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B315" s="5" t="inlineStr">
+        <is>
+          <t>LuxuryGoods</t>
+        </is>
+      </c>
+      <c r="C315" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D315" s="3" t="inlineStr">
+        <is>
+          <t>奢侈品</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B316" s="5" t="inlineStr">
+        <is>
+          <t>Angel</t>
+        </is>
+      </c>
+      <c r="C316" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>天使</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B317" s="5" t="inlineStr">
+        <is>
+          <t>DeathNum</t>
+        </is>
+      </c>
+      <c r="C317" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="D317" s="3" t="inlineStr">
+        <is>
+          <t>死亡次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B318" s="5" t="inlineStr">
+        <is>
+          <t>Perspective</t>
+        </is>
+      </c>
+      <c r="C318" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="D318" s="3" t="inlineStr">
+        <is>
+          <t>使用透视次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B319" s="5" t="inlineStr">
+        <is>
+          <t>OneDamage</t>
+        </is>
+      </c>
+      <c r="C319" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D319" s="3" t="inlineStr">
+        <is>
+          <t>单次打出的伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B320" s="5" t="inlineStr">
+        <is>
+          <t>NumberOfCoinsOwned</t>
+        </is>
+      </c>
+      <c r="C320" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D320" s="3" t="inlineStr">
+        <is>
+          <t>战斗时拥有金币数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B321" s="5" t="inlineStr">
+        <is>
+          <t>CriticalNum</t>
+        </is>
+      </c>
+      <c r="C321" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D321" s="3" t="inlineStr">
+        <is>
+          <t>触发暴击次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="3" t="inlineStr">
+        <is>
+          <t>ContidionType</t>
+        </is>
+      </c>
+      <c r="B322" s="5" t="inlineStr">
+        <is>
+          <t>ThreeCardAttack</t>
+        </is>
+      </c>
+      <c r="C322" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D322" s="3" t="inlineStr">
+        <is>
+          <t>三花聚顶</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="0" t="n"/>
+      <c r="B323" s="0" t="n"/>
+      <c r="D323" s="0" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="0" t="n"/>
+      <c r="B324" s="0" t="n"/>
+      <c r="D324" s="0" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="0" t="inlineStr">
+        <is>
           <t>GuideTriggerType</t>
         </is>
       </c>
-      <c r="B311" s="0" t="inlineStr">
+      <c r="B325" s="0" t="inlineStr">
+        <is>
+          <t>ScreenOpen</t>
+        </is>
+      </c>
+      <c r="C325" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D325" s="0" t="inlineStr">
+        <is>
+          <t>界面打开时触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="0" t="inlineStr">
+        <is>
+          <t>GuideTriggerType</t>
+        </is>
+      </c>
+      <c r="B326" s="0" t="inlineStr">
         <is>
           <t>GamePhase</t>
         </is>
       </c>
-      <c r="C311" s="4" t="n">
+      <c r="C326" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D311" s="0" t="inlineStr">
+      <c r="D326" s="0" t="inlineStr">
         <is>
           <t>对局阶段变化时触发</t>
         </is>
       </c>
     </row>
-    <row r="312">
-      <c r="A312" s="0" t="inlineStr">
+    <row r="327">
+      <c r="A327" s="0" t="inlineStr">
         <is>
           <t>GuideTriggerType</t>
         </is>
       </c>
-      <c r="B312" s="0" t="inlineStr">
+      <c r="B327" s="0" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="C312" s="4" t="n">
+      <c r="C327" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D312" s="0" t="inlineStr">
+      <c r="D327" s="0" t="inlineStr">
         <is>
           <t>代码手动触发</t>
         </is>
       </c>
     </row>
-    <row r="313">
-      <c r="A313" s="0" t="inlineStr">
+    <row r="328">
+      <c r="A328" s="0" t="inlineStr">
         <is>
           <t>GuideStepType</t>
         </is>
       </c>
-      <c r="B313" s="0" t="inlineStr">
+      <c r="B328" s="0" t="inlineStr">
         <is>
           <t>Click</t>
         </is>
       </c>
-      <c r="C313" s="4" t="n">
+      <c r="C328" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D313" s="0" t="inlineStr">
+      <c r="D328" s="0" t="inlineStr">
         <is>
           <t>点击高亮目标后推进</t>
         </is>
       </c>
     </row>
-    <row r="314">
-      <c r="A314" s="0" t="inlineStr">
+    <row r="329">
+      <c r="A329" s="0" t="inlineStr">
         <is>
           <t>GuideStepType</t>
         </is>
       </c>
-      <c r="B314" s="0" t="inlineStr">
+      <c r="B329" s="0" t="inlineStr">
         <is>
           <t>Wait</t>
         </is>
       </c>
-      <c r="C314" s="4" t="n">
+      <c r="C329" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D314" s="0" t="inlineStr">
+      <c r="D329" s="0" t="inlineStr">
         <is>
           <t>等待代码处理器完成后推进</t>
         </is>
       </c>
     </row>
-    <row r="315">
-      <c r="A315" s="0" t="inlineStr">
+    <row r="330">
+      <c r="A330" s="0" t="inlineStr">
         <is>
           <t>GuideStepType</t>
         </is>
       </c>
-      <c r="B315" s="0" t="inlineStr">
+      <c r="B330" s="0" t="inlineStr">
         <is>
           <t>Dialog</t>
         </is>
       </c>
-      <c r="C315" s="4" t="n">
+      <c r="C330" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D315" s="0" t="inlineStr">
+      <c r="D330" s="0" t="inlineStr">
         <is>
           <t>点击气泡下一步后推进</t>
         </is>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="10920" windowHeight="12705"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="574">
   <si>
     <t>Enum</t>
   </si>
@@ -1498,6 +1498,66 @@
     <t>你的A可当作任意花色与任意点数使用</t>
   </si>
   <si>
+    <t>VersatilePersonUp</t>
+  </si>
+  <si>
+    <t>每击杀1名敌人分裂伤害提高</t>
+  </si>
+  <si>
+    <t>UnableCritical</t>
+  </si>
+  <si>
+    <t>无法暴击</t>
+  </si>
+  <si>
+    <t>GainDamageUpWhenHpDecreases</t>
+  </si>
+  <si>
+    <t>每降低血量都会使伤害提高,最多叠加x层</t>
+  </si>
+  <si>
+    <t>UnableReplyHp</t>
+  </si>
+  <si>
+    <t>无法通过圣物回复</t>
+  </si>
+  <si>
+    <t>AoeDamageWhenAttack</t>
+  </si>
+  <si>
+    <t>攻击力达到x时,攻击变为群体伤害</t>
+  </si>
+  <si>
+    <t>RelicReplyHp</t>
+  </si>
+  <si>
+    <t>通过圣物获得的生命回复效果提高</t>
+  </si>
+  <si>
+    <t>MonsterNumDamage</t>
+  </si>
+  <si>
+    <t>每回合开始时会受到场上当前敌人数量倍数的伤害</t>
+  </si>
+  <si>
+    <t>HolyLightBurning</t>
+  </si>
+  <si>
+    <t>圣光燃烧</t>
+  </si>
+  <si>
+    <t>UnableMissing</t>
+  </si>
+  <si>
+    <t>无法闪避</t>
+  </si>
+  <si>
+    <t>UnableReplyGetGold</t>
+  </si>
+  <si>
+    <t>无法通过圣物效果获得金币</t>
+  </si>
+  <si>
     <t>MaxHp</t>
   </si>
   <si>
@@ -1679,6 +1739,21 @@
   </si>
   <si>
     <t>点击气泡下一步后推进</t>
+  </si>
+  <si>
+    <t>PvpFightKind</t>
+  </si>
+  <si>
+    <t>Monster</t>
+  </si>
+  <si>
+    <t>野怪轮</t>
+  </si>
+  <si>
+    <t>Pvp</t>
+  </si>
+  <si>
+    <t>玩家对战轮</t>
   </si>
 </sst>
 </file>
@@ -2300,7 +2375,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2324,6 +2399,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2673,7 +2751,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:E288"/>
+  <dimension ref="A4:E305"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16.7416666666667" style="1" customWidth="1"/>
@@ -6114,469 +6192,653 @@
         <v>487</v>
       </c>
     </row>
-    <row r="253" spans="1:4">
-      <c r="B253"/>
-      <c r="D253"/>
-    </row>
-    <row r="254" spans="1:4">
-      <c r="A254" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B254" s="3" t="s">
+    <row r="253" s="2" customFormat="1" spans="1:4">
+      <c r="A253" t="s">
+        <v>156</v>
+      </c>
+      <c r="B253" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="C254" s="3">
+      <c r="C253" s="5">
+        <v>169</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="254" s="2" customFormat="1" spans="1:4">
+      <c r="A254" t="s">
+        <v>156</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="C254" s="5">
+        <v>170</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="255" s="2" customFormat="1" spans="1:4">
+      <c r="A255" t="s">
+        <v>156</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="C255" s="5">
+        <v>171</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="256" s="2" customFormat="1" spans="1:4">
+      <c r="A256" t="s">
+        <v>156</v>
+      </c>
+      <c r="B256" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="C256" s="5">
+        <v>172</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="257" s="2" customFormat="1" spans="1:4">
+      <c r="A257" t="s">
+        <v>156</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="C257" s="5">
+        <v>173</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="258" s="2" customFormat="1" spans="1:4">
+      <c r="A258" t="s">
+        <v>156</v>
+      </c>
+      <c r="B258" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="C258" s="5">
+        <v>174</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="259" s="2" customFormat="1" spans="1:4">
+      <c r="A259" t="s">
+        <v>156</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="C259" s="5">
+        <v>175</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="260" s="2" customFormat="1" spans="1:4">
+      <c r="A260" t="s">
+        <v>156</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C260" s="5">
+        <v>176</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="261" s="2" customFormat="1" spans="1:4">
+      <c r="A261" t="s">
+        <v>156</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="C261" s="5">
+        <v>177</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="262" s="2" customFormat="1" spans="1:4">
+      <c r="A262" t="s">
+        <v>156</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="C262" s="5">
+        <v>178</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="B263"/>
+      <c r="D263"/>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="B264"/>
+      <c r="D264"/>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="B265"/>
+      <c r="D265"/>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="B266"/>
+      <c r="D266"/>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="B267"/>
+      <c r="D267"/>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C268" s="3">
         <v>1111</v>
       </c>
-      <c r="D254"/>
-    </row>
-    <row r="255" spans="1:4">
-      <c r="A255" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B255" t="s">
-        <v>489</v>
-      </c>
-      <c r="C255" s="3">
+      <c r="D268"/>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B269" t="s">
+        <v>509</v>
+      </c>
+      <c r="C269" s="3">
         <v>1112</v>
       </c>
-      <c r="D255"/>
-    </row>
-    <row r="256" spans="1:4">
-      <c r="A256" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B256" t="s">
-        <v>490</v>
-      </c>
-      <c r="C256" s="3">
+      <c r="D269"/>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B270" t="s">
+        <v>510</v>
+      </c>
+      <c r="C270" s="3">
         <v>1113</v>
       </c>
-      <c r="D256"/>
-    </row>
-    <row r="257" s="2" customFormat="1" spans="1:4">
-      <c r="A257" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B257" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="C257" s="5">
+      <c r="D270"/>
+    </row>
+    <row r="271" s="2" customFormat="1" spans="1:4">
+      <c r="A271" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B271" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C271" s="5">
         <v>1114</v>
       </c>
-      <c r="D257" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4">
-      <c r="A258" t="s">
-        <v>156</v>
-      </c>
-      <c r="B258" t="s">
-        <v>493</v>
-      </c>
-      <c r="C258" s="3">
+      <c r="D271" s="4" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" t="s">
+        <v>156</v>
+      </c>
+      <c r="B272" t="s">
+        <v>513</v>
+      </c>
+      <c r="C272" s="3">
         <v>1115</v>
       </c>
-      <c r="D258" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4">
-      <c r="A260" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="B260" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C260" s="3">
+      <c r="D272" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C274" s="3">
         <v>1</v>
       </c>
-      <c r="D260" s="1" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4">
-      <c r="A261" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="B261" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="C261" s="3">
+      <c r="D274" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="C275" s="3">
         <v>2</v>
       </c>
-      <c r="D261" s="1" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="262" spans="1:4">
-      <c r="A262" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="B262" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="C262" s="3">
+      <c r="D275" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="C276" s="3">
         <v>3</v>
       </c>
-      <c r="D262" s="1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4">
-      <c r="A263" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="B263" s="3" t="s">
+      <c r="D276" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B277" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C263" s="3">
+      <c r="C277" s="3">
         <v>4</v>
       </c>
-      <c r="D263" s="1" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4">
-      <c r="A264" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="B264" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="C264" s="3">
+      <c r="D277" s="1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="C278" s="3">
         <v>5</v>
       </c>
-      <c r="D264" s="1" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4">
-      <c r="A265" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="B265" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="C265" s="3">
+      <c r="D278" s="1" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="C279" s="3">
         <v>6</v>
       </c>
-      <c r="D265" s="1" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4">
-      <c r="A266" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="B266" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="C266" s="3">
+      <c r="D279" s="1" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="C280" s="3">
         <v>7</v>
       </c>
-      <c r="D266" s="1" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4">
-      <c r="A267" t="s">
-        <v>495</v>
-      </c>
-      <c r="B267" t="s">
+      <c r="D280" s="1" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" t="s">
+        <v>515</v>
+      </c>
+      <c r="B281" t="s">
         <v>17</v>
       </c>
-      <c r="C267" s="3">
+      <c r="C281" s="3">
         <v>8</v>
       </c>
-      <c r="D267" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4">
-      <c r="A268" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="B268" s="6" t="s">
-        <v>509</v>
-      </c>
-      <c r="C268" s="7">
+      <c r="D281" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="C282" s="7">
         <v>9</v>
       </c>
-      <c r="D268" s="6" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4">
-      <c r="A269" t="s">
-        <v>495</v>
-      </c>
-      <c r="B269" t="s">
-        <v>511</v>
-      </c>
-      <c r="C269" s="3">
-        <v>10</v>
-      </c>
-      <c r="D269" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4">
-      <c r="A270" t="s">
-        <v>495</v>
-      </c>
-      <c r="B270" t="s">
-        <v>513</v>
-      </c>
-      <c r="C270" s="3">
-        <v>11</v>
-      </c>
-      <c r="D270" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4">
-      <c r="A271" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="B271" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C271" s="7">
-        <v>12</v>
-      </c>
-      <c r="D271" s="6" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4">
-      <c r="A272" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="B272" s="7" t="s">
-        <v>516</v>
-      </c>
-      <c r="C272" s="7">
-        <v>13</v>
-      </c>
-      <c r="D272" s="6" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4">
-      <c r="A273" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="B273" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="C273" s="7">
-        <v>14</v>
-      </c>
-      <c r="D273" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4">
-      <c r="A274" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="B274" s="7" t="s">
-        <v>520</v>
-      </c>
-      <c r="C274" s="7">
-        <v>15</v>
-      </c>
-      <c r="D274" s="6" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4">
-      <c r="A275" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="B275" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="C275" s="7">
-        <v>16</v>
-      </c>
-      <c r="D275" s="6" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4">
-      <c r="A276" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="B276" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="C276" s="7">
-        <v>17</v>
-      </c>
-      <c r="D276" s="6" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="277" spans="1:4">
-      <c r="A277" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="B277" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="C277" s="7">
-        <v>18</v>
-      </c>
-      <c r="D277" s="6" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4">
-      <c r="A278" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="B278" s="7" t="s">
-        <v>528</v>
-      </c>
-      <c r="C278" s="7">
-        <v>19</v>
-      </c>
-      <c r="D278" s="6" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4">
-      <c r="A279" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="B279" s="7" t="s">
+      <c r="D282" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="C279" s="7">
-        <v>20</v>
-      </c>
-      <c r="D279" s="6" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4">
-      <c r="A280" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="B280" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="C280" s="7">
-        <v>21</v>
-      </c>
-      <c r="D280" s="6" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4">
-      <c r="A281" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="B281" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C281" s="7">
-        <v>22</v>
-      </c>
-      <c r="D281" s="6" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4">
-      <c r="A282"/>
-      <c r="B282"/>
-      <c r="D282"/>
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>535</v>
+        <v>515</v>
       </c>
       <c r="B283" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="C283" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D283" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
+        <v>515</v>
+      </c>
+      <c r="B284" t="s">
+        <v>533</v>
+      </c>
+      <c r="C284" s="3">
+        <v>11</v>
+      </c>
+      <c r="D284" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="B285" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C285" s="7">
+        <v>12</v>
+      </c>
+      <c r="D285" s="6" t="s">
         <v>535</v>
       </c>
-      <c r="B284" t="s">
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="B286" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="C286" s="7">
+        <v>13</v>
+      </c>
+      <c r="D286" s="6" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="B287" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="C284" s="3">
+      <c r="C287" s="7">
+        <v>14</v>
+      </c>
+      <c r="D287" s="6" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="B288" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="C288" s="7">
+        <v>15</v>
+      </c>
+      <c r="D288" s="6" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="B289" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="C289" s="7">
+        <v>16</v>
+      </c>
+      <c r="D289" s="6" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="B290" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="C290" s="7">
+        <v>17</v>
+      </c>
+      <c r="D290" s="6" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="B291" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="C291" s="7">
+        <v>18</v>
+      </c>
+      <c r="D291" s="6" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="B292" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="C292" s="7">
+        <v>19</v>
+      </c>
+      <c r="D292" s="6" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="B293" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="C293" s="7">
+        <v>20</v>
+      </c>
+      <c r="D293" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="B294" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="C294" s="7">
+        <v>21</v>
+      </c>
+      <c r="D294" s="6" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="B295" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C295" s="7">
+        <v>22</v>
+      </c>
+      <c r="D295" s="6" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296"/>
+      <c r="B296"/>
+      <c r="D296"/>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" t="s">
+        <v>555</v>
+      </c>
+      <c r="B297" t="s">
+        <v>556</v>
+      </c>
+      <c r="C297" s="3">
+        <v>1</v>
+      </c>
+      <c r="D297" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" t="s">
+        <v>555</v>
+      </c>
+      <c r="B298" t="s">
+        <v>558</v>
+      </c>
+      <c r="C298" s="3">
         <v>2</v>
       </c>
-      <c r="D284" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4">
-      <c r="A285" t="s">
-        <v>535</v>
-      </c>
-      <c r="B285" t="s">
-        <v>540</v>
-      </c>
-      <c r="C285" s="3">
+      <c r="D298" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" t="s">
+        <v>555</v>
+      </c>
+      <c r="B299" t="s">
+        <v>560</v>
+      </c>
+      <c r="C299" s="3">
         <v>3</v>
       </c>
-      <c r="D285" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4">
-      <c r="A286" t="s">
-        <v>542</v>
-      </c>
-      <c r="B286" t="s">
-        <v>543</v>
-      </c>
-      <c r="C286" s="3">
+      <c r="D299" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" t="s">
+        <v>562</v>
+      </c>
+      <c r="B300" t="s">
+        <v>563</v>
+      </c>
+      <c r="C300" s="3">
         <v>1</v>
       </c>
-      <c r="D286" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4">
-      <c r="A287" t="s">
-        <v>542</v>
-      </c>
-      <c r="B287" t="s">
-        <v>545</v>
-      </c>
-      <c r="C287" s="3">
+      <c r="D300" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" t="s">
+        <v>562</v>
+      </c>
+      <c r="B301" t="s">
+        <v>565</v>
+      </c>
+      <c r="C301" s="3">
         <v>2</v>
       </c>
-      <c r="D287" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4">
-      <c r="A288" t="s">
-        <v>542</v>
-      </c>
-      <c r="B288" t="s">
-        <v>547</v>
-      </c>
-      <c r="C288" s="3">
+      <c r="D301" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" t="s">
+        <v>562</v>
+      </c>
+      <c r="B302" t="s">
+        <v>567</v>
+      </c>
+      <c r="C302" s="3">
         <v>3</v>
       </c>
-      <c r="D288" t="s">
-        <v>548</v>
+      <c r="D302" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="B304" s="8" t="s">
+        <v>570</v>
+      </c>
+      <c r="C304" s="3">
+        <v>1</v>
+      </c>
+      <c r="D304" s="8" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="B305" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C305" s="3">
+        <v>2</v>
+      </c>
+      <c r="D305" s="8" t="s">
+        <v>573</v>
       </c>
     </row>
   </sheetData>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="10920" windowHeight="12705"/>
+    <workbookView windowWidth="8190" windowHeight="9975"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="579">
   <si>
     <t>Enum</t>
   </si>
@@ -1754,6 +1754,21 @@
   </si>
   <si>
     <t>玩家对战轮</t>
+  </si>
+  <si>
+    <t>EffectsType</t>
+  </si>
+  <si>
+    <t>Hit</t>
+  </si>
+  <si>
+    <t>受击特效</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>攻击特效</t>
   </si>
 </sst>
 </file>
@@ -2751,7 +2766,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:E305"/>
+  <dimension ref="A4:E308"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16.7416666666667" style="1" customWidth="1"/>
@@ -6841,6 +6856,34 @@
         <v>573</v>
       </c>
     </row>
+    <row r="307" spans="1:4">
+      <c r="A307" t="s">
+        <v>574</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C307" s="3">
+        <v>1</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308" t="s">
+        <v>574</v>
+      </c>
+      <c r="B308" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="C308" s="3">
+        <v>2</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>578</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="8190" windowHeight="9975"/>
+    <workbookView windowWidth="25080" windowHeight="10920"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="582">
   <si>
     <t>Enum</t>
   </si>
@@ -1769,6 +1769,15 @@
   </si>
   <si>
     <t>攻击特效</t>
+  </si>
+  <si>
+    <t>BindingType</t>
+  </si>
+  <si>
+    <t>Leiting</t>
+  </si>
+  <si>
+    <t>雷霆嘎巴</t>
   </si>
 </sst>
 </file>
@@ -2766,7 +2775,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:E308"/>
+  <dimension ref="A4:E310"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16.7416666666667" style="1" customWidth="1"/>
@@ -6884,6 +6893,20 @@
         <v>578</v>
       </c>
     </row>
+    <row r="310" spans="1:4">
+      <c r="A310" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="C310" s="3">
+        <v>1</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>581</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/EnumConfig.xlsx
+++ b/Config/EnumConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25080" windowHeight="10920"/>
+    <workbookView windowWidth="13320" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="602">
   <si>
     <t>Enum</t>
   </si>
@@ -1774,10 +1774,70 @@
     <t>BindingType</t>
   </si>
   <si>
+    <t>BronzeBook</t>
+  </si>
+  <si>
+    <t>每回合开始,英雄攻击力会永久+1,可一直叠加</t>
+  </si>
+  <si>
+    <t>SilverBook</t>
+  </si>
+  <si>
+    <t>每次攻击时,提供的倍率永久+0.5,可一直叠加</t>
+  </si>
+  <si>
     <t>Leiting</t>
   </si>
   <si>
-    <t>雷霆嘎巴</t>
+    <t>触发暴击时,会对目标造成1次英雄当前攻击力500%的雷霆斩击</t>
+  </si>
+  <si>
+    <t>LuckyNumber</t>
+  </si>
+  <si>
+    <t>攻击时,会随机将本次亮出数字牌的其中1张在后续永久获得强化,在后续亮出的牌中每包含1张强化过的数字牌,就有10%的概率使自身无视比牌规则直接获胜</t>
+  </si>
+  <si>
+    <t>NobilityPower</t>
+  </si>
+  <si>
+    <t>每亮出1次人头牌,就会叠加1层[权力],达到15层后敌人亮牌将有50%概率不会攻击自己,而是攻击其他敌人</t>
+  </si>
+  <si>
+    <t>MagicCoin</t>
+  </si>
+  <si>
+    <t>进行的每次消费行为都会使你后续造成的伤害永久提高2.5%</t>
+  </si>
+  <si>
+    <t>BloodCeremony</t>
+  </si>
+  <si>
+    <t>每次回复生命时,如果场上有敌人,则会对所有敌人造成1次当前恢复生命值的伤害</t>
+  </si>
+  <si>
+    <t>CurseSilence</t>
+  </si>
+  <si>
+    <t>拥有1次复活机会,且每次受到伤害后都会使对方在下回合受到[沉默](无法比牌,直接判负)</t>
+  </si>
+  <si>
+    <t>DoubleAttack</t>
+  </si>
+  <si>
+    <t>攻击时会额外追加1次,且追加的攻击也会触发其他效果(比如暴击),但伤害效益降低至60%</t>
+  </si>
+  <si>
+    <t>RandomAttribute</t>
+  </si>
+  <si>
+    <t>每次使用技能都会随机获得以下属性之一:攻击力永久+3,生命+10,暴击率永久+1%</t>
+  </si>
+  <si>
+    <t>DisableSkill</t>
+  </si>
+  <si>
+    <t>你的技能会被禁用,但不影响技能次数带来的各种收益,且你的牌型无论输赢,总是会对对方造成技能总次数x攻击力的伤害</t>
   </si>
 </sst>
 </file>
@@ -2775,7 +2835,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:E310"/>
+  <dimension ref="A4:E321"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16.7416666666667" style="1" customWidth="1"/>
@@ -6851,7 +6911,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="305" spans="1:4">
+    <row r="305" spans="1:5">
       <c r="A305" s="8" t="s">
         <v>569</v>
       </c>
@@ -6865,7 +6925,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="307" spans="1:4">
+    <row r="307" spans="1:5">
       <c r="A307" t="s">
         <v>574</v>
       </c>
@@ -6879,7 +6939,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="308" spans="1:4">
+    <row r="308" spans="1:5">
       <c r="A308" t="s">
         <v>574</v>
       </c>
@@ -6893,19 +6953,176 @@
         <v>578</v>
       </c>
     </row>
-    <row r="310" spans="1:4">
+    <row r="309" spans="1:5">
+      <c r="E309"/>
+    </row>
+    <row r="310" spans="1:5">
       <c r="A310" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B310" s="1" t="s">
+      <c r="B310" t="s">
         <v>580</v>
       </c>
       <c r="C310" s="3">
         <v>1</v>
       </c>
-      <c r="D310" s="1" t="s">
+      <c r="D310" t="s">
         <v>581</v>
       </c>
+      <c r="E310"/>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B311" t="s">
+        <v>582</v>
+      </c>
+      <c r="C311" s="3">
+        <v>2</v>
+      </c>
+      <c r="D311" t="s">
+        <v>583</v>
+      </c>
+      <c r="E311"/>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B312" t="s">
+        <v>584</v>
+      </c>
+      <c r="C312" s="3">
+        <v>3</v>
+      </c>
+      <c r="D312" t="s">
+        <v>585</v>
+      </c>
+      <c r="E312"/>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B313" t="s">
+        <v>586</v>
+      </c>
+      <c r="C313" s="3">
+        <v>4</v>
+      </c>
+      <c r="D313" t="s">
+        <v>587</v>
+      </c>
+      <c r="E313"/>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B314" t="s">
+        <v>588</v>
+      </c>
+      <c r="C314" s="3">
+        <v>5</v>
+      </c>
+      <c r="D314" t="s">
+        <v>589</v>
+      </c>
+      <c r="E314"/>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B315" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="C315" s="3">
+        <v>6</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="E315"/>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B316" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="C316" s="3">
+        <v>7</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="E316"/>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B317" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="C317" s="3">
+        <v>8</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E317"/>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="C318" s="3">
+        <v>9</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="E318"/>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="C319" s="3">
+        <v>10</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="E319"/>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="C320" s="3">
+        <v>11</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="E320"/>
+    </row>
+    <row r="321" spans="5:5">
+      <c r="E321"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
